--- a/programmes/Kinetix Programmes.xlsx
+++ b/programmes/Kinetix Programmes.xlsx
@@ -155,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="388">
   <si>
     <t xml:space="preserve">Kinetix programmes</t>
   </si>
@@ -328,7 +328,13 @@
     <t xml:space="preserve">Fewer run days than the programme has sessions? The app drops easy and recovery runs first. More days? It adds easy runs.</t>
   </si>
   <si>
-    <t xml:space="preserve">Rep sessions keep their rep lengths; lower-volume runners get fewer reps so hard running stays a sensible share of their week.</t>
+    <t xml:space="preserve">Rep sessions keep their rep lengths; lower-volume runners get fewer reps so hard running stays a sensible share of their week (Rules: fast, threshold and steady reps max).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rep and tempo sessions get an easy warm-up and cool-down (Rules: warm-up). Other runs share what's left: easy 1, recovery 0.75, shakeout 0.6, progression 1.15, within the Rules' run-length limits.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A race date lines the programme up so its last week is race week (early weeks skipped if it's sooner, base weeks repeated first if it's further away). The race is its full distance and isn't counted in the week's %.</t>
   </si>
   <si>
     <t xml:space="preserve">The worked example columns (grey) show what each week would be for a runner at the volume in Rules → 'Example runner'.</t>
@@ -1037,6 +1043,63 @@
   </si>
   <si>
     <t xml:space="preserve">Only for the grey example columns in Run weeks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warm-up and cool-down, each (fraction of week)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added to rep and tempo sessions. Kept between the min and max below.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warm-up minimum (km)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Also used when the long run and sessions already fill the week.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warm-up maximum (km)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fast reps max (fraction of week): I, R, 5K, hills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hard running per session. Lower-volume runners get fewer reps; rep lengths never change.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fast reps floor (km)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Always allowed at least this much, whatever the week's volume.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Threshold reps max (fraction of week): T, 10K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Threshold reps floor (km)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steady reps max (fraction of week): STEADY, M, HM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steady reps floor (km)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recovery run max (fraction of long run)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spare volume beyond these lengths adds an easy run if there's a free day.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Easy run max (fraction of long run)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shakeout max (fraction of week)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recovery week after the programme (fraction of starting)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Easy running only, then the programme repeats from their recent running.</t>
   </si>
   <si>
     <t xml:space="preserve">Current app defaults are filled in; change any yellow value.</t>
@@ -1767,7 +1830,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2111,6 +2174,24 @@
       </c>
       <c r="C42" s="10" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1"/>
+      <c r="B43" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1"/>
+      <c r="B44" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2145,189 +2226,189 @@
         <v>8</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>27</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>76</v>
-      </c>
       <c r="F3" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2335,24 +2416,24 @@
         <v>35</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2360,367 +2441,367 @@
         <v>45</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I12" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I13" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I14" s="6" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I15" s="6" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I16" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I17" s="6" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I18" s="6" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I19" s="6" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I20" s="6" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I21" s="6" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I22" s="6" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I23" s="6" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I24" s="6" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I25" s="6" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I26" s="6" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I27" s="6" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I28" s="6" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I29" s="6" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I30" s="6" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I31" s="6" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I32" s="6" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I33" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I34" s="6" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I35" s="6" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I36" s="6" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I37" s="6" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I38" s="6" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I39" s="6" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I40" s="6" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I41" s="6" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I42" s="6" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I43" s="6" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I44" s="6" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I45" s="6" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I46" s="6" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I47" s="6" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I48" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I49" s="6" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I50" s="6" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I51" s="6" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I52" s="6" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I53" s="6" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I54" s="6" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I55" s="6" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I56" s="6" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I57" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I58" s="6" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I59" s="6" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I60" s="6" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I61" s="6" t="s">
-        <v>345</v>
+        <v>366</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I62" s="6" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I63" s="6" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I64" s="6" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I65" s="6" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I66" s="6" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I67" s="6" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I68" s="6" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I69" s="6" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I70" s="6" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I71" s="6" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I72" s="6" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I73" s="6" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I74" s="6" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I75" s="6" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I76" s="6" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I77" s="6" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I78" s="6" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I79" s="6" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I80" s="6" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I81" s="6" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I82" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I83" s="6" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -2755,63 +2836,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O1" s="11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C2" s="12" t="n">
         <v>8</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E2" s="12" t="n">
         <v>3</v>
@@ -2835,10 +2916,10 @@
         <v>1</v>
       </c>
       <c r="L2" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M2" s="12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N2" s="13" t="n">
         <f aca="false">COUNTIF('Run weeks'!$A$2:$A$401,A2)</f>
@@ -2851,16 +2932,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C3" s="12" t="n">
         <v>10</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>3</v>
@@ -2884,10 +2965,10 @@
         <v>1</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="N3" s="13" t="n">
         <f aca="false">COUNTIF('Run weeks'!$A$2:$A$401,A3)</f>
@@ -2900,16 +2981,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C4" s="12" t="n">
         <v>12</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>3</v>
@@ -2933,10 +3014,10 @@
         <v>2</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N4" s="13" t="n">
         <f aca="false">COUNTIF('Run weeks'!$A$2:$A$401,A4)</f>
@@ -2949,16 +3030,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>4</v>
@@ -2982,10 +3063,10 @@
         <v>3</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M5" s="12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N5" s="13" t="n">
         <f aca="false">COUNTIF('Run weeks'!$A$2:$A$401,A5)</f>
@@ -2998,16 +3079,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>8</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>1</v>
@@ -3031,10 +3112,10 @@
         <v>1</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M6" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N6" s="13" t="n">
         <f aca="false">COUNTIF('Run weeks'!$A$2:$A$401,A6)</f>
@@ -3047,16 +3128,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>8</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>1</v>
@@ -3080,10 +3161,10 @@
         <v>1</v>
       </c>
       <c r="L7" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="N7" s="13" t="n">
         <f aca="false">COUNTIF('Run weeks'!$A$2:$A$401,A7)</f>
@@ -3096,16 +3177,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>8</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2</v>
@@ -3129,10 +3210,10 @@
         <v>1</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="N8" s="13" t="n">
         <f aca="false">COUNTIF('Run weeks'!$A$2:$A$401,A8)</f>
@@ -3145,7 +3226,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -3187,57 +3268,57 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B2" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D2" s="15" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H2" s="13" t="n">
         <f aca="false">IF(A2="","",COUNTIFS('Run sessions'!$A$2:$A$401,A2,'Run sessions'!$B$2:$B$401,B2))</f>
@@ -3254,22 +3335,22 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B3" s="12" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D3" s="15" t="n">
         <v>1.05</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="13" t="n">
@@ -3287,22 +3368,22 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B4" s="12" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D4" s="15" t="n">
         <v>1.1</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G4" s="12"/>
       <c r="H4" s="13" t="n">
@@ -3320,25 +3401,25 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H5" s="13" t="n">
         <f aca="false">IF(A5="","",COUNTIFS('Run sessions'!$A$2:$A$401,A5,'Run sessions'!$B$2:$B$401,B5))</f>
@@ -3355,22 +3436,22 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B6" s="12" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D6" s="15" t="n">
         <v>1.15</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="13" t="n">
@@ -3388,22 +3469,22 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D7" s="15" t="n">
         <v>1.2</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G7" s="12"/>
       <c r="H7" s="13" t="n">
@@ -3421,22 +3502,22 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B8" s="12" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D8" s="15" t="n">
         <v>1.25</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G8" s="12"/>
       <c r="H8" s="13" t="n">
@@ -3454,22 +3535,22 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B9" s="12" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D9" s="15" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="13" t="n">
@@ -3487,25 +3568,25 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>1.3</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H10" s="13" t="n">
         <f aca="false">IF(A10="","",COUNTIFS('Run sessions'!$A$2:$A$401,A10,'Run sessions'!$B$2:$B$401,B10))</f>
@@ -3522,22 +3603,22 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>1.3</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G11" s="12"/>
       <c r="H11" s="13" t="n">
@@ -3555,25 +3636,25 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>11</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.85</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H12" s="13" t="n">
         <f aca="false">IF(A12="","",COUNTIFS('Run sessions'!$A$2:$A$401,A12,'Run sessions'!$B$2:$B$401,B12))</f>
@@ -3590,13 +3671,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B13" s="12" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.55</v>
@@ -3605,10 +3686,10 @@
         <v>45</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H13" s="13" t="n">
         <f aca="false">IF(A13="","",COUNTIFS('Run sessions'!$A$2:$A$401,A13,'Run sessions'!$B$2:$B$401,B13))</f>
@@ -11816,30 +11897,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B2" s="12" t="n">
         <v>1</v>
@@ -11848,19 +11929,19 @@
         <v>1</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B3" s="12" t="n">
         <v>1</v>
@@ -11869,19 +11950,19 @@
         <v>2</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G3" s="12"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B4" s="12" t="n">
         <v>1</v>
@@ -11890,19 +11971,19 @@
         <v>3</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>1</v>
@@ -11911,19 +11992,19 @@
         <v>4</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B6" s="12" t="n">
         <v>2</v>
@@ -11935,16 +12016,16 @@
         <v>35</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>2</v>
@@ -11953,19 +12034,19 @@
         <v>2</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B8" s="12" t="n">
         <v>2</v>
@@ -11974,19 +12055,19 @@
         <v>3</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B9" s="12" t="n">
         <v>2</v>
@@ -11995,19 +12076,19 @@
         <v>4</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>3</v>
@@ -12016,19 +12097,19 @@
         <v>1</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>3</v>
@@ -12037,19 +12118,19 @@
         <v>2</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>3</v>
@@ -12058,19 +12139,19 @@
         <v>3</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B13" s="12" t="n">
         <v>3</v>
@@ -12079,19 +12160,19 @@
         <v>4</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B14" s="12" t="n">
         <v>4</v>
@@ -12100,19 +12181,19 @@
         <v>1</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B15" s="12" t="n">
         <v>4</v>
@@ -12121,19 +12202,19 @@
         <v>2</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B16" s="12" t="n">
         <v>4</v>
@@ -12142,19 +12223,19 @@
         <v>3</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B17" s="12" t="n">
         <v>4</v>
@@ -12163,19 +12244,19 @@
         <v>4</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B18" s="12" t="n">
         <v>5</v>
@@ -12187,16 +12268,16 @@
         <v>35</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B19" s="12" t="n">
         <v>5</v>
@@ -12205,19 +12286,19 @@
         <v>2</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G19" s="12"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B20" s="12" t="n">
         <v>5</v>
@@ -12226,19 +12307,19 @@
         <v>3</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B21" s="12" t="n">
         <v>5</v>
@@ -12247,19 +12328,19 @@
         <v>4</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G21" s="12"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B22" s="12" t="n">
         <v>6</v>
@@ -12268,19 +12349,19 @@
         <v>1</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G22" s="12"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B23" s="12" t="n">
         <v>6</v>
@@ -12289,19 +12370,19 @@
         <v>2</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B24" s="12" t="n">
         <v>6</v>
@@ -12310,19 +12391,19 @@
         <v>3</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B25" s="12" t="n">
         <v>6</v>
@@ -12331,19 +12412,19 @@
         <v>4</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>7</v>
@@ -12352,19 +12433,19 @@
         <v>1</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>7</v>
@@ -12373,19 +12454,19 @@
         <v>2</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B28" s="12" t="n">
         <v>7</v>
@@ -12394,19 +12475,19 @@
         <v>3</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B29" s="12" t="n">
         <v>7</v>
@@ -12415,19 +12496,19 @@
         <v>4</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B30" s="12" t="n">
         <v>8</v>
@@ -12439,16 +12520,16 @@
         <v>35</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B31" s="12" t="n">
         <v>8</v>
@@ -12457,19 +12538,19 @@
         <v>2</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B32" s="12" t="n">
         <v>8</v>
@@ -12478,19 +12559,19 @@
         <v>3</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G32" s="12"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B33" s="12" t="n">
         <v>8</v>
@@ -12499,19 +12580,19 @@
         <v>4</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G33" s="12"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B34" s="12" t="n">
         <v>9</v>
@@ -12520,19 +12601,19 @@
         <v>1</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G34" s="12"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B35" s="12" t="n">
         <v>9</v>
@@ -12541,19 +12622,19 @@
         <v>2</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G35" s="12"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B36" s="12" t="n">
         <v>9</v>
@@ -12562,19 +12643,19 @@
         <v>3</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G36" s="12"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B37" s="12" t="n">
         <v>9</v>
@@ -12583,19 +12664,19 @@
         <v>4</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G37" s="12"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B38" s="12" t="n">
         <v>10</v>
@@ -12604,19 +12685,19 @@
         <v>1</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G38" s="12"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B39" s="12" t="n">
         <v>10</v>
@@ -12625,19 +12706,19 @@
         <v>2</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G39" s="12"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B40" s="12" t="n">
         <v>10</v>
@@ -12646,19 +12727,19 @@
         <v>3</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G40" s="12"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B41" s="12" t="n">
         <v>10</v>
@@ -12667,19 +12748,19 @@
         <v>4</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G41" s="12"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B42" s="12" t="n">
         <v>11</v>
@@ -12688,19 +12769,19 @@
         <v>1</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G42" s="12"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B43" s="12" t="n">
         <v>11</v>
@@ -12709,19 +12790,19 @@
         <v>2</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G43" s="12"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B44" s="12" t="n">
         <v>11</v>
@@ -12730,19 +12811,19 @@
         <v>3</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G44" s="12"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B45" s="12" t="n">
         <v>11</v>
@@ -12751,19 +12832,19 @@
         <v>4</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G45" s="12"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B46" s="12" t="n">
         <v>12</v>
@@ -12772,19 +12853,19 @@
         <v>1</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G46" s="12"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B47" s="12" t="n">
         <v>12</v>
@@ -12793,19 +12874,19 @@
         <v>2</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G47" s="12"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B48" s="12" t="n">
         <v>12</v>
@@ -12814,10 +12895,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F48" s="12" t="s">
         <v>42</v>
@@ -12826,7 +12907,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B49" s="12" t="n">
         <v>12</v>
@@ -12838,10 +12919,10 @@
         <v>45</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G49" s="12"/>
     </row>
@@ -16053,189 +16134,189 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F3" s="12"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B5" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>184</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>182</v>
       </c>
       <c r="F5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B9" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>201</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>199</v>
       </c>
       <c r="F9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F10" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -16267,39 +16348,39 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B2" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F2" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A2)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
@@ -16308,19 +16389,19 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B3" s="12" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D3" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>221</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>219</v>
       </c>
       <c r="F3" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A3)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
@@ -16329,19 +16410,19 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B4" s="12" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F4" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A4)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
@@ -16350,19 +16431,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F5" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A5)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
@@ -16371,19 +16452,19 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B6" s="12" t="n">
         <v>3</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F6" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A6)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
@@ -16392,19 +16473,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F7" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A7)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
@@ -16413,19 +16494,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B8" s="12" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F8" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A8)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
@@ -16434,19 +16515,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B9" s="12" t="n">
         <v>5</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F9" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A9)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
@@ -16490,51 +16571,51 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C2" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
@@ -16544,19 +16625,19 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C3" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F3" s="12"/>
       <c r="G3" s="12"/>
@@ -16566,19 +16647,19 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C4" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="12"/>
@@ -16588,19 +16669,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="12"/>
@@ -16610,19 +16691,19 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>5</v>
       </c>
       <c r="D6" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>252</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>250</v>
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
@@ -16632,19 +16713,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="12"/>
@@ -16654,19 +16735,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
@@ -16676,19 +16757,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
@@ -16698,19 +16779,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="12"/>
@@ -16720,19 +16801,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>5</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="12"/>
@@ -16742,19 +16823,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C12" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
@@ -16764,19 +16845,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="E13" s="12" t="s">
         <v>249</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>247</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="12"/>
@@ -16786,19 +16867,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="12"/>
@@ -16808,19 +16889,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C15" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="12"/>
@@ -16830,19 +16911,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C16" s="12" t="n">
         <v>5</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="12"/>
@@ -16852,19 +16933,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C17" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="12"/>
@@ -16874,19 +16955,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C18" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="12"/>
@@ -16896,19 +16977,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C19" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="12"/>
@@ -16918,19 +16999,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C20" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="12"/>
@@ -16940,19 +17021,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C21" s="12" t="n">
         <v>5</v>
       </c>
       <c r="D21" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="E21" s="12" t="s">
         <v>252</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>250</v>
       </c>
       <c r="F21" s="12"/>
       <c r="G21" s="12"/>
@@ -16962,19 +17043,19 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C22" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F22" s="12"/>
       <c r="G22" s="12"/>
@@ -16984,19 +17065,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C23" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F23" s="12"/>
       <c r="G23" s="12"/>
@@ -17006,19 +17087,19 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C24" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F24" s="12"/>
       <c r="G24" s="12"/>
@@ -17028,19 +17109,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C25" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F25" s="12"/>
       <c r="G25" s="12"/>
@@ -17050,19 +17131,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C26" s="12" t="n">
         <v>5</v>
       </c>
       <c r="D26" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="E26" s="12" t="s">
         <v>252</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>250</v>
       </c>
       <c r="F26" s="12"/>
       <c r="G26" s="12"/>
@@ -17072,19 +17153,19 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C27" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F27" s="12"/>
       <c r="G27" s="12"/>
@@ -17094,19 +17175,19 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C28" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F28" s="12"/>
       <c r="G28" s="12"/>
@@ -17116,19 +17197,19 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C29" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F29" s="12"/>
       <c r="G29" s="12"/>
@@ -17138,19 +17219,19 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C30" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F30" s="12"/>
       <c r="G30" s="12"/>
@@ -17160,19 +17241,19 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C31" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>4</v>
@@ -17190,19 +17271,19 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C32" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F32" s="12"/>
       <c r="G32" s="12"/>
@@ -17212,19 +17293,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C33" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F33" s="12"/>
       <c r="G33" s="12"/>
@@ -17234,19 +17315,19 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C34" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F34" s="12"/>
       <c r="G34" s="12"/>
@@ -17256,19 +17337,19 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C35" s="12" t="n">
         <v>5</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F35" s="12"/>
       <c r="G35" s="12"/>
@@ -17290,7 +17371,7 @@
     </row>
     <row r="37" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="17" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
@@ -21713,33 +21794,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C2" s="12" t="n">
         <v>3</v>
@@ -21757,10 +21838,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C3" s="12" t="n">
         <v>2</v>
@@ -21778,10 +21859,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C4" s="12" t="n">
         <v>3</v>
@@ -21799,10 +21880,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>2</v>
@@ -21820,10 +21901,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>3</v>
@@ -21841,10 +21922,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>2</v>
@@ -21862,10 +21943,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>3</v>
@@ -21883,10 +21964,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>2</v>
@@ -21904,10 +21985,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>5</v>
@@ -21925,10 +22006,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>3</v>
@@ -21946,10 +22027,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C12" s="12" t="n">
         <v>4</v>
@@ -21967,10 +22048,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>3</v>
@@ -21988,10 +22069,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>4</v>
@@ -22009,10 +22090,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C15" s="12" t="n">
         <v>3</v>
@@ -22030,12 +22111,12 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -22054,7 +22135,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
@@ -22064,24 +22145,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B2" s="18" t="n">
         <v>8</v>
@@ -22093,12 +22174,12 @@
         <v>25</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B3" s="18" t="n">
         <v>8</v>
@@ -22110,12 +22191,12 @@
         <v>25</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B4" s="18" t="n">
         <v>30</v>
@@ -22127,12 +22208,12 @@
         <v>100</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B5" s="18" t="n">
         <v>10</v>
@@ -22144,12 +22225,12 @@
         <v>32</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B6" s="18" t="n">
         <v>3</v>
@@ -22161,12 +22242,12 @@
         <v>4</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B7" s="19" t="n">
         <v>0.1</v>
@@ -22178,12 +22259,12 @@
         <v>0.12</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B8" s="19" t="n">
         <v>0.3</v>
@@ -22195,12 +22276,12 @@
         <v>0.32</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B9" s="18" t="n">
         <v>15</v>
@@ -22212,12 +22293,219 @@
         <v>50</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>293</v>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
-        <v>294</v>
+      <c r="A11" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="B11" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="B12" s="18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E12" s="14"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C13" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="B14" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E15" s="14"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="B16" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="14"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="B17" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C17" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E17" s="14"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="B18" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" s="14"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C19" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C20" s="19" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D20" s="19" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E20" s="14"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C21" s="19" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E21" s="14"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="B22" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C22" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="14" t="s">
+        <v>315</v>
       </c>
     </row>
   </sheetData>

--- a/programmes/Kinetix Programmes.xlsx
+++ b/programmes/Kinetix Programmes.xlsx
@@ -28,6 +28,28 @@
 </workbook>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">The weekly volume this race needs at each level. Run weeks' % are a % of this. Runners below it build up to it; runners above it ease down to it.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
@@ -42,7 +64,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">100% = the runner's starting volume (from onboarding). 1.2 = 120%.</t>
+          <t xml:space="preserve">100% = the programme's race-ready volume for the runner's level (Programmes tab), reached gradually from where they are now. 1.2 = 120%.</t>
         </r>
       </text>
     </comment>
@@ -66,7 +88,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">For the intermediate example runner in Rules.</t>
+          <t xml:space="preserve">An intermediate runner already at race-ready volume (Programmes tab).</t>
         </r>
       </text>
     </comment>
@@ -155,7 +177,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="397">
   <si>
     <t xml:space="preserve">Kinetix programmes</t>
   </si>
@@ -316,7 +338,13 @@
     <t xml:space="preserve">•</t>
   </si>
   <si>
-    <t xml:space="preserve">Starting volume = the runner's answer to 'How far do you run in a typical week?' (km), kept between the minimum and maximum in Rules for their level. 100% in Run weeks = that starting volume.</t>
+    <t xml:space="preserve">100% in Run weeks = the programme's race-ready volume for the runner's level (Programmes tab).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where they start: their answer to 'How far do you run in a typical week?' (pre-filled from their last 4 weeks of runs when the app has them), kept between the minimum and maximum in Rules. Below race-ready, they build up to it (within the max weekly increase); above it, they ease down to it (Rules: ease down per week). Your weekly % shape, deloads and taper are kept either way.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raced in the last two weeks? Onboarding asks, and if they want it they get an easy first week before week 1. Nothing else adds that week.</t>
   </si>
   <si>
     <t xml:space="preserve">'auto' easy runs share whatever volume is left in the week after the long run and the workouts, evenly.</t>
@@ -370,6 +398,15 @@
     <t xml:space="preserve">Weekly volume cap (km)</t>
   </si>
   <si>
+    <t xml:space="preserve">Race-ready volume: beginner (km/week)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Race-ready volume: intermediate (km/week)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Race-ready volume: advanced (km/week)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Taper weeks</t>
   </si>
   <si>
@@ -451,7 +488,7 @@
     <t xml:space="preserve">Phase</t>
   </si>
   <si>
-    <t xml:space="preserve">Volume (% of starting)</t>
+    <t xml:space="preserve">Volume (% of race-ready)</t>
   </si>
   <si>
     <t xml:space="preserve">Long run</t>
@@ -1100,6 +1137,18 @@
   </si>
   <si>
     <t xml:space="preserve">Easy running only, then the programme repeats from their recent running.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ease down per week when above race-ready (fraction)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Runners doing more than the race needs come down to its race-ready volume this much a week.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Easy first week after a race (fraction of current)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only if they say in onboarding they've raced in the last two weeks and want an easy week.</t>
   </si>
   <si>
     <t xml:space="preserve">Current app defaults are filled in; change any yellow value.</t>
@@ -1830,7 +1879,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2192,6 +2241,24 @@
       </c>
       <c r="C44" s="10" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1"/>
+      <c r="B45" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1"/>
+      <c r="B46" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -2226,189 +2293,189 @@
         <v>8</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>27</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2416,24 +2483,24 @@
         <v>35</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2441,367 +2508,367 @@
         <v>45</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I12" s="6" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I13" s="6" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I14" s="6" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I15" s="6" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I16" s="6" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I17" s="6" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I18" s="6" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I19" s="6" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I20" s="6" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I21" s="6" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I22" s="6" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I23" s="6" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I24" s="6" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I25" s="6" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I26" s="6" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I27" s="6" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I28" s="6" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I29" s="6" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I30" s="6" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I31" s="6" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I32" s="6" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I33" s="6" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I34" s="6" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I35" s="6" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I36" s="6" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I37" s="6" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I38" s="6" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I39" s="6" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I40" s="6" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I41" s="6" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I42" s="6" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I43" s="6" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I44" s="6" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I45" s="6" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I46" s="6" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I47" s="6" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I48" s="6" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I49" s="6" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I50" s="6" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I51" s="6" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I52" s="6" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I53" s="6" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I54" s="6" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I55" s="6" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I56" s="6" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I57" s="6" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I58" s="6" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I59" s="6" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I60" s="6" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I61" s="6" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I62" s="6" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I63" s="6" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I64" s="6" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I65" s="6" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I66" s="6" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I67" s="6" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I68" s="6" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I69" s="6" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I70" s="6" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I71" s="6" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I72" s="6" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I73" s="6" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I74" s="6" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I75" s="6" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I76" s="6" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I77" s="6" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I78" s="6" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I79" s="6" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I80" s="6" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I81" s="6" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I82" s="6" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I83" s="6" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -2820,7 +2887,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
@@ -2828,71 +2895,81 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="5" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="11" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O1" s="11" t="s">
-        <v>75</v>
+        <v>77</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q1" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C2" s="12" t="n">
         <v>8</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E2" s="12" t="n">
         <v>3</v>
@@ -2913,35 +2990,44 @@
         <v>25</v>
       </c>
       <c r="K2" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L2" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="M2" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="N2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="M2" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="N2" s="13" t="n">
+      <c r="O2" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q2" s="13" t="n">
         <f aca="false">COUNTIF('Run weeks'!$A$2:$A$401,A2)</f>
         <v>0</v>
       </c>
-      <c r="O2" s="13" t="n">
+      <c r="R2" s="13" t="n">
         <f aca="false">COUNTIF('Run sessions'!$A$2:$A$401,A2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C3" s="12" t="n">
         <v>10</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>3</v>
@@ -2962,35 +3048,44 @@
         <v>45</v>
       </c>
       <c r="K3" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="L3" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="M3" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="N3" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L3" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="M3" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="N3" s="13" t="n">
+      <c r="O3" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="P3" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q3" s="13" t="n">
         <f aca="false">COUNTIF('Run weeks'!$A$2:$A$401,A3)</f>
         <v>0</v>
       </c>
-      <c r="O3" s="13" t="n">
+      <c r="R3" s="13" t="n">
         <f aca="false">COUNTIF('Run sessions'!$A$2:$A$401,A3)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C4" s="12" t="n">
         <v>12</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>3</v>
@@ -3011,35 +3106,44 @@
         <v>70</v>
       </c>
       <c r="K4" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="L4" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="M4" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="N4" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L4" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="M4" s="12" t="s">
+      <c r="O4" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="N4" s="13" t="n">
+      <c r="P4" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q4" s="13" t="n">
         <f aca="false">COUNTIF('Run weeks'!$A$2:$A$401,A4)</f>
         <v>12</v>
       </c>
-      <c r="O4" s="13" t="n">
+      <c r="R4" s="13" t="n">
         <f aca="false">COUNTIF('Run sessions'!$A$2:$A$401,A4)</f>
         <v>48</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>16</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>4</v>
@@ -3060,35 +3164,44 @@
         <v>100</v>
       </c>
       <c r="K5" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="L5" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="M5" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="N5" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L5" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="M5" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="N5" s="13" t="n">
+      <c r="O5" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="P5" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q5" s="13" t="n">
         <f aca="false">COUNTIF('Run weeks'!$A$2:$A$401,A5)</f>
         <v>0</v>
       </c>
-      <c r="O5" s="13" t="n">
+      <c r="R5" s="13" t="n">
         <f aca="false">COUNTIF('Run sessions'!$A$2:$A$401,A5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>8</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>1</v>
@@ -3109,35 +3222,44 @@
         <v>25</v>
       </c>
       <c r="K6" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L6" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="M6" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="N6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L6" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="M6" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="N6" s="13" t="n">
+      <c r="O6" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="P6" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q6" s="13" t="n">
         <f aca="false">COUNTIF('Run weeks'!$A$2:$A$401,A6)</f>
         <v>0</v>
       </c>
-      <c r="O6" s="13" t="n">
+      <c r="R6" s="13" t="n">
         <f aca="false">COUNTIF('Run sessions'!$A$2:$A$401,A6)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>8</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>1</v>
@@ -3158,35 +3280,44 @@
         <v>25</v>
       </c>
       <c r="K7" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="M7" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="N7" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="M7" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="N7" s="13" t="n">
+      <c r="O7" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="P7" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q7" s="13" t="n">
         <f aca="false">COUNTIF('Run weeks'!$A$2:$A$401,A7)</f>
         <v>0</v>
       </c>
-      <c r="O7" s="13" t="n">
+      <c r="R7" s="13" t="n">
         <f aca="false">COUNTIF('Run sessions'!$A$2:$A$401,A7)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>8</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>2</v>
@@ -3207,26 +3338,35 @@
         <v>35</v>
       </c>
       <c r="K8" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L8" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="M8" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="N8" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L8" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="M8" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="N8" s="13" t="n">
+      <c r="O8" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="P8" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q8" s="13" t="n">
         <f aca="false">COUNTIF('Run weeks'!$A$2:$A$401,A8)</f>
         <v>0</v>
       </c>
-      <c r="O8" s="13" t="n">
+      <c r="R8" s="13" t="n">
         <f aca="false">COUNTIF('Run sessions'!$A$2:$A$401,A8)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -3235,7 +3375,7 @@
       <formula1>"Repeat,Repeat harder,Maintenance,Stop"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Pick one of the options in the drop-down." errorStyle="stop" errorTitle="Choose from the list" operator="between" prompt="The split suggested in onboarding (the user can change it)." promptTitle="Tip" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="L2:L8" type="list">
+    <dataValidation allowBlank="true" error="Pick one of the options in the drop-down." errorStyle="stop" errorTitle="Choose from the list" operator="between" prompt="The split suggested in onboarding (the user can change it)." promptTitle="Tip" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="O2:O8" type="list">
       <formula1>Lists!$E$2:$E$9</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3247,6 +3387,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3268,89 +3409,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B2" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D2" s="15" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H2" s="13" t="n">
         <f aca="false">IF(A2="","",COUNTIFS('Run sessions'!$A$2:$A$401,A2,'Run sessions'!$B$2:$B$401,B2))</f>
         <v>4</v>
       </c>
       <c r="I2" s="13" t="n">
-        <f aca="false">IF(OR(A2="",D2=""),"",ROUND(D2*Rules!$C$9,1))</f>
-        <v>30</v>
+        <f aca="false">IF(OR(A2="",D2=""),"",ROUND(D2*INDEX(Programmes!$L$2:$L$8,MATCH(A2,Programmes!$A$2:$A$8,0)),1))</f>
+        <v>45</v>
       </c>
       <c r="J2" s="13" t="n">
         <f aca="false">IF(I2="","",IF(LOWER(E2)="auto",ROUND(I2*Rules!$C$8,1),IF(RIGHT(E2,1)="%",ROUND(I2*VALUE(LEFT(E2,LEN(E2)-1))/100,1),IF(RIGHT(LOWER(E2),2)="km",VALUE(LEFT(E2,LEN(E2)-2)),IF(LOWER(E2)="race","race",E2)))))</f>
-        <v>9</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B3" s="12" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D3" s="15" t="n">
         <v>1.05</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="13" t="n">
@@ -3358,32 +3499,32 @@
         <v>4</v>
       </c>
       <c r="I3" s="13" t="n">
-        <f aca="false">IF(OR(A3="",D3=""),"",ROUND(D3*Rules!$C$9,1))</f>
-        <v>31.5</v>
+        <f aca="false">IF(OR(A3="",D3=""),"",ROUND(D3*INDEX(Programmes!$L$2:$L$8,MATCH(A3,Programmes!$A$2:$A$8,0)),1))</f>
+        <v>47.3</v>
       </c>
       <c r="J3" s="13" t="n">
         <f aca="false">IF(I3="","",IF(LOWER(E3)="auto",ROUND(I3*Rules!$C$8,1),IF(RIGHT(E3,1)="%",ROUND(I3*VALUE(LEFT(E3,LEN(E3)-1))/100,1),IF(RIGHT(LOWER(E3),2)="km",VALUE(LEFT(E3,LEN(E3)-2)),IF(LOWER(E3)="race","race",E3)))))</f>
-        <v>9.5</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B4" s="12" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D4" s="15" t="n">
         <v>1.1</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G4" s="12"/>
       <c r="H4" s="13" t="n">
@@ -3391,67 +3532,67 @@
         <v>4</v>
       </c>
       <c r="I4" s="13" t="n">
-        <f aca="false">IF(OR(A4="",D4=""),"",ROUND(D4*Rules!$C$9,1))</f>
-        <v>33</v>
+        <f aca="false">IF(OR(A4="",D4=""),"",ROUND(D4*INDEX(Programmes!$L$2:$L$8,MATCH(A4,Programmes!$A$2:$A$8,0)),1))</f>
+        <v>49.5</v>
       </c>
       <c r="J4" s="13" t="n">
         <f aca="false">IF(I4="","",IF(LOWER(E4)="auto",ROUND(I4*Rules!$C$8,1),IF(RIGHT(E4,1)="%",ROUND(I4*VALUE(LEFT(E4,LEN(E4)-1))/100,1),IF(RIGHT(LOWER(E4),2)="km",VALUE(LEFT(E4,LEN(E4)-2)),IF(LOWER(E4)="race","race",E4)))))</f>
-        <v>9.9</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="H5" s="13" t="n">
         <f aca="false">IF(A5="","",COUNTIFS('Run sessions'!$A$2:$A$401,A5,'Run sessions'!$B$2:$B$401,B5))</f>
         <v>4</v>
       </c>
       <c r="I5" s="13" t="n">
-        <f aca="false">IF(OR(A5="",D5=""),"",ROUND(D5*Rules!$C$9,1))</f>
-        <v>27</v>
+        <f aca="false">IF(OR(A5="",D5=""),"",ROUND(D5*INDEX(Programmes!$L$2:$L$8,MATCH(A5,Programmes!$A$2:$A$8,0)),1))</f>
+        <v>40.5</v>
       </c>
       <c r="J5" s="13" t="n">
         <f aca="false">IF(I5="","",IF(LOWER(E5)="auto",ROUND(I5*Rules!$C$8,1),IF(RIGHT(E5,1)="%",ROUND(I5*VALUE(LEFT(E5,LEN(E5)-1))/100,1),IF(RIGHT(LOWER(E5),2)="km",VALUE(LEFT(E5,LEN(E5)-2)),IF(LOWER(E5)="race","race",E5)))))</f>
-        <v>8.1</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B6" s="12" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D6" s="15" t="n">
         <v>1.15</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="13" t="n">
@@ -3459,32 +3600,32 @@
         <v>4</v>
       </c>
       <c r="I6" s="13" t="n">
-        <f aca="false">IF(OR(A6="",D6=""),"",ROUND(D6*Rules!$C$9,1))</f>
-        <v>34.5</v>
+        <f aca="false">IF(OR(A6="",D6=""),"",ROUND(D6*INDEX(Programmes!$L$2:$L$8,MATCH(A6,Programmes!$A$2:$A$8,0)),1))</f>
+        <v>51.8</v>
       </c>
       <c r="J6" s="13" t="n">
         <f aca="false">IF(I6="","",IF(LOWER(E6)="auto",ROUND(I6*Rules!$C$8,1),IF(RIGHT(E6,1)="%",ROUND(I6*VALUE(LEFT(E6,LEN(E6)-1))/100,1),IF(RIGHT(LOWER(E6),2)="km",VALUE(LEFT(E6,LEN(E6)-2)),IF(LOWER(E6)="race","race",E6)))))</f>
-        <v>10.4</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D7" s="15" t="n">
         <v>1.2</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G7" s="12"/>
       <c r="H7" s="13" t="n">
@@ -3492,32 +3633,32 @@
         <v>4</v>
       </c>
       <c r="I7" s="13" t="n">
-        <f aca="false">IF(OR(A7="",D7=""),"",ROUND(D7*Rules!$C$9,1))</f>
-        <v>36</v>
+        <f aca="false">IF(OR(A7="",D7=""),"",ROUND(D7*INDEX(Programmes!$L$2:$L$8,MATCH(A7,Programmes!$A$2:$A$8,0)),1))</f>
+        <v>54</v>
       </c>
       <c r="J7" s="13" t="n">
         <f aca="false">IF(I7="","",IF(LOWER(E7)="auto",ROUND(I7*Rules!$C$8,1),IF(RIGHT(E7,1)="%",ROUND(I7*VALUE(LEFT(E7,LEN(E7)-1))/100,1),IF(RIGHT(LOWER(E7),2)="km",VALUE(LEFT(E7,LEN(E7)-2)),IF(LOWER(E7)="race","race",E7)))))</f>
-        <v>10.8</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B8" s="12" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D8" s="15" t="n">
         <v>1.25</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G8" s="12"/>
       <c r="H8" s="13" t="n">
@@ -3525,32 +3666,32 @@
         <v>4</v>
       </c>
       <c r="I8" s="13" t="n">
-        <f aca="false">IF(OR(A8="",D8=""),"",ROUND(D8*Rules!$C$9,1))</f>
-        <v>37.5</v>
+        <f aca="false">IF(OR(A8="",D8=""),"",ROUND(D8*INDEX(Programmes!$L$2:$L$8,MATCH(A8,Programmes!$A$2:$A$8,0)),1))</f>
+        <v>56.3</v>
       </c>
       <c r="J8" s="13" t="n">
         <f aca="false">IF(I8="","",IF(LOWER(E8)="auto",ROUND(I8*Rules!$C$8,1),IF(RIGHT(E8,1)="%",ROUND(I8*VALUE(LEFT(E8,LEN(E8)-1))/100,1),IF(RIGHT(LOWER(E8),2)="km",VALUE(LEFT(E8,LEN(E8)-2)),IF(LOWER(E8)="race","race",E8)))))</f>
-        <v>11.3</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B9" s="12" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D9" s="15" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="13" t="n">
@@ -3558,43 +3699,43 @@
         <v>4</v>
       </c>
       <c r="I9" s="13" t="n">
-        <f aca="false">IF(OR(A9="",D9=""),"",ROUND(D9*Rules!$C$9,1))</f>
-        <v>30</v>
+        <f aca="false">IF(OR(A9="",D9=""),"",ROUND(D9*INDEX(Programmes!$L$2:$L$8,MATCH(A9,Programmes!$A$2:$A$8,0)),1))</f>
+        <v>45</v>
       </c>
       <c r="J9" s="13" t="n">
         <f aca="false">IF(I9="","",IF(LOWER(E9)="auto",ROUND(I9*Rules!$C$8,1),IF(RIGHT(E9,1)="%",ROUND(I9*VALUE(LEFT(E9,LEN(E9)-1))/100,1),IF(RIGHT(LOWER(E9),2)="km",VALUE(LEFT(E9,LEN(E9)-2)),IF(LOWER(E9)="race","race",E9)))))</f>
-        <v>9</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>1.3</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="H10" s="13" t="n">
         <f aca="false">IF(A10="","",COUNTIFS('Run sessions'!$A$2:$A$401,A10,'Run sessions'!$B$2:$B$401,B10))</f>
         <v>4</v>
       </c>
       <c r="I10" s="13" t="n">
-        <f aca="false">IF(OR(A10="",D10=""),"",ROUND(D10*Rules!$C$9,1))</f>
-        <v>39</v>
+        <f aca="false">IF(OR(A10="",D10=""),"",ROUND(D10*INDEX(Programmes!$L$2:$L$8,MATCH(A10,Programmes!$A$2:$A$8,0)),1))</f>
+        <v>58.5</v>
       </c>
       <c r="J10" s="13" t="n">
         <f aca="false">IF(I10="","",IF(LOWER(E10)="auto",ROUND(I10*Rules!$C$8,1),IF(RIGHT(E10,1)="%",ROUND(I10*VALUE(LEFT(E10,LEN(E10)-1))/100,1),IF(RIGHT(LOWER(E10),2)="km",VALUE(LEFT(E10,LEN(E10)-2)),IF(LOWER(E10)="race","race",E10)))))</f>
@@ -3603,22 +3744,22 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>1.3</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G11" s="12"/>
       <c r="H11" s="13" t="n">
@@ -3626,58 +3767,58 @@
         <v>4</v>
       </c>
       <c r="I11" s="13" t="n">
-        <f aca="false">IF(OR(A11="",D11=""),"",ROUND(D11*Rules!$C$9,1))</f>
-        <v>39</v>
+        <f aca="false">IF(OR(A11="",D11=""),"",ROUND(D11*INDEX(Programmes!$L$2:$L$8,MATCH(A11,Programmes!$A$2:$A$8,0)),1))</f>
+        <v>58.5</v>
       </c>
       <c r="J11" s="13" t="n">
         <f aca="false">IF(I11="","",IF(LOWER(E11)="auto",ROUND(I11*Rules!$C$8,1),IF(RIGHT(E11,1)="%",ROUND(I11*VALUE(LEFT(E11,LEN(E11)-1))/100,1),IF(RIGHT(LOWER(E11),2)="km",VALUE(LEFT(E11,LEN(E11)-2)),IF(LOWER(E11)="race","race",E11)))))</f>
-        <v>11.7</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>11</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.85</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H12" s="13" t="n">
         <f aca="false">IF(A12="","",COUNTIFS('Run sessions'!$A$2:$A$401,A12,'Run sessions'!$B$2:$B$401,B12))</f>
         <v>4</v>
       </c>
       <c r="I12" s="13" t="n">
-        <f aca="false">IF(OR(A12="",D12=""),"",ROUND(D12*Rules!$C$9,1))</f>
-        <v>25.5</v>
+        <f aca="false">IF(OR(A12="",D12=""),"",ROUND(D12*INDEX(Programmes!$L$2:$L$8,MATCH(A12,Programmes!$A$2:$A$8,0)),1))</f>
+        <v>38.3</v>
       </c>
       <c r="J12" s="13" t="n">
         <f aca="false">IF(I12="","",IF(LOWER(E12)="auto",ROUND(I12*Rules!$C$8,1),IF(RIGHT(E12,1)="%",ROUND(I12*VALUE(LEFT(E12,LEN(E12)-1))/100,1),IF(RIGHT(LOWER(E12),2)="km",VALUE(LEFT(E12,LEN(E12)-2)),IF(LOWER(E12)="race","race",E12)))))</f>
-        <v>7.7</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B13" s="12" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.55</v>
@@ -3686,18 +3827,18 @@
         <v>45</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H13" s="13" t="n">
         <f aca="false">IF(A13="","",COUNTIFS('Run sessions'!$A$2:$A$401,A13,'Run sessions'!$B$2:$B$401,B13))</f>
         <v>4</v>
       </c>
       <c r="I13" s="13" t="n">
-        <f aca="false">IF(OR(A13="",D13=""),"",ROUND(D13*Rules!$C$9,1))</f>
-        <v>16.5</v>
+        <f aca="false">IF(OR(A13="",D13=""),"",ROUND(D13*INDEX(Programmes!$L$2:$L$8,MATCH(A13,Programmes!$A$2:$A$8,0)),1))</f>
+        <v>24.8</v>
       </c>
       <c r="J13" s="13" t="str">
         <f aca="false">IF(I13="","",IF(LOWER(E13)="auto",ROUND(I13*Rules!$C$8,1),IF(RIGHT(E13,1)="%",ROUND(I13*VALUE(LEFT(E13,LEN(E13)-1))/100,1),IF(RIGHT(LOWER(E13),2)="km",VALUE(LEFT(E13,LEN(E13)-2)),IF(LOWER(E13)="race","race",E13)))))</f>
@@ -3717,7 +3858,7 @@
         <v/>
       </c>
       <c r="I14" s="13" t="str">
-        <f aca="false">IF(OR(A14="",D14=""),"",ROUND(D14*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A14="",D14=""),"",ROUND(D14*INDEX(Programmes!$L$2:$L$8,MATCH(A14,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J14" s="13" t="str">
@@ -3738,7 +3879,7 @@
         <v/>
       </c>
       <c r="I15" s="13" t="str">
-        <f aca="false">IF(OR(A15="",D15=""),"",ROUND(D15*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A15="",D15=""),"",ROUND(D15*INDEX(Programmes!$L$2:$L$8,MATCH(A15,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J15" s="13" t="str">
@@ -3759,7 +3900,7 @@
         <v/>
       </c>
       <c r="I16" s="13" t="str">
-        <f aca="false">IF(OR(A16="",D16=""),"",ROUND(D16*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A16="",D16=""),"",ROUND(D16*INDEX(Programmes!$L$2:$L$8,MATCH(A16,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J16" s="13" t="str">
@@ -3780,7 +3921,7 @@
         <v/>
       </c>
       <c r="I17" s="13" t="str">
-        <f aca="false">IF(OR(A17="",D17=""),"",ROUND(D17*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A17="",D17=""),"",ROUND(D17*INDEX(Programmes!$L$2:$L$8,MATCH(A17,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J17" s="13" t="str">
@@ -3801,7 +3942,7 @@
         <v/>
       </c>
       <c r="I18" s="13" t="str">
-        <f aca="false">IF(OR(A18="",D18=""),"",ROUND(D18*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A18="",D18=""),"",ROUND(D18*INDEX(Programmes!$L$2:$L$8,MATCH(A18,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J18" s="13" t="str">
@@ -3822,7 +3963,7 @@
         <v/>
       </c>
       <c r="I19" s="13" t="str">
-        <f aca="false">IF(OR(A19="",D19=""),"",ROUND(D19*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A19="",D19=""),"",ROUND(D19*INDEX(Programmes!$L$2:$L$8,MATCH(A19,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J19" s="13" t="str">
@@ -3843,7 +3984,7 @@
         <v/>
       </c>
       <c r="I20" s="13" t="str">
-        <f aca="false">IF(OR(A20="",D20=""),"",ROUND(D20*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A20="",D20=""),"",ROUND(D20*INDEX(Programmes!$L$2:$L$8,MATCH(A20,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J20" s="13" t="str">
@@ -3864,7 +4005,7 @@
         <v/>
       </c>
       <c r="I21" s="13" t="str">
-        <f aca="false">IF(OR(A21="",D21=""),"",ROUND(D21*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A21="",D21=""),"",ROUND(D21*INDEX(Programmes!$L$2:$L$8,MATCH(A21,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J21" s="13" t="str">
@@ -3885,7 +4026,7 @@
         <v/>
       </c>
       <c r="I22" s="13" t="str">
-        <f aca="false">IF(OR(A22="",D22=""),"",ROUND(D22*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A22="",D22=""),"",ROUND(D22*INDEX(Programmes!$L$2:$L$8,MATCH(A22,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J22" s="13" t="str">
@@ -3906,7 +4047,7 @@
         <v/>
       </c>
       <c r="I23" s="13" t="str">
-        <f aca="false">IF(OR(A23="",D23=""),"",ROUND(D23*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A23="",D23=""),"",ROUND(D23*INDEX(Programmes!$L$2:$L$8,MATCH(A23,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J23" s="13" t="str">
@@ -3927,7 +4068,7 @@
         <v/>
       </c>
       <c r="I24" s="13" t="str">
-        <f aca="false">IF(OR(A24="",D24=""),"",ROUND(D24*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A24="",D24=""),"",ROUND(D24*INDEX(Programmes!$L$2:$L$8,MATCH(A24,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J24" s="13" t="str">
@@ -3948,7 +4089,7 @@
         <v/>
       </c>
       <c r="I25" s="13" t="str">
-        <f aca="false">IF(OR(A25="",D25=""),"",ROUND(D25*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A25="",D25=""),"",ROUND(D25*INDEX(Programmes!$L$2:$L$8,MATCH(A25,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J25" s="13" t="str">
@@ -3969,7 +4110,7 @@
         <v/>
       </c>
       <c r="I26" s="13" t="str">
-        <f aca="false">IF(OR(A26="",D26=""),"",ROUND(D26*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A26="",D26=""),"",ROUND(D26*INDEX(Programmes!$L$2:$L$8,MATCH(A26,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J26" s="13" t="str">
@@ -3990,7 +4131,7 @@
         <v/>
       </c>
       <c r="I27" s="13" t="str">
-        <f aca="false">IF(OR(A27="",D27=""),"",ROUND(D27*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A27="",D27=""),"",ROUND(D27*INDEX(Programmes!$L$2:$L$8,MATCH(A27,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J27" s="13" t="str">
@@ -4011,7 +4152,7 @@
         <v/>
       </c>
       <c r="I28" s="13" t="str">
-        <f aca="false">IF(OR(A28="",D28=""),"",ROUND(D28*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A28="",D28=""),"",ROUND(D28*INDEX(Programmes!$L$2:$L$8,MATCH(A28,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J28" s="13" t="str">
@@ -4032,7 +4173,7 @@
         <v/>
       </c>
       <c r="I29" s="13" t="str">
-        <f aca="false">IF(OR(A29="",D29=""),"",ROUND(D29*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A29="",D29=""),"",ROUND(D29*INDEX(Programmes!$L$2:$L$8,MATCH(A29,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J29" s="13" t="str">
@@ -4053,7 +4194,7 @@
         <v/>
       </c>
       <c r="I30" s="13" t="str">
-        <f aca="false">IF(OR(A30="",D30=""),"",ROUND(D30*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A30="",D30=""),"",ROUND(D30*INDEX(Programmes!$L$2:$L$8,MATCH(A30,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J30" s="13" t="str">
@@ -4074,7 +4215,7 @@
         <v/>
       </c>
       <c r="I31" s="13" t="str">
-        <f aca="false">IF(OR(A31="",D31=""),"",ROUND(D31*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A31="",D31=""),"",ROUND(D31*INDEX(Programmes!$L$2:$L$8,MATCH(A31,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J31" s="13" t="str">
@@ -4095,7 +4236,7 @@
         <v/>
       </c>
       <c r="I32" s="13" t="str">
-        <f aca="false">IF(OR(A32="",D32=""),"",ROUND(D32*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A32="",D32=""),"",ROUND(D32*INDEX(Programmes!$L$2:$L$8,MATCH(A32,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J32" s="13" t="str">
@@ -4116,7 +4257,7 @@
         <v/>
       </c>
       <c r="I33" s="13" t="str">
-        <f aca="false">IF(OR(A33="",D33=""),"",ROUND(D33*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A33="",D33=""),"",ROUND(D33*INDEX(Programmes!$L$2:$L$8,MATCH(A33,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J33" s="13" t="str">
@@ -4137,7 +4278,7 @@
         <v/>
       </c>
       <c r="I34" s="13" t="str">
-        <f aca="false">IF(OR(A34="",D34=""),"",ROUND(D34*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A34="",D34=""),"",ROUND(D34*INDEX(Programmes!$L$2:$L$8,MATCH(A34,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J34" s="13" t="str">
@@ -4158,7 +4299,7 @@
         <v/>
       </c>
       <c r="I35" s="13" t="str">
-        <f aca="false">IF(OR(A35="",D35=""),"",ROUND(D35*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A35="",D35=""),"",ROUND(D35*INDEX(Programmes!$L$2:$L$8,MATCH(A35,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J35" s="13" t="str">
@@ -4179,7 +4320,7 @@
         <v/>
       </c>
       <c r="I36" s="13" t="str">
-        <f aca="false">IF(OR(A36="",D36=""),"",ROUND(D36*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A36="",D36=""),"",ROUND(D36*INDEX(Programmes!$L$2:$L$8,MATCH(A36,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J36" s="13" t="str">
@@ -4200,7 +4341,7 @@
         <v/>
       </c>
       <c r="I37" s="13" t="str">
-        <f aca="false">IF(OR(A37="",D37=""),"",ROUND(D37*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A37="",D37=""),"",ROUND(D37*INDEX(Programmes!$L$2:$L$8,MATCH(A37,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J37" s="13" t="str">
@@ -4221,7 +4362,7 @@
         <v/>
       </c>
       <c r="I38" s="13" t="str">
-        <f aca="false">IF(OR(A38="",D38=""),"",ROUND(D38*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A38="",D38=""),"",ROUND(D38*INDEX(Programmes!$L$2:$L$8,MATCH(A38,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J38" s="13" t="str">
@@ -4242,7 +4383,7 @@
         <v/>
       </c>
       <c r="I39" s="13" t="str">
-        <f aca="false">IF(OR(A39="",D39=""),"",ROUND(D39*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A39="",D39=""),"",ROUND(D39*INDEX(Programmes!$L$2:$L$8,MATCH(A39,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J39" s="13" t="str">
@@ -4263,7 +4404,7 @@
         <v/>
       </c>
       <c r="I40" s="13" t="str">
-        <f aca="false">IF(OR(A40="",D40=""),"",ROUND(D40*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A40="",D40=""),"",ROUND(D40*INDEX(Programmes!$L$2:$L$8,MATCH(A40,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J40" s="13" t="str">
@@ -4284,7 +4425,7 @@
         <v/>
       </c>
       <c r="I41" s="13" t="str">
-        <f aca="false">IF(OR(A41="",D41=""),"",ROUND(D41*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A41="",D41=""),"",ROUND(D41*INDEX(Programmes!$L$2:$L$8,MATCH(A41,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J41" s="13" t="str">
@@ -4305,7 +4446,7 @@
         <v/>
       </c>
       <c r="I42" s="13" t="str">
-        <f aca="false">IF(OR(A42="",D42=""),"",ROUND(D42*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A42="",D42=""),"",ROUND(D42*INDEX(Programmes!$L$2:$L$8,MATCH(A42,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J42" s="13" t="str">
@@ -4326,7 +4467,7 @@
         <v/>
       </c>
       <c r="I43" s="13" t="str">
-        <f aca="false">IF(OR(A43="",D43=""),"",ROUND(D43*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A43="",D43=""),"",ROUND(D43*INDEX(Programmes!$L$2:$L$8,MATCH(A43,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J43" s="13" t="str">
@@ -4347,7 +4488,7 @@
         <v/>
       </c>
       <c r="I44" s="13" t="str">
-        <f aca="false">IF(OR(A44="",D44=""),"",ROUND(D44*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A44="",D44=""),"",ROUND(D44*INDEX(Programmes!$L$2:$L$8,MATCH(A44,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J44" s="13" t="str">
@@ -4368,7 +4509,7 @@
         <v/>
       </c>
       <c r="I45" s="13" t="str">
-        <f aca="false">IF(OR(A45="",D45=""),"",ROUND(D45*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A45="",D45=""),"",ROUND(D45*INDEX(Programmes!$L$2:$L$8,MATCH(A45,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J45" s="13" t="str">
@@ -4389,7 +4530,7 @@
         <v/>
       </c>
       <c r="I46" s="13" t="str">
-        <f aca="false">IF(OR(A46="",D46=""),"",ROUND(D46*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A46="",D46=""),"",ROUND(D46*INDEX(Programmes!$L$2:$L$8,MATCH(A46,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J46" s="13" t="str">
@@ -4410,7 +4551,7 @@
         <v/>
       </c>
       <c r="I47" s="13" t="str">
-        <f aca="false">IF(OR(A47="",D47=""),"",ROUND(D47*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A47="",D47=""),"",ROUND(D47*INDEX(Programmes!$L$2:$L$8,MATCH(A47,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J47" s="13" t="str">
@@ -4431,7 +4572,7 @@
         <v/>
       </c>
       <c r="I48" s="13" t="str">
-        <f aca="false">IF(OR(A48="",D48=""),"",ROUND(D48*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A48="",D48=""),"",ROUND(D48*INDEX(Programmes!$L$2:$L$8,MATCH(A48,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J48" s="13" t="str">
@@ -4452,7 +4593,7 @@
         <v/>
       </c>
       <c r="I49" s="13" t="str">
-        <f aca="false">IF(OR(A49="",D49=""),"",ROUND(D49*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A49="",D49=""),"",ROUND(D49*INDEX(Programmes!$L$2:$L$8,MATCH(A49,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J49" s="13" t="str">
@@ -4473,7 +4614,7 @@
         <v/>
       </c>
       <c r="I50" s="13" t="str">
-        <f aca="false">IF(OR(A50="",D50=""),"",ROUND(D50*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A50="",D50=""),"",ROUND(D50*INDEX(Programmes!$L$2:$L$8,MATCH(A50,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J50" s="13" t="str">
@@ -4494,7 +4635,7 @@
         <v/>
       </c>
       <c r="I51" s="13" t="str">
-        <f aca="false">IF(OR(A51="",D51=""),"",ROUND(D51*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A51="",D51=""),"",ROUND(D51*INDEX(Programmes!$L$2:$L$8,MATCH(A51,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J51" s="13" t="str">
@@ -4515,7 +4656,7 @@
         <v/>
       </c>
       <c r="I52" s="13" t="str">
-        <f aca="false">IF(OR(A52="",D52=""),"",ROUND(D52*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A52="",D52=""),"",ROUND(D52*INDEX(Programmes!$L$2:$L$8,MATCH(A52,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J52" s="13" t="str">
@@ -4536,7 +4677,7 @@
         <v/>
       </c>
       <c r="I53" s="13" t="str">
-        <f aca="false">IF(OR(A53="",D53=""),"",ROUND(D53*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A53="",D53=""),"",ROUND(D53*INDEX(Programmes!$L$2:$L$8,MATCH(A53,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J53" s="13" t="str">
@@ -4557,7 +4698,7 @@
         <v/>
       </c>
       <c r="I54" s="13" t="str">
-        <f aca="false">IF(OR(A54="",D54=""),"",ROUND(D54*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A54="",D54=""),"",ROUND(D54*INDEX(Programmes!$L$2:$L$8,MATCH(A54,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J54" s="13" t="str">
@@ -4578,7 +4719,7 @@
         <v/>
       </c>
       <c r="I55" s="13" t="str">
-        <f aca="false">IF(OR(A55="",D55=""),"",ROUND(D55*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A55="",D55=""),"",ROUND(D55*INDEX(Programmes!$L$2:$L$8,MATCH(A55,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J55" s="13" t="str">
@@ -4599,7 +4740,7 @@
         <v/>
       </c>
       <c r="I56" s="13" t="str">
-        <f aca="false">IF(OR(A56="",D56=""),"",ROUND(D56*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A56="",D56=""),"",ROUND(D56*INDEX(Programmes!$L$2:$L$8,MATCH(A56,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J56" s="13" t="str">
@@ -4620,7 +4761,7 @@
         <v/>
       </c>
       <c r="I57" s="13" t="str">
-        <f aca="false">IF(OR(A57="",D57=""),"",ROUND(D57*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A57="",D57=""),"",ROUND(D57*INDEX(Programmes!$L$2:$L$8,MATCH(A57,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J57" s="13" t="str">
@@ -4641,7 +4782,7 @@
         <v/>
       </c>
       <c r="I58" s="13" t="str">
-        <f aca="false">IF(OR(A58="",D58=""),"",ROUND(D58*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A58="",D58=""),"",ROUND(D58*INDEX(Programmes!$L$2:$L$8,MATCH(A58,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J58" s="13" t="str">
@@ -4662,7 +4803,7 @@
         <v/>
       </c>
       <c r="I59" s="13" t="str">
-        <f aca="false">IF(OR(A59="",D59=""),"",ROUND(D59*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A59="",D59=""),"",ROUND(D59*INDEX(Programmes!$L$2:$L$8,MATCH(A59,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J59" s="13" t="str">
@@ -4683,7 +4824,7 @@
         <v/>
       </c>
       <c r="I60" s="13" t="str">
-        <f aca="false">IF(OR(A60="",D60=""),"",ROUND(D60*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A60="",D60=""),"",ROUND(D60*INDEX(Programmes!$L$2:$L$8,MATCH(A60,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J60" s="13" t="str">
@@ -4704,7 +4845,7 @@
         <v/>
       </c>
       <c r="I61" s="13" t="str">
-        <f aca="false">IF(OR(A61="",D61=""),"",ROUND(D61*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A61="",D61=""),"",ROUND(D61*INDEX(Programmes!$L$2:$L$8,MATCH(A61,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J61" s="13" t="str">
@@ -4725,7 +4866,7 @@
         <v/>
       </c>
       <c r="I62" s="13" t="str">
-        <f aca="false">IF(OR(A62="",D62=""),"",ROUND(D62*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A62="",D62=""),"",ROUND(D62*INDEX(Programmes!$L$2:$L$8,MATCH(A62,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J62" s="13" t="str">
@@ -4746,7 +4887,7 @@
         <v/>
       </c>
       <c r="I63" s="13" t="str">
-        <f aca="false">IF(OR(A63="",D63=""),"",ROUND(D63*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A63="",D63=""),"",ROUND(D63*INDEX(Programmes!$L$2:$L$8,MATCH(A63,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J63" s="13" t="str">
@@ -4767,7 +4908,7 @@
         <v/>
       </c>
       <c r="I64" s="13" t="str">
-        <f aca="false">IF(OR(A64="",D64=""),"",ROUND(D64*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A64="",D64=""),"",ROUND(D64*INDEX(Programmes!$L$2:$L$8,MATCH(A64,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J64" s="13" t="str">
@@ -4788,7 +4929,7 @@
         <v/>
       </c>
       <c r="I65" s="13" t="str">
-        <f aca="false">IF(OR(A65="",D65=""),"",ROUND(D65*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A65="",D65=""),"",ROUND(D65*INDEX(Programmes!$L$2:$L$8,MATCH(A65,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J65" s="13" t="str">
@@ -4809,7 +4950,7 @@
         <v/>
       </c>
       <c r="I66" s="13" t="str">
-        <f aca="false">IF(OR(A66="",D66=""),"",ROUND(D66*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A66="",D66=""),"",ROUND(D66*INDEX(Programmes!$L$2:$L$8,MATCH(A66,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J66" s="13" t="str">
@@ -4830,7 +4971,7 @@
         <v/>
       </c>
       <c r="I67" s="13" t="str">
-        <f aca="false">IF(OR(A67="",D67=""),"",ROUND(D67*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A67="",D67=""),"",ROUND(D67*INDEX(Programmes!$L$2:$L$8,MATCH(A67,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J67" s="13" t="str">
@@ -4851,7 +4992,7 @@
         <v/>
       </c>
       <c r="I68" s="13" t="str">
-        <f aca="false">IF(OR(A68="",D68=""),"",ROUND(D68*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A68="",D68=""),"",ROUND(D68*INDEX(Programmes!$L$2:$L$8,MATCH(A68,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J68" s="13" t="str">
@@ -4872,7 +5013,7 @@
         <v/>
       </c>
       <c r="I69" s="13" t="str">
-        <f aca="false">IF(OR(A69="",D69=""),"",ROUND(D69*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A69="",D69=""),"",ROUND(D69*INDEX(Programmes!$L$2:$L$8,MATCH(A69,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J69" s="13" t="str">
@@ -4893,7 +5034,7 @@
         <v/>
       </c>
       <c r="I70" s="13" t="str">
-        <f aca="false">IF(OR(A70="",D70=""),"",ROUND(D70*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A70="",D70=""),"",ROUND(D70*INDEX(Programmes!$L$2:$L$8,MATCH(A70,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J70" s="13" t="str">
@@ -4914,7 +5055,7 @@
         <v/>
       </c>
       <c r="I71" s="13" t="str">
-        <f aca="false">IF(OR(A71="",D71=""),"",ROUND(D71*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A71="",D71=""),"",ROUND(D71*INDEX(Programmes!$L$2:$L$8,MATCH(A71,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J71" s="13" t="str">
@@ -4935,7 +5076,7 @@
         <v/>
       </c>
       <c r="I72" s="13" t="str">
-        <f aca="false">IF(OR(A72="",D72=""),"",ROUND(D72*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A72="",D72=""),"",ROUND(D72*INDEX(Programmes!$L$2:$L$8,MATCH(A72,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J72" s="13" t="str">
@@ -4956,7 +5097,7 @@
         <v/>
       </c>
       <c r="I73" s="13" t="str">
-        <f aca="false">IF(OR(A73="",D73=""),"",ROUND(D73*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A73="",D73=""),"",ROUND(D73*INDEX(Programmes!$L$2:$L$8,MATCH(A73,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J73" s="13" t="str">
@@ -4977,7 +5118,7 @@
         <v/>
       </c>
       <c r="I74" s="13" t="str">
-        <f aca="false">IF(OR(A74="",D74=""),"",ROUND(D74*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A74="",D74=""),"",ROUND(D74*INDEX(Programmes!$L$2:$L$8,MATCH(A74,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J74" s="13" t="str">
@@ -4998,7 +5139,7 @@
         <v/>
       </c>
       <c r="I75" s="13" t="str">
-        <f aca="false">IF(OR(A75="",D75=""),"",ROUND(D75*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A75="",D75=""),"",ROUND(D75*INDEX(Programmes!$L$2:$L$8,MATCH(A75,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J75" s="13" t="str">
@@ -5019,7 +5160,7 @@
         <v/>
       </c>
       <c r="I76" s="13" t="str">
-        <f aca="false">IF(OR(A76="",D76=""),"",ROUND(D76*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A76="",D76=""),"",ROUND(D76*INDEX(Programmes!$L$2:$L$8,MATCH(A76,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J76" s="13" t="str">
@@ -5040,7 +5181,7 @@
         <v/>
       </c>
       <c r="I77" s="13" t="str">
-        <f aca="false">IF(OR(A77="",D77=""),"",ROUND(D77*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A77="",D77=""),"",ROUND(D77*INDEX(Programmes!$L$2:$L$8,MATCH(A77,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J77" s="13" t="str">
@@ -5061,7 +5202,7 @@
         <v/>
       </c>
       <c r="I78" s="13" t="str">
-        <f aca="false">IF(OR(A78="",D78=""),"",ROUND(D78*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A78="",D78=""),"",ROUND(D78*INDEX(Programmes!$L$2:$L$8,MATCH(A78,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J78" s="13" t="str">
@@ -5082,7 +5223,7 @@
         <v/>
       </c>
       <c r="I79" s="13" t="str">
-        <f aca="false">IF(OR(A79="",D79=""),"",ROUND(D79*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A79="",D79=""),"",ROUND(D79*INDEX(Programmes!$L$2:$L$8,MATCH(A79,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J79" s="13" t="str">
@@ -5103,7 +5244,7 @@
         <v/>
       </c>
       <c r="I80" s="13" t="str">
-        <f aca="false">IF(OR(A80="",D80=""),"",ROUND(D80*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A80="",D80=""),"",ROUND(D80*INDEX(Programmes!$L$2:$L$8,MATCH(A80,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J80" s="13" t="str">
@@ -5124,7 +5265,7 @@
         <v/>
       </c>
       <c r="I81" s="13" t="str">
-        <f aca="false">IF(OR(A81="",D81=""),"",ROUND(D81*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A81="",D81=""),"",ROUND(D81*INDEX(Programmes!$L$2:$L$8,MATCH(A81,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J81" s="13" t="str">
@@ -5145,7 +5286,7 @@
         <v/>
       </c>
       <c r="I82" s="13" t="str">
-        <f aca="false">IF(OR(A82="",D82=""),"",ROUND(D82*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A82="",D82=""),"",ROUND(D82*INDEX(Programmes!$L$2:$L$8,MATCH(A82,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J82" s="13" t="str">
@@ -5166,7 +5307,7 @@
         <v/>
       </c>
       <c r="I83" s="13" t="str">
-        <f aca="false">IF(OR(A83="",D83=""),"",ROUND(D83*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A83="",D83=""),"",ROUND(D83*INDEX(Programmes!$L$2:$L$8,MATCH(A83,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J83" s="13" t="str">
@@ -5187,7 +5328,7 @@
         <v/>
       </c>
       <c r="I84" s="13" t="str">
-        <f aca="false">IF(OR(A84="",D84=""),"",ROUND(D84*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A84="",D84=""),"",ROUND(D84*INDEX(Programmes!$L$2:$L$8,MATCH(A84,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J84" s="13" t="str">
@@ -5208,7 +5349,7 @@
         <v/>
       </c>
       <c r="I85" s="13" t="str">
-        <f aca="false">IF(OR(A85="",D85=""),"",ROUND(D85*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A85="",D85=""),"",ROUND(D85*INDEX(Programmes!$L$2:$L$8,MATCH(A85,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J85" s="13" t="str">
@@ -5229,7 +5370,7 @@
         <v/>
       </c>
       <c r="I86" s="13" t="str">
-        <f aca="false">IF(OR(A86="",D86=""),"",ROUND(D86*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A86="",D86=""),"",ROUND(D86*INDEX(Programmes!$L$2:$L$8,MATCH(A86,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J86" s="13" t="str">
@@ -5250,7 +5391,7 @@
         <v/>
       </c>
       <c r="I87" s="13" t="str">
-        <f aca="false">IF(OR(A87="",D87=""),"",ROUND(D87*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A87="",D87=""),"",ROUND(D87*INDEX(Programmes!$L$2:$L$8,MATCH(A87,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J87" s="13" t="str">
@@ -5271,7 +5412,7 @@
         <v/>
       </c>
       <c r="I88" s="13" t="str">
-        <f aca="false">IF(OR(A88="",D88=""),"",ROUND(D88*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A88="",D88=""),"",ROUND(D88*INDEX(Programmes!$L$2:$L$8,MATCH(A88,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J88" s="13" t="str">
@@ -5292,7 +5433,7 @@
         <v/>
       </c>
       <c r="I89" s="13" t="str">
-        <f aca="false">IF(OR(A89="",D89=""),"",ROUND(D89*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A89="",D89=""),"",ROUND(D89*INDEX(Programmes!$L$2:$L$8,MATCH(A89,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J89" s="13" t="str">
@@ -5313,7 +5454,7 @@
         <v/>
       </c>
       <c r="I90" s="13" t="str">
-        <f aca="false">IF(OR(A90="",D90=""),"",ROUND(D90*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A90="",D90=""),"",ROUND(D90*INDEX(Programmes!$L$2:$L$8,MATCH(A90,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J90" s="13" t="str">
@@ -5334,7 +5475,7 @@
         <v/>
       </c>
       <c r="I91" s="13" t="str">
-        <f aca="false">IF(OR(A91="",D91=""),"",ROUND(D91*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A91="",D91=""),"",ROUND(D91*INDEX(Programmes!$L$2:$L$8,MATCH(A91,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J91" s="13" t="str">
@@ -5355,7 +5496,7 @@
         <v/>
       </c>
       <c r="I92" s="13" t="str">
-        <f aca="false">IF(OR(A92="",D92=""),"",ROUND(D92*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A92="",D92=""),"",ROUND(D92*INDEX(Programmes!$L$2:$L$8,MATCH(A92,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J92" s="13" t="str">
@@ -5376,7 +5517,7 @@
         <v/>
       </c>
       <c r="I93" s="13" t="str">
-        <f aca="false">IF(OR(A93="",D93=""),"",ROUND(D93*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A93="",D93=""),"",ROUND(D93*INDEX(Programmes!$L$2:$L$8,MATCH(A93,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J93" s="13" t="str">
@@ -5397,7 +5538,7 @@
         <v/>
       </c>
       <c r="I94" s="13" t="str">
-        <f aca="false">IF(OR(A94="",D94=""),"",ROUND(D94*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A94="",D94=""),"",ROUND(D94*INDEX(Programmes!$L$2:$L$8,MATCH(A94,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J94" s="13" t="str">
@@ -5418,7 +5559,7 @@
         <v/>
       </c>
       <c r="I95" s="13" t="str">
-        <f aca="false">IF(OR(A95="",D95=""),"",ROUND(D95*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A95="",D95=""),"",ROUND(D95*INDEX(Programmes!$L$2:$L$8,MATCH(A95,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J95" s="13" t="str">
@@ -5439,7 +5580,7 @@
         <v/>
       </c>
       <c r="I96" s="13" t="str">
-        <f aca="false">IF(OR(A96="",D96=""),"",ROUND(D96*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A96="",D96=""),"",ROUND(D96*INDEX(Programmes!$L$2:$L$8,MATCH(A96,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J96" s="13" t="str">
@@ -5460,7 +5601,7 @@
         <v/>
       </c>
       <c r="I97" s="13" t="str">
-        <f aca="false">IF(OR(A97="",D97=""),"",ROUND(D97*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A97="",D97=""),"",ROUND(D97*INDEX(Programmes!$L$2:$L$8,MATCH(A97,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J97" s="13" t="str">
@@ -5481,7 +5622,7 @@
         <v/>
       </c>
       <c r="I98" s="13" t="str">
-        <f aca="false">IF(OR(A98="",D98=""),"",ROUND(D98*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A98="",D98=""),"",ROUND(D98*INDEX(Programmes!$L$2:$L$8,MATCH(A98,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J98" s="13" t="str">
@@ -5502,7 +5643,7 @@
         <v/>
       </c>
       <c r="I99" s="13" t="str">
-        <f aca="false">IF(OR(A99="",D99=""),"",ROUND(D99*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A99="",D99=""),"",ROUND(D99*INDEX(Programmes!$L$2:$L$8,MATCH(A99,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J99" s="13" t="str">
@@ -5523,7 +5664,7 @@
         <v/>
       </c>
       <c r="I100" s="13" t="str">
-        <f aca="false">IF(OR(A100="",D100=""),"",ROUND(D100*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A100="",D100=""),"",ROUND(D100*INDEX(Programmes!$L$2:$L$8,MATCH(A100,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J100" s="13" t="str">
@@ -5544,7 +5685,7 @@
         <v/>
       </c>
       <c r="I101" s="13" t="str">
-        <f aca="false">IF(OR(A101="",D101=""),"",ROUND(D101*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A101="",D101=""),"",ROUND(D101*INDEX(Programmes!$L$2:$L$8,MATCH(A101,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J101" s="13" t="str">
@@ -5565,7 +5706,7 @@
         <v/>
       </c>
       <c r="I102" s="13" t="str">
-        <f aca="false">IF(OR(A102="",D102=""),"",ROUND(D102*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A102="",D102=""),"",ROUND(D102*INDEX(Programmes!$L$2:$L$8,MATCH(A102,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J102" s="13" t="str">
@@ -5586,7 +5727,7 @@
         <v/>
       </c>
       <c r="I103" s="13" t="str">
-        <f aca="false">IF(OR(A103="",D103=""),"",ROUND(D103*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A103="",D103=""),"",ROUND(D103*INDEX(Programmes!$L$2:$L$8,MATCH(A103,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J103" s="13" t="str">
@@ -5607,7 +5748,7 @@
         <v/>
       </c>
       <c r="I104" s="13" t="str">
-        <f aca="false">IF(OR(A104="",D104=""),"",ROUND(D104*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A104="",D104=""),"",ROUND(D104*INDEX(Programmes!$L$2:$L$8,MATCH(A104,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J104" s="13" t="str">
@@ -5628,7 +5769,7 @@
         <v/>
       </c>
       <c r="I105" s="13" t="str">
-        <f aca="false">IF(OR(A105="",D105=""),"",ROUND(D105*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A105="",D105=""),"",ROUND(D105*INDEX(Programmes!$L$2:$L$8,MATCH(A105,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J105" s="13" t="str">
@@ -5649,7 +5790,7 @@
         <v/>
       </c>
       <c r="I106" s="13" t="str">
-        <f aca="false">IF(OR(A106="",D106=""),"",ROUND(D106*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A106="",D106=""),"",ROUND(D106*INDEX(Programmes!$L$2:$L$8,MATCH(A106,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J106" s="13" t="str">
@@ -5670,7 +5811,7 @@
         <v/>
       </c>
       <c r="I107" s="13" t="str">
-        <f aca="false">IF(OR(A107="",D107=""),"",ROUND(D107*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A107="",D107=""),"",ROUND(D107*INDEX(Programmes!$L$2:$L$8,MATCH(A107,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J107" s="13" t="str">
@@ -5691,7 +5832,7 @@
         <v/>
       </c>
       <c r="I108" s="13" t="str">
-        <f aca="false">IF(OR(A108="",D108=""),"",ROUND(D108*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A108="",D108=""),"",ROUND(D108*INDEX(Programmes!$L$2:$L$8,MATCH(A108,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J108" s="13" t="str">
@@ -5712,7 +5853,7 @@
         <v/>
       </c>
       <c r="I109" s="13" t="str">
-        <f aca="false">IF(OR(A109="",D109=""),"",ROUND(D109*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A109="",D109=""),"",ROUND(D109*INDEX(Programmes!$L$2:$L$8,MATCH(A109,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J109" s="13" t="str">
@@ -5733,7 +5874,7 @@
         <v/>
       </c>
       <c r="I110" s="13" t="str">
-        <f aca="false">IF(OR(A110="",D110=""),"",ROUND(D110*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A110="",D110=""),"",ROUND(D110*INDEX(Programmes!$L$2:$L$8,MATCH(A110,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J110" s="13" t="str">
@@ -5754,7 +5895,7 @@
         <v/>
       </c>
       <c r="I111" s="13" t="str">
-        <f aca="false">IF(OR(A111="",D111=""),"",ROUND(D111*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A111="",D111=""),"",ROUND(D111*INDEX(Programmes!$L$2:$L$8,MATCH(A111,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J111" s="13" t="str">
@@ -5775,7 +5916,7 @@
         <v/>
       </c>
       <c r="I112" s="13" t="str">
-        <f aca="false">IF(OR(A112="",D112=""),"",ROUND(D112*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A112="",D112=""),"",ROUND(D112*INDEX(Programmes!$L$2:$L$8,MATCH(A112,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J112" s="13" t="str">
@@ -5796,7 +5937,7 @@
         <v/>
       </c>
       <c r="I113" s="13" t="str">
-        <f aca="false">IF(OR(A113="",D113=""),"",ROUND(D113*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A113="",D113=""),"",ROUND(D113*INDEX(Programmes!$L$2:$L$8,MATCH(A113,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J113" s="13" t="str">
@@ -5817,7 +5958,7 @@
         <v/>
       </c>
       <c r="I114" s="13" t="str">
-        <f aca="false">IF(OR(A114="",D114=""),"",ROUND(D114*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A114="",D114=""),"",ROUND(D114*INDEX(Programmes!$L$2:$L$8,MATCH(A114,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J114" s="13" t="str">
@@ -5838,7 +5979,7 @@
         <v/>
       </c>
       <c r="I115" s="13" t="str">
-        <f aca="false">IF(OR(A115="",D115=""),"",ROUND(D115*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A115="",D115=""),"",ROUND(D115*INDEX(Programmes!$L$2:$L$8,MATCH(A115,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J115" s="13" t="str">
@@ -5859,7 +6000,7 @@
         <v/>
       </c>
       <c r="I116" s="13" t="str">
-        <f aca="false">IF(OR(A116="",D116=""),"",ROUND(D116*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A116="",D116=""),"",ROUND(D116*INDEX(Programmes!$L$2:$L$8,MATCH(A116,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J116" s="13" t="str">
@@ -5880,7 +6021,7 @@
         <v/>
       </c>
       <c r="I117" s="13" t="str">
-        <f aca="false">IF(OR(A117="",D117=""),"",ROUND(D117*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A117="",D117=""),"",ROUND(D117*INDEX(Programmes!$L$2:$L$8,MATCH(A117,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J117" s="13" t="str">
@@ -5901,7 +6042,7 @@
         <v/>
       </c>
       <c r="I118" s="13" t="str">
-        <f aca="false">IF(OR(A118="",D118=""),"",ROUND(D118*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A118="",D118=""),"",ROUND(D118*INDEX(Programmes!$L$2:$L$8,MATCH(A118,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J118" s="13" t="str">
@@ -5922,7 +6063,7 @@
         <v/>
       </c>
       <c r="I119" s="13" t="str">
-        <f aca="false">IF(OR(A119="",D119=""),"",ROUND(D119*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A119="",D119=""),"",ROUND(D119*INDEX(Programmes!$L$2:$L$8,MATCH(A119,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J119" s="13" t="str">
@@ -5943,7 +6084,7 @@
         <v/>
       </c>
       <c r="I120" s="13" t="str">
-        <f aca="false">IF(OR(A120="",D120=""),"",ROUND(D120*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A120="",D120=""),"",ROUND(D120*INDEX(Programmes!$L$2:$L$8,MATCH(A120,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J120" s="13" t="str">
@@ -5964,7 +6105,7 @@
         <v/>
       </c>
       <c r="I121" s="13" t="str">
-        <f aca="false">IF(OR(A121="",D121=""),"",ROUND(D121*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A121="",D121=""),"",ROUND(D121*INDEX(Programmes!$L$2:$L$8,MATCH(A121,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J121" s="13" t="str">
@@ -5985,7 +6126,7 @@
         <v/>
       </c>
       <c r="I122" s="13" t="str">
-        <f aca="false">IF(OR(A122="",D122=""),"",ROUND(D122*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A122="",D122=""),"",ROUND(D122*INDEX(Programmes!$L$2:$L$8,MATCH(A122,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J122" s="13" t="str">
@@ -6006,7 +6147,7 @@
         <v/>
       </c>
       <c r="I123" s="13" t="str">
-        <f aca="false">IF(OR(A123="",D123=""),"",ROUND(D123*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A123="",D123=""),"",ROUND(D123*INDEX(Programmes!$L$2:$L$8,MATCH(A123,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J123" s="13" t="str">
@@ -6027,7 +6168,7 @@
         <v/>
       </c>
       <c r="I124" s="13" t="str">
-        <f aca="false">IF(OR(A124="",D124=""),"",ROUND(D124*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A124="",D124=""),"",ROUND(D124*INDEX(Programmes!$L$2:$L$8,MATCH(A124,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J124" s="13" t="str">
@@ -6048,7 +6189,7 @@
         <v/>
       </c>
       <c r="I125" s="13" t="str">
-        <f aca="false">IF(OR(A125="",D125=""),"",ROUND(D125*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A125="",D125=""),"",ROUND(D125*INDEX(Programmes!$L$2:$L$8,MATCH(A125,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J125" s="13" t="str">
@@ -6069,7 +6210,7 @@
         <v/>
       </c>
       <c r="I126" s="13" t="str">
-        <f aca="false">IF(OR(A126="",D126=""),"",ROUND(D126*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A126="",D126=""),"",ROUND(D126*INDEX(Programmes!$L$2:$L$8,MATCH(A126,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J126" s="13" t="str">
@@ -6090,7 +6231,7 @@
         <v/>
       </c>
       <c r="I127" s="13" t="str">
-        <f aca="false">IF(OR(A127="",D127=""),"",ROUND(D127*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A127="",D127=""),"",ROUND(D127*INDEX(Programmes!$L$2:$L$8,MATCH(A127,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J127" s="13" t="str">
@@ -6111,7 +6252,7 @@
         <v/>
       </c>
       <c r="I128" s="13" t="str">
-        <f aca="false">IF(OR(A128="",D128=""),"",ROUND(D128*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A128="",D128=""),"",ROUND(D128*INDEX(Programmes!$L$2:$L$8,MATCH(A128,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J128" s="13" t="str">
@@ -6132,7 +6273,7 @@
         <v/>
       </c>
       <c r="I129" s="13" t="str">
-        <f aca="false">IF(OR(A129="",D129=""),"",ROUND(D129*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A129="",D129=""),"",ROUND(D129*INDEX(Programmes!$L$2:$L$8,MATCH(A129,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J129" s="13" t="str">
@@ -6153,7 +6294,7 @@
         <v/>
       </c>
       <c r="I130" s="13" t="str">
-        <f aca="false">IF(OR(A130="",D130=""),"",ROUND(D130*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A130="",D130=""),"",ROUND(D130*INDEX(Programmes!$L$2:$L$8,MATCH(A130,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J130" s="13" t="str">
@@ -6174,7 +6315,7 @@
         <v/>
       </c>
       <c r="I131" s="13" t="str">
-        <f aca="false">IF(OR(A131="",D131=""),"",ROUND(D131*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A131="",D131=""),"",ROUND(D131*INDEX(Programmes!$L$2:$L$8,MATCH(A131,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J131" s="13" t="str">
@@ -6195,7 +6336,7 @@
         <v/>
       </c>
       <c r="I132" s="13" t="str">
-        <f aca="false">IF(OR(A132="",D132=""),"",ROUND(D132*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A132="",D132=""),"",ROUND(D132*INDEX(Programmes!$L$2:$L$8,MATCH(A132,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J132" s="13" t="str">
@@ -6216,7 +6357,7 @@
         <v/>
       </c>
       <c r="I133" s="13" t="str">
-        <f aca="false">IF(OR(A133="",D133=""),"",ROUND(D133*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A133="",D133=""),"",ROUND(D133*INDEX(Programmes!$L$2:$L$8,MATCH(A133,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J133" s="13" t="str">
@@ -6237,7 +6378,7 @@
         <v/>
       </c>
       <c r="I134" s="13" t="str">
-        <f aca="false">IF(OR(A134="",D134=""),"",ROUND(D134*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A134="",D134=""),"",ROUND(D134*INDEX(Programmes!$L$2:$L$8,MATCH(A134,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J134" s="13" t="str">
@@ -6258,7 +6399,7 @@
         <v/>
       </c>
       <c r="I135" s="13" t="str">
-        <f aca="false">IF(OR(A135="",D135=""),"",ROUND(D135*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A135="",D135=""),"",ROUND(D135*INDEX(Programmes!$L$2:$L$8,MATCH(A135,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J135" s="13" t="str">
@@ -6279,7 +6420,7 @@
         <v/>
       </c>
       <c r="I136" s="13" t="str">
-        <f aca="false">IF(OR(A136="",D136=""),"",ROUND(D136*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A136="",D136=""),"",ROUND(D136*INDEX(Programmes!$L$2:$L$8,MATCH(A136,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J136" s="13" t="str">
@@ -6300,7 +6441,7 @@
         <v/>
       </c>
       <c r="I137" s="13" t="str">
-        <f aca="false">IF(OR(A137="",D137=""),"",ROUND(D137*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A137="",D137=""),"",ROUND(D137*INDEX(Programmes!$L$2:$L$8,MATCH(A137,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J137" s="13" t="str">
@@ -6321,7 +6462,7 @@
         <v/>
       </c>
       <c r="I138" s="13" t="str">
-        <f aca="false">IF(OR(A138="",D138=""),"",ROUND(D138*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A138="",D138=""),"",ROUND(D138*INDEX(Programmes!$L$2:$L$8,MATCH(A138,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J138" s="13" t="str">
@@ -6342,7 +6483,7 @@
         <v/>
       </c>
       <c r="I139" s="13" t="str">
-        <f aca="false">IF(OR(A139="",D139=""),"",ROUND(D139*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A139="",D139=""),"",ROUND(D139*INDEX(Programmes!$L$2:$L$8,MATCH(A139,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J139" s="13" t="str">
@@ -6363,7 +6504,7 @@
         <v/>
       </c>
       <c r="I140" s="13" t="str">
-        <f aca="false">IF(OR(A140="",D140=""),"",ROUND(D140*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A140="",D140=""),"",ROUND(D140*INDEX(Programmes!$L$2:$L$8,MATCH(A140,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J140" s="13" t="str">
@@ -6384,7 +6525,7 @@
         <v/>
       </c>
       <c r="I141" s="13" t="str">
-        <f aca="false">IF(OR(A141="",D141=""),"",ROUND(D141*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A141="",D141=""),"",ROUND(D141*INDEX(Programmes!$L$2:$L$8,MATCH(A141,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J141" s="13" t="str">
@@ -6405,7 +6546,7 @@
         <v/>
       </c>
       <c r="I142" s="13" t="str">
-        <f aca="false">IF(OR(A142="",D142=""),"",ROUND(D142*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A142="",D142=""),"",ROUND(D142*INDEX(Programmes!$L$2:$L$8,MATCH(A142,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J142" s="13" t="str">
@@ -6426,7 +6567,7 @@
         <v/>
       </c>
       <c r="I143" s="13" t="str">
-        <f aca="false">IF(OR(A143="",D143=""),"",ROUND(D143*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A143="",D143=""),"",ROUND(D143*INDEX(Programmes!$L$2:$L$8,MATCH(A143,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J143" s="13" t="str">
@@ -6447,7 +6588,7 @@
         <v/>
       </c>
       <c r="I144" s="13" t="str">
-        <f aca="false">IF(OR(A144="",D144=""),"",ROUND(D144*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A144="",D144=""),"",ROUND(D144*INDEX(Programmes!$L$2:$L$8,MATCH(A144,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J144" s="13" t="str">
@@ -6468,7 +6609,7 @@
         <v/>
       </c>
       <c r="I145" s="13" t="str">
-        <f aca="false">IF(OR(A145="",D145=""),"",ROUND(D145*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A145="",D145=""),"",ROUND(D145*INDEX(Programmes!$L$2:$L$8,MATCH(A145,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J145" s="13" t="str">
@@ -6489,7 +6630,7 @@
         <v/>
       </c>
       <c r="I146" s="13" t="str">
-        <f aca="false">IF(OR(A146="",D146=""),"",ROUND(D146*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A146="",D146=""),"",ROUND(D146*INDEX(Programmes!$L$2:$L$8,MATCH(A146,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J146" s="13" t="str">
@@ -6510,7 +6651,7 @@
         <v/>
       </c>
       <c r="I147" s="13" t="str">
-        <f aca="false">IF(OR(A147="",D147=""),"",ROUND(D147*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A147="",D147=""),"",ROUND(D147*INDEX(Programmes!$L$2:$L$8,MATCH(A147,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J147" s="13" t="str">
@@ -6531,7 +6672,7 @@
         <v/>
       </c>
       <c r="I148" s="13" t="str">
-        <f aca="false">IF(OR(A148="",D148=""),"",ROUND(D148*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A148="",D148=""),"",ROUND(D148*INDEX(Programmes!$L$2:$L$8,MATCH(A148,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J148" s="13" t="str">
@@ -6552,7 +6693,7 @@
         <v/>
       </c>
       <c r="I149" s="13" t="str">
-        <f aca="false">IF(OR(A149="",D149=""),"",ROUND(D149*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A149="",D149=""),"",ROUND(D149*INDEX(Programmes!$L$2:$L$8,MATCH(A149,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J149" s="13" t="str">
@@ -6573,7 +6714,7 @@
         <v/>
       </c>
       <c r="I150" s="13" t="str">
-        <f aca="false">IF(OR(A150="",D150=""),"",ROUND(D150*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A150="",D150=""),"",ROUND(D150*INDEX(Programmes!$L$2:$L$8,MATCH(A150,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J150" s="13" t="str">
@@ -6594,7 +6735,7 @@
         <v/>
       </c>
       <c r="I151" s="13" t="str">
-        <f aca="false">IF(OR(A151="",D151=""),"",ROUND(D151*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A151="",D151=""),"",ROUND(D151*INDEX(Programmes!$L$2:$L$8,MATCH(A151,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J151" s="13" t="str">
@@ -6615,7 +6756,7 @@
         <v/>
       </c>
       <c r="I152" s="13" t="str">
-        <f aca="false">IF(OR(A152="",D152=""),"",ROUND(D152*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A152="",D152=""),"",ROUND(D152*INDEX(Programmes!$L$2:$L$8,MATCH(A152,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J152" s="13" t="str">
@@ -6636,7 +6777,7 @@
         <v/>
       </c>
       <c r="I153" s="13" t="str">
-        <f aca="false">IF(OR(A153="",D153=""),"",ROUND(D153*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A153="",D153=""),"",ROUND(D153*INDEX(Programmes!$L$2:$L$8,MATCH(A153,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J153" s="13" t="str">
@@ -6657,7 +6798,7 @@
         <v/>
       </c>
       <c r="I154" s="13" t="str">
-        <f aca="false">IF(OR(A154="",D154=""),"",ROUND(D154*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A154="",D154=""),"",ROUND(D154*INDEX(Programmes!$L$2:$L$8,MATCH(A154,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J154" s="13" t="str">
@@ -6678,7 +6819,7 @@
         <v/>
       </c>
       <c r="I155" s="13" t="str">
-        <f aca="false">IF(OR(A155="",D155=""),"",ROUND(D155*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A155="",D155=""),"",ROUND(D155*INDEX(Programmes!$L$2:$L$8,MATCH(A155,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J155" s="13" t="str">
@@ -6699,7 +6840,7 @@
         <v/>
       </c>
       <c r="I156" s="13" t="str">
-        <f aca="false">IF(OR(A156="",D156=""),"",ROUND(D156*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A156="",D156=""),"",ROUND(D156*INDEX(Programmes!$L$2:$L$8,MATCH(A156,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J156" s="13" t="str">
@@ -6720,7 +6861,7 @@
         <v/>
       </c>
       <c r="I157" s="13" t="str">
-        <f aca="false">IF(OR(A157="",D157=""),"",ROUND(D157*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A157="",D157=""),"",ROUND(D157*INDEX(Programmes!$L$2:$L$8,MATCH(A157,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J157" s="13" t="str">
@@ -6741,7 +6882,7 @@
         <v/>
       </c>
       <c r="I158" s="13" t="str">
-        <f aca="false">IF(OR(A158="",D158=""),"",ROUND(D158*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A158="",D158=""),"",ROUND(D158*INDEX(Programmes!$L$2:$L$8,MATCH(A158,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J158" s="13" t="str">
@@ -6762,7 +6903,7 @@
         <v/>
       </c>
       <c r="I159" s="13" t="str">
-        <f aca="false">IF(OR(A159="",D159=""),"",ROUND(D159*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A159="",D159=""),"",ROUND(D159*INDEX(Programmes!$L$2:$L$8,MATCH(A159,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J159" s="13" t="str">
@@ -6783,7 +6924,7 @@
         <v/>
       </c>
       <c r="I160" s="13" t="str">
-        <f aca="false">IF(OR(A160="",D160=""),"",ROUND(D160*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A160="",D160=""),"",ROUND(D160*INDEX(Programmes!$L$2:$L$8,MATCH(A160,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J160" s="13" t="str">
@@ -6804,7 +6945,7 @@
         <v/>
       </c>
       <c r="I161" s="13" t="str">
-        <f aca="false">IF(OR(A161="",D161=""),"",ROUND(D161*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A161="",D161=""),"",ROUND(D161*INDEX(Programmes!$L$2:$L$8,MATCH(A161,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J161" s="13" t="str">
@@ -6825,7 +6966,7 @@
         <v/>
       </c>
       <c r="I162" s="13" t="str">
-        <f aca="false">IF(OR(A162="",D162=""),"",ROUND(D162*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A162="",D162=""),"",ROUND(D162*INDEX(Programmes!$L$2:$L$8,MATCH(A162,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J162" s="13" t="str">
@@ -6846,7 +6987,7 @@
         <v/>
       </c>
       <c r="I163" s="13" t="str">
-        <f aca="false">IF(OR(A163="",D163=""),"",ROUND(D163*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A163="",D163=""),"",ROUND(D163*INDEX(Programmes!$L$2:$L$8,MATCH(A163,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J163" s="13" t="str">
@@ -6867,7 +7008,7 @@
         <v/>
       </c>
       <c r="I164" s="13" t="str">
-        <f aca="false">IF(OR(A164="",D164=""),"",ROUND(D164*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A164="",D164=""),"",ROUND(D164*INDEX(Programmes!$L$2:$L$8,MATCH(A164,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J164" s="13" t="str">
@@ -6888,7 +7029,7 @@
         <v/>
       </c>
       <c r="I165" s="13" t="str">
-        <f aca="false">IF(OR(A165="",D165=""),"",ROUND(D165*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A165="",D165=""),"",ROUND(D165*INDEX(Programmes!$L$2:$L$8,MATCH(A165,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J165" s="13" t="str">
@@ -6909,7 +7050,7 @@
         <v/>
       </c>
       <c r="I166" s="13" t="str">
-        <f aca="false">IF(OR(A166="",D166=""),"",ROUND(D166*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A166="",D166=""),"",ROUND(D166*INDEX(Programmes!$L$2:$L$8,MATCH(A166,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J166" s="13" t="str">
@@ -6930,7 +7071,7 @@
         <v/>
       </c>
       <c r="I167" s="13" t="str">
-        <f aca="false">IF(OR(A167="",D167=""),"",ROUND(D167*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A167="",D167=""),"",ROUND(D167*INDEX(Programmes!$L$2:$L$8,MATCH(A167,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J167" s="13" t="str">
@@ -6951,7 +7092,7 @@
         <v/>
       </c>
       <c r="I168" s="13" t="str">
-        <f aca="false">IF(OR(A168="",D168=""),"",ROUND(D168*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A168="",D168=""),"",ROUND(D168*INDEX(Programmes!$L$2:$L$8,MATCH(A168,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J168" s="13" t="str">
@@ -6972,7 +7113,7 @@
         <v/>
       </c>
       <c r="I169" s="13" t="str">
-        <f aca="false">IF(OR(A169="",D169=""),"",ROUND(D169*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A169="",D169=""),"",ROUND(D169*INDEX(Programmes!$L$2:$L$8,MATCH(A169,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J169" s="13" t="str">
@@ -6993,7 +7134,7 @@
         <v/>
       </c>
       <c r="I170" s="13" t="str">
-        <f aca="false">IF(OR(A170="",D170=""),"",ROUND(D170*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A170="",D170=""),"",ROUND(D170*INDEX(Programmes!$L$2:$L$8,MATCH(A170,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J170" s="13" t="str">
@@ -7014,7 +7155,7 @@
         <v/>
       </c>
       <c r="I171" s="13" t="str">
-        <f aca="false">IF(OR(A171="",D171=""),"",ROUND(D171*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A171="",D171=""),"",ROUND(D171*INDEX(Programmes!$L$2:$L$8,MATCH(A171,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J171" s="13" t="str">
@@ -7035,7 +7176,7 @@
         <v/>
       </c>
       <c r="I172" s="13" t="str">
-        <f aca="false">IF(OR(A172="",D172=""),"",ROUND(D172*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A172="",D172=""),"",ROUND(D172*INDEX(Programmes!$L$2:$L$8,MATCH(A172,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J172" s="13" t="str">
@@ -7056,7 +7197,7 @@
         <v/>
       </c>
       <c r="I173" s="13" t="str">
-        <f aca="false">IF(OR(A173="",D173=""),"",ROUND(D173*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A173="",D173=""),"",ROUND(D173*INDEX(Programmes!$L$2:$L$8,MATCH(A173,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J173" s="13" t="str">
@@ -7077,7 +7218,7 @@
         <v/>
       </c>
       <c r="I174" s="13" t="str">
-        <f aca="false">IF(OR(A174="",D174=""),"",ROUND(D174*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A174="",D174=""),"",ROUND(D174*INDEX(Programmes!$L$2:$L$8,MATCH(A174,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J174" s="13" t="str">
@@ -7098,7 +7239,7 @@
         <v/>
       </c>
       <c r="I175" s="13" t="str">
-        <f aca="false">IF(OR(A175="",D175=""),"",ROUND(D175*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A175="",D175=""),"",ROUND(D175*INDEX(Programmes!$L$2:$L$8,MATCH(A175,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J175" s="13" t="str">
@@ -7119,7 +7260,7 @@
         <v/>
       </c>
       <c r="I176" s="13" t="str">
-        <f aca="false">IF(OR(A176="",D176=""),"",ROUND(D176*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A176="",D176=""),"",ROUND(D176*INDEX(Programmes!$L$2:$L$8,MATCH(A176,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J176" s="13" t="str">
@@ -7140,7 +7281,7 @@
         <v/>
       </c>
       <c r="I177" s="13" t="str">
-        <f aca="false">IF(OR(A177="",D177=""),"",ROUND(D177*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A177="",D177=""),"",ROUND(D177*INDEX(Programmes!$L$2:$L$8,MATCH(A177,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J177" s="13" t="str">
@@ -7161,7 +7302,7 @@
         <v/>
       </c>
       <c r="I178" s="13" t="str">
-        <f aca="false">IF(OR(A178="",D178=""),"",ROUND(D178*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A178="",D178=""),"",ROUND(D178*INDEX(Programmes!$L$2:$L$8,MATCH(A178,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J178" s="13" t="str">
@@ -7182,7 +7323,7 @@
         <v/>
       </c>
       <c r="I179" s="13" t="str">
-        <f aca="false">IF(OR(A179="",D179=""),"",ROUND(D179*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A179="",D179=""),"",ROUND(D179*INDEX(Programmes!$L$2:$L$8,MATCH(A179,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J179" s="13" t="str">
@@ -7203,7 +7344,7 @@
         <v/>
       </c>
       <c r="I180" s="13" t="str">
-        <f aca="false">IF(OR(A180="",D180=""),"",ROUND(D180*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A180="",D180=""),"",ROUND(D180*INDEX(Programmes!$L$2:$L$8,MATCH(A180,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J180" s="13" t="str">
@@ -7224,7 +7365,7 @@
         <v/>
       </c>
       <c r="I181" s="13" t="str">
-        <f aca="false">IF(OR(A181="",D181=""),"",ROUND(D181*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A181="",D181=""),"",ROUND(D181*INDEX(Programmes!$L$2:$L$8,MATCH(A181,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J181" s="13" t="str">
@@ -7245,7 +7386,7 @@
         <v/>
       </c>
       <c r="I182" s="13" t="str">
-        <f aca="false">IF(OR(A182="",D182=""),"",ROUND(D182*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A182="",D182=""),"",ROUND(D182*INDEX(Programmes!$L$2:$L$8,MATCH(A182,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J182" s="13" t="str">
@@ -7266,7 +7407,7 @@
         <v/>
       </c>
       <c r="I183" s="13" t="str">
-        <f aca="false">IF(OR(A183="",D183=""),"",ROUND(D183*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A183="",D183=""),"",ROUND(D183*INDEX(Programmes!$L$2:$L$8,MATCH(A183,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J183" s="13" t="str">
@@ -7287,7 +7428,7 @@
         <v/>
       </c>
       <c r="I184" s="13" t="str">
-        <f aca="false">IF(OR(A184="",D184=""),"",ROUND(D184*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A184="",D184=""),"",ROUND(D184*INDEX(Programmes!$L$2:$L$8,MATCH(A184,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J184" s="13" t="str">
@@ -7308,7 +7449,7 @@
         <v/>
       </c>
       <c r="I185" s="13" t="str">
-        <f aca="false">IF(OR(A185="",D185=""),"",ROUND(D185*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A185="",D185=""),"",ROUND(D185*INDEX(Programmes!$L$2:$L$8,MATCH(A185,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J185" s="13" t="str">
@@ -7329,7 +7470,7 @@
         <v/>
       </c>
       <c r="I186" s="13" t="str">
-        <f aca="false">IF(OR(A186="",D186=""),"",ROUND(D186*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A186="",D186=""),"",ROUND(D186*INDEX(Programmes!$L$2:$L$8,MATCH(A186,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J186" s="13" t="str">
@@ -7350,7 +7491,7 @@
         <v/>
       </c>
       <c r="I187" s="13" t="str">
-        <f aca="false">IF(OR(A187="",D187=""),"",ROUND(D187*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A187="",D187=""),"",ROUND(D187*INDEX(Programmes!$L$2:$L$8,MATCH(A187,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J187" s="13" t="str">
@@ -7371,7 +7512,7 @@
         <v/>
       </c>
       <c r="I188" s="13" t="str">
-        <f aca="false">IF(OR(A188="",D188=""),"",ROUND(D188*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A188="",D188=""),"",ROUND(D188*INDEX(Programmes!$L$2:$L$8,MATCH(A188,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J188" s="13" t="str">
@@ -7392,7 +7533,7 @@
         <v/>
       </c>
       <c r="I189" s="13" t="str">
-        <f aca="false">IF(OR(A189="",D189=""),"",ROUND(D189*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A189="",D189=""),"",ROUND(D189*INDEX(Programmes!$L$2:$L$8,MATCH(A189,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J189" s="13" t="str">
@@ -7413,7 +7554,7 @@
         <v/>
       </c>
       <c r="I190" s="13" t="str">
-        <f aca="false">IF(OR(A190="",D190=""),"",ROUND(D190*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A190="",D190=""),"",ROUND(D190*INDEX(Programmes!$L$2:$L$8,MATCH(A190,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J190" s="13" t="str">
@@ -7434,7 +7575,7 @@
         <v/>
       </c>
       <c r="I191" s="13" t="str">
-        <f aca="false">IF(OR(A191="",D191=""),"",ROUND(D191*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A191="",D191=""),"",ROUND(D191*INDEX(Programmes!$L$2:$L$8,MATCH(A191,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J191" s="13" t="str">
@@ -7455,7 +7596,7 @@
         <v/>
       </c>
       <c r="I192" s="13" t="str">
-        <f aca="false">IF(OR(A192="",D192=""),"",ROUND(D192*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A192="",D192=""),"",ROUND(D192*INDEX(Programmes!$L$2:$L$8,MATCH(A192,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J192" s="13" t="str">
@@ -7476,7 +7617,7 @@
         <v/>
       </c>
       <c r="I193" s="13" t="str">
-        <f aca="false">IF(OR(A193="",D193=""),"",ROUND(D193*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A193="",D193=""),"",ROUND(D193*INDEX(Programmes!$L$2:$L$8,MATCH(A193,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J193" s="13" t="str">
@@ -7497,7 +7638,7 @@
         <v/>
       </c>
       <c r="I194" s="13" t="str">
-        <f aca="false">IF(OR(A194="",D194=""),"",ROUND(D194*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A194="",D194=""),"",ROUND(D194*INDEX(Programmes!$L$2:$L$8,MATCH(A194,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J194" s="13" t="str">
@@ -7518,7 +7659,7 @@
         <v/>
       </c>
       <c r="I195" s="13" t="str">
-        <f aca="false">IF(OR(A195="",D195=""),"",ROUND(D195*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A195="",D195=""),"",ROUND(D195*INDEX(Programmes!$L$2:$L$8,MATCH(A195,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J195" s="13" t="str">
@@ -7539,7 +7680,7 @@
         <v/>
       </c>
       <c r="I196" s="13" t="str">
-        <f aca="false">IF(OR(A196="",D196=""),"",ROUND(D196*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A196="",D196=""),"",ROUND(D196*INDEX(Programmes!$L$2:$L$8,MATCH(A196,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J196" s="13" t="str">
@@ -7560,7 +7701,7 @@
         <v/>
       </c>
       <c r="I197" s="13" t="str">
-        <f aca="false">IF(OR(A197="",D197=""),"",ROUND(D197*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A197="",D197=""),"",ROUND(D197*INDEX(Programmes!$L$2:$L$8,MATCH(A197,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J197" s="13" t="str">
@@ -7581,7 +7722,7 @@
         <v/>
       </c>
       <c r="I198" s="13" t="str">
-        <f aca="false">IF(OR(A198="",D198=""),"",ROUND(D198*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A198="",D198=""),"",ROUND(D198*INDEX(Programmes!$L$2:$L$8,MATCH(A198,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J198" s="13" t="str">
@@ -7602,7 +7743,7 @@
         <v/>
       </c>
       <c r="I199" s="13" t="str">
-        <f aca="false">IF(OR(A199="",D199=""),"",ROUND(D199*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A199="",D199=""),"",ROUND(D199*INDEX(Programmes!$L$2:$L$8,MATCH(A199,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J199" s="13" t="str">
@@ -7623,7 +7764,7 @@
         <v/>
       </c>
       <c r="I200" s="13" t="str">
-        <f aca="false">IF(OR(A200="",D200=""),"",ROUND(D200*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A200="",D200=""),"",ROUND(D200*INDEX(Programmes!$L$2:$L$8,MATCH(A200,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J200" s="13" t="str">
@@ -7644,7 +7785,7 @@
         <v/>
       </c>
       <c r="I201" s="13" t="str">
-        <f aca="false">IF(OR(A201="",D201=""),"",ROUND(D201*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A201="",D201=""),"",ROUND(D201*INDEX(Programmes!$L$2:$L$8,MATCH(A201,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J201" s="13" t="str">
@@ -7665,7 +7806,7 @@
         <v/>
       </c>
       <c r="I202" s="13" t="str">
-        <f aca="false">IF(OR(A202="",D202=""),"",ROUND(D202*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A202="",D202=""),"",ROUND(D202*INDEX(Programmes!$L$2:$L$8,MATCH(A202,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J202" s="13" t="str">
@@ -7686,7 +7827,7 @@
         <v/>
       </c>
       <c r="I203" s="13" t="str">
-        <f aca="false">IF(OR(A203="",D203=""),"",ROUND(D203*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A203="",D203=""),"",ROUND(D203*INDEX(Programmes!$L$2:$L$8,MATCH(A203,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J203" s="13" t="str">
@@ -7707,7 +7848,7 @@
         <v/>
       </c>
       <c r="I204" s="13" t="str">
-        <f aca="false">IF(OR(A204="",D204=""),"",ROUND(D204*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A204="",D204=""),"",ROUND(D204*INDEX(Programmes!$L$2:$L$8,MATCH(A204,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J204" s="13" t="str">
@@ -7728,7 +7869,7 @@
         <v/>
       </c>
       <c r="I205" s="13" t="str">
-        <f aca="false">IF(OR(A205="",D205=""),"",ROUND(D205*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A205="",D205=""),"",ROUND(D205*INDEX(Programmes!$L$2:$L$8,MATCH(A205,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J205" s="13" t="str">
@@ -7749,7 +7890,7 @@
         <v/>
       </c>
       <c r="I206" s="13" t="str">
-        <f aca="false">IF(OR(A206="",D206=""),"",ROUND(D206*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A206="",D206=""),"",ROUND(D206*INDEX(Programmes!$L$2:$L$8,MATCH(A206,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J206" s="13" t="str">
@@ -7770,7 +7911,7 @@
         <v/>
       </c>
       <c r="I207" s="13" t="str">
-        <f aca="false">IF(OR(A207="",D207=""),"",ROUND(D207*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A207="",D207=""),"",ROUND(D207*INDEX(Programmes!$L$2:$L$8,MATCH(A207,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J207" s="13" t="str">
@@ -7791,7 +7932,7 @@
         <v/>
       </c>
       <c r="I208" s="13" t="str">
-        <f aca="false">IF(OR(A208="",D208=""),"",ROUND(D208*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A208="",D208=""),"",ROUND(D208*INDEX(Programmes!$L$2:$L$8,MATCH(A208,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J208" s="13" t="str">
@@ -7812,7 +7953,7 @@
         <v/>
       </c>
       <c r="I209" s="13" t="str">
-        <f aca="false">IF(OR(A209="",D209=""),"",ROUND(D209*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A209="",D209=""),"",ROUND(D209*INDEX(Programmes!$L$2:$L$8,MATCH(A209,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J209" s="13" t="str">
@@ -7833,7 +7974,7 @@
         <v/>
       </c>
       <c r="I210" s="13" t="str">
-        <f aca="false">IF(OR(A210="",D210=""),"",ROUND(D210*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A210="",D210=""),"",ROUND(D210*INDEX(Programmes!$L$2:$L$8,MATCH(A210,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J210" s="13" t="str">
@@ -7854,7 +7995,7 @@
         <v/>
       </c>
       <c r="I211" s="13" t="str">
-        <f aca="false">IF(OR(A211="",D211=""),"",ROUND(D211*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A211="",D211=""),"",ROUND(D211*INDEX(Programmes!$L$2:$L$8,MATCH(A211,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J211" s="13" t="str">
@@ -7875,7 +8016,7 @@
         <v/>
       </c>
       <c r="I212" s="13" t="str">
-        <f aca="false">IF(OR(A212="",D212=""),"",ROUND(D212*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A212="",D212=""),"",ROUND(D212*INDEX(Programmes!$L$2:$L$8,MATCH(A212,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J212" s="13" t="str">
@@ -7896,7 +8037,7 @@
         <v/>
       </c>
       <c r="I213" s="13" t="str">
-        <f aca="false">IF(OR(A213="",D213=""),"",ROUND(D213*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A213="",D213=""),"",ROUND(D213*INDEX(Programmes!$L$2:$L$8,MATCH(A213,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J213" s="13" t="str">
@@ -7917,7 +8058,7 @@
         <v/>
       </c>
       <c r="I214" s="13" t="str">
-        <f aca="false">IF(OR(A214="",D214=""),"",ROUND(D214*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A214="",D214=""),"",ROUND(D214*INDEX(Programmes!$L$2:$L$8,MATCH(A214,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J214" s="13" t="str">
@@ -7938,7 +8079,7 @@
         <v/>
       </c>
       <c r="I215" s="13" t="str">
-        <f aca="false">IF(OR(A215="",D215=""),"",ROUND(D215*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A215="",D215=""),"",ROUND(D215*INDEX(Programmes!$L$2:$L$8,MATCH(A215,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J215" s="13" t="str">
@@ -7959,7 +8100,7 @@
         <v/>
       </c>
       <c r="I216" s="13" t="str">
-        <f aca="false">IF(OR(A216="",D216=""),"",ROUND(D216*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A216="",D216=""),"",ROUND(D216*INDEX(Programmes!$L$2:$L$8,MATCH(A216,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J216" s="13" t="str">
@@ -7980,7 +8121,7 @@
         <v/>
       </c>
       <c r="I217" s="13" t="str">
-        <f aca="false">IF(OR(A217="",D217=""),"",ROUND(D217*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A217="",D217=""),"",ROUND(D217*INDEX(Programmes!$L$2:$L$8,MATCH(A217,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J217" s="13" t="str">
@@ -8001,7 +8142,7 @@
         <v/>
       </c>
       <c r="I218" s="13" t="str">
-        <f aca="false">IF(OR(A218="",D218=""),"",ROUND(D218*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A218="",D218=""),"",ROUND(D218*INDEX(Programmes!$L$2:$L$8,MATCH(A218,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J218" s="13" t="str">
@@ -8022,7 +8163,7 @@
         <v/>
       </c>
       <c r="I219" s="13" t="str">
-        <f aca="false">IF(OR(A219="",D219=""),"",ROUND(D219*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A219="",D219=""),"",ROUND(D219*INDEX(Programmes!$L$2:$L$8,MATCH(A219,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J219" s="13" t="str">
@@ -8043,7 +8184,7 @@
         <v/>
       </c>
       <c r="I220" s="13" t="str">
-        <f aca="false">IF(OR(A220="",D220=""),"",ROUND(D220*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A220="",D220=""),"",ROUND(D220*INDEX(Programmes!$L$2:$L$8,MATCH(A220,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J220" s="13" t="str">
@@ -8064,7 +8205,7 @@
         <v/>
       </c>
       <c r="I221" s="13" t="str">
-        <f aca="false">IF(OR(A221="",D221=""),"",ROUND(D221*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A221="",D221=""),"",ROUND(D221*INDEX(Programmes!$L$2:$L$8,MATCH(A221,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J221" s="13" t="str">
@@ -8085,7 +8226,7 @@
         <v/>
       </c>
       <c r="I222" s="13" t="str">
-        <f aca="false">IF(OR(A222="",D222=""),"",ROUND(D222*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A222="",D222=""),"",ROUND(D222*INDEX(Programmes!$L$2:$L$8,MATCH(A222,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J222" s="13" t="str">
@@ -8106,7 +8247,7 @@
         <v/>
       </c>
       <c r="I223" s="13" t="str">
-        <f aca="false">IF(OR(A223="",D223=""),"",ROUND(D223*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A223="",D223=""),"",ROUND(D223*INDEX(Programmes!$L$2:$L$8,MATCH(A223,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J223" s="13" t="str">
@@ -8127,7 +8268,7 @@
         <v/>
       </c>
       <c r="I224" s="13" t="str">
-        <f aca="false">IF(OR(A224="",D224=""),"",ROUND(D224*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A224="",D224=""),"",ROUND(D224*INDEX(Programmes!$L$2:$L$8,MATCH(A224,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J224" s="13" t="str">
@@ -8148,7 +8289,7 @@
         <v/>
       </c>
       <c r="I225" s="13" t="str">
-        <f aca="false">IF(OR(A225="",D225=""),"",ROUND(D225*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A225="",D225=""),"",ROUND(D225*INDEX(Programmes!$L$2:$L$8,MATCH(A225,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J225" s="13" t="str">
@@ -8169,7 +8310,7 @@
         <v/>
       </c>
       <c r="I226" s="13" t="str">
-        <f aca="false">IF(OR(A226="",D226=""),"",ROUND(D226*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A226="",D226=""),"",ROUND(D226*INDEX(Programmes!$L$2:$L$8,MATCH(A226,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J226" s="13" t="str">
@@ -8190,7 +8331,7 @@
         <v/>
       </c>
       <c r="I227" s="13" t="str">
-        <f aca="false">IF(OR(A227="",D227=""),"",ROUND(D227*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A227="",D227=""),"",ROUND(D227*INDEX(Programmes!$L$2:$L$8,MATCH(A227,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J227" s="13" t="str">
@@ -8211,7 +8352,7 @@
         <v/>
       </c>
       <c r="I228" s="13" t="str">
-        <f aca="false">IF(OR(A228="",D228=""),"",ROUND(D228*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A228="",D228=""),"",ROUND(D228*INDEX(Programmes!$L$2:$L$8,MATCH(A228,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J228" s="13" t="str">
@@ -8232,7 +8373,7 @@
         <v/>
       </c>
       <c r="I229" s="13" t="str">
-        <f aca="false">IF(OR(A229="",D229=""),"",ROUND(D229*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A229="",D229=""),"",ROUND(D229*INDEX(Programmes!$L$2:$L$8,MATCH(A229,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J229" s="13" t="str">
@@ -8253,7 +8394,7 @@
         <v/>
       </c>
       <c r="I230" s="13" t="str">
-        <f aca="false">IF(OR(A230="",D230=""),"",ROUND(D230*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A230="",D230=""),"",ROUND(D230*INDEX(Programmes!$L$2:$L$8,MATCH(A230,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J230" s="13" t="str">
@@ -8274,7 +8415,7 @@
         <v/>
       </c>
       <c r="I231" s="13" t="str">
-        <f aca="false">IF(OR(A231="",D231=""),"",ROUND(D231*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A231="",D231=""),"",ROUND(D231*INDEX(Programmes!$L$2:$L$8,MATCH(A231,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J231" s="13" t="str">
@@ -8295,7 +8436,7 @@
         <v/>
       </c>
       <c r="I232" s="13" t="str">
-        <f aca="false">IF(OR(A232="",D232=""),"",ROUND(D232*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A232="",D232=""),"",ROUND(D232*INDEX(Programmes!$L$2:$L$8,MATCH(A232,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J232" s="13" t="str">
@@ -8316,7 +8457,7 @@
         <v/>
       </c>
       <c r="I233" s="13" t="str">
-        <f aca="false">IF(OR(A233="",D233=""),"",ROUND(D233*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A233="",D233=""),"",ROUND(D233*INDEX(Programmes!$L$2:$L$8,MATCH(A233,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J233" s="13" t="str">
@@ -8337,7 +8478,7 @@
         <v/>
       </c>
       <c r="I234" s="13" t="str">
-        <f aca="false">IF(OR(A234="",D234=""),"",ROUND(D234*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A234="",D234=""),"",ROUND(D234*INDEX(Programmes!$L$2:$L$8,MATCH(A234,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J234" s="13" t="str">
@@ -8358,7 +8499,7 @@
         <v/>
       </c>
       <c r="I235" s="13" t="str">
-        <f aca="false">IF(OR(A235="",D235=""),"",ROUND(D235*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A235="",D235=""),"",ROUND(D235*INDEX(Programmes!$L$2:$L$8,MATCH(A235,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J235" s="13" t="str">
@@ -8379,7 +8520,7 @@
         <v/>
       </c>
       <c r="I236" s="13" t="str">
-        <f aca="false">IF(OR(A236="",D236=""),"",ROUND(D236*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A236="",D236=""),"",ROUND(D236*INDEX(Programmes!$L$2:$L$8,MATCH(A236,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J236" s="13" t="str">
@@ -8400,7 +8541,7 @@
         <v/>
       </c>
       <c r="I237" s="13" t="str">
-        <f aca="false">IF(OR(A237="",D237=""),"",ROUND(D237*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A237="",D237=""),"",ROUND(D237*INDEX(Programmes!$L$2:$L$8,MATCH(A237,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J237" s="13" t="str">
@@ -8421,7 +8562,7 @@
         <v/>
       </c>
       <c r="I238" s="13" t="str">
-        <f aca="false">IF(OR(A238="",D238=""),"",ROUND(D238*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A238="",D238=""),"",ROUND(D238*INDEX(Programmes!$L$2:$L$8,MATCH(A238,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J238" s="13" t="str">
@@ -8442,7 +8583,7 @@
         <v/>
       </c>
       <c r="I239" s="13" t="str">
-        <f aca="false">IF(OR(A239="",D239=""),"",ROUND(D239*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A239="",D239=""),"",ROUND(D239*INDEX(Programmes!$L$2:$L$8,MATCH(A239,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J239" s="13" t="str">
@@ -8463,7 +8604,7 @@
         <v/>
       </c>
       <c r="I240" s="13" t="str">
-        <f aca="false">IF(OR(A240="",D240=""),"",ROUND(D240*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A240="",D240=""),"",ROUND(D240*INDEX(Programmes!$L$2:$L$8,MATCH(A240,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J240" s="13" t="str">
@@ -8484,7 +8625,7 @@
         <v/>
       </c>
       <c r="I241" s="13" t="str">
-        <f aca="false">IF(OR(A241="",D241=""),"",ROUND(D241*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A241="",D241=""),"",ROUND(D241*INDEX(Programmes!$L$2:$L$8,MATCH(A241,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J241" s="13" t="str">
@@ -8505,7 +8646,7 @@
         <v/>
       </c>
       <c r="I242" s="13" t="str">
-        <f aca="false">IF(OR(A242="",D242=""),"",ROUND(D242*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A242="",D242=""),"",ROUND(D242*INDEX(Programmes!$L$2:$L$8,MATCH(A242,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J242" s="13" t="str">
@@ -8526,7 +8667,7 @@
         <v/>
       </c>
       <c r="I243" s="13" t="str">
-        <f aca="false">IF(OR(A243="",D243=""),"",ROUND(D243*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A243="",D243=""),"",ROUND(D243*INDEX(Programmes!$L$2:$L$8,MATCH(A243,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J243" s="13" t="str">
@@ -8547,7 +8688,7 @@
         <v/>
       </c>
       <c r="I244" s="13" t="str">
-        <f aca="false">IF(OR(A244="",D244=""),"",ROUND(D244*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A244="",D244=""),"",ROUND(D244*INDEX(Programmes!$L$2:$L$8,MATCH(A244,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J244" s="13" t="str">
@@ -8568,7 +8709,7 @@
         <v/>
       </c>
       <c r="I245" s="13" t="str">
-        <f aca="false">IF(OR(A245="",D245=""),"",ROUND(D245*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A245="",D245=""),"",ROUND(D245*INDEX(Programmes!$L$2:$L$8,MATCH(A245,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J245" s="13" t="str">
@@ -8589,7 +8730,7 @@
         <v/>
       </c>
       <c r="I246" s="13" t="str">
-        <f aca="false">IF(OR(A246="",D246=""),"",ROUND(D246*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A246="",D246=""),"",ROUND(D246*INDEX(Programmes!$L$2:$L$8,MATCH(A246,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J246" s="13" t="str">
@@ -8610,7 +8751,7 @@
         <v/>
       </c>
       <c r="I247" s="13" t="str">
-        <f aca="false">IF(OR(A247="",D247=""),"",ROUND(D247*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A247="",D247=""),"",ROUND(D247*INDEX(Programmes!$L$2:$L$8,MATCH(A247,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J247" s="13" t="str">
@@ -8631,7 +8772,7 @@
         <v/>
       </c>
       <c r="I248" s="13" t="str">
-        <f aca="false">IF(OR(A248="",D248=""),"",ROUND(D248*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A248="",D248=""),"",ROUND(D248*INDEX(Programmes!$L$2:$L$8,MATCH(A248,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J248" s="13" t="str">
@@ -8652,7 +8793,7 @@
         <v/>
       </c>
       <c r="I249" s="13" t="str">
-        <f aca="false">IF(OR(A249="",D249=""),"",ROUND(D249*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A249="",D249=""),"",ROUND(D249*INDEX(Programmes!$L$2:$L$8,MATCH(A249,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J249" s="13" t="str">
@@ -8673,7 +8814,7 @@
         <v/>
       </c>
       <c r="I250" s="13" t="str">
-        <f aca="false">IF(OR(A250="",D250=""),"",ROUND(D250*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A250="",D250=""),"",ROUND(D250*INDEX(Programmes!$L$2:$L$8,MATCH(A250,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J250" s="13" t="str">
@@ -8694,7 +8835,7 @@
         <v/>
       </c>
       <c r="I251" s="13" t="str">
-        <f aca="false">IF(OR(A251="",D251=""),"",ROUND(D251*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A251="",D251=""),"",ROUND(D251*INDEX(Programmes!$L$2:$L$8,MATCH(A251,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J251" s="13" t="str">
@@ -8715,7 +8856,7 @@
         <v/>
       </c>
       <c r="I252" s="13" t="str">
-        <f aca="false">IF(OR(A252="",D252=""),"",ROUND(D252*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A252="",D252=""),"",ROUND(D252*INDEX(Programmes!$L$2:$L$8,MATCH(A252,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J252" s="13" t="str">
@@ -8736,7 +8877,7 @@
         <v/>
       </c>
       <c r="I253" s="13" t="str">
-        <f aca="false">IF(OR(A253="",D253=""),"",ROUND(D253*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A253="",D253=""),"",ROUND(D253*INDEX(Programmes!$L$2:$L$8,MATCH(A253,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J253" s="13" t="str">
@@ -8757,7 +8898,7 @@
         <v/>
       </c>
       <c r="I254" s="13" t="str">
-        <f aca="false">IF(OR(A254="",D254=""),"",ROUND(D254*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A254="",D254=""),"",ROUND(D254*INDEX(Programmes!$L$2:$L$8,MATCH(A254,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J254" s="13" t="str">
@@ -8778,7 +8919,7 @@
         <v/>
       </c>
       <c r="I255" s="13" t="str">
-        <f aca="false">IF(OR(A255="",D255=""),"",ROUND(D255*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A255="",D255=""),"",ROUND(D255*INDEX(Programmes!$L$2:$L$8,MATCH(A255,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J255" s="13" t="str">
@@ -8799,7 +8940,7 @@
         <v/>
       </c>
       <c r="I256" s="13" t="str">
-        <f aca="false">IF(OR(A256="",D256=""),"",ROUND(D256*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A256="",D256=""),"",ROUND(D256*INDEX(Programmes!$L$2:$L$8,MATCH(A256,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J256" s="13" t="str">
@@ -8820,7 +8961,7 @@
         <v/>
       </c>
       <c r="I257" s="13" t="str">
-        <f aca="false">IF(OR(A257="",D257=""),"",ROUND(D257*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A257="",D257=""),"",ROUND(D257*INDEX(Programmes!$L$2:$L$8,MATCH(A257,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J257" s="13" t="str">
@@ -8841,7 +8982,7 @@
         <v/>
       </c>
       <c r="I258" s="13" t="str">
-        <f aca="false">IF(OR(A258="",D258=""),"",ROUND(D258*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A258="",D258=""),"",ROUND(D258*INDEX(Programmes!$L$2:$L$8,MATCH(A258,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J258" s="13" t="str">
@@ -8862,7 +9003,7 @@
         <v/>
       </c>
       <c r="I259" s="13" t="str">
-        <f aca="false">IF(OR(A259="",D259=""),"",ROUND(D259*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A259="",D259=""),"",ROUND(D259*INDEX(Programmes!$L$2:$L$8,MATCH(A259,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J259" s="13" t="str">
@@ -8883,7 +9024,7 @@
         <v/>
       </c>
       <c r="I260" s="13" t="str">
-        <f aca="false">IF(OR(A260="",D260=""),"",ROUND(D260*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A260="",D260=""),"",ROUND(D260*INDEX(Programmes!$L$2:$L$8,MATCH(A260,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J260" s="13" t="str">
@@ -8904,7 +9045,7 @@
         <v/>
       </c>
       <c r="I261" s="13" t="str">
-        <f aca="false">IF(OR(A261="",D261=""),"",ROUND(D261*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A261="",D261=""),"",ROUND(D261*INDEX(Programmes!$L$2:$L$8,MATCH(A261,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J261" s="13" t="str">
@@ -8925,7 +9066,7 @@
         <v/>
       </c>
       <c r="I262" s="13" t="str">
-        <f aca="false">IF(OR(A262="",D262=""),"",ROUND(D262*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A262="",D262=""),"",ROUND(D262*INDEX(Programmes!$L$2:$L$8,MATCH(A262,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J262" s="13" t="str">
@@ -8946,7 +9087,7 @@
         <v/>
       </c>
       <c r="I263" s="13" t="str">
-        <f aca="false">IF(OR(A263="",D263=""),"",ROUND(D263*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A263="",D263=""),"",ROUND(D263*INDEX(Programmes!$L$2:$L$8,MATCH(A263,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J263" s="13" t="str">
@@ -8967,7 +9108,7 @@
         <v/>
       </c>
       <c r="I264" s="13" t="str">
-        <f aca="false">IF(OR(A264="",D264=""),"",ROUND(D264*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A264="",D264=""),"",ROUND(D264*INDEX(Programmes!$L$2:$L$8,MATCH(A264,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J264" s="13" t="str">
@@ -8988,7 +9129,7 @@
         <v/>
       </c>
       <c r="I265" s="13" t="str">
-        <f aca="false">IF(OR(A265="",D265=""),"",ROUND(D265*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A265="",D265=""),"",ROUND(D265*INDEX(Programmes!$L$2:$L$8,MATCH(A265,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J265" s="13" t="str">
@@ -9009,7 +9150,7 @@
         <v/>
       </c>
       <c r="I266" s="13" t="str">
-        <f aca="false">IF(OR(A266="",D266=""),"",ROUND(D266*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A266="",D266=""),"",ROUND(D266*INDEX(Programmes!$L$2:$L$8,MATCH(A266,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J266" s="13" t="str">
@@ -9030,7 +9171,7 @@
         <v/>
       </c>
       <c r="I267" s="13" t="str">
-        <f aca="false">IF(OR(A267="",D267=""),"",ROUND(D267*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A267="",D267=""),"",ROUND(D267*INDEX(Programmes!$L$2:$L$8,MATCH(A267,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J267" s="13" t="str">
@@ -9051,7 +9192,7 @@
         <v/>
       </c>
       <c r="I268" s="13" t="str">
-        <f aca="false">IF(OR(A268="",D268=""),"",ROUND(D268*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A268="",D268=""),"",ROUND(D268*INDEX(Programmes!$L$2:$L$8,MATCH(A268,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J268" s="13" t="str">
@@ -9072,7 +9213,7 @@
         <v/>
       </c>
       <c r="I269" s="13" t="str">
-        <f aca="false">IF(OR(A269="",D269=""),"",ROUND(D269*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A269="",D269=""),"",ROUND(D269*INDEX(Programmes!$L$2:$L$8,MATCH(A269,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J269" s="13" t="str">
@@ -9093,7 +9234,7 @@
         <v/>
       </c>
       <c r="I270" s="13" t="str">
-        <f aca="false">IF(OR(A270="",D270=""),"",ROUND(D270*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A270="",D270=""),"",ROUND(D270*INDEX(Programmes!$L$2:$L$8,MATCH(A270,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J270" s="13" t="str">
@@ -9114,7 +9255,7 @@
         <v/>
       </c>
       <c r="I271" s="13" t="str">
-        <f aca="false">IF(OR(A271="",D271=""),"",ROUND(D271*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A271="",D271=""),"",ROUND(D271*INDEX(Programmes!$L$2:$L$8,MATCH(A271,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J271" s="13" t="str">
@@ -9135,7 +9276,7 @@
         <v/>
       </c>
       <c r="I272" s="13" t="str">
-        <f aca="false">IF(OR(A272="",D272=""),"",ROUND(D272*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A272="",D272=""),"",ROUND(D272*INDEX(Programmes!$L$2:$L$8,MATCH(A272,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J272" s="13" t="str">
@@ -9156,7 +9297,7 @@
         <v/>
       </c>
       <c r="I273" s="13" t="str">
-        <f aca="false">IF(OR(A273="",D273=""),"",ROUND(D273*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A273="",D273=""),"",ROUND(D273*INDEX(Programmes!$L$2:$L$8,MATCH(A273,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J273" s="13" t="str">
@@ -9177,7 +9318,7 @@
         <v/>
       </c>
       <c r="I274" s="13" t="str">
-        <f aca="false">IF(OR(A274="",D274=""),"",ROUND(D274*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A274="",D274=""),"",ROUND(D274*INDEX(Programmes!$L$2:$L$8,MATCH(A274,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J274" s="13" t="str">
@@ -9198,7 +9339,7 @@
         <v/>
       </c>
       <c r="I275" s="13" t="str">
-        <f aca="false">IF(OR(A275="",D275=""),"",ROUND(D275*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A275="",D275=""),"",ROUND(D275*INDEX(Programmes!$L$2:$L$8,MATCH(A275,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J275" s="13" t="str">
@@ -9219,7 +9360,7 @@
         <v/>
       </c>
       <c r="I276" s="13" t="str">
-        <f aca="false">IF(OR(A276="",D276=""),"",ROUND(D276*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A276="",D276=""),"",ROUND(D276*INDEX(Programmes!$L$2:$L$8,MATCH(A276,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J276" s="13" t="str">
@@ -9240,7 +9381,7 @@
         <v/>
       </c>
       <c r="I277" s="13" t="str">
-        <f aca="false">IF(OR(A277="",D277=""),"",ROUND(D277*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A277="",D277=""),"",ROUND(D277*INDEX(Programmes!$L$2:$L$8,MATCH(A277,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J277" s="13" t="str">
@@ -9261,7 +9402,7 @@
         <v/>
       </c>
       <c r="I278" s="13" t="str">
-        <f aca="false">IF(OR(A278="",D278=""),"",ROUND(D278*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A278="",D278=""),"",ROUND(D278*INDEX(Programmes!$L$2:$L$8,MATCH(A278,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J278" s="13" t="str">
@@ -9282,7 +9423,7 @@
         <v/>
       </c>
       <c r="I279" s="13" t="str">
-        <f aca="false">IF(OR(A279="",D279=""),"",ROUND(D279*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A279="",D279=""),"",ROUND(D279*INDEX(Programmes!$L$2:$L$8,MATCH(A279,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J279" s="13" t="str">
@@ -9303,7 +9444,7 @@
         <v/>
       </c>
       <c r="I280" s="13" t="str">
-        <f aca="false">IF(OR(A280="",D280=""),"",ROUND(D280*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A280="",D280=""),"",ROUND(D280*INDEX(Programmes!$L$2:$L$8,MATCH(A280,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J280" s="13" t="str">
@@ -9324,7 +9465,7 @@
         <v/>
       </c>
       <c r="I281" s="13" t="str">
-        <f aca="false">IF(OR(A281="",D281=""),"",ROUND(D281*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A281="",D281=""),"",ROUND(D281*INDEX(Programmes!$L$2:$L$8,MATCH(A281,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J281" s="13" t="str">
@@ -9345,7 +9486,7 @@
         <v/>
       </c>
       <c r="I282" s="13" t="str">
-        <f aca="false">IF(OR(A282="",D282=""),"",ROUND(D282*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A282="",D282=""),"",ROUND(D282*INDEX(Programmes!$L$2:$L$8,MATCH(A282,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J282" s="13" t="str">
@@ -9366,7 +9507,7 @@
         <v/>
       </c>
       <c r="I283" s="13" t="str">
-        <f aca="false">IF(OR(A283="",D283=""),"",ROUND(D283*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A283="",D283=""),"",ROUND(D283*INDEX(Programmes!$L$2:$L$8,MATCH(A283,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J283" s="13" t="str">
@@ -9387,7 +9528,7 @@
         <v/>
       </c>
       <c r="I284" s="13" t="str">
-        <f aca="false">IF(OR(A284="",D284=""),"",ROUND(D284*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A284="",D284=""),"",ROUND(D284*INDEX(Programmes!$L$2:$L$8,MATCH(A284,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J284" s="13" t="str">
@@ -9408,7 +9549,7 @@
         <v/>
       </c>
       <c r="I285" s="13" t="str">
-        <f aca="false">IF(OR(A285="",D285=""),"",ROUND(D285*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A285="",D285=""),"",ROUND(D285*INDEX(Programmes!$L$2:$L$8,MATCH(A285,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J285" s="13" t="str">
@@ -9429,7 +9570,7 @@
         <v/>
       </c>
       <c r="I286" s="13" t="str">
-        <f aca="false">IF(OR(A286="",D286=""),"",ROUND(D286*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A286="",D286=""),"",ROUND(D286*INDEX(Programmes!$L$2:$L$8,MATCH(A286,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J286" s="13" t="str">
@@ -9450,7 +9591,7 @@
         <v/>
       </c>
       <c r="I287" s="13" t="str">
-        <f aca="false">IF(OR(A287="",D287=""),"",ROUND(D287*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A287="",D287=""),"",ROUND(D287*INDEX(Programmes!$L$2:$L$8,MATCH(A287,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J287" s="13" t="str">
@@ -9471,7 +9612,7 @@
         <v/>
       </c>
       <c r="I288" s="13" t="str">
-        <f aca="false">IF(OR(A288="",D288=""),"",ROUND(D288*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A288="",D288=""),"",ROUND(D288*INDEX(Programmes!$L$2:$L$8,MATCH(A288,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J288" s="13" t="str">
@@ -9492,7 +9633,7 @@
         <v/>
       </c>
       <c r="I289" s="13" t="str">
-        <f aca="false">IF(OR(A289="",D289=""),"",ROUND(D289*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A289="",D289=""),"",ROUND(D289*INDEX(Programmes!$L$2:$L$8,MATCH(A289,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J289" s="13" t="str">
@@ -9513,7 +9654,7 @@
         <v/>
       </c>
       <c r="I290" s="13" t="str">
-        <f aca="false">IF(OR(A290="",D290=""),"",ROUND(D290*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A290="",D290=""),"",ROUND(D290*INDEX(Programmes!$L$2:$L$8,MATCH(A290,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J290" s="13" t="str">
@@ -9534,7 +9675,7 @@
         <v/>
       </c>
       <c r="I291" s="13" t="str">
-        <f aca="false">IF(OR(A291="",D291=""),"",ROUND(D291*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A291="",D291=""),"",ROUND(D291*INDEX(Programmes!$L$2:$L$8,MATCH(A291,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J291" s="13" t="str">
@@ -9555,7 +9696,7 @@
         <v/>
       </c>
       <c r="I292" s="13" t="str">
-        <f aca="false">IF(OR(A292="",D292=""),"",ROUND(D292*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A292="",D292=""),"",ROUND(D292*INDEX(Programmes!$L$2:$L$8,MATCH(A292,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J292" s="13" t="str">
@@ -9576,7 +9717,7 @@
         <v/>
       </c>
       <c r="I293" s="13" t="str">
-        <f aca="false">IF(OR(A293="",D293=""),"",ROUND(D293*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A293="",D293=""),"",ROUND(D293*INDEX(Programmes!$L$2:$L$8,MATCH(A293,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J293" s="13" t="str">
@@ -9597,7 +9738,7 @@
         <v/>
       </c>
       <c r="I294" s="13" t="str">
-        <f aca="false">IF(OR(A294="",D294=""),"",ROUND(D294*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A294="",D294=""),"",ROUND(D294*INDEX(Programmes!$L$2:$L$8,MATCH(A294,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J294" s="13" t="str">
@@ -9618,7 +9759,7 @@
         <v/>
       </c>
       <c r="I295" s="13" t="str">
-        <f aca="false">IF(OR(A295="",D295=""),"",ROUND(D295*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A295="",D295=""),"",ROUND(D295*INDEX(Programmes!$L$2:$L$8,MATCH(A295,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J295" s="13" t="str">
@@ -9639,7 +9780,7 @@
         <v/>
       </c>
       <c r="I296" s="13" t="str">
-        <f aca="false">IF(OR(A296="",D296=""),"",ROUND(D296*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A296="",D296=""),"",ROUND(D296*INDEX(Programmes!$L$2:$L$8,MATCH(A296,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J296" s="13" t="str">
@@ -9660,7 +9801,7 @@
         <v/>
       </c>
       <c r="I297" s="13" t="str">
-        <f aca="false">IF(OR(A297="",D297=""),"",ROUND(D297*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A297="",D297=""),"",ROUND(D297*INDEX(Programmes!$L$2:$L$8,MATCH(A297,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J297" s="13" t="str">
@@ -9681,7 +9822,7 @@
         <v/>
       </c>
       <c r="I298" s="13" t="str">
-        <f aca="false">IF(OR(A298="",D298=""),"",ROUND(D298*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A298="",D298=""),"",ROUND(D298*INDEX(Programmes!$L$2:$L$8,MATCH(A298,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J298" s="13" t="str">
@@ -9702,7 +9843,7 @@
         <v/>
       </c>
       <c r="I299" s="13" t="str">
-        <f aca="false">IF(OR(A299="",D299=""),"",ROUND(D299*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A299="",D299=""),"",ROUND(D299*INDEX(Programmes!$L$2:$L$8,MATCH(A299,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J299" s="13" t="str">
@@ -9723,7 +9864,7 @@
         <v/>
       </c>
       <c r="I300" s="13" t="str">
-        <f aca="false">IF(OR(A300="",D300=""),"",ROUND(D300*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A300="",D300=""),"",ROUND(D300*INDEX(Programmes!$L$2:$L$8,MATCH(A300,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J300" s="13" t="str">
@@ -9744,7 +9885,7 @@
         <v/>
       </c>
       <c r="I301" s="13" t="str">
-        <f aca="false">IF(OR(A301="",D301=""),"",ROUND(D301*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A301="",D301=""),"",ROUND(D301*INDEX(Programmes!$L$2:$L$8,MATCH(A301,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J301" s="13" t="str">
@@ -9765,7 +9906,7 @@
         <v/>
       </c>
       <c r="I302" s="13" t="str">
-        <f aca="false">IF(OR(A302="",D302=""),"",ROUND(D302*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A302="",D302=""),"",ROUND(D302*INDEX(Programmes!$L$2:$L$8,MATCH(A302,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J302" s="13" t="str">
@@ -9786,7 +9927,7 @@
         <v/>
       </c>
       <c r="I303" s="13" t="str">
-        <f aca="false">IF(OR(A303="",D303=""),"",ROUND(D303*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A303="",D303=""),"",ROUND(D303*INDEX(Programmes!$L$2:$L$8,MATCH(A303,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J303" s="13" t="str">
@@ -9807,7 +9948,7 @@
         <v/>
       </c>
       <c r="I304" s="13" t="str">
-        <f aca="false">IF(OR(A304="",D304=""),"",ROUND(D304*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A304="",D304=""),"",ROUND(D304*INDEX(Programmes!$L$2:$L$8,MATCH(A304,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J304" s="13" t="str">
@@ -9828,7 +9969,7 @@
         <v/>
       </c>
       <c r="I305" s="13" t="str">
-        <f aca="false">IF(OR(A305="",D305=""),"",ROUND(D305*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A305="",D305=""),"",ROUND(D305*INDEX(Programmes!$L$2:$L$8,MATCH(A305,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J305" s="13" t="str">
@@ -9849,7 +9990,7 @@
         <v/>
       </c>
       <c r="I306" s="13" t="str">
-        <f aca="false">IF(OR(A306="",D306=""),"",ROUND(D306*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A306="",D306=""),"",ROUND(D306*INDEX(Programmes!$L$2:$L$8,MATCH(A306,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J306" s="13" t="str">
@@ -9870,7 +10011,7 @@
         <v/>
       </c>
       <c r="I307" s="13" t="str">
-        <f aca="false">IF(OR(A307="",D307=""),"",ROUND(D307*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A307="",D307=""),"",ROUND(D307*INDEX(Programmes!$L$2:$L$8,MATCH(A307,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J307" s="13" t="str">
@@ -9891,7 +10032,7 @@
         <v/>
       </c>
       <c r="I308" s="13" t="str">
-        <f aca="false">IF(OR(A308="",D308=""),"",ROUND(D308*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A308="",D308=""),"",ROUND(D308*INDEX(Programmes!$L$2:$L$8,MATCH(A308,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J308" s="13" t="str">
@@ -9912,7 +10053,7 @@
         <v/>
       </c>
       <c r="I309" s="13" t="str">
-        <f aca="false">IF(OR(A309="",D309=""),"",ROUND(D309*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A309="",D309=""),"",ROUND(D309*INDEX(Programmes!$L$2:$L$8,MATCH(A309,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J309" s="13" t="str">
@@ -9933,7 +10074,7 @@
         <v/>
       </c>
       <c r="I310" s="13" t="str">
-        <f aca="false">IF(OR(A310="",D310=""),"",ROUND(D310*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A310="",D310=""),"",ROUND(D310*INDEX(Programmes!$L$2:$L$8,MATCH(A310,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J310" s="13" t="str">
@@ -9954,7 +10095,7 @@
         <v/>
       </c>
       <c r="I311" s="13" t="str">
-        <f aca="false">IF(OR(A311="",D311=""),"",ROUND(D311*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A311="",D311=""),"",ROUND(D311*INDEX(Programmes!$L$2:$L$8,MATCH(A311,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J311" s="13" t="str">
@@ -9975,7 +10116,7 @@
         <v/>
       </c>
       <c r="I312" s="13" t="str">
-        <f aca="false">IF(OR(A312="",D312=""),"",ROUND(D312*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A312="",D312=""),"",ROUND(D312*INDEX(Programmes!$L$2:$L$8,MATCH(A312,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J312" s="13" t="str">
@@ -9996,7 +10137,7 @@
         <v/>
       </c>
       <c r="I313" s="13" t="str">
-        <f aca="false">IF(OR(A313="",D313=""),"",ROUND(D313*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A313="",D313=""),"",ROUND(D313*INDEX(Programmes!$L$2:$L$8,MATCH(A313,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J313" s="13" t="str">
@@ -10017,7 +10158,7 @@
         <v/>
       </c>
       <c r="I314" s="13" t="str">
-        <f aca="false">IF(OR(A314="",D314=""),"",ROUND(D314*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A314="",D314=""),"",ROUND(D314*INDEX(Programmes!$L$2:$L$8,MATCH(A314,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J314" s="13" t="str">
@@ -10038,7 +10179,7 @@
         <v/>
       </c>
       <c r="I315" s="13" t="str">
-        <f aca="false">IF(OR(A315="",D315=""),"",ROUND(D315*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A315="",D315=""),"",ROUND(D315*INDEX(Programmes!$L$2:$L$8,MATCH(A315,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J315" s="13" t="str">
@@ -10059,7 +10200,7 @@
         <v/>
       </c>
       <c r="I316" s="13" t="str">
-        <f aca="false">IF(OR(A316="",D316=""),"",ROUND(D316*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A316="",D316=""),"",ROUND(D316*INDEX(Programmes!$L$2:$L$8,MATCH(A316,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J316" s="13" t="str">
@@ -10080,7 +10221,7 @@
         <v/>
       </c>
       <c r="I317" s="13" t="str">
-        <f aca="false">IF(OR(A317="",D317=""),"",ROUND(D317*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A317="",D317=""),"",ROUND(D317*INDEX(Programmes!$L$2:$L$8,MATCH(A317,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J317" s="13" t="str">
@@ -10101,7 +10242,7 @@
         <v/>
       </c>
       <c r="I318" s="13" t="str">
-        <f aca="false">IF(OR(A318="",D318=""),"",ROUND(D318*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A318="",D318=""),"",ROUND(D318*INDEX(Programmes!$L$2:$L$8,MATCH(A318,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J318" s="13" t="str">
@@ -10122,7 +10263,7 @@
         <v/>
       </c>
       <c r="I319" s="13" t="str">
-        <f aca="false">IF(OR(A319="",D319=""),"",ROUND(D319*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A319="",D319=""),"",ROUND(D319*INDEX(Programmes!$L$2:$L$8,MATCH(A319,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J319" s="13" t="str">
@@ -10143,7 +10284,7 @@
         <v/>
       </c>
       <c r="I320" s="13" t="str">
-        <f aca="false">IF(OR(A320="",D320=""),"",ROUND(D320*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A320="",D320=""),"",ROUND(D320*INDEX(Programmes!$L$2:$L$8,MATCH(A320,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J320" s="13" t="str">
@@ -10164,7 +10305,7 @@
         <v/>
       </c>
       <c r="I321" s="13" t="str">
-        <f aca="false">IF(OR(A321="",D321=""),"",ROUND(D321*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A321="",D321=""),"",ROUND(D321*INDEX(Programmes!$L$2:$L$8,MATCH(A321,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J321" s="13" t="str">
@@ -10185,7 +10326,7 @@
         <v/>
       </c>
       <c r="I322" s="13" t="str">
-        <f aca="false">IF(OR(A322="",D322=""),"",ROUND(D322*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A322="",D322=""),"",ROUND(D322*INDEX(Programmes!$L$2:$L$8,MATCH(A322,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J322" s="13" t="str">
@@ -10206,7 +10347,7 @@
         <v/>
       </c>
       <c r="I323" s="13" t="str">
-        <f aca="false">IF(OR(A323="",D323=""),"",ROUND(D323*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A323="",D323=""),"",ROUND(D323*INDEX(Programmes!$L$2:$L$8,MATCH(A323,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J323" s="13" t="str">
@@ -10227,7 +10368,7 @@
         <v/>
       </c>
       <c r="I324" s="13" t="str">
-        <f aca="false">IF(OR(A324="",D324=""),"",ROUND(D324*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A324="",D324=""),"",ROUND(D324*INDEX(Programmes!$L$2:$L$8,MATCH(A324,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J324" s="13" t="str">
@@ -10248,7 +10389,7 @@
         <v/>
       </c>
       <c r="I325" s="13" t="str">
-        <f aca="false">IF(OR(A325="",D325=""),"",ROUND(D325*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A325="",D325=""),"",ROUND(D325*INDEX(Programmes!$L$2:$L$8,MATCH(A325,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J325" s="13" t="str">
@@ -10269,7 +10410,7 @@
         <v/>
       </c>
       <c r="I326" s="13" t="str">
-        <f aca="false">IF(OR(A326="",D326=""),"",ROUND(D326*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A326="",D326=""),"",ROUND(D326*INDEX(Programmes!$L$2:$L$8,MATCH(A326,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J326" s="13" t="str">
@@ -10290,7 +10431,7 @@
         <v/>
       </c>
       <c r="I327" s="13" t="str">
-        <f aca="false">IF(OR(A327="",D327=""),"",ROUND(D327*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A327="",D327=""),"",ROUND(D327*INDEX(Programmes!$L$2:$L$8,MATCH(A327,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J327" s="13" t="str">
@@ -10311,7 +10452,7 @@
         <v/>
       </c>
       <c r="I328" s="13" t="str">
-        <f aca="false">IF(OR(A328="",D328=""),"",ROUND(D328*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A328="",D328=""),"",ROUND(D328*INDEX(Programmes!$L$2:$L$8,MATCH(A328,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J328" s="13" t="str">
@@ -10332,7 +10473,7 @@
         <v/>
       </c>
       <c r="I329" s="13" t="str">
-        <f aca="false">IF(OR(A329="",D329=""),"",ROUND(D329*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A329="",D329=""),"",ROUND(D329*INDEX(Programmes!$L$2:$L$8,MATCH(A329,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J329" s="13" t="str">
@@ -10353,7 +10494,7 @@
         <v/>
       </c>
       <c r="I330" s="13" t="str">
-        <f aca="false">IF(OR(A330="",D330=""),"",ROUND(D330*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A330="",D330=""),"",ROUND(D330*INDEX(Programmes!$L$2:$L$8,MATCH(A330,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J330" s="13" t="str">
@@ -10374,7 +10515,7 @@
         <v/>
       </c>
       <c r="I331" s="13" t="str">
-        <f aca="false">IF(OR(A331="",D331=""),"",ROUND(D331*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A331="",D331=""),"",ROUND(D331*INDEX(Programmes!$L$2:$L$8,MATCH(A331,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J331" s="13" t="str">
@@ -10395,7 +10536,7 @@
         <v/>
       </c>
       <c r="I332" s="13" t="str">
-        <f aca="false">IF(OR(A332="",D332=""),"",ROUND(D332*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A332="",D332=""),"",ROUND(D332*INDEX(Programmes!$L$2:$L$8,MATCH(A332,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J332" s="13" t="str">
@@ -10416,7 +10557,7 @@
         <v/>
       </c>
       <c r="I333" s="13" t="str">
-        <f aca="false">IF(OR(A333="",D333=""),"",ROUND(D333*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A333="",D333=""),"",ROUND(D333*INDEX(Programmes!$L$2:$L$8,MATCH(A333,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J333" s="13" t="str">
@@ -10437,7 +10578,7 @@
         <v/>
       </c>
       <c r="I334" s="13" t="str">
-        <f aca="false">IF(OR(A334="",D334=""),"",ROUND(D334*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A334="",D334=""),"",ROUND(D334*INDEX(Programmes!$L$2:$L$8,MATCH(A334,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J334" s="13" t="str">
@@ -10458,7 +10599,7 @@
         <v/>
       </c>
       <c r="I335" s="13" t="str">
-        <f aca="false">IF(OR(A335="",D335=""),"",ROUND(D335*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A335="",D335=""),"",ROUND(D335*INDEX(Programmes!$L$2:$L$8,MATCH(A335,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J335" s="13" t="str">
@@ -10479,7 +10620,7 @@
         <v/>
       </c>
       <c r="I336" s="13" t="str">
-        <f aca="false">IF(OR(A336="",D336=""),"",ROUND(D336*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A336="",D336=""),"",ROUND(D336*INDEX(Programmes!$L$2:$L$8,MATCH(A336,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J336" s="13" t="str">
@@ -10500,7 +10641,7 @@
         <v/>
       </c>
       <c r="I337" s="13" t="str">
-        <f aca="false">IF(OR(A337="",D337=""),"",ROUND(D337*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A337="",D337=""),"",ROUND(D337*INDEX(Programmes!$L$2:$L$8,MATCH(A337,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J337" s="13" t="str">
@@ -10521,7 +10662,7 @@
         <v/>
       </c>
       <c r="I338" s="13" t="str">
-        <f aca="false">IF(OR(A338="",D338=""),"",ROUND(D338*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A338="",D338=""),"",ROUND(D338*INDEX(Programmes!$L$2:$L$8,MATCH(A338,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J338" s="13" t="str">
@@ -10542,7 +10683,7 @@
         <v/>
       </c>
       <c r="I339" s="13" t="str">
-        <f aca="false">IF(OR(A339="",D339=""),"",ROUND(D339*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A339="",D339=""),"",ROUND(D339*INDEX(Programmes!$L$2:$L$8,MATCH(A339,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J339" s="13" t="str">
@@ -10563,7 +10704,7 @@
         <v/>
       </c>
       <c r="I340" s="13" t="str">
-        <f aca="false">IF(OR(A340="",D340=""),"",ROUND(D340*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A340="",D340=""),"",ROUND(D340*INDEX(Programmes!$L$2:$L$8,MATCH(A340,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J340" s="13" t="str">
@@ -10584,7 +10725,7 @@
         <v/>
       </c>
       <c r="I341" s="13" t="str">
-        <f aca="false">IF(OR(A341="",D341=""),"",ROUND(D341*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A341="",D341=""),"",ROUND(D341*INDEX(Programmes!$L$2:$L$8,MATCH(A341,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J341" s="13" t="str">
@@ -10605,7 +10746,7 @@
         <v/>
       </c>
       <c r="I342" s="13" t="str">
-        <f aca="false">IF(OR(A342="",D342=""),"",ROUND(D342*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A342="",D342=""),"",ROUND(D342*INDEX(Programmes!$L$2:$L$8,MATCH(A342,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J342" s="13" t="str">
@@ -10626,7 +10767,7 @@
         <v/>
       </c>
       <c r="I343" s="13" t="str">
-        <f aca="false">IF(OR(A343="",D343=""),"",ROUND(D343*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A343="",D343=""),"",ROUND(D343*INDEX(Programmes!$L$2:$L$8,MATCH(A343,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J343" s="13" t="str">
@@ -10647,7 +10788,7 @@
         <v/>
       </c>
       <c r="I344" s="13" t="str">
-        <f aca="false">IF(OR(A344="",D344=""),"",ROUND(D344*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A344="",D344=""),"",ROUND(D344*INDEX(Programmes!$L$2:$L$8,MATCH(A344,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J344" s="13" t="str">
@@ -10668,7 +10809,7 @@
         <v/>
       </c>
       <c r="I345" s="13" t="str">
-        <f aca="false">IF(OR(A345="",D345=""),"",ROUND(D345*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A345="",D345=""),"",ROUND(D345*INDEX(Programmes!$L$2:$L$8,MATCH(A345,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J345" s="13" t="str">
@@ -10689,7 +10830,7 @@
         <v/>
       </c>
       <c r="I346" s="13" t="str">
-        <f aca="false">IF(OR(A346="",D346=""),"",ROUND(D346*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A346="",D346=""),"",ROUND(D346*INDEX(Programmes!$L$2:$L$8,MATCH(A346,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J346" s="13" t="str">
@@ -10710,7 +10851,7 @@
         <v/>
       </c>
       <c r="I347" s="13" t="str">
-        <f aca="false">IF(OR(A347="",D347=""),"",ROUND(D347*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A347="",D347=""),"",ROUND(D347*INDEX(Programmes!$L$2:$L$8,MATCH(A347,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J347" s="13" t="str">
@@ -10731,7 +10872,7 @@
         <v/>
       </c>
       <c r="I348" s="13" t="str">
-        <f aca="false">IF(OR(A348="",D348=""),"",ROUND(D348*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A348="",D348=""),"",ROUND(D348*INDEX(Programmes!$L$2:$L$8,MATCH(A348,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J348" s="13" t="str">
@@ -10752,7 +10893,7 @@
         <v/>
       </c>
       <c r="I349" s="13" t="str">
-        <f aca="false">IF(OR(A349="",D349=""),"",ROUND(D349*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A349="",D349=""),"",ROUND(D349*INDEX(Programmes!$L$2:$L$8,MATCH(A349,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J349" s="13" t="str">
@@ -10773,7 +10914,7 @@
         <v/>
       </c>
       <c r="I350" s="13" t="str">
-        <f aca="false">IF(OR(A350="",D350=""),"",ROUND(D350*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A350="",D350=""),"",ROUND(D350*INDEX(Programmes!$L$2:$L$8,MATCH(A350,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J350" s="13" t="str">
@@ -10794,7 +10935,7 @@
         <v/>
       </c>
       <c r="I351" s="13" t="str">
-        <f aca="false">IF(OR(A351="",D351=""),"",ROUND(D351*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A351="",D351=""),"",ROUND(D351*INDEX(Programmes!$L$2:$L$8,MATCH(A351,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J351" s="13" t="str">
@@ -10815,7 +10956,7 @@
         <v/>
       </c>
       <c r="I352" s="13" t="str">
-        <f aca="false">IF(OR(A352="",D352=""),"",ROUND(D352*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A352="",D352=""),"",ROUND(D352*INDEX(Programmes!$L$2:$L$8,MATCH(A352,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J352" s="13" t="str">
@@ -10836,7 +10977,7 @@
         <v/>
       </c>
       <c r="I353" s="13" t="str">
-        <f aca="false">IF(OR(A353="",D353=""),"",ROUND(D353*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A353="",D353=""),"",ROUND(D353*INDEX(Programmes!$L$2:$L$8,MATCH(A353,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J353" s="13" t="str">
@@ -10857,7 +10998,7 @@
         <v/>
       </c>
       <c r="I354" s="13" t="str">
-        <f aca="false">IF(OR(A354="",D354=""),"",ROUND(D354*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A354="",D354=""),"",ROUND(D354*INDEX(Programmes!$L$2:$L$8,MATCH(A354,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J354" s="13" t="str">
@@ -10878,7 +11019,7 @@
         <v/>
       </c>
       <c r="I355" s="13" t="str">
-        <f aca="false">IF(OR(A355="",D355=""),"",ROUND(D355*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A355="",D355=""),"",ROUND(D355*INDEX(Programmes!$L$2:$L$8,MATCH(A355,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J355" s="13" t="str">
@@ -10899,7 +11040,7 @@
         <v/>
       </c>
       <c r="I356" s="13" t="str">
-        <f aca="false">IF(OR(A356="",D356=""),"",ROUND(D356*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A356="",D356=""),"",ROUND(D356*INDEX(Programmes!$L$2:$L$8,MATCH(A356,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J356" s="13" t="str">
@@ -10920,7 +11061,7 @@
         <v/>
       </c>
       <c r="I357" s="13" t="str">
-        <f aca="false">IF(OR(A357="",D357=""),"",ROUND(D357*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A357="",D357=""),"",ROUND(D357*INDEX(Programmes!$L$2:$L$8,MATCH(A357,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J357" s="13" t="str">
@@ -10941,7 +11082,7 @@
         <v/>
       </c>
       <c r="I358" s="13" t="str">
-        <f aca="false">IF(OR(A358="",D358=""),"",ROUND(D358*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A358="",D358=""),"",ROUND(D358*INDEX(Programmes!$L$2:$L$8,MATCH(A358,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J358" s="13" t="str">
@@ -10962,7 +11103,7 @@
         <v/>
       </c>
       <c r="I359" s="13" t="str">
-        <f aca="false">IF(OR(A359="",D359=""),"",ROUND(D359*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A359="",D359=""),"",ROUND(D359*INDEX(Programmes!$L$2:$L$8,MATCH(A359,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J359" s="13" t="str">
@@ -10983,7 +11124,7 @@
         <v/>
       </c>
       <c r="I360" s="13" t="str">
-        <f aca="false">IF(OR(A360="",D360=""),"",ROUND(D360*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A360="",D360=""),"",ROUND(D360*INDEX(Programmes!$L$2:$L$8,MATCH(A360,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J360" s="13" t="str">
@@ -11004,7 +11145,7 @@
         <v/>
       </c>
       <c r="I361" s="13" t="str">
-        <f aca="false">IF(OR(A361="",D361=""),"",ROUND(D361*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A361="",D361=""),"",ROUND(D361*INDEX(Programmes!$L$2:$L$8,MATCH(A361,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J361" s="13" t="str">
@@ -11025,7 +11166,7 @@
         <v/>
       </c>
       <c r="I362" s="13" t="str">
-        <f aca="false">IF(OR(A362="",D362=""),"",ROUND(D362*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A362="",D362=""),"",ROUND(D362*INDEX(Programmes!$L$2:$L$8,MATCH(A362,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J362" s="13" t="str">
@@ -11046,7 +11187,7 @@
         <v/>
       </c>
       <c r="I363" s="13" t="str">
-        <f aca="false">IF(OR(A363="",D363=""),"",ROUND(D363*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A363="",D363=""),"",ROUND(D363*INDEX(Programmes!$L$2:$L$8,MATCH(A363,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J363" s="13" t="str">
@@ -11067,7 +11208,7 @@
         <v/>
       </c>
       <c r="I364" s="13" t="str">
-        <f aca="false">IF(OR(A364="",D364=""),"",ROUND(D364*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A364="",D364=""),"",ROUND(D364*INDEX(Programmes!$L$2:$L$8,MATCH(A364,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J364" s="13" t="str">
@@ -11088,7 +11229,7 @@
         <v/>
       </c>
       <c r="I365" s="13" t="str">
-        <f aca="false">IF(OR(A365="",D365=""),"",ROUND(D365*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A365="",D365=""),"",ROUND(D365*INDEX(Programmes!$L$2:$L$8,MATCH(A365,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J365" s="13" t="str">
@@ -11109,7 +11250,7 @@
         <v/>
       </c>
       <c r="I366" s="13" t="str">
-        <f aca="false">IF(OR(A366="",D366=""),"",ROUND(D366*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A366="",D366=""),"",ROUND(D366*INDEX(Programmes!$L$2:$L$8,MATCH(A366,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J366" s="13" t="str">
@@ -11130,7 +11271,7 @@
         <v/>
       </c>
       <c r="I367" s="13" t="str">
-        <f aca="false">IF(OR(A367="",D367=""),"",ROUND(D367*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A367="",D367=""),"",ROUND(D367*INDEX(Programmes!$L$2:$L$8,MATCH(A367,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J367" s="13" t="str">
@@ -11151,7 +11292,7 @@
         <v/>
       </c>
       <c r="I368" s="13" t="str">
-        <f aca="false">IF(OR(A368="",D368=""),"",ROUND(D368*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A368="",D368=""),"",ROUND(D368*INDEX(Programmes!$L$2:$L$8,MATCH(A368,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J368" s="13" t="str">
@@ -11172,7 +11313,7 @@
         <v/>
       </c>
       <c r="I369" s="13" t="str">
-        <f aca="false">IF(OR(A369="",D369=""),"",ROUND(D369*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A369="",D369=""),"",ROUND(D369*INDEX(Programmes!$L$2:$L$8,MATCH(A369,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J369" s="13" t="str">
@@ -11193,7 +11334,7 @@
         <v/>
       </c>
       <c r="I370" s="13" t="str">
-        <f aca="false">IF(OR(A370="",D370=""),"",ROUND(D370*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A370="",D370=""),"",ROUND(D370*INDEX(Programmes!$L$2:$L$8,MATCH(A370,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J370" s="13" t="str">
@@ -11214,7 +11355,7 @@
         <v/>
       </c>
       <c r="I371" s="13" t="str">
-        <f aca="false">IF(OR(A371="",D371=""),"",ROUND(D371*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A371="",D371=""),"",ROUND(D371*INDEX(Programmes!$L$2:$L$8,MATCH(A371,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J371" s="13" t="str">
@@ -11235,7 +11376,7 @@
         <v/>
       </c>
       <c r="I372" s="13" t="str">
-        <f aca="false">IF(OR(A372="",D372=""),"",ROUND(D372*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A372="",D372=""),"",ROUND(D372*INDEX(Programmes!$L$2:$L$8,MATCH(A372,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J372" s="13" t="str">
@@ -11256,7 +11397,7 @@
         <v/>
       </c>
       <c r="I373" s="13" t="str">
-        <f aca="false">IF(OR(A373="",D373=""),"",ROUND(D373*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A373="",D373=""),"",ROUND(D373*INDEX(Programmes!$L$2:$L$8,MATCH(A373,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J373" s="13" t="str">
@@ -11277,7 +11418,7 @@
         <v/>
       </c>
       <c r="I374" s="13" t="str">
-        <f aca="false">IF(OR(A374="",D374=""),"",ROUND(D374*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A374="",D374=""),"",ROUND(D374*INDEX(Programmes!$L$2:$L$8,MATCH(A374,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J374" s="13" t="str">
@@ -11298,7 +11439,7 @@
         <v/>
       </c>
       <c r="I375" s="13" t="str">
-        <f aca="false">IF(OR(A375="",D375=""),"",ROUND(D375*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A375="",D375=""),"",ROUND(D375*INDEX(Programmes!$L$2:$L$8,MATCH(A375,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J375" s="13" t="str">
@@ -11319,7 +11460,7 @@
         <v/>
       </c>
       <c r="I376" s="13" t="str">
-        <f aca="false">IF(OR(A376="",D376=""),"",ROUND(D376*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A376="",D376=""),"",ROUND(D376*INDEX(Programmes!$L$2:$L$8,MATCH(A376,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J376" s="13" t="str">
@@ -11340,7 +11481,7 @@
         <v/>
       </c>
       <c r="I377" s="13" t="str">
-        <f aca="false">IF(OR(A377="",D377=""),"",ROUND(D377*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A377="",D377=""),"",ROUND(D377*INDEX(Programmes!$L$2:$L$8,MATCH(A377,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J377" s="13" t="str">
@@ -11361,7 +11502,7 @@
         <v/>
       </c>
       <c r="I378" s="13" t="str">
-        <f aca="false">IF(OR(A378="",D378=""),"",ROUND(D378*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A378="",D378=""),"",ROUND(D378*INDEX(Programmes!$L$2:$L$8,MATCH(A378,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J378" s="13" t="str">
@@ -11382,7 +11523,7 @@
         <v/>
       </c>
       <c r="I379" s="13" t="str">
-        <f aca="false">IF(OR(A379="",D379=""),"",ROUND(D379*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A379="",D379=""),"",ROUND(D379*INDEX(Programmes!$L$2:$L$8,MATCH(A379,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J379" s="13" t="str">
@@ -11403,7 +11544,7 @@
         <v/>
       </c>
       <c r="I380" s="13" t="str">
-        <f aca="false">IF(OR(A380="",D380=""),"",ROUND(D380*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A380="",D380=""),"",ROUND(D380*INDEX(Programmes!$L$2:$L$8,MATCH(A380,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J380" s="13" t="str">
@@ -11424,7 +11565,7 @@
         <v/>
       </c>
       <c r="I381" s="13" t="str">
-        <f aca="false">IF(OR(A381="",D381=""),"",ROUND(D381*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A381="",D381=""),"",ROUND(D381*INDEX(Programmes!$L$2:$L$8,MATCH(A381,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J381" s="13" t="str">
@@ -11445,7 +11586,7 @@
         <v/>
       </c>
       <c r="I382" s="13" t="str">
-        <f aca="false">IF(OR(A382="",D382=""),"",ROUND(D382*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A382="",D382=""),"",ROUND(D382*INDEX(Programmes!$L$2:$L$8,MATCH(A382,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J382" s="13" t="str">
@@ -11466,7 +11607,7 @@
         <v/>
       </c>
       <c r="I383" s="13" t="str">
-        <f aca="false">IF(OR(A383="",D383=""),"",ROUND(D383*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A383="",D383=""),"",ROUND(D383*INDEX(Programmes!$L$2:$L$8,MATCH(A383,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J383" s="13" t="str">
@@ -11487,7 +11628,7 @@
         <v/>
       </c>
       <c r="I384" s="13" t="str">
-        <f aca="false">IF(OR(A384="",D384=""),"",ROUND(D384*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A384="",D384=""),"",ROUND(D384*INDEX(Programmes!$L$2:$L$8,MATCH(A384,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J384" s="13" t="str">
@@ -11508,7 +11649,7 @@
         <v/>
       </c>
       <c r="I385" s="13" t="str">
-        <f aca="false">IF(OR(A385="",D385=""),"",ROUND(D385*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A385="",D385=""),"",ROUND(D385*INDEX(Programmes!$L$2:$L$8,MATCH(A385,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J385" s="13" t="str">
@@ -11529,7 +11670,7 @@
         <v/>
       </c>
       <c r="I386" s="13" t="str">
-        <f aca="false">IF(OR(A386="",D386=""),"",ROUND(D386*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A386="",D386=""),"",ROUND(D386*INDEX(Programmes!$L$2:$L$8,MATCH(A386,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J386" s="13" t="str">
@@ -11550,7 +11691,7 @@
         <v/>
       </c>
       <c r="I387" s="13" t="str">
-        <f aca="false">IF(OR(A387="",D387=""),"",ROUND(D387*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A387="",D387=""),"",ROUND(D387*INDEX(Programmes!$L$2:$L$8,MATCH(A387,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J387" s="13" t="str">
@@ -11571,7 +11712,7 @@
         <v/>
       </c>
       <c r="I388" s="13" t="str">
-        <f aca="false">IF(OR(A388="",D388=""),"",ROUND(D388*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A388="",D388=""),"",ROUND(D388*INDEX(Programmes!$L$2:$L$8,MATCH(A388,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J388" s="13" t="str">
@@ -11592,7 +11733,7 @@
         <v/>
       </c>
       <c r="I389" s="13" t="str">
-        <f aca="false">IF(OR(A389="",D389=""),"",ROUND(D389*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A389="",D389=""),"",ROUND(D389*INDEX(Programmes!$L$2:$L$8,MATCH(A389,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J389" s="13" t="str">
@@ -11613,7 +11754,7 @@
         <v/>
       </c>
       <c r="I390" s="13" t="str">
-        <f aca="false">IF(OR(A390="",D390=""),"",ROUND(D390*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A390="",D390=""),"",ROUND(D390*INDEX(Programmes!$L$2:$L$8,MATCH(A390,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J390" s="13" t="str">
@@ -11634,7 +11775,7 @@
         <v/>
       </c>
       <c r="I391" s="13" t="str">
-        <f aca="false">IF(OR(A391="",D391=""),"",ROUND(D391*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A391="",D391=""),"",ROUND(D391*INDEX(Programmes!$L$2:$L$8,MATCH(A391,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J391" s="13" t="str">
@@ -11655,7 +11796,7 @@
         <v/>
       </c>
       <c r="I392" s="13" t="str">
-        <f aca="false">IF(OR(A392="",D392=""),"",ROUND(D392*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A392="",D392=""),"",ROUND(D392*INDEX(Programmes!$L$2:$L$8,MATCH(A392,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J392" s="13" t="str">
@@ -11676,7 +11817,7 @@
         <v/>
       </c>
       <c r="I393" s="13" t="str">
-        <f aca="false">IF(OR(A393="",D393=""),"",ROUND(D393*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A393="",D393=""),"",ROUND(D393*INDEX(Programmes!$L$2:$L$8,MATCH(A393,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J393" s="13" t="str">
@@ -11697,7 +11838,7 @@
         <v/>
       </c>
       <c r="I394" s="13" t="str">
-        <f aca="false">IF(OR(A394="",D394=""),"",ROUND(D394*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A394="",D394=""),"",ROUND(D394*INDEX(Programmes!$L$2:$L$8,MATCH(A394,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J394" s="13" t="str">
@@ -11718,7 +11859,7 @@
         <v/>
       </c>
       <c r="I395" s="13" t="str">
-        <f aca="false">IF(OR(A395="",D395=""),"",ROUND(D395*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A395="",D395=""),"",ROUND(D395*INDEX(Programmes!$L$2:$L$8,MATCH(A395,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J395" s="13" t="str">
@@ -11739,7 +11880,7 @@
         <v/>
       </c>
       <c r="I396" s="13" t="str">
-        <f aca="false">IF(OR(A396="",D396=""),"",ROUND(D396*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A396="",D396=""),"",ROUND(D396*INDEX(Programmes!$L$2:$L$8,MATCH(A396,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J396" s="13" t="str">
@@ -11760,7 +11901,7 @@
         <v/>
       </c>
       <c r="I397" s="13" t="str">
-        <f aca="false">IF(OR(A397="",D397=""),"",ROUND(D397*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A397="",D397=""),"",ROUND(D397*INDEX(Programmes!$L$2:$L$8,MATCH(A397,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J397" s="13" t="str">
@@ -11781,7 +11922,7 @@
         <v/>
       </c>
       <c r="I398" s="13" t="str">
-        <f aca="false">IF(OR(A398="",D398=""),"",ROUND(D398*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A398="",D398=""),"",ROUND(D398*INDEX(Programmes!$L$2:$L$8,MATCH(A398,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J398" s="13" t="str">
@@ -11802,7 +11943,7 @@
         <v/>
       </c>
       <c r="I399" s="13" t="str">
-        <f aca="false">IF(OR(A399="",D399=""),"",ROUND(D399*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A399="",D399=""),"",ROUND(D399*INDEX(Programmes!$L$2:$L$8,MATCH(A399,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J399" s="13" t="str">
@@ -11823,7 +11964,7 @@
         <v/>
       </c>
       <c r="I400" s="13" t="str">
-        <f aca="false">IF(OR(A400="",D400=""),"",ROUND(D400*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A400="",D400=""),"",ROUND(D400*INDEX(Programmes!$L$2:$L$8,MATCH(A400,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J400" s="13" t="str">
@@ -11844,7 +11985,7 @@
         <v/>
       </c>
       <c r="I401" s="13" t="str">
-        <f aca="false">IF(OR(A401="",D401=""),"",ROUND(D401*Rules!$C$9,1))</f>
+        <f aca="false">IF(OR(A401="",D401=""),"",ROUND(D401*INDEX(Programmes!$L$2:$L$8,MATCH(A401,Programmes!$A$2:$A$8,0)),1))</f>
         <v/>
       </c>
       <c r="J401" s="13" t="str">
@@ -11897,30 +12038,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B2" s="12" t="n">
         <v>1</v>
@@ -11929,19 +12070,19 @@
         <v>1</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B3" s="12" t="n">
         <v>1</v>
@@ -11950,19 +12091,19 @@
         <v>2</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G3" s="12"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B4" s="12" t="n">
         <v>1</v>
@@ -11971,19 +12112,19 @@
         <v>3</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>1</v>
@@ -11992,19 +12133,19 @@
         <v>4</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B6" s="12" t="n">
         <v>2</v>
@@ -12016,16 +12157,16 @@
         <v>35</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>2</v>
@@ -12034,19 +12175,19 @@
         <v>2</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B8" s="12" t="n">
         <v>2</v>
@@ -12055,19 +12196,19 @@
         <v>3</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B9" s="12" t="n">
         <v>2</v>
@@ -12076,19 +12217,19 @@
         <v>4</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>3</v>
@@ -12097,19 +12238,19 @@
         <v>1</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>3</v>
@@ -12118,19 +12259,19 @@
         <v>2</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>3</v>
@@ -12139,19 +12280,19 @@
         <v>3</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B13" s="12" t="n">
         <v>3</v>
@@ -12160,19 +12301,19 @@
         <v>4</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B14" s="12" t="n">
         <v>4</v>
@@ -12181,19 +12322,19 @@
         <v>1</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="G14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B15" s="12" t="n">
         <v>4</v>
@@ -12202,19 +12343,19 @@
         <v>2</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B16" s="12" t="n">
         <v>4</v>
@@ -12223,19 +12364,19 @@
         <v>3</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B17" s="12" t="n">
         <v>4</v>
@@ -12244,19 +12385,19 @@
         <v>4</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="G17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B18" s="12" t="n">
         <v>5</v>
@@ -12268,16 +12409,16 @@
         <v>35</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B19" s="12" t="n">
         <v>5</v>
@@ -12286,19 +12427,19 @@
         <v>2</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G19" s="12"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B20" s="12" t="n">
         <v>5</v>
@@ -12307,19 +12448,19 @@
         <v>3</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B21" s="12" t="n">
         <v>5</v>
@@ -12328,19 +12469,19 @@
         <v>4</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G21" s="12"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B22" s="12" t="n">
         <v>6</v>
@@ -12349,19 +12490,19 @@
         <v>1</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G22" s="12"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B23" s="12" t="n">
         <v>6</v>
@@ -12370,19 +12511,19 @@
         <v>2</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B24" s="12" t="n">
         <v>6</v>
@@ -12391,19 +12532,19 @@
         <v>3</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="G24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B25" s="12" t="n">
         <v>6</v>
@@ -12412,19 +12553,19 @@
         <v>4</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>7</v>
@@ -12433,19 +12574,19 @@
         <v>1</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>7</v>
@@ -12454,19 +12595,19 @@
         <v>2</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B28" s="12" t="n">
         <v>7</v>
@@ -12475,19 +12616,19 @@
         <v>3</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B29" s="12" t="n">
         <v>7</v>
@@ -12496,19 +12637,19 @@
         <v>4</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B30" s="12" t="n">
         <v>8</v>
@@ -12520,16 +12661,16 @@
         <v>35</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="G30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B31" s="12" t="n">
         <v>8</v>
@@ -12538,19 +12679,19 @@
         <v>2</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B32" s="12" t="n">
         <v>8</v>
@@ -12559,19 +12700,19 @@
         <v>3</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G32" s="12"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B33" s="12" t="n">
         <v>8</v>
@@ -12580,19 +12721,19 @@
         <v>4</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="G33" s="12"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B34" s="12" t="n">
         <v>9</v>
@@ -12601,19 +12742,19 @@
         <v>1</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="G34" s="12"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B35" s="12" t="n">
         <v>9</v>
@@ -12622,19 +12763,19 @@
         <v>2</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G35" s="12"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B36" s="12" t="n">
         <v>9</v>
@@ -12643,19 +12784,19 @@
         <v>3</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G36" s="12"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B37" s="12" t="n">
         <v>9</v>
@@ -12664,19 +12805,19 @@
         <v>4</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G37" s="12"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B38" s="12" t="n">
         <v>10</v>
@@ -12685,19 +12826,19 @@
         <v>1</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G38" s="12"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B39" s="12" t="n">
         <v>10</v>
@@ -12706,19 +12847,19 @@
         <v>2</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G39" s="12"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B40" s="12" t="n">
         <v>10</v>
@@ -12727,19 +12868,19 @@
         <v>3</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="G40" s="12"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B41" s="12" t="n">
         <v>10</v>
@@ -12748,19 +12889,19 @@
         <v>4</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="G41" s="12"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B42" s="12" t="n">
         <v>11</v>
@@ -12769,19 +12910,19 @@
         <v>1</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G42" s="12"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B43" s="12" t="n">
         <v>11</v>
@@ -12790,19 +12931,19 @@
         <v>2</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G43" s="12"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B44" s="12" t="n">
         <v>11</v>
@@ -12811,19 +12952,19 @@
         <v>3</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G44" s="12"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B45" s="12" t="n">
         <v>11</v>
@@ -12832,19 +12973,19 @@
         <v>4</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="G45" s="12"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B46" s="12" t="n">
         <v>12</v>
@@ -12853,19 +12994,19 @@
         <v>1</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G46" s="12"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B47" s="12" t="n">
         <v>12</v>
@@ -12874,19 +13015,19 @@
         <v>2</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G47" s="12"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B48" s="12" t="n">
         <v>12</v>
@@ -12895,10 +13036,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F48" s="12" t="s">
         <v>42</v>
@@ -12907,7 +13048,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B49" s="12" t="n">
         <v>12</v>
@@ -12919,10 +13060,10 @@
         <v>45</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G49" s="12"/>
     </row>
@@ -16134,189 +16275,189 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="F2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F3" s="12"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F10" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -16348,39 +16489,39 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B2" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F2" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A2)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
@@ -16389,19 +16530,19 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B3" s="12" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F3" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A3)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
@@ -16410,19 +16551,19 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B4" s="12" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F4" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A4)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
@@ -16431,19 +16572,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>226</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>221</v>
       </c>
       <c r="F5" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A5)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
@@ -16452,19 +16593,19 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B6" s="12" t="n">
         <v>3</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F6" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A6)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
@@ -16473,19 +16614,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F7" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A7)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
@@ -16494,19 +16635,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B8" s="12" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F8" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A8)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
@@ -16515,19 +16656,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B9" s="12" t="n">
         <v>5</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F9" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A9)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
@@ -16571,51 +16712,51 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C2" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
@@ -16625,19 +16766,19 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C3" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F3" s="12"/>
       <c r="G3" s="12"/>
@@ -16647,19 +16788,19 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C4" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="12"/>
@@ -16669,19 +16810,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="12"/>
@@ -16691,19 +16832,19 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>5</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
@@ -16713,19 +16854,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="12"/>
@@ -16735,19 +16876,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
@@ -16757,19 +16898,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
@@ -16779,19 +16920,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="12"/>
@@ -16801,19 +16942,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>5</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="12"/>
@@ -16823,19 +16964,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C12" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
@@ -16845,19 +16986,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="12"/>
@@ -16867,19 +17008,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D14" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="E14" s="12" t="s">
         <v>257</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>252</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="12"/>
@@ -16889,19 +17030,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C15" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="12"/>
@@ -16911,19 +17052,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C16" s="12" t="n">
         <v>5</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="12"/>
@@ -16933,19 +17074,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C17" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="12"/>
@@ -16955,19 +17096,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C18" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="12"/>
@@ -16977,19 +17118,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C19" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="12"/>
@@ -16999,19 +17140,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C20" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="12"/>
@@ -17021,19 +17162,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C21" s="12" t="n">
         <v>5</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F21" s="12"/>
       <c r="G21" s="12"/>
@@ -17043,19 +17184,19 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C22" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F22" s="12"/>
       <c r="G22" s="12"/>
@@ -17065,19 +17206,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C23" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F23" s="12"/>
       <c r="G23" s="12"/>
@@ -17087,19 +17228,19 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C24" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F24" s="12"/>
       <c r="G24" s="12"/>
@@ -17109,19 +17250,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C25" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F25" s="12"/>
       <c r="G25" s="12"/>
@@ -17131,19 +17272,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C26" s="12" t="n">
         <v>5</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F26" s="12"/>
       <c r="G26" s="12"/>
@@ -17153,19 +17294,19 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C27" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F27" s="12"/>
       <c r="G27" s="12"/>
@@ -17175,19 +17316,19 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C28" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F28" s="12"/>
       <c r="G28" s="12"/>
@@ -17197,19 +17338,19 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C29" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F29" s="12"/>
       <c r="G29" s="12"/>
@@ -17219,19 +17360,19 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C30" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F30" s="12"/>
       <c r="G30" s="12"/>
@@ -17241,19 +17382,19 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C31" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>4</v>
@@ -17271,19 +17412,19 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C32" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F32" s="12"/>
       <c r="G32" s="12"/>
@@ -17293,19 +17434,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C33" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F33" s="12"/>
       <c r="G33" s="12"/>
@@ -17315,19 +17456,19 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C34" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F34" s="12"/>
       <c r="G34" s="12"/>
@@ -17337,19 +17478,19 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C35" s="12" t="n">
         <v>5</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F35" s="12"/>
       <c r="G35" s="12"/>
@@ -17371,7 +17512,7 @@
     </row>
     <row r="37" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="17" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
@@ -21794,33 +21935,33 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C2" s="12" t="n">
         <v>3</v>
@@ -21838,10 +21979,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C3" s="12" t="n">
         <v>2</v>
@@ -21859,10 +22000,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C4" s="12" t="n">
         <v>3</v>
@@ -21880,10 +22021,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>2</v>
@@ -21901,10 +22042,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>3</v>
@@ -21922,10 +22063,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>2</v>
@@ -21943,10 +22084,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>3</v>
@@ -21964,10 +22105,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>2</v>
@@ -21985,10 +22126,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>5</v>
@@ -22006,10 +22147,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>3</v>
@@ -22027,10 +22168,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C12" s="12" t="n">
         <v>4</v>
@@ -22048,10 +22189,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>3</v>
@@ -22069,10 +22210,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>4</v>
@@ -22090,10 +22231,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C15" s="12" t="n">
         <v>3</v>
@@ -22111,12 +22252,12 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -22135,7 +22276,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
@@ -22145,24 +22286,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B2" s="18" t="n">
         <v>8</v>
@@ -22174,12 +22315,12 @@
         <v>25</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B3" s="18" t="n">
         <v>8</v>
@@ -22191,12 +22332,12 @@
         <v>25</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B4" s="18" t="n">
         <v>30</v>
@@ -22208,12 +22349,12 @@
         <v>100</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B5" s="18" t="n">
         <v>10</v>
@@ -22225,12 +22366,12 @@
         <v>32</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B6" s="18" t="n">
         <v>3</v>
@@ -22242,12 +22383,12 @@
         <v>4</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B7" s="19" t="n">
         <v>0.1</v>
@@ -22259,12 +22400,12 @@
         <v>0.12</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B8" s="19" t="n">
         <v>0.3</v>
@@ -22276,12 +22417,12 @@
         <v>0.32</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B9" s="18" t="n">
         <v>15</v>
@@ -22293,12 +22434,12 @@
         <v>50</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B10" s="19" t="n">
         <v>0.06</v>
@@ -22310,12 +22451,12 @@
         <v>0.06</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B11" s="18" t="n">
         <v>1.5</v>
@@ -22327,12 +22468,12 @@
         <v>1.5</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B12" s="18" t="n">
         <v>2.5</v>
@@ -22347,7 +22488,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B13" s="19" t="n">
         <v>0.1</v>
@@ -22359,12 +22500,12 @@
         <v>0.1</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B14" s="18" t="n">
         <v>2</v>
@@ -22376,12 +22517,12 @@
         <v>2</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B15" s="19" t="n">
         <v>0.15</v>
@@ -22396,7 +22537,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B16" s="18" t="n">
         <v>3</v>
@@ -22411,7 +22552,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B17" s="19" t="n">
         <v>0.25</v>
@@ -22426,7 +22567,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B18" s="18" t="n">
         <v>4</v>
@@ -22441,7 +22582,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B19" s="19" t="n">
         <v>0.6</v>
@@ -22453,12 +22594,12 @@
         <v>0.6</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B20" s="19" t="n">
         <v>0.85</v>
@@ -22473,7 +22614,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B21" s="19" t="n">
         <v>0.15</v>
@@ -22488,7 +22629,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B22" s="19" t="n">
         <v>0.6</v>
@@ -22500,12 +22641,46 @@
         <v>0.6</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>314</v>
+        <v>319</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="B23" s="19" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C23" s="19" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14" t="s">
-        <v>315</v>
+      <c r="A24" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="B24" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C24" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D24" s="19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="14" t="s">
+        <v>324</v>
       </c>
     </row>
   </sheetData>

--- a/programmes/Kinetix Programmes.xlsx
+++ b/programmes/Kinetix Programmes.xlsx
@@ -43,6 +43,18 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">The weekly volume this race needs at each level. Run weeks' % are a % of this. Runners below it build up to it; runners above it ease down to it.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Which runners see this goal in onboarding, by their running experience.</t>
         </r>
       </text>
     </comment>
@@ -177,7 +189,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="402">
   <si>
     <t xml:space="preserve">Kinetix programmes</t>
   </si>
@@ -416,6 +428,9 @@
     <t xml:space="preserve">Description shown in onboarding</t>
   </si>
   <si>
+    <t xml:space="preserve">Available to</t>
+  </si>
+  <si>
     <t xml:space="preserve">Weeks written</t>
   </si>
   <si>
@@ -432,6 +447,18 @@
   </si>
   <si>
     <t xml:space="preserve">Build up to running 5K comfortably, then race it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beginner only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faster 5K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speed, VO2max and threshold work to lower your 5K time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All levels</t>
   </si>
   <si>
     <t xml:space="preserve">Faster 10K</t>
@@ -2293,214 +2320,217 @@
         <v>8</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>27</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="B9" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="6" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2508,367 +2538,367 @@
         <v>45</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I12" s="6" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I13" s="6" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I14" s="6" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I15" s="6" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I16" s="6" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I17" s="6" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I18" s="6" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I19" s="6" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I20" s="6" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I21" s="6" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I22" s="6" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I23" s="6" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I24" s="6" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I25" s="6" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I26" s="6" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I27" s="6" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I28" s="6" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I29" s="6" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I30" s="6" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I31" s="6" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I32" s="6" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I33" s="6" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I34" s="6" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I35" s="6" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I36" s="6" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I37" s="6" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I38" s="6" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I39" s="6" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I40" s="6" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I41" s="6" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I42" s="6" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I43" s="6" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I44" s="6" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I45" s="6" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I46" s="6" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I47" s="6" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I48" s="6" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I49" s="6" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I50" s="6" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I51" s="6" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I52" s="6" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I53" s="6" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I54" s="6" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I55" s="6" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I56" s="6" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I57" s="6" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I58" s="6" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I59" s="6" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I60" s="6" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I61" s="6" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I62" s="6" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I63" s="6" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I64" s="6" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I65" s="6" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I66" s="6" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I67" s="6" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I68" s="6" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I69" s="6" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I70" s="6" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I71" s="6" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I72" s="6" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I73" s="6" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I74" s="6" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I75" s="6" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I76" s="6" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I77" s="6" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I78" s="6" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I79" s="6" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I80" s="6" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I81" s="6" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I82" s="6" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I83" s="6" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -2887,7 +2917,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
@@ -2899,7 +2929,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2957,19 +2988,22 @@
       <c r="R1" s="11" t="s">
         <v>80</v>
       </c>
+      <c r="S1" s="11" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C2" s="12" t="n">
         <v>8</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E2" s="12" t="n">
         <v>3</v>
@@ -2992,42 +3026,41 @@
       <c r="K2" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="L2" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="M2" s="12" t="n">
-        <v>45</v>
-      </c>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
       <c r="N2" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O2" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P2" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q2" s="13" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="R2" s="13" t="n">
         <f aca="false">COUNTIF('Run weeks'!$A$2:$A$401,A2)</f>
         <v>0</v>
       </c>
-      <c r="R2" s="13" t="n">
+      <c r="S2" s="13" t="n">
         <f aca="false">COUNTIF('Run sessions'!$A$2:$A$401,A2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C3" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>3</v>
@@ -3042,50 +3075,53 @@
         <v>2</v>
       </c>
       <c r="I3" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J3" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="K3" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L3" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="M3" s="12" t="n">
         <v>45</v>
-      </c>
-      <c r="K3" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="L3" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="M3" s="12" t="n">
-        <v>55</v>
       </c>
       <c r="N3" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O3" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q3" s="13" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q3" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="R3" s="13" t="n">
         <f aca="false">COUNTIF('Run weeks'!$A$2:$A$401,A3)</f>
         <v>0</v>
       </c>
-      <c r="R3" s="13" t="n">
+      <c r="S3" s="13" t="n">
         <f aca="false">COUNTIF('Run sessions'!$A$2:$A$401,A3)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C4" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>3</v>
@@ -3100,56 +3136,59 @@
         <v>2</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J4" s="12" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="K4" s="12" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="M4" s="12" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="N4" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q4" s="13" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q4" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="R4" s="13" t="n">
         <f aca="false">COUNTIF('Run weeks'!$A$2:$A$401,A4)</f>
-        <v>12</v>
-      </c>
-      <c r="R4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="13" t="n">
         <f aca="false">COUNTIF('Run sessions'!$A$2:$A$401,A4)</f>
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C5" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" s="12" t="n">
         <v>1</v>
@@ -3158,108 +3197,114 @@
         <v>2</v>
       </c>
       <c r="I5" s="12" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="K5" s="12" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O5" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q5" s="13" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q5" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="R5" s="13" t="n">
         <f aca="false">COUNTIF('Run weeks'!$A$2:$A$401,A5)</f>
-        <v>0</v>
-      </c>
-      <c r="R5" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="S5" s="13" t="n">
         <f aca="false">COUNTIF('Run sessions'!$A$2:$A$401,A5)</f>
-        <v>0</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E6" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="H6" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="J6" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="K6" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="L6" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="M6" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="N6" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J6" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="K6" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="L6" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="M6" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="N6" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="O6" s="12" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="P6" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q6" s="13" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q6" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="R6" s="13" t="n">
         <f aca="false">COUNTIF('Run weeks'!$A$2:$A$401,A6)</f>
         <v>0</v>
       </c>
-      <c r="R6" s="13" t="n">
+      <c r="S6" s="13" t="n">
         <f aca="false">COUNTIF('Run sessions'!$A$2:$A$401,A6)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>8</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>1</v>
@@ -3268,10 +3313,10 @@
         <v>3</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I7" s="12" t="n">
         <v>10</v>
@@ -3292,91 +3337,162 @@
         <v>1</v>
       </c>
       <c r="O7" s="12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q7" s="13" t="n">
+        <v>98</v>
+      </c>
+      <c r="Q7" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="R7" s="13" t="n">
         <f aca="false">COUNTIF('Run weeks'!$A$2:$A$401,A7)</f>
         <v>0</v>
       </c>
-      <c r="R7" s="13" t="n">
+      <c r="S7" s="13" t="n">
         <f aca="false">COUNTIF('Run sessions'!$A$2:$A$401,A7)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>8</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E8" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K8" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L8" s="12" t="n">
+      <c r="M8" s="12" t="n">
         <v>25</v>
-      </c>
-      <c r="M8" s="12" t="n">
-        <v>40</v>
       </c>
       <c r="N8" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O8" s="12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q8" s="13" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q8" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="R8" s="13" t="n">
         <f aca="false">COUNTIF('Run weeks'!$A$2:$A$401,A8)</f>
         <v>0</v>
       </c>
-      <c r="R8" s="13" t="n">
+      <c r="S8" s="13" t="n">
         <f aca="false">COUNTIF('Run sessions'!$A$2:$A$401,A8)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
-        <v>100</v>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="K9" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L9" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="M9" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="N9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="P9" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q9" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="R9" s="13" t="n">
+        <f aca="false">COUNTIF('Run weeks'!$A$2:$A$401,A9)</f>
+        <v>0</v>
+      </c>
+      <c r="S9" s="13" t="n">
+        <f aca="false">COUNTIF('Run sessions'!$A$2:$A$401,A9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="14" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation allowBlank="true" error="Pick one of the options in the drop-down." errorStyle="stop" errorTitle="Choose from the list" operator="between" prompt="What happens when the last week is done." promptTitle="Tip" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D2:D8" type="list">
+  <dataValidations count="3">
+    <dataValidation allowBlank="true" error="Pick one of the options in the drop-down." errorStyle="stop" errorTitle="Choose from the list" operator="between" prompt="What happens when the last week is done." promptTitle="Tip" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D2:D9" type="list">
       <formula1>"Repeat,Repeat harder,Maintenance,Stop"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Pick one of the options in the drop-down." errorStyle="stop" errorTitle="Choose from the list" operator="between" prompt="The split suggested in onboarding (the user can change it)." promptTitle="Tip" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="O2:O8" type="list">
+    <dataValidation allowBlank="true" error="Pick one of the options in the drop-down." errorStyle="stop" errorTitle="Choose from the list" operator="between" prompt="The split suggested in onboarding (the user can change it)." promptTitle="Tip" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="O2:O9" type="list">
       <formula1>Lists!$E$2:$E$9</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Pick one of the options in the drop-down." errorStyle="stop" errorTitle="Choose from the list" operator="between" prompt="Which runners see this goal in onboarding." promptTitle="Tip" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="Q2:Q9" type="list">
+      <formula1>"All levels,Beginner only,Beginner and intermediate,Intermediate and advanced,Advanced only"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -3412,61 +3528,61 @@
         <v>63</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B2" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D2" s="15" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="H2" s="13" t="n">
         <f aca="false">IF(A2="","",COUNTIFS('Run sessions'!$A$2:$A$401,A2,'Run sessions'!$B$2:$B$401,B2))</f>
         <v>4</v>
       </c>
       <c r="I2" s="13" t="n">
-        <f aca="false">IF(OR(A2="",D2=""),"",ROUND(D2*INDEX(Programmes!$L$2:$L$8,MATCH(A2,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A2="",D2=""),"",IFERROR(ROUND(D2*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A2,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A2,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A2,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v>45</v>
       </c>
       <c r="J2" s="13" t="n">
@@ -3476,22 +3592,22 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B3" s="12" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D3" s="15" t="n">
         <v>1.05</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="13" t="n">
@@ -3499,7 +3615,7 @@
         <v>4</v>
       </c>
       <c r="I3" s="13" t="n">
-        <f aca="false">IF(OR(A3="",D3=""),"",ROUND(D3*INDEX(Programmes!$L$2:$L$8,MATCH(A3,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A3="",D3=""),"",IFERROR(ROUND(D3*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A3,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A3,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A3,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v>47.3</v>
       </c>
       <c r="J3" s="13" t="n">
@@ -3509,22 +3625,22 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B4" s="12" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D4" s="15" t="n">
         <v>1.1</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G4" s="12"/>
       <c r="H4" s="13" t="n">
@@ -3532,7 +3648,7 @@
         <v>4</v>
       </c>
       <c r="I4" s="13" t="n">
-        <f aca="false">IF(OR(A4="",D4=""),"",ROUND(D4*INDEX(Programmes!$L$2:$L$8,MATCH(A4,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A4="",D4=""),"",IFERROR(ROUND(D4*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A4,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A4,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A4,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v>49.5</v>
       </c>
       <c r="J4" s="13" t="n">
@@ -3542,32 +3658,32 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>0.9</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H5" s="13" t="n">
         <f aca="false">IF(A5="","",COUNTIFS('Run sessions'!$A$2:$A$401,A5,'Run sessions'!$B$2:$B$401,B5))</f>
         <v>4</v>
       </c>
       <c r="I5" s="13" t="n">
-        <f aca="false">IF(OR(A5="",D5=""),"",ROUND(D5*INDEX(Programmes!$L$2:$L$8,MATCH(A5,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A5="",D5=""),"",IFERROR(ROUND(D5*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A5,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A5,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A5,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v>40.5</v>
       </c>
       <c r="J5" s="13" t="n">
@@ -3577,22 +3693,22 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B6" s="12" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D6" s="15" t="n">
         <v>1.15</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G6" s="12"/>
       <c r="H6" s="13" t="n">
@@ -3600,7 +3716,7 @@
         <v>4</v>
       </c>
       <c r="I6" s="13" t="n">
-        <f aca="false">IF(OR(A6="",D6=""),"",ROUND(D6*INDEX(Programmes!$L$2:$L$8,MATCH(A6,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A6="",D6=""),"",IFERROR(ROUND(D6*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A6,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A6,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A6,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v>51.8</v>
       </c>
       <c r="J6" s="13" t="n">
@@ -3610,22 +3726,22 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D7" s="15" t="n">
         <v>1.2</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G7" s="12"/>
       <c r="H7" s="13" t="n">
@@ -3633,7 +3749,7 @@
         <v>4</v>
       </c>
       <c r="I7" s="13" t="n">
-        <f aca="false">IF(OR(A7="",D7=""),"",ROUND(D7*INDEX(Programmes!$L$2:$L$8,MATCH(A7,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A7="",D7=""),"",IFERROR(ROUND(D7*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A7,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A7,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A7,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v>54</v>
       </c>
       <c r="J7" s="13" t="n">
@@ -3643,22 +3759,22 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B8" s="12" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D8" s="15" t="n">
         <v>1.25</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G8" s="12"/>
       <c r="H8" s="13" t="n">
@@ -3666,7 +3782,7 @@
         <v>4</v>
       </c>
       <c r="I8" s="13" t="n">
-        <f aca="false">IF(OR(A8="",D8=""),"",ROUND(D8*INDEX(Programmes!$L$2:$L$8,MATCH(A8,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A8="",D8=""),"",IFERROR(ROUND(D8*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A8,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A8,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A8,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v>56.3</v>
       </c>
       <c r="J8" s="13" t="n">
@@ -3676,22 +3792,22 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B9" s="12" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D9" s="15" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G9" s="12"/>
       <c r="H9" s="13" t="n">
@@ -3699,7 +3815,7 @@
         <v>4</v>
       </c>
       <c r="I9" s="13" t="n">
-        <f aca="false">IF(OR(A9="",D9=""),"",ROUND(D9*INDEX(Programmes!$L$2:$L$8,MATCH(A9,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A9="",D9=""),"",IFERROR(ROUND(D9*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A9,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A9,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A9,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v>45</v>
       </c>
       <c r="J9" s="13" t="n">
@@ -3709,32 +3825,32 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>1.3</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H10" s="13" t="n">
         <f aca="false">IF(A10="","",COUNTIFS('Run sessions'!$A$2:$A$401,A10,'Run sessions'!$B$2:$B$401,B10))</f>
         <v>4</v>
       </c>
       <c r="I10" s="13" t="n">
-        <f aca="false">IF(OR(A10="",D10=""),"",ROUND(D10*INDEX(Programmes!$L$2:$L$8,MATCH(A10,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A10="",D10=""),"",IFERROR(ROUND(D10*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A10,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A10,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A10,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v>58.5</v>
       </c>
       <c r="J10" s="13" t="n">
@@ -3744,22 +3860,22 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D11" s="15" t="n">
         <v>1.3</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G11" s="12"/>
       <c r="H11" s="13" t="n">
@@ -3767,7 +3883,7 @@
         <v>4</v>
       </c>
       <c r="I11" s="13" t="n">
-        <f aca="false">IF(OR(A11="",D11=""),"",ROUND(D11*INDEX(Programmes!$L$2:$L$8,MATCH(A11,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A11="",D11=""),"",IFERROR(ROUND(D11*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A11,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A11,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A11,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v>58.5</v>
       </c>
       <c r="J11" s="13" t="n">
@@ -3777,32 +3893,32 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>11</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D12" s="15" t="n">
         <v>0.85</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="H12" s="13" t="n">
         <f aca="false">IF(A12="","",COUNTIFS('Run sessions'!$A$2:$A$401,A12,'Run sessions'!$B$2:$B$401,B12))</f>
         <v>4</v>
       </c>
       <c r="I12" s="13" t="n">
-        <f aca="false">IF(OR(A12="",D12=""),"",ROUND(D12*INDEX(Programmes!$L$2:$L$8,MATCH(A12,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A12="",D12=""),"",IFERROR(ROUND(D12*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A12,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A12,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A12,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v>38.3</v>
       </c>
       <c r="J12" s="13" t="n">
@@ -3812,13 +3928,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B13" s="12" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.55</v>
@@ -3827,17 +3943,17 @@
         <v>45</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="H13" s="13" t="n">
         <f aca="false">IF(A13="","",COUNTIFS('Run sessions'!$A$2:$A$401,A13,'Run sessions'!$B$2:$B$401,B13))</f>
         <v>4</v>
       </c>
       <c r="I13" s="13" t="n">
-        <f aca="false">IF(OR(A13="",D13=""),"",ROUND(D13*INDEX(Programmes!$L$2:$L$8,MATCH(A13,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A13="",D13=""),"",IFERROR(ROUND(D13*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A13,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A13,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A13,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v>24.8</v>
       </c>
       <c r="J13" s="13" t="str">
@@ -3858,7 +3974,7 @@
         <v/>
       </c>
       <c r="I14" s="13" t="str">
-        <f aca="false">IF(OR(A14="",D14=""),"",ROUND(D14*INDEX(Programmes!$L$2:$L$8,MATCH(A14,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A14="",D14=""),"",IFERROR(ROUND(D14*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A14,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A14,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A14,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J14" s="13" t="str">
@@ -3879,7 +3995,7 @@
         <v/>
       </c>
       <c r="I15" s="13" t="str">
-        <f aca="false">IF(OR(A15="",D15=""),"",ROUND(D15*INDEX(Programmes!$L$2:$L$8,MATCH(A15,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A15="",D15=""),"",IFERROR(ROUND(D15*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A15,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A15,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A15,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J15" s="13" t="str">
@@ -3900,7 +4016,7 @@
         <v/>
       </c>
       <c r="I16" s="13" t="str">
-        <f aca="false">IF(OR(A16="",D16=""),"",ROUND(D16*INDEX(Programmes!$L$2:$L$8,MATCH(A16,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A16="",D16=""),"",IFERROR(ROUND(D16*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A16,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A16,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A16,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J16" s="13" t="str">
@@ -3921,7 +4037,7 @@
         <v/>
       </c>
       <c r="I17" s="13" t="str">
-        <f aca="false">IF(OR(A17="",D17=""),"",ROUND(D17*INDEX(Programmes!$L$2:$L$8,MATCH(A17,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A17="",D17=""),"",IFERROR(ROUND(D17*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A17,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A17,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A17,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J17" s="13" t="str">
@@ -3942,7 +4058,7 @@
         <v/>
       </c>
       <c r="I18" s="13" t="str">
-        <f aca="false">IF(OR(A18="",D18=""),"",ROUND(D18*INDEX(Programmes!$L$2:$L$8,MATCH(A18,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A18="",D18=""),"",IFERROR(ROUND(D18*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A18,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A18,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A18,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J18" s="13" t="str">
@@ -3963,7 +4079,7 @@
         <v/>
       </c>
       <c r="I19" s="13" t="str">
-        <f aca="false">IF(OR(A19="",D19=""),"",ROUND(D19*INDEX(Programmes!$L$2:$L$8,MATCH(A19,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A19="",D19=""),"",IFERROR(ROUND(D19*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A19,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A19,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A19,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J19" s="13" t="str">
@@ -3984,7 +4100,7 @@
         <v/>
       </c>
       <c r="I20" s="13" t="str">
-        <f aca="false">IF(OR(A20="",D20=""),"",ROUND(D20*INDEX(Programmes!$L$2:$L$8,MATCH(A20,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A20="",D20=""),"",IFERROR(ROUND(D20*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A20,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A20,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A20,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J20" s="13" t="str">
@@ -4005,7 +4121,7 @@
         <v/>
       </c>
       <c r="I21" s="13" t="str">
-        <f aca="false">IF(OR(A21="",D21=""),"",ROUND(D21*INDEX(Programmes!$L$2:$L$8,MATCH(A21,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A21="",D21=""),"",IFERROR(ROUND(D21*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A21,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A21,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A21,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J21" s="13" t="str">
@@ -4026,7 +4142,7 @@
         <v/>
       </c>
       <c r="I22" s="13" t="str">
-        <f aca="false">IF(OR(A22="",D22=""),"",ROUND(D22*INDEX(Programmes!$L$2:$L$8,MATCH(A22,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A22="",D22=""),"",IFERROR(ROUND(D22*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A22,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A22,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A22,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J22" s="13" t="str">
@@ -4047,7 +4163,7 @@
         <v/>
       </c>
       <c r="I23" s="13" t="str">
-        <f aca="false">IF(OR(A23="",D23=""),"",ROUND(D23*INDEX(Programmes!$L$2:$L$8,MATCH(A23,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A23="",D23=""),"",IFERROR(ROUND(D23*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A23,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A23,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A23,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J23" s="13" t="str">
@@ -4068,7 +4184,7 @@
         <v/>
       </c>
       <c r="I24" s="13" t="str">
-        <f aca="false">IF(OR(A24="",D24=""),"",ROUND(D24*INDEX(Programmes!$L$2:$L$8,MATCH(A24,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A24="",D24=""),"",IFERROR(ROUND(D24*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A24,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A24,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A24,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J24" s="13" t="str">
@@ -4089,7 +4205,7 @@
         <v/>
       </c>
       <c r="I25" s="13" t="str">
-        <f aca="false">IF(OR(A25="",D25=""),"",ROUND(D25*INDEX(Programmes!$L$2:$L$8,MATCH(A25,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A25="",D25=""),"",IFERROR(ROUND(D25*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A25,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A25,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A25,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J25" s="13" t="str">
@@ -4110,7 +4226,7 @@
         <v/>
       </c>
       <c r="I26" s="13" t="str">
-        <f aca="false">IF(OR(A26="",D26=""),"",ROUND(D26*INDEX(Programmes!$L$2:$L$8,MATCH(A26,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A26="",D26=""),"",IFERROR(ROUND(D26*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A26,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A26,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A26,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J26" s="13" t="str">
@@ -4131,7 +4247,7 @@
         <v/>
       </c>
       <c r="I27" s="13" t="str">
-        <f aca="false">IF(OR(A27="",D27=""),"",ROUND(D27*INDEX(Programmes!$L$2:$L$8,MATCH(A27,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A27="",D27=""),"",IFERROR(ROUND(D27*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A27,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A27,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A27,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J27" s="13" t="str">
@@ -4152,7 +4268,7 @@
         <v/>
       </c>
       <c r="I28" s="13" t="str">
-        <f aca="false">IF(OR(A28="",D28=""),"",ROUND(D28*INDEX(Programmes!$L$2:$L$8,MATCH(A28,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A28="",D28=""),"",IFERROR(ROUND(D28*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A28,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A28,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A28,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J28" s="13" t="str">
@@ -4173,7 +4289,7 @@
         <v/>
       </c>
       <c r="I29" s="13" t="str">
-        <f aca="false">IF(OR(A29="",D29=""),"",ROUND(D29*INDEX(Programmes!$L$2:$L$8,MATCH(A29,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A29="",D29=""),"",IFERROR(ROUND(D29*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A29,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A29,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A29,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J29" s="13" t="str">
@@ -4194,7 +4310,7 @@
         <v/>
       </c>
       <c r="I30" s="13" t="str">
-        <f aca="false">IF(OR(A30="",D30=""),"",ROUND(D30*INDEX(Programmes!$L$2:$L$8,MATCH(A30,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A30="",D30=""),"",IFERROR(ROUND(D30*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A30,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A30,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A30,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J30" s="13" t="str">
@@ -4215,7 +4331,7 @@
         <v/>
       </c>
       <c r="I31" s="13" t="str">
-        <f aca="false">IF(OR(A31="",D31=""),"",ROUND(D31*INDEX(Programmes!$L$2:$L$8,MATCH(A31,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A31="",D31=""),"",IFERROR(ROUND(D31*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A31,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A31,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A31,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J31" s="13" t="str">
@@ -4236,7 +4352,7 @@
         <v/>
       </c>
       <c r="I32" s="13" t="str">
-        <f aca="false">IF(OR(A32="",D32=""),"",ROUND(D32*INDEX(Programmes!$L$2:$L$8,MATCH(A32,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A32="",D32=""),"",IFERROR(ROUND(D32*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A32,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A32,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A32,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J32" s="13" t="str">
@@ -4257,7 +4373,7 @@
         <v/>
       </c>
       <c r="I33" s="13" t="str">
-        <f aca="false">IF(OR(A33="",D33=""),"",ROUND(D33*INDEX(Programmes!$L$2:$L$8,MATCH(A33,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A33="",D33=""),"",IFERROR(ROUND(D33*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A33,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A33,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A33,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J33" s="13" t="str">
@@ -4278,7 +4394,7 @@
         <v/>
       </c>
       <c r="I34" s="13" t="str">
-        <f aca="false">IF(OR(A34="",D34=""),"",ROUND(D34*INDEX(Programmes!$L$2:$L$8,MATCH(A34,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A34="",D34=""),"",IFERROR(ROUND(D34*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A34,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A34,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A34,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J34" s="13" t="str">
@@ -4299,7 +4415,7 @@
         <v/>
       </c>
       <c r="I35" s="13" t="str">
-        <f aca="false">IF(OR(A35="",D35=""),"",ROUND(D35*INDEX(Programmes!$L$2:$L$8,MATCH(A35,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A35="",D35=""),"",IFERROR(ROUND(D35*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A35,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A35,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A35,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J35" s="13" t="str">
@@ -4320,7 +4436,7 @@
         <v/>
       </c>
       <c r="I36" s="13" t="str">
-        <f aca="false">IF(OR(A36="",D36=""),"",ROUND(D36*INDEX(Programmes!$L$2:$L$8,MATCH(A36,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A36="",D36=""),"",IFERROR(ROUND(D36*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A36,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A36,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A36,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J36" s="13" t="str">
@@ -4341,7 +4457,7 @@
         <v/>
       </c>
       <c r="I37" s="13" t="str">
-        <f aca="false">IF(OR(A37="",D37=""),"",ROUND(D37*INDEX(Programmes!$L$2:$L$8,MATCH(A37,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A37="",D37=""),"",IFERROR(ROUND(D37*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A37,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A37,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A37,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J37" s="13" t="str">
@@ -4362,7 +4478,7 @@
         <v/>
       </c>
       <c r="I38" s="13" t="str">
-        <f aca="false">IF(OR(A38="",D38=""),"",ROUND(D38*INDEX(Programmes!$L$2:$L$8,MATCH(A38,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A38="",D38=""),"",IFERROR(ROUND(D38*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A38,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A38,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A38,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J38" s="13" t="str">
@@ -4383,7 +4499,7 @@
         <v/>
       </c>
       <c r="I39" s="13" t="str">
-        <f aca="false">IF(OR(A39="",D39=""),"",ROUND(D39*INDEX(Programmes!$L$2:$L$8,MATCH(A39,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A39="",D39=""),"",IFERROR(ROUND(D39*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A39,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A39,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A39,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J39" s="13" t="str">
@@ -4404,7 +4520,7 @@
         <v/>
       </c>
       <c r="I40" s="13" t="str">
-        <f aca="false">IF(OR(A40="",D40=""),"",ROUND(D40*INDEX(Programmes!$L$2:$L$8,MATCH(A40,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A40="",D40=""),"",IFERROR(ROUND(D40*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A40,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A40,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A40,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J40" s="13" t="str">
@@ -4425,7 +4541,7 @@
         <v/>
       </c>
       <c r="I41" s="13" t="str">
-        <f aca="false">IF(OR(A41="",D41=""),"",ROUND(D41*INDEX(Programmes!$L$2:$L$8,MATCH(A41,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A41="",D41=""),"",IFERROR(ROUND(D41*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A41,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A41,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A41,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J41" s="13" t="str">
@@ -4446,7 +4562,7 @@
         <v/>
       </c>
       <c r="I42" s="13" t="str">
-        <f aca="false">IF(OR(A42="",D42=""),"",ROUND(D42*INDEX(Programmes!$L$2:$L$8,MATCH(A42,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A42="",D42=""),"",IFERROR(ROUND(D42*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A42,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A42,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A42,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J42" s="13" t="str">
@@ -4467,7 +4583,7 @@
         <v/>
       </c>
       <c r="I43" s="13" t="str">
-        <f aca="false">IF(OR(A43="",D43=""),"",ROUND(D43*INDEX(Programmes!$L$2:$L$8,MATCH(A43,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A43="",D43=""),"",IFERROR(ROUND(D43*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A43,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A43,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A43,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J43" s="13" t="str">
@@ -4488,7 +4604,7 @@
         <v/>
       </c>
       <c r="I44" s="13" t="str">
-        <f aca="false">IF(OR(A44="",D44=""),"",ROUND(D44*INDEX(Programmes!$L$2:$L$8,MATCH(A44,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A44="",D44=""),"",IFERROR(ROUND(D44*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A44,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A44,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A44,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J44" s="13" t="str">
@@ -4509,7 +4625,7 @@
         <v/>
       </c>
       <c r="I45" s="13" t="str">
-        <f aca="false">IF(OR(A45="",D45=""),"",ROUND(D45*INDEX(Programmes!$L$2:$L$8,MATCH(A45,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A45="",D45=""),"",IFERROR(ROUND(D45*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A45,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A45,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A45,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J45" s="13" t="str">
@@ -4530,7 +4646,7 @@
         <v/>
       </c>
       <c r="I46" s="13" t="str">
-        <f aca="false">IF(OR(A46="",D46=""),"",ROUND(D46*INDEX(Programmes!$L$2:$L$8,MATCH(A46,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A46="",D46=""),"",IFERROR(ROUND(D46*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A46,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A46,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A46,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J46" s="13" t="str">
@@ -4551,7 +4667,7 @@
         <v/>
       </c>
       <c r="I47" s="13" t="str">
-        <f aca="false">IF(OR(A47="",D47=""),"",ROUND(D47*INDEX(Programmes!$L$2:$L$8,MATCH(A47,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A47="",D47=""),"",IFERROR(ROUND(D47*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A47,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A47,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A47,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J47" s="13" t="str">
@@ -4572,7 +4688,7 @@
         <v/>
       </c>
       <c r="I48" s="13" t="str">
-        <f aca="false">IF(OR(A48="",D48=""),"",ROUND(D48*INDEX(Programmes!$L$2:$L$8,MATCH(A48,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A48="",D48=""),"",IFERROR(ROUND(D48*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A48,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A48,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A48,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J48" s="13" t="str">
@@ -4593,7 +4709,7 @@
         <v/>
       </c>
       <c r="I49" s="13" t="str">
-        <f aca="false">IF(OR(A49="",D49=""),"",ROUND(D49*INDEX(Programmes!$L$2:$L$8,MATCH(A49,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A49="",D49=""),"",IFERROR(ROUND(D49*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A49,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A49,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A49,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J49" s="13" t="str">
@@ -4614,7 +4730,7 @@
         <v/>
       </c>
       <c r="I50" s="13" t="str">
-        <f aca="false">IF(OR(A50="",D50=""),"",ROUND(D50*INDEX(Programmes!$L$2:$L$8,MATCH(A50,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A50="",D50=""),"",IFERROR(ROUND(D50*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A50,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A50,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A50,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J50" s="13" t="str">
@@ -4635,7 +4751,7 @@
         <v/>
       </c>
       <c r="I51" s="13" t="str">
-        <f aca="false">IF(OR(A51="",D51=""),"",ROUND(D51*INDEX(Programmes!$L$2:$L$8,MATCH(A51,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A51="",D51=""),"",IFERROR(ROUND(D51*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A51,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A51,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A51,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J51" s="13" t="str">
@@ -4656,7 +4772,7 @@
         <v/>
       </c>
       <c r="I52" s="13" t="str">
-        <f aca="false">IF(OR(A52="",D52=""),"",ROUND(D52*INDEX(Programmes!$L$2:$L$8,MATCH(A52,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A52="",D52=""),"",IFERROR(ROUND(D52*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A52,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A52,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A52,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J52" s="13" t="str">
@@ -4677,7 +4793,7 @@
         <v/>
       </c>
       <c r="I53" s="13" t="str">
-        <f aca="false">IF(OR(A53="",D53=""),"",ROUND(D53*INDEX(Programmes!$L$2:$L$8,MATCH(A53,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A53="",D53=""),"",IFERROR(ROUND(D53*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A53,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A53,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A53,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J53" s="13" t="str">
@@ -4698,7 +4814,7 @@
         <v/>
       </c>
       <c r="I54" s="13" t="str">
-        <f aca="false">IF(OR(A54="",D54=""),"",ROUND(D54*INDEX(Programmes!$L$2:$L$8,MATCH(A54,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A54="",D54=""),"",IFERROR(ROUND(D54*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A54,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A54,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A54,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J54" s="13" t="str">
@@ -4719,7 +4835,7 @@
         <v/>
       </c>
       <c r="I55" s="13" t="str">
-        <f aca="false">IF(OR(A55="",D55=""),"",ROUND(D55*INDEX(Programmes!$L$2:$L$8,MATCH(A55,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A55="",D55=""),"",IFERROR(ROUND(D55*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A55,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A55,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A55,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J55" s="13" t="str">
@@ -4740,7 +4856,7 @@
         <v/>
       </c>
       <c r="I56" s="13" t="str">
-        <f aca="false">IF(OR(A56="",D56=""),"",ROUND(D56*INDEX(Programmes!$L$2:$L$8,MATCH(A56,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A56="",D56=""),"",IFERROR(ROUND(D56*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A56,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A56,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A56,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J56" s="13" t="str">
@@ -4761,7 +4877,7 @@
         <v/>
       </c>
       <c r="I57" s="13" t="str">
-        <f aca="false">IF(OR(A57="",D57=""),"",ROUND(D57*INDEX(Programmes!$L$2:$L$8,MATCH(A57,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A57="",D57=""),"",IFERROR(ROUND(D57*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A57,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A57,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A57,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J57" s="13" t="str">
@@ -4782,7 +4898,7 @@
         <v/>
       </c>
       <c r="I58" s="13" t="str">
-        <f aca="false">IF(OR(A58="",D58=""),"",ROUND(D58*INDEX(Programmes!$L$2:$L$8,MATCH(A58,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A58="",D58=""),"",IFERROR(ROUND(D58*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A58,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A58,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A58,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J58" s="13" t="str">
@@ -4803,7 +4919,7 @@
         <v/>
       </c>
       <c r="I59" s="13" t="str">
-        <f aca="false">IF(OR(A59="",D59=""),"",ROUND(D59*INDEX(Programmes!$L$2:$L$8,MATCH(A59,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A59="",D59=""),"",IFERROR(ROUND(D59*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A59,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A59,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A59,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J59" s="13" t="str">
@@ -4824,7 +4940,7 @@
         <v/>
       </c>
       <c r="I60" s="13" t="str">
-        <f aca="false">IF(OR(A60="",D60=""),"",ROUND(D60*INDEX(Programmes!$L$2:$L$8,MATCH(A60,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A60="",D60=""),"",IFERROR(ROUND(D60*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A60,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A60,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A60,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J60" s="13" t="str">
@@ -4845,7 +4961,7 @@
         <v/>
       </c>
       <c r="I61" s="13" t="str">
-        <f aca="false">IF(OR(A61="",D61=""),"",ROUND(D61*INDEX(Programmes!$L$2:$L$8,MATCH(A61,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A61="",D61=""),"",IFERROR(ROUND(D61*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A61,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A61,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A61,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J61" s="13" t="str">
@@ -4866,7 +4982,7 @@
         <v/>
       </c>
       <c r="I62" s="13" t="str">
-        <f aca="false">IF(OR(A62="",D62=""),"",ROUND(D62*INDEX(Programmes!$L$2:$L$8,MATCH(A62,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A62="",D62=""),"",IFERROR(ROUND(D62*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A62,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A62,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A62,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J62" s="13" t="str">
@@ -4887,7 +5003,7 @@
         <v/>
       </c>
       <c r="I63" s="13" t="str">
-        <f aca="false">IF(OR(A63="",D63=""),"",ROUND(D63*INDEX(Programmes!$L$2:$L$8,MATCH(A63,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A63="",D63=""),"",IFERROR(ROUND(D63*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A63,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A63,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A63,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J63" s="13" t="str">
@@ -4908,7 +5024,7 @@
         <v/>
       </c>
       <c r="I64" s="13" t="str">
-        <f aca="false">IF(OR(A64="",D64=""),"",ROUND(D64*INDEX(Programmes!$L$2:$L$8,MATCH(A64,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A64="",D64=""),"",IFERROR(ROUND(D64*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A64,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A64,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A64,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J64" s="13" t="str">
@@ -4929,7 +5045,7 @@
         <v/>
       </c>
       <c r="I65" s="13" t="str">
-        <f aca="false">IF(OR(A65="",D65=""),"",ROUND(D65*INDEX(Programmes!$L$2:$L$8,MATCH(A65,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A65="",D65=""),"",IFERROR(ROUND(D65*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A65,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A65,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A65,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J65" s="13" t="str">
@@ -4950,7 +5066,7 @@
         <v/>
       </c>
       <c r="I66" s="13" t="str">
-        <f aca="false">IF(OR(A66="",D66=""),"",ROUND(D66*INDEX(Programmes!$L$2:$L$8,MATCH(A66,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A66="",D66=""),"",IFERROR(ROUND(D66*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A66,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A66,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A66,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J66" s="13" t="str">
@@ -4971,7 +5087,7 @@
         <v/>
       </c>
       <c r="I67" s="13" t="str">
-        <f aca="false">IF(OR(A67="",D67=""),"",ROUND(D67*INDEX(Programmes!$L$2:$L$8,MATCH(A67,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A67="",D67=""),"",IFERROR(ROUND(D67*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A67,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A67,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A67,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J67" s="13" t="str">
@@ -4992,7 +5108,7 @@
         <v/>
       </c>
       <c r="I68" s="13" t="str">
-        <f aca="false">IF(OR(A68="",D68=""),"",ROUND(D68*INDEX(Programmes!$L$2:$L$8,MATCH(A68,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A68="",D68=""),"",IFERROR(ROUND(D68*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A68,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A68,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A68,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J68" s="13" t="str">
@@ -5013,7 +5129,7 @@
         <v/>
       </c>
       <c r="I69" s="13" t="str">
-        <f aca="false">IF(OR(A69="",D69=""),"",ROUND(D69*INDEX(Programmes!$L$2:$L$8,MATCH(A69,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A69="",D69=""),"",IFERROR(ROUND(D69*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A69,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A69,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A69,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J69" s="13" t="str">
@@ -5034,7 +5150,7 @@
         <v/>
       </c>
       <c r="I70" s="13" t="str">
-        <f aca="false">IF(OR(A70="",D70=""),"",ROUND(D70*INDEX(Programmes!$L$2:$L$8,MATCH(A70,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A70="",D70=""),"",IFERROR(ROUND(D70*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A70,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A70,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A70,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J70" s="13" t="str">
@@ -5055,7 +5171,7 @@
         <v/>
       </c>
       <c r="I71" s="13" t="str">
-        <f aca="false">IF(OR(A71="",D71=""),"",ROUND(D71*INDEX(Programmes!$L$2:$L$8,MATCH(A71,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A71="",D71=""),"",IFERROR(ROUND(D71*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A71,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A71,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A71,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J71" s="13" t="str">
@@ -5076,7 +5192,7 @@
         <v/>
       </c>
       <c r="I72" s="13" t="str">
-        <f aca="false">IF(OR(A72="",D72=""),"",ROUND(D72*INDEX(Programmes!$L$2:$L$8,MATCH(A72,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A72="",D72=""),"",IFERROR(ROUND(D72*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A72,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A72,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A72,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J72" s="13" t="str">
@@ -5097,7 +5213,7 @@
         <v/>
       </c>
       <c r="I73" s="13" t="str">
-        <f aca="false">IF(OR(A73="",D73=""),"",ROUND(D73*INDEX(Programmes!$L$2:$L$8,MATCH(A73,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A73="",D73=""),"",IFERROR(ROUND(D73*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A73,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A73,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A73,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J73" s="13" t="str">
@@ -5118,7 +5234,7 @@
         <v/>
       </c>
       <c r="I74" s="13" t="str">
-        <f aca="false">IF(OR(A74="",D74=""),"",ROUND(D74*INDEX(Programmes!$L$2:$L$8,MATCH(A74,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A74="",D74=""),"",IFERROR(ROUND(D74*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A74,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A74,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A74,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J74" s="13" t="str">
@@ -5139,7 +5255,7 @@
         <v/>
       </c>
       <c r="I75" s="13" t="str">
-        <f aca="false">IF(OR(A75="",D75=""),"",ROUND(D75*INDEX(Programmes!$L$2:$L$8,MATCH(A75,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A75="",D75=""),"",IFERROR(ROUND(D75*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A75,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A75,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A75,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J75" s="13" t="str">
@@ -5160,7 +5276,7 @@
         <v/>
       </c>
       <c r="I76" s="13" t="str">
-        <f aca="false">IF(OR(A76="",D76=""),"",ROUND(D76*INDEX(Programmes!$L$2:$L$8,MATCH(A76,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A76="",D76=""),"",IFERROR(ROUND(D76*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A76,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A76,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A76,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J76" s="13" t="str">
@@ -5181,7 +5297,7 @@
         <v/>
       </c>
       <c r="I77" s="13" t="str">
-        <f aca="false">IF(OR(A77="",D77=""),"",ROUND(D77*INDEX(Programmes!$L$2:$L$8,MATCH(A77,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A77="",D77=""),"",IFERROR(ROUND(D77*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A77,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A77,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A77,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J77" s="13" t="str">
@@ -5202,7 +5318,7 @@
         <v/>
       </c>
       <c r="I78" s="13" t="str">
-        <f aca="false">IF(OR(A78="",D78=""),"",ROUND(D78*INDEX(Programmes!$L$2:$L$8,MATCH(A78,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A78="",D78=""),"",IFERROR(ROUND(D78*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A78,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A78,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A78,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J78" s="13" t="str">
@@ -5223,7 +5339,7 @@
         <v/>
       </c>
       <c r="I79" s="13" t="str">
-        <f aca="false">IF(OR(A79="",D79=""),"",ROUND(D79*INDEX(Programmes!$L$2:$L$8,MATCH(A79,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A79="",D79=""),"",IFERROR(ROUND(D79*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A79,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A79,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A79,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J79" s="13" t="str">
@@ -5244,7 +5360,7 @@
         <v/>
       </c>
       <c r="I80" s="13" t="str">
-        <f aca="false">IF(OR(A80="",D80=""),"",ROUND(D80*INDEX(Programmes!$L$2:$L$8,MATCH(A80,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A80="",D80=""),"",IFERROR(ROUND(D80*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A80,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A80,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A80,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J80" s="13" t="str">
@@ -5265,7 +5381,7 @@
         <v/>
       </c>
       <c r="I81" s="13" t="str">
-        <f aca="false">IF(OR(A81="",D81=""),"",ROUND(D81*INDEX(Programmes!$L$2:$L$8,MATCH(A81,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A81="",D81=""),"",IFERROR(ROUND(D81*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A81,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A81,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A81,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J81" s="13" t="str">
@@ -5286,7 +5402,7 @@
         <v/>
       </c>
       <c r="I82" s="13" t="str">
-        <f aca="false">IF(OR(A82="",D82=""),"",ROUND(D82*INDEX(Programmes!$L$2:$L$8,MATCH(A82,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A82="",D82=""),"",IFERROR(ROUND(D82*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A82,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A82,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A82,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J82" s="13" t="str">
@@ -5307,7 +5423,7 @@
         <v/>
       </c>
       <c r="I83" s="13" t="str">
-        <f aca="false">IF(OR(A83="",D83=""),"",ROUND(D83*INDEX(Programmes!$L$2:$L$8,MATCH(A83,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A83="",D83=""),"",IFERROR(ROUND(D83*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A83,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A83,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A83,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J83" s="13" t="str">
@@ -5328,7 +5444,7 @@
         <v/>
       </c>
       <c r="I84" s="13" t="str">
-        <f aca="false">IF(OR(A84="",D84=""),"",ROUND(D84*INDEX(Programmes!$L$2:$L$8,MATCH(A84,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A84="",D84=""),"",IFERROR(ROUND(D84*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A84,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A84,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A84,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J84" s="13" t="str">
@@ -5349,7 +5465,7 @@
         <v/>
       </c>
       <c r="I85" s="13" t="str">
-        <f aca="false">IF(OR(A85="",D85=""),"",ROUND(D85*INDEX(Programmes!$L$2:$L$8,MATCH(A85,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A85="",D85=""),"",IFERROR(ROUND(D85*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A85,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A85,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A85,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J85" s="13" t="str">
@@ -5370,7 +5486,7 @@
         <v/>
       </c>
       <c r="I86" s="13" t="str">
-        <f aca="false">IF(OR(A86="",D86=""),"",ROUND(D86*INDEX(Programmes!$L$2:$L$8,MATCH(A86,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A86="",D86=""),"",IFERROR(ROUND(D86*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A86,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A86,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A86,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J86" s="13" t="str">
@@ -5391,7 +5507,7 @@
         <v/>
       </c>
       <c r="I87" s="13" t="str">
-        <f aca="false">IF(OR(A87="",D87=""),"",ROUND(D87*INDEX(Programmes!$L$2:$L$8,MATCH(A87,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A87="",D87=""),"",IFERROR(ROUND(D87*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A87,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A87,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A87,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J87" s="13" t="str">
@@ -5412,7 +5528,7 @@
         <v/>
       </c>
       <c r="I88" s="13" t="str">
-        <f aca="false">IF(OR(A88="",D88=""),"",ROUND(D88*INDEX(Programmes!$L$2:$L$8,MATCH(A88,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A88="",D88=""),"",IFERROR(ROUND(D88*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A88,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A88,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A88,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J88" s="13" t="str">
@@ -5433,7 +5549,7 @@
         <v/>
       </c>
       <c r="I89" s="13" t="str">
-        <f aca="false">IF(OR(A89="",D89=""),"",ROUND(D89*INDEX(Programmes!$L$2:$L$8,MATCH(A89,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A89="",D89=""),"",IFERROR(ROUND(D89*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A89,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A89,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A89,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J89" s="13" t="str">
@@ -5454,7 +5570,7 @@
         <v/>
       </c>
       <c r="I90" s="13" t="str">
-        <f aca="false">IF(OR(A90="",D90=""),"",ROUND(D90*INDEX(Programmes!$L$2:$L$8,MATCH(A90,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A90="",D90=""),"",IFERROR(ROUND(D90*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A90,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A90,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A90,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J90" s="13" t="str">
@@ -5475,7 +5591,7 @@
         <v/>
       </c>
       <c r="I91" s="13" t="str">
-        <f aca="false">IF(OR(A91="",D91=""),"",ROUND(D91*INDEX(Programmes!$L$2:$L$8,MATCH(A91,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A91="",D91=""),"",IFERROR(ROUND(D91*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A91,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A91,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A91,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J91" s="13" t="str">
@@ -5496,7 +5612,7 @@
         <v/>
       </c>
       <c r="I92" s="13" t="str">
-        <f aca="false">IF(OR(A92="",D92=""),"",ROUND(D92*INDEX(Programmes!$L$2:$L$8,MATCH(A92,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A92="",D92=""),"",IFERROR(ROUND(D92*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A92,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A92,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A92,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J92" s="13" t="str">
@@ -5517,7 +5633,7 @@
         <v/>
       </c>
       <c r="I93" s="13" t="str">
-        <f aca="false">IF(OR(A93="",D93=""),"",ROUND(D93*INDEX(Programmes!$L$2:$L$8,MATCH(A93,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A93="",D93=""),"",IFERROR(ROUND(D93*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A93,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A93,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A93,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J93" s="13" t="str">
@@ -5538,7 +5654,7 @@
         <v/>
       </c>
       <c r="I94" s="13" t="str">
-        <f aca="false">IF(OR(A94="",D94=""),"",ROUND(D94*INDEX(Programmes!$L$2:$L$8,MATCH(A94,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A94="",D94=""),"",IFERROR(ROUND(D94*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A94,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A94,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A94,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J94" s="13" t="str">
@@ -5559,7 +5675,7 @@
         <v/>
       </c>
       <c r="I95" s="13" t="str">
-        <f aca="false">IF(OR(A95="",D95=""),"",ROUND(D95*INDEX(Programmes!$L$2:$L$8,MATCH(A95,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A95="",D95=""),"",IFERROR(ROUND(D95*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A95,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A95,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A95,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J95" s="13" t="str">
@@ -5580,7 +5696,7 @@
         <v/>
       </c>
       <c r="I96" s="13" t="str">
-        <f aca="false">IF(OR(A96="",D96=""),"",ROUND(D96*INDEX(Programmes!$L$2:$L$8,MATCH(A96,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A96="",D96=""),"",IFERROR(ROUND(D96*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A96,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A96,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A96,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J96" s="13" t="str">
@@ -5601,7 +5717,7 @@
         <v/>
       </c>
       <c r="I97" s="13" t="str">
-        <f aca="false">IF(OR(A97="",D97=""),"",ROUND(D97*INDEX(Programmes!$L$2:$L$8,MATCH(A97,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A97="",D97=""),"",IFERROR(ROUND(D97*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A97,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A97,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A97,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J97" s="13" t="str">
@@ -5622,7 +5738,7 @@
         <v/>
       </c>
       <c r="I98" s="13" t="str">
-        <f aca="false">IF(OR(A98="",D98=""),"",ROUND(D98*INDEX(Programmes!$L$2:$L$8,MATCH(A98,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A98="",D98=""),"",IFERROR(ROUND(D98*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A98,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A98,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A98,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J98" s="13" t="str">
@@ -5643,7 +5759,7 @@
         <v/>
       </c>
       <c r="I99" s="13" t="str">
-        <f aca="false">IF(OR(A99="",D99=""),"",ROUND(D99*INDEX(Programmes!$L$2:$L$8,MATCH(A99,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A99="",D99=""),"",IFERROR(ROUND(D99*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A99,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A99,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A99,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J99" s="13" t="str">
@@ -5664,7 +5780,7 @@
         <v/>
       </c>
       <c r="I100" s="13" t="str">
-        <f aca="false">IF(OR(A100="",D100=""),"",ROUND(D100*INDEX(Programmes!$L$2:$L$8,MATCH(A100,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A100="",D100=""),"",IFERROR(ROUND(D100*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A100,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A100,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A100,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J100" s="13" t="str">
@@ -5685,7 +5801,7 @@
         <v/>
       </c>
       <c r="I101" s="13" t="str">
-        <f aca="false">IF(OR(A101="",D101=""),"",ROUND(D101*INDEX(Programmes!$L$2:$L$8,MATCH(A101,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A101="",D101=""),"",IFERROR(ROUND(D101*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A101,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A101,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A101,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J101" s="13" t="str">
@@ -5706,7 +5822,7 @@
         <v/>
       </c>
       <c r="I102" s="13" t="str">
-        <f aca="false">IF(OR(A102="",D102=""),"",ROUND(D102*INDEX(Programmes!$L$2:$L$8,MATCH(A102,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A102="",D102=""),"",IFERROR(ROUND(D102*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A102,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A102,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A102,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J102" s="13" t="str">
@@ -5727,7 +5843,7 @@
         <v/>
       </c>
       <c r="I103" s="13" t="str">
-        <f aca="false">IF(OR(A103="",D103=""),"",ROUND(D103*INDEX(Programmes!$L$2:$L$8,MATCH(A103,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A103="",D103=""),"",IFERROR(ROUND(D103*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A103,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A103,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A103,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J103" s="13" t="str">
@@ -5748,7 +5864,7 @@
         <v/>
       </c>
       <c r="I104" s="13" t="str">
-        <f aca="false">IF(OR(A104="",D104=""),"",ROUND(D104*INDEX(Programmes!$L$2:$L$8,MATCH(A104,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A104="",D104=""),"",IFERROR(ROUND(D104*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A104,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A104,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A104,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J104" s="13" t="str">
@@ -5769,7 +5885,7 @@
         <v/>
       </c>
       <c r="I105" s="13" t="str">
-        <f aca="false">IF(OR(A105="",D105=""),"",ROUND(D105*INDEX(Programmes!$L$2:$L$8,MATCH(A105,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A105="",D105=""),"",IFERROR(ROUND(D105*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A105,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A105,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A105,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J105" s="13" t="str">
@@ -5790,7 +5906,7 @@
         <v/>
       </c>
       <c r="I106" s="13" t="str">
-        <f aca="false">IF(OR(A106="",D106=""),"",ROUND(D106*INDEX(Programmes!$L$2:$L$8,MATCH(A106,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A106="",D106=""),"",IFERROR(ROUND(D106*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A106,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A106,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A106,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J106" s="13" t="str">
@@ -5811,7 +5927,7 @@
         <v/>
       </c>
       <c r="I107" s="13" t="str">
-        <f aca="false">IF(OR(A107="",D107=""),"",ROUND(D107*INDEX(Programmes!$L$2:$L$8,MATCH(A107,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A107="",D107=""),"",IFERROR(ROUND(D107*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A107,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A107,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A107,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J107" s="13" t="str">
@@ -5832,7 +5948,7 @@
         <v/>
       </c>
       <c r="I108" s="13" t="str">
-        <f aca="false">IF(OR(A108="",D108=""),"",ROUND(D108*INDEX(Programmes!$L$2:$L$8,MATCH(A108,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A108="",D108=""),"",IFERROR(ROUND(D108*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A108,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A108,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A108,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J108" s="13" t="str">
@@ -5853,7 +5969,7 @@
         <v/>
       </c>
       <c r="I109" s="13" t="str">
-        <f aca="false">IF(OR(A109="",D109=""),"",ROUND(D109*INDEX(Programmes!$L$2:$L$8,MATCH(A109,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A109="",D109=""),"",IFERROR(ROUND(D109*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A109,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A109,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A109,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J109" s="13" t="str">
@@ -5874,7 +5990,7 @@
         <v/>
       </c>
       <c r="I110" s="13" t="str">
-        <f aca="false">IF(OR(A110="",D110=""),"",ROUND(D110*INDEX(Programmes!$L$2:$L$8,MATCH(A110,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A110="",D110=""),"",IFERROR(ROUND(D110*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A110,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A110,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A110,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J110" s="13" t="str">
@@ -5895,7 +6011,7 @@
         <v/>
       </c>
       <c r="I111" s="13" t="str">
-        <f aca="false">IF(OR(A111="",D111=""),"",ROUND(D111*INDEX(Programmes!$L$2:$L$8,MATCH(A111,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A111="",D111=""),"",IFERROR(ROUND(D111*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A111,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A111,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A111,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J111" s="13" t="str">
@@ -5916,7 +6032,7 @@
         <v/>
       </c>
       <c r="I112" s="13" t="str">
-        <f aca="false">IF(OR(A112="",D112=""),"",ROUND(D112*INDEX(Programmes!$L$2:$L$8,MATCH(A112,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A112="",D112=""),"",IFERROR(ROUND(D112*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A112,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A112,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A112,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J112" s="13" t="str">
@@ -5937,7 +6053,7 @@
         <v/>
       </c>
       <c r="I113" s="13" t="str">
-        <f aca="false">IF(OR(A113="",D113=""),"",ROUND(D113*INDEX(Programmes!$L$2:$L$8,MATCH(A113,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A113="",D113=""),"",IFERROR(ROUND(D113*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A113,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A113,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A113,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J113" s="13" t="str">
@@ -5958,7 +6074,7 @@
         <v/>
       </c>
       <c r="I114" s="13" t="str">
-        <f aca="false">IF(OR(A114="",D114=""),"",ROUND(D114*INDEX(Programmes!$L$2:$L$8,MATCH(A114,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A114="",D114=""),"",IFERROR(ROUND(D114*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A114,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A114,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A114,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J114" s="13" t="str">
@@ -5979,7 +6095,7 @@
         <v/>
       </c>
       <c r="I115" s="13" t="str">
-        <f aca="false">IF(OR(A115="",D115=""),"",ROUND(D115*INDEX(Programmes!$L$2:$L$8,MATCH(A115,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A115="",D115=""),"",IFERROR(ROUND(D115*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A115,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A115,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A115,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J115" s="13" t="str">
@@ -6000,7 +6116,7 @@
         <v/>
       </c>
       <c r="I116" s="13" t="str">
-        <f aca="false">IF(OR(A116="",D116=""),"",ROUND(D116*INDEX(Programmes!$L$2:$L$8,MATCH(A116,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A116="",D116=""),"",IFERROR(ROUND(D116*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A116,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A116,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A116,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J116" s="13" t="str">
@@ -6021,7 +6137,7 @@
         <v/>
       </c>
       <c r="I117" s="13" t="str">
-        <f aca="false">IF(OR(A117="",D117=""),"",ROUND(D117*INDEX(Programmes!$L$2:$L$8,MATCH(A117,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A117="",D117=""),"",IFERROR(ROUND(D117*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A117,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A117,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A117,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J117" s="13" t="str">
@@ -6042,7 +6158,7 @@
         <v/>
       </c>
       <c r="I118" s="13" t="str">
-        <f aca="false">IF(OR(A118="",D118=""),"",ROUND(D118*INDEX(Programmes!$L$2:$L$8,MATCH(A118,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A118="",D118=""),"",IFERROR(ROUND(D118*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A118,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A118,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A118,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J118" s="13" t="str">
@@ -6063,7 +6179,7 @@
         <v/>
       </c>
       <c r="I119" s="13" t="str">
-        <f aca="false">IF(OR(A119="",D119=""),"",ROUND(D119*INDEX(Programmes!$L$2:$L$8,MATCH(A119,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A119="",D119=""),"",IFERROR(ROUND(D119*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A119,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A119,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A119,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J119" s="13" t="str">
@@ -6084,7 +6200,7 @@
         <v/>
       </c>
       <c r="I120" s="13" t="str">
-        <f aca="false">IF(OR(A120="",D120=""),"",ROUND(D120*INDEX(Programmes!$L$2:$L$8,MATCH(A120,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A120="",D120=""),"",IFERROR(ROUND(D120*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A120,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A120,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A120,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J120" s="13" t="str">
@@ -6105,7 +6221,7 @@
         <v/>
       </c>
       <c r="I121" s="13" t="str">
-        <f aca="false">IF(OR(A121="",D121=""),"",ROUND(D121*INDEX(Programmes!$L$2:$L$8,MATCH(A121,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A121="",D121=""),"",IFERROR(ROUND(D121*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A121,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A121,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A121,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J121" s="13" t="str">
@@ -6126,7 +6242,7 @@
         <v/>
       </c>
       <c r="I122" s="13" t="str">
-        <f aca="false">IF(OR(A122="",D122=""),"",ROUND(D122*INDEX(Programmes!$L$2:$L$8,MATCH(A122,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A122="",D122=""),"",IFERROR(ROUND(D122*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A122,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A122,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A122,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J122" s="13" t="str">
@@ -6147,7 +6263,7 @@
         <v/>
       </c>
       <c r="I123" s="13" t="str">
-        <f aca="false">IF(OR(A123="",D123=""),"",ROUND(D123*INDEX(Programmes!$L$2:$L$8,MATCH(A123,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A123="",D123=""),"",IFERROR(ROUND(D123*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A123,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A123,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A123,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J123" s="13" t="str">
@@ -6168,7 +6284,7 @@
         <v/>
       </c>
       <c r="I124" s="13" t="str">
-        <f aca="false">IF(OR(A124="",D124=""),"",ROUND(D124*INDEX(Programmes!$L$2:$L$8,MATCH(A124,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A124="",D124=""),"",IFERROR(ROUND(D124*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A124,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A124,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A124,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J124" s="13" t="str">
@@ -6189,7 +6305,7 @@
         <v/>
       </c>
       <c r="I125" s="13" t="str">
-        <f aca="false">IF(OR(A125="",D125=""),"",ROUND(D125*INDEX(Programmes!$L$2:$L$8,MATCH(A125,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A125="",D125=""),"",IFERROR(ROUND(D125*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A125,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A125,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A125,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J125" s="13" t="str">
@@ -6210,7 +6326,7 @@
         <v/>
       </c>
       <c r="I126" s="13" t="str">
-        <f aca="false">IF(OR(A126="",D126=""),"",ROUND(D126*INDEX(Programmes!$L$2:$L$8,MATCH(A126,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A126="",D126=""),"",IFERROR(ROUND(D126*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A126,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A126,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A126,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J126" s="13" t="str">
@@ -6231,7 +6347,7 @@
         <v/>
       </c>
       <c r="I127" s="13" t="str">
-        <f aca="false">IF(OR(A127="",D127=""),"",ROUND(D127*INDEX(Programmes!$L$2:$L$8,MATCH(A127,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A127="",D127=""),"",IFERROR(ROUND(D127*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A127,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A127,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A127,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J127" s="13" t="str">
@@ -6252,7 +6368,7 @@
         <v/>
       </c>
       <c r="I128" s="13" t="str">
-        <f aca="false">IF(OR(A128="",D128=""),"",ROUND(D128*INDEX(Programmes!$L$2:$L$8,MATCH(A128,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A128="",D128=""),"",IFERROR(ROUND(D128*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A128,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A128,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A128,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J128" s="13" t="str">
@@ -6273,7 +6389,7 @@
         <v/>
       </c>
       <c r="I129" s="13" t="str">
-        <f aca="false">IF(OR(A129="",D129=""),"",ROUND(D129*INDEX(Programmes!$L$2:$L$8,MATCH(A129,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A129="",D129=""),"",IFERROR(ROUND(D129*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A129,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A129,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A129,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J129" s="13" t="str">
@@ -6294,7 +6410,7 @@
         <v/>
       </c>
       <c r="I130" s="13" t="str">
-        <f aca="false">IF(OR(A130="",D130=""),"",ROUND(D130*INDEX(Programmes!$L$2:$L$8,MATCH(A130,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A130="",D130=""),"",IFERROR(ROUND(D130*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A130,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A130,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A130,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J130" s="13" t="str">
@@ -6315,7 +6431,7 @@
         <v/>
       </c>
       <c r="I131" s="13" t="str">
-        <f aca="false">IF(OR(A131="",D131=""),"",ROUND(D131*INDEX(Programmes!$L$2:$L$8,MATCH(A131,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A131="",D131=""),"",IFERROR(ROUND(D131*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A131,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A131,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A131,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J131" s="13" t="str">
@@ -6336,7 +6452,7 @@
         <v/>
       </c>
       <c r="I132" s="13" t="str">
-        <f aca="false">IF(OR(A132="",D132=""),"",ROUND(D132*INDEX(Programmes!$L$2:$L$8,MATCH(A132,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A132="",D132=""),"",IFERROR(ROUND(D132*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A132,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A132,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A132,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J132" s="13" t="str">
@@ -6357,7 +6473,7 @@
         <v/>
       </c>
       <c r="I133" s="13" t="str">
-        <f aca="false">IF(OR(A133="",D133=""),"",ROUND(D133*INDEX(Programmes!$L$2:$L$8,MATCH(A133,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A133="",D133=""),"",IFERROR(ROUND(D133*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A133,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A133,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A133,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J133" s="13" t="str">
@@ -6378,7 +6494,7 @@
         <v/>
       </c>
       <c r="I134" s="13" t="str">
-        <f aca="false">IF(OR(A134="",D134=""),"",ROUND(D134*INDEX(Programmes!$L$2:$L$8,MATCH(A134,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A134="",D134=""),"",IFERROR(ROUND(D134*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A134,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A134,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A134,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J134" s="13" t="str">
@@ -6399,7 +6515,7 @@
         <v/>
       </c>
       <c r="I135" s="13" t="str">
-        <f aca="false">IF(OR(A135="",D135=""),"",ROUND(D135*INDEX(Programmes!$L$2:$L$8,MATCH(A135,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A135="",D135=""),"",IFERROR(ROUND(D135*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A135,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A135,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A135,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J135" s="13" t="str">
@@ -6420,7 +6536,7 @@
         <v/>
       </c>
       <c r="I136" s="13" t="str">
-        <f aca="false">IF(OR(A136="",D136=""),"",ROUND(D136*INDEX(Programmes!$L$2:$L$8,MATCH(A136,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A136="",D136=""),"",IFERROR(ROUND(D136*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A136,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A136,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A136,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J136" s="13" t="str">
@@ -6441,7 +6557,7 @@
         <v/>
       </c>
       <c r="I137" s="13" t="str">
-        <f aca="false">IF(OR(A137="",D137=""),"",ROUND(D137*INDEX(Programmes!$L$2:$L$8,MATCH(A137,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A137="",D137=""),"",IFERROR(ROUND(D137*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A137,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A137,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A137,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J137" s="13" t="str">
@@ -6462,7 +6578,7 @@
         <v/>
       </c>
       <c r="I138" s="13" t="str">
-        <f aca="false">IF(OR(A138="",D138=""),"",ROUND(D138*INDEX(Programmes!$L$2:$L$8,MATCH(A138,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A138="",D138=""),"",IFERROR(ROUND(D138*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A138,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A138,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A138,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J138" s="13" t="str">
@@ -6483,7 +6599,7 @@
         <v/>
       </c>
       <c r="I139" s="13" t="str">
-        <f aca="false">IF(OR(A139="",D139=""),"",ROUND(D139*INDEX(Programmes!$L$2:$L$8,MATCH(A139,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A139="",D139=""),"",IFERROR(ROUND(D139*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A139,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A139,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A139,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J139" s="13" t="str">
@@ -6504,7 +6620,7 @@
         <v/>
       </c>
       <c r="I140" s="13" t="str">
-        <f aca="false">IF(OR(A140="",D140=""),"",ROUND(D140*INDEX(Programmes!$L$2:$L$8,MATCH(A140,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A140="",D140=""),"",IFERROR(ROUND(D140*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A140,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A140,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A140,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J140" s="13" t="str">
@@ -6525,7 +6641,7 @@
         <v/>
       </c>
       <c r="I141" s="13" t="str">
-        <f aca="false">IF(OR(A141="",D141=""),"",ROUND(D141*INDEX(Programmes!$L$2:$L$8,MATCH(A141,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A141="",D141=""),"",IFERROR(ROUND(D141*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A141,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A141,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A141,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J141" s="13" t="str">
@@ -6546,7 +6662,7 @@
         <v/>
       </c>
       <c r="I142" s="13" t="str">
-        <f aca="false">IF(OR(A142="",D142=""),"",ROUND(D142*INDEX(Programmes!$L$2:$L$8,MATCH(A142,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A142="",D142=""),"",IFERROR(ROUND(D142*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A142,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A142,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A142,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J142" s="13" t="str">
@@ -6567,7 +6683,7 @@
         <v/>
       </c>
       <c r="I143" s="13" t="str">
-        <f aca="false">IF(OR(A143="",D143=""),"",ROUND(D143*INDEX(Programmes!$L$2:$L$8,MATCH(A143,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A143="",D143=""),"",IFERROR(ROUND(D143*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A143,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A143,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A143,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J143" s="13" t="str">
@@ -6588,7 +6704,7 @@
         <v/>
       </c>
       <c r="I144" s="13" t="str">
-        <f aca="false">IF(OR(A144="",D144=""),"",ROUND(D144*INDEX(Programmes!$L$2:$L$8,MATCH(A144,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A144="",D144=""),"",IFERROR(ROUND(D144*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A144,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A144,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A144,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J144" s="13" t="str">
@@ -6609,7 +6725,7 @@
         <v/>
       </c>
       <c r="I145" s="13" t="str">
-        <f aca="false">IF(OR(A145="",D145=""),"",ROUND(D145*INDEX(Programmes!$L$2:$L$8,MATCH(A145,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A145="",D145=""),"",IFERROR(ROUND(D145*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A145,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A145,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A145,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J145" s="13" t="str">
@@ -6630,7 +6746,7 @@
         <v/>
       </c>
       <c r="I146" s="13" t="str">
-        <f aca="false">IF(OR(A146="",D146=""),"",ROUND(D146*INDEX(Programmes!$L$2:$L$8,MATCH(A146,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A146="",D146=""),"",IFERROR(ROUND(D146*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A146,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A146,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A146,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J146" s="13" t="str">
@@ -6651,7 +6767,7 @@
         <v/>
       </c>
       <c r="I147" s="13" t="str">
-        <f aca="false">IF(OR(A147="",D147=""),"",ROUND(D147*INDEX(Programmes!$L$2:$L$8,MATCH(A147,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A147="",D147=""),"",IFERROR(ROUND(D147*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A147,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A147,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A147,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J147" s="13" t="str">
@@ -6672,7 +6788,7 @@
         <v/>
       </c>
       <c r="I148" s="13" t="str">
-        <f aca="false">IF(OR(A148="",D148=""),"",ROUND(D148*INDEX(Programmes!$L$2:$L$8,MATCH(A148,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A148="",D148=""),"",IFERROR(ROUND(D148*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A148,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A148,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A148,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J148" s="13" t="str">
@@ -6693,7 +6809,7 @@
         <v/>
       </c>
       <c r="I149" s="13" t="str">
-        <f aca="false">IF(OR(A149="",D149=""),"",ROUND(D149*INDEX(Programmes!$L$2:$L$8,MATCH(A149,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A149="",D149=""),"",IFERROR(ROUND(D149*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A149,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A149,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A149,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J149" s="13" t="str">
@@ -6714,7 +6830,7 @@
         <v/>
       </c>
       <c r="I150" s="13" t="str">
-        <f aca="false">IF(OR(A150="",D150=""),"",ROUND(D150*INDEX(Programmes!$L$2:$L$8,MATCH(A150,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A150="",D150=""),"",IFERROR(ROUND(D150*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A150,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A150,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A150,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J150" s="13" t="str">
@@ -6735,7 +6851,7 @@
         <v/>
       </c>
       <c r="I151" s="13" t="str">
-        <f aca="false">IF(OR(A151="",D151=""),"",ROUND(D151*INDEX(Programmes!$L$2:$L$8,MATCH(A151,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A151="",D151=""),"",IFERROR(ROUND(D151*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A151,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A151,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A151,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J151" s="13" t="str">
@@ -6756,7 +6872,7 @@
         <v/>
       </c>
       <c r="I152" s="13" t="str">
-        <f aca="false">IF(OR(A152="",D152=""),"",ROUND(D152*INDEX(Programmes!$L$2:$L$8,MATCH(A152,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A152="",D152=""),"",IFERROR(ROUND(D152*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A152,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A152,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A152,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J152" s="13" t="str">
@@ -6777,7 +6893,7 @@
         <v/>
       </c>
       <c r="I153" s="13" t="str">
-        <f aca="false">IF(OR(A153="",D153=""),"",ROUND(D153*INDEX(Programmes!$L$2:$L$8,MATCH(A153,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A153="",D153=""),"",IFERROR(ROUND(D153*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A153,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A153,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A153,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J153" s="13" t="str">
@@ -6798,7 +6914,7 @@
         <v/>
       </c>
       <c r="I154" s="13" t="str">
-        <f aca="false">IF(OR(A154="",D154=""),"",ROUND(D154*INDEX(Programmes!$L$2:$L$8,MATCH(A154,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A154="",D154=""),"",IFERROR(ROUND(D154*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A154,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A154,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A154,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J154" s="13" t="str">
@@ -6819,7 +6935,7 @@
         <v/>
       </c>
       <c r="I155" s="13" t="str">
-        <f aca="false">IF(OR(A155="",D155=""),"",ROUND(D155*INDEX(Programmes!$L$2:$L$8,MATCH(A155,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A155="",D155=""),"",IFERROR(ROUND(D155*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A155,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A155,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A155,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J155" s="13" t="str">
@@ -6840,7 +6956,7 @@
         <v/>
       </c>
       <c r="I156" s="13" t="str">
-        <f aca="false">IF(OR(A156="",D156=""),"",ROUND(D156*INDEX(Programmes!$L$2:$L$8,MATCH(A156,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A156="",D156=""),"",IFERROR(ROUND(D156*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A156,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A156,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A156,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J156" s="13" t="str">
@@ -6861,7 +6977,7 @@
         <v/>
       </c>
       <c r="I157" s="13" t="str">
-        <f aca="false">IF(OR(A157="",D157=""),"",ROUND(D157*INDEX(Programmes!$L$2:$L$8,MATCH(A157,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A157="",D157=""),"",IFERROR(ROUND(D157*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A157,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A157,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A157,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J157" s="13" t="str">
@@ -6882,7 +6998,7 @@
         <v/>
       </c>
       <c r="I158" s="13" t="str">
-        <f aca="false">IF(OR(A158="",D158=""),"",ROUND(D158*INDEX(Programmes!$L$2:$L$8,MATCH(A158,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A158="",D158=""),"",IFERROR(ROUND(D158*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A158,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A158,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A158,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J158" s="13" t="str">
@@ -6903,7 +7019,7 @@
         <v/>
       </c>
       <c r="I159" s="13" t="str">
-        <f aca="false">IF(OR(A159="",D159=""),"",ROUND(D159*INDEX(Programmes!$L$2:$L$8,MATCH(A159,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A159="",D159=""),"",IFERROR(ROUND(D159*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A159,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A159,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A159,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J159" s="13" t="str">
@@ -6924,7 +7040,7 @@
         <v/>
       </c>
       <c r="I160" s="13" t="str">
-        <f aca="false">IF(OR(A160="",D160=""),"",ROUND(D160*INDEX(Programmes!$L$2:$L$8,MATCH(A160,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A160="",D160=""),"",IFERROR(ROUND(D160*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A160,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A160,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A160,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J160" s="13" t="str">
@@ -6945,7 +7061,7 @@
         <v/>
       </c>
       <c r="I161" s="13" t="str">
-        <f aca="false">IF(OR(A161="",D161=""),"",ROUND(D161*INDEX(Programmes!$L$2:$L$8,MATCH(A161,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A161="",D161=""),"",IFERROR(ROUND(D161*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A161,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A161,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A161,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J161" s="13" t="str">
@@ -6966,7 +7082,7 @@
         <v/>
       </c>
       <c r="I162" s="13" t="str">
-        <f aca="false">IF(OR(A162="",D162=""),"",ROUND(D162*INDEX(Programmes!$L$2:$L$8,MATCH(A162,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A162="",D162=""),"",IFERROR(ROUND(D162*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A162,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A162,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A162,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J162" s="13" t="str">
@@ -6987,7 +7103,7 @@
         <v/>
       </c>
       <c r="I163" s="13" t="str">
-        <f aca="false">IF(OR(A163="",D163=""),"",ROUND(D163*INDEX(Programmes!$L$2:$L$8,MATCH(A163,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A163="",D163=""),"",IFERROR(ROUND(D163*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A163,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A163,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A163,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J163" s="13" t="str">
@@ -7008,7 +7124,7 @@
         <v/>
       </c>
       <c r="I164" s="13" t="str">
-        <f aca="false">IF(OR(A164="",D164=""),"",ROUND(D164*INDEX(Programmes!$L$2:$L$8,MATCH(A164,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A164="",D164=""),"",IFERROR(ROUND(D164*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A164,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A164,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A164,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J164" s="13" t="str">
@@ -7029,7 +7145,7 @@
         <v/>
       </c>
       <c r="I165" s="13" t="str">
-        <f aca="false">IF(OR(A165="",D165=""),"",ROUND(D165*INDEX(Programmes!$L$2:$L$8,MATCH(A165,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A165="",D165=""),"",IFERROR(ROUND(D165*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A165,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A165,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A165,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J165" s="13" t="str">
@@ -7050,7 +7166,7 @@
         <v/>
       </c>
       <c r="I166" s="13" t="str">
-        <f aca="false">IF(OR(A166="",D166=""),"",ROUND(D166*INDEX(Programmes!$L$2:$L$8,MATCH(A166,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A166="",D166=""),"",IFERROR(ROUND(D166*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A166,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A166,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A166,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J166" s="13" t="str">
@@ -7071,7 +7187,7 @@
         <v/>
       </c>
       <c r="I167" s="13" t="str">
-        <f aca="false">IF(OR(A167="",D167=""),"",ROUND(D167*INDEX(Programmes!$L$2:$L$8,MATCH(A167,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A167="",D167=""),"",IFERROR(ROUND(D167*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A167,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A167,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A167,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J167" s="13" t="str">
@@ -7092,7 +7208,7 @@
         <v/>
       </c>
       <c r="I168" s="13" t="str">
-        <f aca="false">IF(OR(A168="",D168=""),"",ROUND(D168*INDEX(Programmes!$L$2:$L$8,MATCH(A168,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A168="",D168=""),"",IFERROR(ROUND(D168*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A168,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A168,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A168,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J168" s="13" t="str">
@@ -7113,7 +7229,7 @@
         <v/>
       </c>
       <c r="I169" s="13" t="str">
-        <f aca="false">IF(OR(A169="",D169=""),"",ROUND(D169*INDEX(Programmes!$L$2:$L$8,MATCH(A169,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A169="",D169=""),"",IFERROR(ROUND(D169*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A169,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A169,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A169,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J169" s="13" t="str">
@@ -7134,7 +7250,7 @@
         <v/>
       </c>
       <c r="I170" s="13" t="str">
-        <f aca="false">IF(OR(A170="",D170=""),"",ROUND(D170*INDEX(Programmes!$L$2:$L$8,MATCH(A170,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A170="",D170=""),"",IFERROR(ROUND(D170*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A170,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A170,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A170,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J170" s="13" t="str">
@@ -7155,7 +7271,7 @@
         <v/>
       </c>
       <c r="I171" s="13" t="str">
-        <f aca="false">IF(OR(A171="",D171=""),"",ROUND(D171*INDEX(Programmes!$L$2:$L$8,MATCH(A171,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A171="",D171=""),"",IFERROR(ROUND(D171*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A171,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A171,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A171,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J171" s="13" t="str">
@@ -7176,7 +7292,7 @@
         <v/>
       </c>
       <c r="I172" s="13" t="str">
-        <f aca="false">IF(OR(A172="",D172=""),"",ROUND(D172*INDEX(Programmes!$L$2:$L$8,MATCH(A172,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A172="",D172=""),"",IFERROR(ROUND(D172*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A172,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A172,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A172,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J172" s="13" t="str">
@@ -7197,7 +7313,7 @@
         <v/>
       </c>
       <c r="I173" s="13" t="str">
-        <f aca="false">IF(OR(A173="",D173=""),"",ROUND(D173*INDEX(Programmes!$L$2:$L$8,MATCH(A173,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A173="",D173=""),"",IFERROR(ROUND(D173*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A173,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A173,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A173,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J173" s="13" t="str">
@@ -7218,7 +7334,7 @@
         <v/>
       </c>
       <c r="I174" s="13" t="str">
-        <f aca="false">IF(OR(A174="",D174=""),"",ROUND(D174*INDEX(Programmes!$L$2:$L$8,MATCH(A174,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A174="",D174=""),"",IFERROR(ROUND(D174*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A174,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A174,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A174,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J174" s="13" t="str">
@@ -7239,7 +7355,7 @@
         <v/>
       </c>
       <c r="I175" s="13" t="str">
-        <f aca="false">IF(OR(A175="",D175=""),"",ROUND(D175*INDEX(Programmes!$L$2:$L$8,MATCH(A175,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A175="",D175=""),"",IFERROR(ROUND(D175*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A175,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A175,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A175,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J175" s="13" t="str">
@@ -7260,7 +7376,7 @@
         <v/>
       </c>
       <c r="I176" s="13" t="str">
-        <f aca="false">IF(OR(A176="",D176=""),"",ROUND(D176*INDEX(Programmes!$L$2:$L$8,MATCH(A176,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A176="",D176=""),"",IFERROR(ROUND(D176*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A176,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A176,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A176,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J176" s="13" t="str">
@@ -7281,7 +7397,7 @@
         <v/>
       </c>
       <c r="I177" s="13" t="str">
-        <f aca="false">IF(OR(A177="",D177=""),"",ROUND(D177*INDEX(Programmes!$L$2:$L$8,MATCH(A177,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A177="",D177=""),"",IFERROR(ROUND(D177*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A177,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A177,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A177,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J177" s="13" t="str">
@@ -7302,7 +7418,7 @@
         <v/>
       </c>
       <c r="I178" s="13" t="str">
-        <f aca="false">IF(OR(A178="",D178=""),"",ROUND(D178*INDEX(Programmes!$L$2:$L$8,MATCH(A178,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A178="",D178=""),"",IFERROR(ROUND(D178*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A178,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A178,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A178,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J178" s="13" t="str">
@@ -7323,7 +7439,7 @@
         <v/>
       </c>
       <c r="I179" s="13" t="str">
-        <f aca="false">IF(OR(A179="",D179=""),"",ROUND(D179*INDEX(Programmes!$L$2:$L$8,MATCH(A179,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A179="",D179=""),"",IFERROR(ROUND(D179*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A179,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A179,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A179,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J179" s="13" t="str">
@@ -7344,7 +7460,7 @@
         <v/>
       </c>
       <c r="I180" s="13" t="str">
-        <f aca="false">IF(OR(A180="",D180=""),"",ROUND(D180*INDEX(Programmes!$L$2:$L$8,MATCH(A180,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A180="",D180=""),"",IFERROR(ROUND(D180*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A180,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A180,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A180,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J180" s="13" t="str">
@@ -7365,7 +7481,7 @@
         <v/>
       </c>
       <c r="I181" s="13" t="str">
-        <f aca="false">IF(OR(A181="",D181=""),"",ROUND(D181*INDEX(Programmes!$L$2:$L$8,MATCH(A181,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A181="",D181=""),"",IFERROR(ROUND(D181*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A181,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A181,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A181,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J181" s="13" t="str">
@@ -7386,7 +7502,7 @@
         <v/>
       </c>
       <c r="I182" s="13" t="str">
-        <f aca="false">IF(OR(A182="",D182=""),"",ROUND(D182*INDEX(Programmes!$L$2:$L$8,MATCH(A182,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A182="",D182=""),"",IFERROR(ROUND(D182*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A182,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A182,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A182,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J182" s="13" t="str">
@@ -7407,7 +7523,7 @@
         <v/>
       </c>
       <c r="I183" s="13" t="str">
-        <f aca="false">IF(OR(A183="",D183=""),"",ROUND(D183*INDEX(Programmes!$L$2:$L$8,MATCH(A183,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A183="",D183=""),"",IFERROR(ROUND(D183*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A183,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A183,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A183,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J183" s="13" t="str">
@@ -7428,7 +7544,7 @@
         <v/>
       </c>
       <c r="I184" s="13" t="str">
-        <f aca="false">IF(OR(A184="",D184=""),"",ROUND(D184*INDEX(Programmes!$L$2:$L$8,MATCH(A184,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A184="",D184=""),"",IFERROR(ROUND(D184*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A184,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A184,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A184,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J184" s="13" t="str">
@@ -7449,7 +7565,7 @@
         <v/>
       </c>
       <c r="I185" s="13" t="str">
-        <f aca="false">IF(OR(A185="",D185=""),"",ROUND(D185*INDEX(Programmes!$L$2:$L$8,MATCH(A185,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A185="",D185=""),"",IFERROR(ROUND(D185*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A185,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A185,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A185,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J185" s="13" t="str">
@@ -7470,7 +7586,7 @@
         <v/>
       </c>
       <c r="I186" s="13" t="str">
-        <f aca="false">IF(OR(A186="",D186=""),"",ROUND(D186*INDEX(Programmes!$L$2:$L$8,MATCH(A186,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A186="",D186=""),"",IFERROR(ROUND(D186*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A186,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A186,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A186,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J186" s="13" t="str">
@@ -7491,7 +7607,7 @@
         <v/>
       </c>
       <c r="I187" s="13" t="str">
-        <f aca="false">IF(OR(A187="",D187=""),"",ROUND(D187*INDEX(Programmes!$L$2:$L$8,MATCH(A187,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A187="",D187=""),"",IFERROR(ROUND(D187*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A187,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A187,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A187,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J187" s="13" t="str">
@@ -7512,7 +7628,7 @@
         <v/>
       </c>
       <c r="I188" s="13" t="str">
-        <f aca="false">IF(OR(A188="",D188=""),"",ROUND(D188*INDEX(Programmes!$L$2:$L$8,MATCH(A188,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A188="",D188=""),"",IFERROR(ROUND(D188*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A188,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A188,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A188,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J188" s="13" t="str">
@@ -7533,7 +7649,7 @@
         <v/>
       </c>
       <c r="I189" s="13" t="str">
-        <f aca="false">IF(OR(A189="",D189=""),"",ROUND(D189*INDEX(Programmes!$L$2:$L$8,MATCH(A189,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A189="",D189=""),"",IFERROR(ROUND(D189*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A189,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A189,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A189,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J189" s="13" t="str">
@@ -7554,7 +7670,7 @@
         <v/>
       </c>
       <c r="I190" s="13" t="str">
-        <f aca="false">IF(OR(A190="",D190=""),"",ROUND(D190*INDEX(Programmes!$L$2:$L$8,MATCH(A190,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A190="",D190=""),"",IFERROR(ROUND(D190*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A190,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A190,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A190,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J190" s="13" t="str">
@@ -7575,7 +7691,7 @@
         <v/>
       </c>
       <c r="I191" s="13" t="str">
-        <f aca="false">IF(OR(A191="",D191=""),"",ROUND(D191*INDEX(Programmes!$L$2:$L$8,MATCH(A191,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A191="",D191=""),"",IFERROR(ROUND(D191*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A191,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A191,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A191,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J191" s="13" t="str">
@@ -7596,7 +7712,7 @@
         <v/>
       </c>
       <c r="I192" s="13" t="str">
-        <f aca="false">IF(OR(A192="",D192=""),"",ROUND(D192*INDEX(Programmes!$L$2:$L$8,MATCH(A192,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A192="",D192=""),"",IFERROR(ROUND(D192*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A192,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A192,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A192,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J192" s="13" t="str">
@@ -7617,7 +7733,7 @@
         <v/>
       </c>
       <c r="I193" s="13" t="str">
-        <f aca="false">IF(OR(A193="",D193=""),"",ROUND(D193*INDEX(Programmes!$L$2:$L$8,MATCH(A193,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A193="",D193=""),"",IFERROR(ROUND(D193*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A193,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A193,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A193,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J193" s="13" t="str">
@@ -7638,7 +7754,7 @@
         <v/>
       </c>
       <c r="I194" s="13" t="str">
-        <f aca="false">IF(OR(A194="",D194=""),"",ROUND(D194*INDEX(Programmes!$L$2:$L$8,MATCH(A194,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A194="",D194=""),"",IFERROR(ROUND(D194*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A194,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A194,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A194,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J194" s="13" t="str">
@@ -7659,7 +7775,7 @@
         <v/>
       </c>
       <c r="I195" s="13" t="str">
-        <f aca="false">IF(OR(A195="",D195=""),"",ROUND(D195*INDEX(Programmes!$L$2:$L$8,MATCH(A195,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A195="",D195=""),"",IFERROR(ROUND(D195*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A195,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A195,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A195,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J195" s="13" t="str">
@@ -7680,7 +7796,7 @@
         <v/>
       </c>
       <c r="I196" s="13" t="str">
-        <f aca="false">IF(OR(A196="",D196=""),"",ROUND(D196*INDEX(Programmes!$L$2:$L$8,MATCH(A196,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A196="",D196=""),"",IFERROR(ROUND(D196*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A196,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A196,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A196,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J196" s="13" t="str">
@@ -7701,7 +7817,7 @@
         <v/>
       </c>
       <c r="I197" s="13" t="str">
-        <f aca="false">IF(OR(A197="",D197=""),"",ROUND(D197*INDEX(Programmes!$L$2:$L$8,MATCH(A197,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A197="",D197=""),"",IFERROR(ROUND(D197*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A197,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A197,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A197,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J197" s="13" t="str">
@@ -7722,7 +7838,7 @@
         <v/>
       </c>
       <c r="I198" s="13" t="str">
-        <f aca="false">IF(OR(A198="",D198=""),"",ROUND(D198*INDEX(Programmes!$L$2:$L$8,MATCH(A198,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A198="",D198=""),"",IFERROR(ROUND(D198*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A198,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A198,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A198,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J198" s="13" t="str">
@@ -7743,7 +7859,7 @@
         <v/>
       </c>
       <c r="I199" s="13" t="str">
-        <f aca="false">IF(OR(A199="",D199=""),"",ROUND(D199*INDEX(Programmes!$L$2:$L$8,MATCH(A199,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A199="",D199=""),"",IFERROR(ROUND(D199*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A199,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A199,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A199,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J199" s="13" t="str">
@@ -7764,7 +7880,7 @@
         <v/>
       </c>
       <c r="I200" s="13" t="str">
-        <f aca="false">IF(OR(A200="",D200=""),"",ROUND(D200*INDEX(Programmes!$L$2:$L$8,MATCH(A200,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A200="",D200=""),"",IFERROR(ROUND(D200*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A200,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A200,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A200,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J200" s="13" t="str">
@@ -7785,7 +7901,7 @@
         <v/>
       </c>
       <c r="I201" s="13" t="str">
-        <f aca="false">IF(OR(A201="",D201=""),"",ROUND(D201*INDEX(Programmes!$L$2:$L$8,MATCH(A201,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A201="",D201=""),"",IFERROR(ROUND(D201*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A201,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A201,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A201,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J201" s="13" t="str">
@@ -7806,7 +7922,7 @@
         <v/>
       </c>
       <c r="I202" s="13" t="str">
-        <f aca="false">IF(OR(A202="",D202=""),"",ROUND(D202*INDEX(Programmes!$L$2:$L$8,MATCH(A202,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A202="",D202=""),"",IFERROR(ROUND(D202*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A202,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A202,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A202,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J202" s="13" t="str">
@@ -7827,7 +7943,7 @@
         <v/>
       </c>
       <c r="I203" s="13" t="str">
-        <f aca="false">IF(OR(A203="",D203=""),"",ROUND(D203*INDEX(Programmes!$L$2:$L$8,MATCH(A203,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A203="",D203=""),"",IFERROR(ROUND(D203*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A203,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A203,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A203,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J203" s="13" t="str">
@@ -7848,7 +7964,7 @@
         <v/>
       </c>
       <c r="I204" s="13" t="str">
-        <f aca="false">IF(OR(A204="",D204=""),"",ROUND(D204*INDEX(Programmes!$L$2:$L$8,MATCH(A204,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A204="",D204=""),"",IFERROR(ROUND(D204*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A204,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A204,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A204,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J204" s="13" t="str">
@@ -7869,7 +7985,7 @@
         <v/>
       </c>
       <c r="I205" s="13" t="str">
-        <f aca="false">IF(OR(A205="",D205=""),"",ROUND(D205*INDEX(Programmes!$L$2:$L$8,MATCH(A205,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A205="",D205=""),"",IFERROR(ROUND(D205*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A205,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A205,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A205,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J205" s="13" t="str">
@@ -7890,7 +8006,7 @@
         <v/>
       </c>
       <c r="I206" s="13" t="str">
-        <f aca="false">IF(OR(A206="",D206=""),"",ROUND(D206*INDEX(Programmes!$L$2:$L$8,MATCH(A206,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A206="",D206=""),"",IFERROR(ROUND(D206*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A206,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A206,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A206,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J206" s="13" t="str">
@@ -7911,7 +8027,7 @@
         <v/>
       </c>
       <c r="I207" s="13" t="str">
-        <f aca="false">IF(OR(A207="",D207=""),"",ROUND(D207*INDEX(Programmes!$L$2:$L$8,MATCH(A207,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A207="",D207=""),"",IFERROR(ROUND(D207*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A207,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A207,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A207,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J207" s="13" t="str">
@@ -7932,7 +8048,7 @@
         <v/>
       </c>
       <c r="I208" s="13" t="str">
-        <f aca="false">IF(OR(A208="",D208=""),"",ROUND(D208*INDEX(Programmes!$L$2:$L$8,MATCH(A208,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A208="",D208=""),"",IFERROR(ROUND(D208*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A208,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A208,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A208,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J208" s="13" t="str">
@@ -7953,7 +8069,7 @@
         <v/>
       </c>
       <c r="I209" s="13" t="str">
-        <f aca="false">IF(OR(A209="",D209=""),"",ROUND(D209*INDEX(Programmes!$L$2:$L$8,MATCH(A209,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A209="",D209=""),"",IFERROR(ROUND(D209*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A209,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A209,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A209,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J209" s="13" t="str">
@@ -7974,7 +8090,7 @@
         <v/>
       </c>
       <c r="I210" s="13" t="str">
-        <f aca="false">IF(OR(A210="",D210=""),"",ROUND(D210*INDEX(Programmes!$L$2:$L$8,MATCH(A210,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A210="",D210=""),"",IFERROR(ROUND(D210*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A210,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A210,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A210,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J210" s="13" t="str">
@@ -7995,7 +8111,7 @@
         <v/>
       </c>
       <c r="I211" s="13" t="str">
-        <f aca="false">IF(OR(A211="",D211=""),"",ROUND(D211*INDEX(Programmes!$L$2:$L$8,MATCH(A211,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A211="",D211=""),"",IFERROR(ROUND(D211*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A211,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A211,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A211,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J211" s="13" t="str">
@@ -8016,7 +8132,7 @@
         <v/>
       </c>
       <c r="I212" s="13" t="str">
-        <f aca="false">IF(OR(A212="",D212=""),"",ROUND(D212*INDEX(Programmes!$L$2:$L$8,MATCH(A212,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A212="",D212=""),"",IFERROR(ROUND(D212*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A212,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A212,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A212,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J212" s="13" t="str">
@@ -8037,7 +8153,7 @@
         <v/>
       </c>
       <c r="I213" s="13" t="str">
-        <f aca="false">IF(OR(A213="",D213=""),"",ROUND(D213*INDEX(Programmes!$L$2:$L$8,MATCH(A213,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A213="",D213=""),"",IFERROR(ROUND(D213*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A213,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A213,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A213,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J213" s="13" t="str">
@@ -8058,7 +8174,7 @@
         <v/>
       </c>
       <c r="I214" s="13" t="str">
-        <f aca="false">IF(OR(A214="",D214=""),"",ROUND(D214*INDEX(Programmes!$L$2:$L$8,MATCH(A214,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A214="",D214=""),"",IFERROR(ROUND(D214*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A214,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A214,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A214,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J214" s="13" t="str">
@@ -8079,7 +8195,7 @@
         <v/>
       </c>
       <c r="I215" s="13" t="str">
-        <f aca="false">IF(OR(A215="",D215=""),"",ROUND(D215*INDEX(Programmes!$L$2:$L$8,MATCH(A215,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A215="",D215=""),"",IFERROR(ROUND(D215*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A215,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A215,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A215,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J215" s="13" t="str">
@@ -8100,7 +8216,7 @@
         <v/>
       </c>
       <c r="I216" s="13" t="str">
-        <f aca="false">IF(OR(A216="",D216=""),"",ROUND(D216*INDEX(Programmes!$L$2:$L$8,MATCH(A216,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A216="",D216=""),"",IFERROR(ROUND(D216*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A216,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A216,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A216,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J216" s="13" t="str">
@@ -8121,7 +8237,7 @@
         <v/>
       </c>
       <c r="I217" s="13" t="str">
-        <f aca="false">IF(OR(A217="",D217=""),"",ROUND(D217*INDEX(Programmes!$L$2:$L$8,MATCH(A217,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A217="",D217=""),"",IFERROR(ROUND(D217*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A217,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A217,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A217,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J217" s="13" t="str">
@@ -8142,7 +8258,7 @@
         <v/>
       </c>
       <c r="I218" s="13" t="str">
-        <f aca="false">IF(OR(A218="",D218=""),"",ROUND(D218*INDEX(Programmes!$L$2:$L$8,MATCH(A218,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A218="",D218=""),"",IFERROR(ROUND(D218*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A218,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A218,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A218,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J218" s="13" t="str">
@@ -8163,7 +8279,7 @@
         <v/>
       </c>
       <c r="I219" s="13" t="str">
-        <f aca="false">IF(OR(A219="",D219=""),"",ROUND(D219*INDEX(Programmes!$L$2:$L$8,MATCH(A219,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A219="",D219=""),"",IFERROR(ROUND(D219*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A219,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A219,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A219,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J219" s="13" t="str">
@@ -8184,7 +8300,7 @@
         <v/>
       </c>
       <c r="I220" s="13" t="str">
-        <f aca="false">IF(OR(A220="",D220=""),"",ROUND(D220*INDEX(Programmes!$L$2:$L$8,MATCH(A220,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A220="",D220=""),"",IFERROR(ROUND(D220*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A220,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A220,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A220,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J220" s="13" t="str">
@@ -8205,7 +8321,7 @@
         <v/>
       </c>
       <c r="I221" s="13" t="str">
-        <f aca="false">IF(OR(A221="",D221=""),"",ROUND(D221*INDEX(Programmes!$L$2:$L$8,MATCH(A221,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A221="",D221=""),"",IFERROR(ROUND(D221*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A221,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A221,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A221,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J221" s="13" t="str">
@@ -8226,7 +8342,7 @@
         <v/>
       </c>
       <c r="I222" s="13" t="str">
-        <f aca="false">IF(OR(A222="",D222=""),"",ROUND(D222*INDEX(Programmes!$L$2:$L$8,MATCH(A222,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A222="",D222=""),"",IFERROR(ROUND(D222*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A222,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A222,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A222,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J222" s="13" t="str">
@@ -8247,7 +8363,7 @@
         <v/>
       </c>
       <c r="I223" s="13" t="str">
-        <f aca="false">IF(OR(A223="",D223=""),"",ROUND(D223*INDEX(Programmes!$L$2:$L$8,MATCH(A223,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A223="",D223=""),"",IFERROR(ROUND(D223*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A223,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A223,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A223,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J223" s="13" t="str">
@@ -8268,7 +8384,7 @@
         <v/>
       </c>
       <c r="I224" s="13" t="str">
-        <f aca="false">IF(OR(A224="",D224=""),"",ROUND(D224*INDEX(Programmes!$L$2:$L$8,MATCH(A224,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A224="",D224=""),"",IFERROR(ROUND(D224*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A224,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A224,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A224,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J224" s="13" t="str">
@@ -8289,7 +8405,7 @@
         <v/>
       </c>
       <c r="I225" s="13" t="str">
-        <f aca="false">IF(OR(A225="",D225=""),"",ROUND(D225*INDEX(Programmes!$L$2:$L$8,MATCH(A225,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A225="",D225=""),"",IFERROR(ROUND(D225*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A225,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A225,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A225,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J225" s="13" t="str">
@@ -8310,7 +8426,7 @@
         <v/>
       </c>
       <c r="I226" s="13" t="str">
-        <f aca="false">IF(OR(A226="",D226=""),"",ROUND(D226*INDEX(Programmes!$L$2:$L$8,MATCH(A226,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A226="",D226=""),"",IFERROR(ROUND(D226*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A226,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A226,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A226,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J226" s="13" t="str">
@@ -8331,7 +8447,7 @@
         <v/>
       </c>
       <c r="I227" s="13" t="str">
-        <f aca="false">IF(OR(A227="",D227=""),"",ROUND(D227*INDEX(Programmes!$L$2:$L$8,MATCH(A227,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A227="",D227=""),"",IFERROR(ROUND(D227*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A227,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A227,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A227,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J227" s="13" t="str">
@@ -8352,7 +8468,7 @@
         <v/>
       </c>
       <c r="I228" s="13" t="str">
-        <f aca="false">IF(OR(A228="",D228=""),"",ROUND(D228*INDEX(Programmes!$L$2:$L$8,MATCH(A228,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A228="",D228=""),"",IFERROR(ROUND(D228*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A228,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A228,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A228,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J228" s="13" t="str">
@@ -8373,7 +8489,7 @@
         <v/>
       </c>
       <c r="I229" s="13" t="str">
-        <f aca="false">IF(OR(A229="",D229=""),"",ROUND(D229*INDEX(Programmes!$L$2:$L$8,MATCH(A229,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A229="",D229=""),"",IFERROR(ROUND(D229*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A229,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A229,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A229,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J229" s="13" t="str">
@@ -8394,7 +8510,7 @@
         <v/>
       </c>
       <c r="I230" s="13" t="str">
-        <f aca="false">IF(OR(A230="",D230=""),"",ROUND(D230*INDEX(Programmes!$L$2:$L$8,MATCH(A230,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A230="",D230=""),"",IFERROR(ROUND(D230*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A230,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A230,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A230,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J230" s="13" t="str">
@@ -8415,7 +8531,7 @@
         <v/>
       </c>
       <c r="I231" s="13" t="str">
-        <f aca="false">IF(OR(A231="",D231=""),"",ROUND(D231*INDEX(Programmes!$L$2:$L$8,MATCH(A231,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A231="",D231=""),"",IFERROR(ROUND(D231*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A231,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A231,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A231,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J231" s="13" t="str">
@@ -8436,7 +8552,7 @@
         <v/>
       </c>
       <c r="I232" s="13" t="str">
-        <f aca="false">IF(OR(A232="",D232=""),"",ROUND(D232*INDEX(Programmes!$L$2:$L$8,MATCH(A232,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A232="",D232=""),"",IFERROR(ROUND(D232*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A232,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A232,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A232,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J232" s="13" t="str">
@@ -8457,7 +8573,7 @@
         <v/>
       </c>
       <c r="I233" s="13" t="str">
-        <f aca="false">IF(OR(A233="",D233=""),"",ROUND(D233*INDEX(Programmes!$L$2:$L$8,MATCH(A233,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A233="",D233=""),"",IFERROR(ROUND(D233*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A233,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A233,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A233,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J233" s="13" t="str">
@@ -8478,7 +8594,7 @@
         <v/>
       </c>
       <c r="I234" s="13" t="str">
-        <f aca="false">IF(OR(A234="",D234=""),"",ROUND(D234*INDEX(Programmes!$L$2:$L$8,MATCH(A234,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A234="",D234=""),"",IFERROR(ROUND(D234*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A234,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A234,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A234,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J234" s="13" t="str">
@@ -8499,7 +8615,7 @@
         <v/>
       </c>
       <c r="I235" s="13" t="str">
-        <f aca="false">IF(OR(A235="",D235=""),"",ROUND(D235*INDEX(Programmes!$L$2:$L$8,MATCH(A235,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A235="",D235=""),"",IFERROR(ROUND(D235*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A235,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A235,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A235,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J235" s="13" t="str">
@@ -8520,7 +8636,7 @@
         <v/>
       </c>
       <c r="I236" s="13" t="str">
-        <f aca="false">IF(OR(A236="",D236=""),"",ROUND(D236*INDEX(Programmes!$L$2:$L$8,MATCH(A236,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A236="",D236=""),"",IFERROR(ROUND(D236*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A236,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A236,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A236,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J236" s="13" t="str">
@@ -8541,7 +8657,7 @@
         <v/>
       </c>
       <c r="I237" s="13" t="str">
-        <f aca="false">IF(OR(A237="",D237=""),"",ROUND(D237*INDEX(Programmes!$L$2:$L$8,MATCH(A237,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A237="",D237=""),"",IFERROR(ROUND(D237*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A237,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A237,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A237,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J237" s="13" t="str">
@@ -8562,7 +8678,7 @@
         <v/>
       </c>
       <c r="I238" s="13" t="str">
-        <f aca="false">IF(OR(A238="",D238=""),"",ROUND(D238*INDEX(Programmes!$L$2:$L$8,MATCH(A238,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A238="",D238=""),"",IFERROR(ROUND(D238*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A238,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A238,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A238,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J238" s="13" t="str">
@@ -8583,7 +8699,7 @@
         <v/>
       </c>
       <c r="I239" s="13" t="str">
-        <f aca="false">IF(OR(A239="",D239=""),"",ROUND(D239*INDEX(Programmes!$L$2:$L$8,MATCH(A239,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A239="",D239=""),"",IFERROR(ROUND(D239*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A239,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A239,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A239,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J239" s="13" t="str">
@@ -8604,7 +8720,7 @@
         <v/>
       </c>
       <c r="I240" s="13" t="str">
-        <f aca="false">IF(OR(A240="",D240=""),"",ROUND(D240*INDEX(Programmes!$L$2:$L$8,MATCH(A240,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A240="",D240=""),"",IFERROR(ROUND(D240*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A240,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A240,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A240,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J240" s="13" t="str">
@@ -8625,7 +8741,7 @@
         <v/>
       </c>
       <c r="I241" s="13" t="str">
-        <f aca="false">IF(OR(A241="",D241=""),"",ROUND(D241*INDEX(Programmes!$L$2:$L$8,MATCH(A241,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A241="",D241=""),"",IFERROR(ROUND(D241*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A241,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A241,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A241,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J241" s="13" t="str">
@@ -8646,7 +8762,7 @@
         <v/>
       </c>
       <c r="I242" s="13" t="str">
-        <f aca="false">IF(OR(A242="",D242=""),"",ROUND(D242*INDEX(Programmes!$L$2:$L$8,MATCH(A242,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A242="",D242=""),"",IFERROR(ROUND(D242*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A242,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A242,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A242,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J242" s="13" t="str">
@@ -8667,7 +8783,7 @@
         <v/>
       </c>
       <c r="I243" s="13" t="str">
-        <f aca="false">IF(OR(A243="",D243=""),"",ROUND(D243*INDEX(Programmes!$L$2:$L$8,MATCH(A243,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A243="",D243=""),"",IFERROR(ROUND(D243*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A243,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A243,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A243,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J243" s="13" t="str">
@@ -8688,7 +8804,7 @@
         <v/>
       </c>
       <c r="I244" s="13" t="str">
-        <f aca="false">IF(OR(A244="",D244=""),"",ROUND(D244*INDEX(Programmes!$L$2:$L$8,MATCH(A244,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A244="",D244=""),"",IFERROR(ROUND(D244*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A244,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A244,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A244,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J244" s="13" t="str">
@@ -8709,7 +8825,7 @@
         <v/>
       </c>
       <c r="I245" s="13" t="str">
-        <f aca="false">IF(OR(A245="",D245=""),"",ROUND(D245*INDEX(Programmes!$L$2:$L$8,MATCH(A245,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A245="",D245=""),"",IFERROR(ROUND(D245*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A245,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A245,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A245,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J245" s="13" t="str">
@@ -8730,7 +8846,7 @@
         <v/>
       </c>
       <c r="I246" s="13" t="str">
-        <f aca="false">IF(OR(A246="",D246=""),"",ROUND(D246*INDEX(Programmes!$L$2:$L$8,MATCH(A246,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A246="",D246=""),"",IFERROR(ROUND(D246*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A246,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A246,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A246,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J246" s="13" t="str">
@@ -8751,7 +8867,7 @@
         <v/>
       </c>
       <c r="I247" s="13" t="str">
-        <f aca="false">IF(OR(A247="",D247=""),"",ROUND(D247*INDEX(Programmes!$L$2:$L$8,MATCH(A247,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A247="",D247=""),"",IFERROR(ROUND(D247*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A247,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A247,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A247,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J247" s="13" t="str">
@@ -8772,7 +8888,7 @@
         <v/>
       </c>
       <c r="I248" s="13" t="str">
-        <f aca="false">IF(OR(A248="",D248=""),"",ROUND(D248*INDEX(Programmes!$L$2:$L$8,MATCH(A248,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A248="",D248=""),"",IFERROR(ROUND(D248*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A248,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A248,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A248,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J248" s="13" t="str">
@@ -8793,7 +8909,7 @@
         <v/>
       </c>
       <c r="I249" s="13" t="str">
-        <f aca="false">IF(OR(A249="",D249=""),"",ROUND(D249*INDEX(Programmes!$L$2:$L$8,MATCH(A249,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A249="",D249=""),"",IFERROR(ROUND(D249*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A249,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A249,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A249,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J249" s="13" t="str">
@@ -8814,7 +8930,7 @@
         <v/>
       </c>
       <c r="I250" s="13" t="str">
-        <f aca="false">IF(OR(A250="",D250=""),"",ROUND(D250*INDEX(Programmes!$L$2:$L$8,MATCH(A250,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A250="",D250=""),"",IFERROR(ROUND(D250*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A250,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A250,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A250,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J250" s="13" t="str">
@@ -8835,7 +8951,7 @@
         <v/>
       </c>
       <c r="I251" s="13" t="str">
-        <f aca="false">IF(OR(A251="",D251=""),"",ROUND(D251*INDEX(Programmes!$L$2:$L$8,MATCH(A251,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A251="",D251=""),"",IFERROR(ROUND(D251*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A251,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A251,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A251,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J251" s="13" t="str">
@@ -8856,7 +8972,7 @@
         <v/>
       </c>
       <c r="I252" s="13" t="str">
-        <f aca="false">IF(OR(A252="",D252=""),"",ROUND(D252*INDEX(Programmes!$L$2:$L$8,MATCH(A252,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A252="",D252=""),"",IFERROR(ROUND(D252*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A252,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A252,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A252,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J252" s="13" t="str">
@@ -8877,7 +8993,7 @@
         <v/>
       </c>
       <c r="I253" s="13" t="str">
-        <f aca="false">IF(OR(A253="",D253=""),"",ROUND(D253*INDEX(Programmes!$L$2:$L$8,MATCH(A253,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A253="",D253=""),"",IFERROR(ROUND(D253*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A253,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A253,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A253,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J253" s="13" t="str">
@@ -8898,7 +9014,7 @@
         <v/>
       </c>
       <c r="I254" s="13" t="str">
-        <f aca="false">IF(OR(A254="",D254=""),"",ROUND(D254*INDEX(Programmes!$L$2:$L$8,MATCH(A254,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A254="",D254=""),"",IFERROR(ROUND(D254*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A254,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A254,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A254,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J254" s="13" t="str">
@@ -8919,7 +9035,7 @@
         <v/>
       </c>
       <c r="I255" s="13" t="str">
-        <f aca="false">IF(OR(A255="",D255=""),"",ROUND(D255*INDEX(Programmes!$L$2:$L$8,MATCH(A255,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A255="",D255=""),"",IFERROR(ROUND(D255*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A255,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A255,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A255,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J255" s="13" t="str">
@@ -8940,7 +9056,7 @@
         <v/>
       </c>
       <c r="I256" s="13" t="str">
-        <f aca="false">IF(OR(A256="",D256=""),"",ROUND(D256*INDEX(Programmes!$L$2:$L$8,MATCH(A256,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A256="",D256=""),"",IFERROR(ROUND(D256*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A256,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A256,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A256,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J256" s="13" t="str">
@@ -8961,7 +9077,7 @@
         <v/>
       </c>
       <c r="I257" s="13" t="str">
-        <f aca="false">IF(OR(A257="",D257=""),"",ROUND(D257*INDEX(Programmes!$L$2:$L$8,MATCH(A257,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A257="",D257=""),"",IFERROR(ROUND(D257*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A257,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A257,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A257,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J257" s="13" t="str">
@@ -8982,7 +9098,7 @@
         <v/>
       </c>
       <c r="I258" s="13" t="str">
-        <f aca="false">IF(OR(A258="",D258=""),"",ROUND(D258*INDEX(Programmes!$L$2:$L$8,MATCH(A258,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A258="",D258=""),"",IFERROR(ROUND(D258*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A258,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A258,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A258,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J258" s="13" t="str">
@@ -9003,7 +9119,7 @@
         <v/>
       </c>
       <c r="I259" s="13" t="str">
-        <f aca="false">IF(OR(A259="",D259=""),"",ROUND(D259*INDEX(Programmes!$L$2:$L$8,MATCH(A259,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A259="",D259=""),"",IFERROR(ROUND(D259*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A259,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A259,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A259,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J259" s="13" t="str">
@@ -9024,7 +9140,7 @@
         <v/>
       </c>
       <c r="I260" s="13" t="str">
-        <f aca="false">IF(OR(A260="",D260=""),"",ROUND(D260*INDEX(Programmes!$L$2:$L$8,MATCH(A260,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A260="",D260=""),"",IFERROR(ROUND(D260*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A260,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A260,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A260,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J260" s="13" t="str">
@@ -9045,7 +9161,7 @@
         <v/>
       </c>
       <c r="I261" s="13" t="str">
-        <f aca="false">IF(OR(A261="",D261=""),"",ROUND(D261*INDEX(Programmes!$L$2:$L$8,MATCH(A261,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A261="",D261=""),"",IFERROR(ROUND(D261*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A261,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A261,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A261,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J261" s="13" t="str">
@@ -9066,7 +9182,7 @@
         <v/>
       </c>
       <c r="I262" s="13" t="str">
-        <f aca="false">IF(OR(A262="",D262=""),"",ROUND(D262*INDEX(Programmes!$L$2:$L$8,MATCH(A262,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A262="",D262=""),"",IFERROR(ROUND(D262*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A262,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A262,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A262,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J262" s="13" t="str">
@@ -9087,7 +9203,7 @@
         <v/>
       </c>
       <c r="I263" s="13" t="str">
-        <f aca="false">IF(OR(A263="",D263=""),"",ROUND(D263*INDEX(Programmes!$L$2:$L$8,MATCH(A263,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A263="",D263=""),"",IFERROR(ROUND(D263*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A263,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A263,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A263,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J263" s="13" t="str">
@@ -9108,7 +9224,7 @@
         <v/>
       </c>
       <c r="I264" s="13" t="str">
-        <f aca="false">IF(OR(A264="",D264=""),"",ROUND(D264*INDEX(Programmes!$L$2:$L$8,MATCH(A264,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A264="",D264=""),"",IFERROR(ROUND(D264*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A264,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A264,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A264,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J264" s="13" t="str">
@@ -9129,7 +9245,7 @@
         <v/>
       </c>
       <c r="I265" s="13" t="str">
-        <f aca="false">IF(OR(A265="",D265=""),"",ROUND(D265*INDEX(Programmes!$L$2:$L$8,MATCH(A265,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A265="",D265=""),"",IFERROR(ROUND(D265*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A265,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A265,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A265,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J265" s="13" t="str">
@@ -9150,7 +9266,7 @@
         <v/>
       </c>
       <c r="I266" s="13" t="str">
-        <f aca="false">IF(OR(A266="",D266=""),"",ROUND(D266*INDEX(Programmes!$L$2:$L$8,MATCH(A266,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A266="",D266=""),"",IFERROR(ROUND(D266*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A266,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A266,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A266,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J266" s="13" t="str">
@@ -9171,7 +9287,7 @@
         <v/>
       </c>
       <c r="I267" s="13" t="str">
-        <f aca="false">IF(OR(A267="",D267=""),"",ROUND(D267*INDEX(Programmes!$L$2:$L$8,MATCH(A267,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A267="",D267=""),"",IFERROR(ROUND(D267*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A267,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A267,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A267,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J267" s="13" t="str">
@@ -9192,7 +9308,7 @@
         <v/>
       </c>
       <c r="I268" s="13" t="str">
-        <f aca="false">IF(OR(A268="",D268=""),"",ROUND(D268*INDEX(Programmes!$L$2:$L$8,MATCH(A268,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A268="",D268=""),"",IFERROR(ROUND(D268*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A268,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A268,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A268,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J268" s="13" t="str">
@@ -9213,7 +9329,7 @@
         <v/>
       </c>
       <c r="I269" s="13" t="str">
-        <f aca="false">IF(OR(A269="",D269=""),"",ROUND(D269*INDEX(Programmes!$L$2:$L$8,MATCH(A269,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A269="",D269=""),"",IFERROR(ROUND(D269*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A269,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A269,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A269,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J269" s="13" t="str">
@@ -9234,7 +9350,7 @@
         <v/>
       </c>
       <c r="I270" s="13" t="str">
-        <f aca="false">IF(OR(A270="",D270=""),"",ROUND(D270*INDEX(Programmes!$L$2:$L$8,MATCH(A270,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A270="",D270=""),"",IFERROR(ROUND(D270*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A270,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A270,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A270,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J270" s="13" t="str">
@@ -9255,7 +9371,7 @@
         <v/>
       </c>
       <c r="I271" s="13" t="str">
-        <f aca="false">IF(OR(A271="",D271=""),"",ROUND(D271*INDEX(Programmes!$L$2:$L$8,MATCH(A271,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A271="",D271=""),"",IFERROR(ROUND(D271*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A271,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A271,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A271,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J271" s="13" t="str">
@@ -9276,7 +9392,7 @@
         <v/>
       </c>
       <c r="I272" s="13" t="str">
-        <f aca="false">IF(OR(A272="",D272=""),"",ROUND(D272*INDEX(Programmes!$L$2:$L$8,MATCH(A272,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A272="",D272=""),"",IFERROR(ROUND(D272*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A272,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A272,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A272,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J272" s="13" t="str">
@@ -9297,7 +9413,7 @@
         <v/>
       </c>
       <c r="I273" s="13" t="str">
-        <f aca="false">IF(OR(A273="",D273=""),"",ROUND(D273*INDEX(Programmes!$L$2:$L$8,MATCH(A273,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A273="",D273=""),"",IFERROR(ROUND(D273*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A273,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A273,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A273,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J273" s="13" t="str">
@@ -9318,7 +9434,7 @@
         <v/>
       </c>
       <c r="I274" s="13" t="str">
-        <f aca="false">IF(OR(A274="",D274=""),"",ROUND(D274*INDEX(Programmes!$L$2:$L$8,MATCH(A274,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A274="",D274=""),"",IFERROR(ROUND(D274*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A274,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A274,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A274,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J274" s="13" t="str">
@@ -9339,7 +9455,7 @@
         <v/>
       </c>
       <c r="I275" s="13" t="str">
-        <f aca="false">IF(OR(A275="",D275=""),"",ROUND(D275*INDEX(Programmes!$L$2:$L$8,MATCH(A275,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A275="",D275=""),"",IFERROR(ROUND(D275*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A275,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A275,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A275,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J275" s="13" t="str">
@@ -9360,7 +9476,7 @@
         <v/>
       </c>
       <c r="I276" s="13" t="str">
-        <f aca="false">IF(OR(A276="",D276=""),"",ROUND(D276*INDEX(Programmes!$L$2:$L$8,MATCH(A276,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A276="",D276=""),"",IFERROR(ROUND(D276*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A276,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A276,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A276,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J276" s="13" t="str">
@@ -9381,7 +9497,7 @@
         <v/>
       </c>
       <c r="I277" s="13" t="str">
-        <f aca="false">IF(OR(A277="",D277=""),"",ROUND(D277*INDEX(Programmes!$L$2:$L$8,MATCH(A277,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A277="",D277=""),"",IFERROR(ROUND(D277*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A277,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A277,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A277,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J277" s="13" t="str">
@@ -9402,7 +9518,7 @@
         <v/>
       </c>
       <c r="I278" s="13" t="str">
-        <f aca="false">IF(OR(A278="",D278=""),"",ROUND(D278*INDEX(Programmes!$L$2:$L$8,MATCH(A278,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A278="",D278=""),"",IFERROR(ROUND(D278*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A278,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A278,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A278,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J278" s="13" t="str">
@@ -9423,7 +9539,7 @@
         <v/>
       </c>
       <c r="I279" s="13" t="str">
-        <f aca="false">IF(OR(A279="",D279=""),"",ROUND(D279*INDEX(Programmes!$L$2:$L$8,MATCH(A279,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A279="",D279=""),"",IFERROR(ROUND(D279*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A279,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A279,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A279,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J279" s="13" t="str">
@@ -9444,7 +9560,7 @@
         <v/>
       </c>
       <c r="I280" s="13" t="str">
-        <f aca="false">IF(OR(A280="",D280=""),"",ROUND(D280*INDEX(Programmes!$L$2:$L$8,MATCH(A280,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A280="",D280=""),"",IFERROR(ROUND(D280*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A280,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A280,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A280,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J280" s="13" t="str">
@@ -9465,7 +9581,7 @@
         <v/>
       </c>
       <c r="I281" s="13" t="str">
-        <f aca="false">IF(OR(A281="",D281=""),"",ROUND(D281*INDEX(Programmes!$L$2:$L$8,MATCH(A281,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A281="",D281=""),"",IFERROR(ROUND(D281*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A281,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A281,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A281,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J281" s="13" t="str">
@@ -9486,7 +9602,7 @@
         <v/>
       </c>
       <c r="I282" s="13" t="str">
-        <f aca="false">IF(OR(A282="",D282=""),"",ROUND(D282*INDEX(Programmes!$L$2:$L$8,MATCH(A282,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A282="",D282=""),"",IFERROR(ROUND(D282*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A282,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A282,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A282,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J282" s="13" t="str">
@@ -9507,7 +9623,7 @@
         <v/>
       </c>
       <c r="I283" s="13" t="str">
-        <f aca="false">IF(OR(A283="",D283=""),"",ROUND(D283*INDEX(Programmes!$L$2:$L$8,MATCH(A283,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A283="",D283=""),"",IFERROR(ROUND(D283*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A283,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A283,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A283,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J283" s="13" t="str">
@@ -9528,7 +9644,7 @@
         <v/>
       </c>
       <c r="I284" s="13" t="str">
-        <f aca="false">IF(OR(A284="",D284=""),"",ROUND(D284*INDEX(Programmes!$L$2:$L$8,MATCH(A284,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A284="",D284=""),"",IFERROR(ROUND(D284*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A284,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A284,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A284,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J284" s="13" t="str">
@@ -9549,7 +9665,7 @@
         <v/>
       </c>
       <c r="I285" s="13" t="str">
-        <f aca="false">IF(OR(A285="",D285=""),"",ROUND(D285*INDEX(Programmes!$L$2:$L$8,MATCH(A285,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A285="",D285=""),"",IFERROR(ROUND(D285*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A285,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A285,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A285,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J285" s="13" t="str">
@@ -9570,7 +9686,7 @@
         <v/>
       </c>
       <c r="I286" s="13" t="str">
-        <f aca="false">IF(OR(A286="",D286=""),"",ROUND(D286*INDEX(Programmes!$L$2:$L$8,MATCH(A286,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A286="",D286=""),"",IFERROR(ROUND(D286*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A286,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A286,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A286,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J286" s="13" t="str">
@@ -9591,7 +9707,7 @@
         <v/>
       </c>
       <c r="I287" s="13" t="str">
-        <f aca="false">IF(OR(A287="",D287=""),"",ROUND(D287*INDEX(Programmes!$L$2:$L$8,MATCH(A287,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A287="",D287=""),"",IFERROR(ROUND(D287*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A287,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A287,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A287,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J287" s="13" t="str">
@@ -9612,7 +9728,7 @@
         <v/>
       </c>
       <c r="I288" s="13" t="str">
-        <f aca="false">IF(OR(A288="",D288=""),"",ROUND(D288*INDEX(Programmes!$L$2:$L$8,MATCH(A288,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A288="",D288=""),"",IFERROR(ROUND(D288*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A288,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A288,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A288,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J288" s="13" t="str">
@@ -9633,7 +9749,7 @@
         <v/>
       </c>
       <c r="I289" s="13" t="str">
-        <f aca="false">IF(OR(A289="",D289=""),"",ROUND(D289*INDEX(Programmes!$L$2:$L$8,MATCH(A289,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A289="",D289=""),"",IFERROR(ROUND(D289*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A289,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A289,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A289,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J289" s="13" t="str">
@@ -9654,7 +9770,7 @@
         <v/>
       </c>
       <c r="I290" s="13" t="str">
-        <f aca="false">IF(OR(A290="",D290=""),"",ROUND(D290*INDEX(Programmes!$L$2:$L$8,MATCH(A290,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A290="",D290=""),"",IFERROR(ROUND(D290*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A290,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A290,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A290,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J290" s="13" t="str">
@@ -9675,7 +9791,7 @@
         <v/>
       </c>
       <c r="I291" s="13" t="str">
-        <f aca="false">IF(OR(A291="",D291=""),"",ROUND(D291*INDEX(Programmes!$L$2:$L$8,MATCH(A291,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A291="",D291=""),"",IFERROR(ROUND(D291*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A291,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A291,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A291,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J291" s="13" t="str">
@@ -9696,7 +9812,7 @@
         <v/>
       </c>
       <c r="I292" s="13" t="str">
-        <f aca="false">IF(OR(A292="",D292=""),"",ROUND(D292*INDEX(Programmes!$L$2:$L$8,MATCH(A292,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A292="",D292=""),"",IFERROR(ROUND(D292*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A292,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A292,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A292,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J292" s="13" t="str">
@@ -9717,7 +9833,7 @@
         <v/>
       </c>
       <c r="I293" s="13" t="str">
-        <f aca="false">IF(OR(A293="",D293=""),"",ROUND(D293*INDEX(Programmes!$L$2:$L$8,MATCH(A293,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A293="",D293=""),"",IFERROR(ROUND(D293*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A293,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A293,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A293,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J293" s="13" t="str">
@@ -9738,7 +9854,7 @@
         <v/>
       </c>
       <c r="I294" s="13" t="str">
-        <f aca="false">IF(OR(A294="",D294=""),"",ROUND(D294*INDEX(Programmes!$L$2:$L$8,MATCH(A294,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A294="",D294=""),"",IFERROR(ROUND(D294*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A294,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A294,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A294,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J294" s="13" t="str">
@@ -9759,7 +9875,7 @@
         <v/>
       </c>
       <c r="I295" s="13" t="str">
-        <f aca="false">IF(OR(A295="",D295=""),"",ROUND(D295*INDEX(Programmes!$L$2:$L$8,MATCH(A295,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A295="",D295=""),"",IFERROR(ROUND(D295*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A295,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A295,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A295,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J295" s="13" t="str">
@@ -9780,7 +9896,7 @@
         <v/>
       </c>
       <c r="I296" s="13" t="str">
-        <f aca="false">IF(OR(A296="",D296=""),"",ROUND(D296*INDEX(Programmes!$L$2:$L$8,MATCH(A296,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A296="",D296=""),"",IFERROR(ROUND(D296*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A296,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A296,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A296,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J296" s="13" t="str">
@@ -9801,7 +9917,7 @@
         <v/>
       </c>
       <c r="I297" s="13" t="str">
-        <f aca="false">IF(OR(A297="",D297=""),"",ROUND(D297*INDEX(Programmes!$L$2:$L$8,MATCH(A297,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A297="",D297=""),"",IFERROR(ROUND(D297*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A297,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A297,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A297,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J297" s="13" t="str">
@@ -9822,7 +9938,7 @@
         <v/>
       </c>
       <c r="I298" s="13" t="str">
-        <f aca="false">IF(OR(A298="",D298=""),"",ROUND(D298*INDEX(Programmes!$L$2:$L$8,MATCH(A298,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A298="",D298=""),"",IFERROR(ROUND(D298*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A298,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A298,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A298,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J298" s="13" t="str">
@@ -9843,7 +9959,7 @@
         <v/>
       </c>
       <c r="I299" s="13" t="str">
-        <f aca="false">IF(OR(A299="",D299=""),"",ROUND(D299*INDEX(Programmes!$L$2:$L$8,MATCH(A299,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A299="",D299=""),"",IFERROR(ROUND(D299*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A299,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A299,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A299,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J299" s="13" t="str">
@@ -9864,7 +9980,7 @@
         <v/>
       </c>
       <c r="I300" s="13" t="str">
-        <f aca="false">IF(OR(A300="",D300=""),"",ROUND(D300*INDEX(Programmes!$L$2:$L$8,MATCH(A300,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A300="",D300=""),"",IFERROR(ROUND(D300*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A300,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A300,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A300,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J300" s="13" t="str">
@@ -9885,7 +10001,7 @@
         <v/>
       </c>
       <c r="I301" s="13" t="str">
-        <f aca="false">IF(OR(A301="",D301=""),"",ROUND(D301*INDEX(Programmes!$L$2:$L$8,MATCH(A301,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A301="",D301=""),"",IFERROR(ROUND(D301*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A301,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A301,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A301,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J301" s="13" t="str">
@@ -9906,7 +10022,7 @@
         <v/>
       </c>
       <c r="I302" s="13" t="str">
-        <f aca="false">IF(OR(A302="",D302=""),"",ROUND(D302*INDEX(Programmes!$L$2:$L$8,MATCH(A302,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A302="",D302=""),"",IFERROR(ROUND(D302*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A302,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A302,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A302,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J302" s="13" t="str">
@@ -9927,7 +10043,7 @@
         <v/>
       </c>
       <c r="I303" s="13" t="str">
-        <f aca="false">IF(OR(A303="",D303=""),"",ROUND(D303*INDEX(Programmes!$L$2:$L$8,MATCH(A303,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A303="",D303=""),"",IFERROR(ROUND(D303*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A303,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A303,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A303,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J303" s="13" t="str">
@@ -9948,7 +10064,7 @@
         <v/>
       </c>
       <c r="I304" s="13" t="str">
-        <f aca="false">IF(OR(A304="",D304=""),"",ROUND(D304*INDEX(Programmes!$L$2:$L$8,MATCH(A304,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A304="",D304=""),"",IFERROR(ROUND(D304*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A304,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A304,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A304,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J304" s="13" t="str">
@@ -9969,7 +10085,7 @@
         <v/>
       </c>
       <c r="I305" s="13" t="str">
-        <f aca="false">IF(OR(A305="",D305=""),"",ROUND(D305*INDEX(Programmes!$L$2:$L$8,MATCH(A305,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A305="",D305=""),"",IFERROR(ROUND(D305*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A305,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A305,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A305,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J305" s="13" t="str">
@@ -9990,7 +10106,7 @@
         <v/>
       </c>
       <c r="I306" s="13" t="str">
-        <f aca="false">IF(OR(A306="",D306=""),"",ROUND(D306*INDEX(Programmes!$L$2:$L$8,MATCH(A306,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A306="",D306=""),"",IFERROR(ROUND(D306*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A306,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A306,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A306,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J306" s="13" t="str">
@@ -10011,7 +10127,7 @@
         <v/>
       </c>
       <c r="I307" s="13" t="str">
-        <f aca="false">IF(OR(A307="",D307=""),"",ROUND(D307*INDEX(Programmes!$L$2:$L$8,MATCH(A307,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A307="",D307=""),"",IFERROR(ROUND(D307*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A307,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A307,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A307,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J307" s="13" t="str">
@@ -10032,7 +10148,7 @@
         <v/>
       </c>
       <c r="I308" s="13" t="str">
-        <f aca="false">IF(OR(A308="",D308=""),"",ROUND(D308*INDEX(Programmes!$L$2:$L$8,MATCH(A308,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A308="",D308=""),"",IFERROR(ROUND(D308*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A308,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A308,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A308,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J308" s="13" t="str">
@@ -10053,7 +10169,7 @@
         <v/>
       </c>
       <c r="I309" s="13" t="str">
-        <f aca="false">IF(OR(A309="",D309=""),"",ROUND(D309*INDEX(Programmes!$L$2:$L$8,MATCH(A309,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A309="",D309=""),"",IFERROR(ROUND(D309*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A309,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A309,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A309,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J309" s="13" t="str">
@@ -10074,7 +10190,7 @@
         <v/>
       </c>
       <c r="I310" s="13" t="str">
-        <f aca="false">IF(OR(A310="",D310=""),"",ROUND(D310*INDEX(Programmes!$L$2:$L$8,MATCH(A310,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A310="",D310=""),"",IFERROR(ROUND(D310*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A310,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A310,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A310,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J310" s="13" t="str">
@@ -10095,7 +10211,7 @@
         <v/>
       </c>
       <c r="I311" s="13" t="str">
-        <f aca="false">IF(OR(A311="",D311=""),"",ROUND(D311*INDEX(Programmes!$L$2:$L$8,MATCH(A311,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A311="",D311=""),"",IFERROR(ROUND(D311*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A311,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A311,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A311,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J311" s="13" t="str">
@@ -10116,7 +10232,7 @@
         <v/>
       </c>
       <c r="I312" s="13" t="str">
-        <f aca="false">IF(OR(A312="",D312=""),"",ROUND(D312*INDEX(Programmes!$L$2:$L$8,MATCH(A312,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A312="",D312=""),"",IFERROR(ROUND(D312*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A312,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A312,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A312,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J312" s="13" t="str">
@@ -10137,7 +10253,7 @@
         <v/>
       </c>
       <c r="I313" s="13" t="str">
-        <f aca="false">IF(OR(A313="",D313=""),"",ROUND(D313*INDEX(Programmes!$L$2:$L$8,MATCH(A313,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A313="",D313=""),"",IFERROR(ROUND(D313*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A313,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A313,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A313,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J313" s="13" t="str">
@@ -10158,7 +10274,7 @@
         <v/>
       </c>
       <c r="I314" s="13" t="str">
-        <f aca="false">IF(OR(A314="",D314=""),"",ROUND(D314*INDEX(Programmes!$L$2:$L$8,MATCH(A314,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A314="",D314=""),"",IFERROR(ROUND(D314*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A314,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A314,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A314,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J314" s="13" t="str">
@@ -10179,7 +10295,7 @@
         <v/>
       </c>
       <c r="I315" s="13" t="str">
-        <f aca="false">IF(OR(A315="",D315=""),"",ROUND(D315*INDEX(Programmes!$L$2:$L$8,MATCH(A315,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A315="",D315=""),"",IFERROR(ROUND(D315*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A315,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A315,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A315,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J315" s="13" t="str">
@@ -10200,7 +10316,7 @@
         <v/>
       </c>
       <c r="I316" s="13" t="str">
-        <f aca="false">IF(OR(A316="",D316=""),"",ROUND(D316*INDEX(Programmes!$L$2:$L$8,MATCH(A316,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A316="",D316=""),"",IFERROR(ROUND(D316*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A316,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A316,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A316,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J316" s="13" t="str">
@@ -10221,7 +10337,7 @@
         <v/>
       </c>
       <c r="I317" s="13" t="str">
-        <f aca="false">IF(OR(A317="",D317=""),"",ROUND(D317*INDEX(Programmes!$L$2:$L$8,MATCH(A317,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A317="",D317=""),"",IFERROR(ROUND(D317*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A317,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A317,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A317,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J317" s="13" t="str">
@@ -10242,7 +10358,7 @@
         <v/>
       </c>
       <c r="I318" s="13" t="str">
-        <f aca="false">IF(OR(A318="",D318=""),"",ROUND(D318*INDEX(Programmes!$L$2:$L$8,MATCH(A318,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A318="",D318=""),"",IFERROR(ROUND(D318*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A318,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A318,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A318,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J318" s="13" t="str">
@@ -10263,7 +10379,7 @@
         <v/>
       </c>
       <c r="I319" s="13" t="str">
-        <f aca="false">IF(OR(A319="",D319=""),"",ROUND(D319*INDEX(Programmes!$L$2:$L$8,MATCH(A319,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A319="",D319=""),"",IFERROR(ROUND(D319*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A319,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A319,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A319,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J319" s="13" t="str">
@@ -10284,7 +10400,7 @@
         <v/>
       </c>
       <c r="I320" s="13" t="str">
-        <f aca="false">IF(OR(A320="",D320=""),"",ROUND(D320*INDEX(Programmes!$L$2:$L$8,MATCH(A320,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A320="",D320=""),"",IFERROR(ROUND(D320*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A320,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A320,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A320,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J320" s="13" t="str">
@@ -10305,7 +10421,7 @@
         <v/>
       </c>
       <c r="I321" s="13" t="str">
-        <f aca="false">IF(OR(A321="",D321=""),"",ROUND(D321*INDEX(Programmes!$L$2:$L$8,MATCH(A321,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A321="",D321=""),"",IFERROR(ROUND(D321*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A321,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A321,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A321,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J321" s="13" t="str">
@@ -10326,7 +10442,7 @@
         <v/>
       </c>
       <c r="I322" s="13" t="str">
-        <f aca="false">IF(OR(A322="",D322=""),"",ROUND(D322*INDEX(Programmes!$L$2:$L$8,MATCH(A322,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A322="",D322=""),"",IFERROR(ROUND(D322*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A322,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A322,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A322,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J322" s="13" t="str">
@@ -10347,7 +10463,7 @@
         <v/>
       </c>
       <c r="I323" s="13" t="str">
-        <f aca="false">IF(OR(A323="",D323=""),"",ROUND(D323*INDEX(Programmes!$L$2:$L$8,MATCH(A323,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A323="",D323=""),"",IFERROR(ROUND(D323*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A323,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A323,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A323,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J323" s="13" t="str">
@@ -10368,7 +10484,7 @@
         <v/>
       </c>
       <c r="I324" s="13" t="str">
-        <f aca="false">IF(OR(A324="",D324=""),"",ROUND(D324*INDEX(Programmes!$L$2:$L$8,MATCH(A324,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A324="",D324=""),"",IFERROR(ROUND(D324*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A324,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A324,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A324,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J324" s="13" t="str">
@@ -10389,7 +10505,7 @@
         <v/>
       </c>
       <c r="I325" s="13" t="str">
-        <f aca="false">IF(OR(A325="",D325=""),"",ROUND(D325*INDEX(Programmes!$L$2:$L$8,MATCH(A325,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A325="",D325=""),"",IFERROR(ROUND(D325*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A325,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A325,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A325,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J325" s="13" t="str">
@@ -10410,7 +10526,7 @@
         <v/>
       </c>
       <c r="I326" s="13" t="str">
-        <f aca="false">IF(OR(A326="",D326=""),"",ROUND(D326*INDEX(Programmes!$L$2:$L$8,MATCH(A326,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A326="",D326=""),"",IFERROR(ROUND(D326*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A326,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A326,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A326,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J326" s="13" t="str">
@@ -10431,7 +10547,7 @@
         <v/>
       </c>
       <c r="I327" s="13" t="str">
-        <f aca="false">IF(OR(A327="",D327=""),"",ROUND(D327*INDEX(Programmes!$L$2:$L$8,MATCH(A327,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A327="",D327=""),"",IFERROR(ROUND(D327*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A327,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A327,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A327,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J327" s="13" t="str">
@@ -10452,7 +10568,7 @@
         <v/>
       </c>
       <c r="I328" s="13" t="str">
-        <f aca="false">IF(OR(A328="",D328=""),"",ROUND(D328*INDEX(Programmes!$L$2:$L$8,MATCH(A328,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A328="",D328=""),"",IFERROR(ROUND(D328*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A328,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A328,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A328,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J328" s="13" t="str">
@@ -10473,7 +10589,7 @@
         <v/>
       </c>
       <c r="I329" s="13" t="str">
-        <f aca="false">IF(OR(A329="",D329=""),"",ROUND(D329*INDEX(Programmes!$L$2:$L$8,MATCH(A329,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A329="",D329=""),"",IFERROR(ROUND(D329*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A329,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A329,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A329,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J329" s="13" t="str">
@@ -10494,7 +10610,7 @@
         <v/>
       </c>
       <c r="I330" s="13" t="str">
-        <f aca="false">IF(OR(A330="",D330=""),"",ROUND(D330*INDEX(Programmes!$L$2:$L$8,MATCH(A330,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A330="",D330=""),"",IFERROR(ROUND(D330*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A330,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A330,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A330,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J330" s="13" t="str">
@@ -10515,7 +10631,7 @@
         <v/>
       </c>
       <c r="I331" s="13" t="str">
-        <f aca="false">IF(OR(A331="",D331=""),"",ROUND(D331*INDEX(Programmes!$L$2:$L$8,MATCH(A331,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A331="",D331=""),"",IFERROR(ROUND(D331*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A331,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A331,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A331,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J331" s="13" t="str">
@@ -10536,7 +10652,7 @@
         <v/>
       </c>
       <c r="I332" s="13" t="str">
-        <f aca="false">IF(OR(A332="",D332=""),"",ROUND(D332*INDEX(Programmes!$L$2:$L$8,MATCH(A332,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A332="",D332=""),"",IFERROR(ROUND(D332*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A332,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A332,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A332,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J332" s="13" t="str">
@@ -10557,7 +10673,7 @@
         <v/>
       </c>
       <c r="I333" s="13" t="str">
-        <f aca="false">IF(OR(A333="",D333=""),"",ROUND(D333*INDEX(Programmes!$L$2:$L$8,MATCH(A333,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A333="",D333=""),"",IFERROR(ROUND(D333*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A333,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A333,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A333,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J333" s="13" t="str">
@@ -10578,7 +10694,7 @@
         <v/>
       </c>
       <c r="I334" s="13" t="str">
-        <f aca="false">IF(OR(A334="",D334=""),"",ROUND(D334*INDEX(Programmes!$L$2:$L$8,MATCH(A334,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A334="",D334=""),"",IFERROR(ROUND(D334*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A334,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A334,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A334,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J334" s="13" t="str">
@@ -10599,7 +10715,7 @@
         <v/>
       </c>
       <c r="I335" s="13" t="str">
-        <f aca="false">IF(OR(A335="",D335=""),"",ROUND(D335*INDEX(Programmes!$L$2:$L$8,MATCH(A335,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A335="",D335=""),"",IFERROR(ROUND(D335*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A335,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A335,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A335,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J335" s="13" t="str">
@@ -10620,7 +10736,7 @@
         <v/>
       </c>
       <c r="I336" s="13" t="str">
-        <f aca="false">IF(OR(A336="",D336=""),"",ROUND(D336*INDEX(Programmes!$L$2:$L$8,MATCH(A336,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A336="",D336=""),"",IFERROR(ROUND(D336*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A336,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A336,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A336,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J336" s="13" t="str">
@@ -10641,7 +10757,7 @@
         <v/>
       </c>
       <c r="I337" s="13" t="str">
-        <f aca="false">IF(OR(A337="",D337=""),"",ROUND(D337*INDEX(Programmes!$L$2:$L$8,MATCH(A337,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A337="",D337=""),"",IFERROR(ROUND(D337*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A337,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A337,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A337,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J337" s="13" t="str">
@@ -10662,7 +10778,7 @@
         <v/>
       </c>
       <c r="I338" s="13" t="str">
-        <f aca="false">IF(OR(A338="",D338=""),"",ROUND(D338*INDEX(Programmes!$L$2:$L$8,MATCH(A338,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A338="",D338=""),"",IFERROR(ROUND(D338*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A338,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A338,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A338,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J338" s="13" t="str">
@@ -10683,7 +10799,7 @@
         <v/>
       </c>
       <c r="I339" s="13" t="str">
-        <f aca="false">IF(OR(A339="",D339=""),"",ROUND(D339*INDEX(Programmes!$L$2:$L$8,MATCH(A339,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A339="",D339=""),"",IFERROR(ROUND(D339*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A339,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A339,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A339,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J339" s="13" t="str">
@@ -10704,7 +10820,7 @@
         <v/>
       </c>
       <c r="I340" s="13" t="str">
-        <f aca="false">IF(OR(A340="",D340=""),"",ROUND(D340*INDEX(Programmes!$L$2:$L$8,MATCH(A340,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A340="",D340=""),"",IFERROR(ROUND(D340*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A340,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A340,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A340,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J340" s="13" t="str">
@@ -10725,7 +10841,7 @@
         <v/>
       </c>
       <c r="I341" s="13" t="str">
-        <f aca="false">IF(OR(A341="",D341=""),"",ROUND(D341*INDEX(Programmes!$L$2:$L$8,MATCH(A341,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A341="",D341=""),"",IFERROR(ROUND(D341*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A341,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A341,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A341,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J341" s="13" t="str">
@@ -10746,7 +10862,7 @@
         <v/>
       </c>
       <c r="I342" s="13" t="str">
-        <f aca="false">IF(OR(A342="",D342=""),"",ROUND(D342*INDEX(Programmes!$L$2:$L$8,MATCH(A342,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A342="",D342=""),"",IFERROR(ROUND(D342*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A342,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A342,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A342,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J342" s="13" t="str">
@@ -10767,7 +10883,7 @@
         <v/>
       </c>
       <c r="I343" s="13" t="str">
-        <f aca="false">IF(OR(A343="",D343=""),"",ROUND(D343*INDEX(Programmes!$L$2:$L$8,MATCH(A343,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A343="",D343=""),"",IFERROR(ROUND(D343*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A343,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A343,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A343,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J343" s="13" t="str">
@@ -10788,7 +10904,7 @@
         <v/>
       </c>
       <c r="I344" s="13" t="str">
-        <f aca="false">IF(OR(A344="",D344=""),"",ROUND(D344*INDEX(Programmes!$L$2:$L$8,MATCH(A344,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A344="",D344=""),"",IFERROR(ROUND(D344*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A344,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A344,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A344,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J344" s="13" t="str">
@@ -10809,7 +10925,7 @@
         <v/>
       </c>
       <c r="I345" s="13" t="str">
-        <f aca="false">IF(OR(A345="",D345=""),"",ROUND(D345*INDEX(Programmes!$L$2:$L$8,MATCH(A345,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A345="",D345=""),"",IFERROR(ROUND(D345*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A345,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A345,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A345,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J345" s="13" t="str">
@@ -10830,7 +10946,7 @@
         <v/>
       </c>
       <c r="I346" s="13" t="str">
-        <f aca="false">IF(OR(A346="",D346=""),"",ROUND(D346*INDEX(Programmes!$L$2:$L$8,MATCH(A346,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A346="",D346=""),"",IFERROR(ROUND(D346*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A346,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A346,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A346,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J346" s="13" t="str">
@@ -10851,7 +10967,7 @@
         <v/>
       </c>
       <c r="I347" s="13" t="str">
-        <f aca="false">IF(OR(A347="",D347=""),"",ROUND(D347*INDEX(Programmes!$L$2:$L$8,MATCH(A347,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A347="",D347=""),"",IFERROR(ROUND(D347*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A347,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A347,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A347,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J347" s="13" t="str">
@@ -10872,7 +10988,7 @@
         <v/>
       </c>
       <c r="I348" s="13" t="str">
-        <f aca="false">IF(OR(A348="",D348=""),"",ROUND(D348*INDEX(Programmes!$L$2:$L$8,MATCH(A348,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A348="",D348=""),"",IFERROR(ROUND(D348*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A348,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A348,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A348,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J348" s="13" t="str">
@@ -10893,7 +11009,7 @@
         <v/>
       </c>
       <c r="I349" s="13" t="str">
-        <f aca="false">IF(OR(A349="",D349=""),"",ROUND(D349*INDEX(Programmes!$L$2:$L$8,MATCH(A349,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A349="",D349=""),"",IFERROR(ROUND(D349*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A349,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A349,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A349,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J349" s="13" t="str">
@@ -10914,7 +11030,7 @@
         <v/>
       </c>
       <c r="I350" s="13" t="str">
-        <f aca="false">IF(OR(A350="",D350=""),"",ROUND(D350*INDEX(Programmes!$L$2:$L$8,MATCH(A350,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A350="",D350=""),"",IFERROR(ROUND(D350*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A350,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A350,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A350,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J350" s="13" t="str">
@@ -10935,7 +11051,7 @@
         <v/>
       </c>
       <c r="I351" s="13" t="str">
-        <f aca="false">IF(OR(A351="",D351=""),"",ROUND(D351*INDEX(Programmes!$L$2:$L$8,MATCH(A351,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A351="",D351=""),"",IFERROR(ROUND(D351*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A351,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A351,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A351,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J351" s="13" t="str">
@@ -10956,7 +11072,7 @@
         <v/>
       </c>
       <c r="I352" s="13" t="str">
-        <f aca="false">IF(OR(A352="",D352=""),"",ROUND(D352*INDEX(Programmes!$L$2:$L$8,MATCH(A352,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A352="",D352=""),"",IFERROR(ROUND(D352*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A352,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A352,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A352,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J352" s="13" t="str">
@@ -10977,7 +11093,7 @@
         <v/>
       </c>
       <c r="I353" s="13" t="str">
-        <f aca="false">IF(OR(A353="",D353=""),"",ROUND(D353*INDEX(Programmes!$L$2:$L$8,MATCH(A353,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A353="",D353=""),"",IFERROR(ROUND(D353*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A353,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A353,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A353,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J353" s="13" t="str">
@@ -10998,7 +11114,7 @@
         <v/>
       </c>
       <c r="I354" s="13" t="str">
-        <f aca="false">IF(OR(A354="",D354=""),"",ROUND(D354*INDEX(Programmes!$L$2:$L$8,MATCH(A354,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A354="",D354=""),"",IFERROR(ROUND(D354*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A354,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A354,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A354,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J354" s="13" t="str">
@@ -11019,7 +11135,7 @@
         <v/>
       </c>
       <c r="I355" s="13" t="str">
-        <f aca="false">IF(OR(A355="",D355=""),"",ROUND(D355*INDEX(Programmes!$L$2:$L$8,MATCH(A355,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A355="",D355=""),"",IFERROR(ROUND(D355*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A355,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A355,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A355,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J355" s="13" t="str">
@@ -11040,7 +11156,7 @@
         <v/>
       </c>
       <c r="I356" s="13" t="str">
-        <f aca="false">IF(OR(A356="",D356=""),"",ROUND(D356*INDEX(Programmes!$L$2:$L$8,MATCH(A356,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A356="",D356=""),"",IFERROR(ROUND(D356*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A356,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A356,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A356,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J356" s="13" t="str">
@@ -11061,7 +11177,7 @@
         <v/>
       </c>
       <c r="I357" s="13" t="str">
-        <f aca="false">IF(OR(A357="",D357=""),"",ROUND(D357*INDEX(Programmes!$L$2:$L$8,MATCH(A357,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A357="",D357=""),"",IFERROR(ROUND(D357*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A357,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A357,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A357,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J357" s="13" t="str">
@@ -11082,7 +11198,7 @@
         <v/>
       </c>
       <c r="I358" s="13" t="str">
-        <f aca="false">IF(OR(A358="",D358=""),"",ROUND(D358*INDEX(Programmes!$L$2:$L$8,MATCH(A358,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A358="",D358=""),"",IFERROR(ROUND(D358*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A358,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A358,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A358,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J358" s="13" t="str">
@@ -11103,7 +11219,7 @@
         <v/>
       </c>
       <c r="I359" s="13" t="str">
-        <f aca="false">IF(OR(A359="",D359=""),"",ROUND(D359*INDEX(Programmes!$L$2:$L$8,MATCH(A359,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A359="",D359=""),"",IFERROR(ROUND(D359*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A359,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A359,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A359,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J359" s="13" t="str">
@@ -11124,7 +11240,7 @@
         <v/>
       </c>
       <c r="I360" s="13" t="str">
-        <f aca="false">IF(OR(A360="",D360=""),"",ROUND(D360*INDEX(Programmes!$L$2:$L$8,MATCH(A360,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A360="",D360=""),"",IFERROR(ROUND(D360*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A360,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A360,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A360,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J360" s="13" t="str">
@@ -11145,7 +11261,7 @@
         <v/>
       </c>
       <c r="I361" s="13" t="str">
-        <f aca="false">IF(OR(A361="",D361=""),"",ROUND(D361*INDEX(Programmes!$L$2:$L$8,MATCH(A361,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A361="",D361=""),"",IFERROR(ROUND(D361*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A361,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A361,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A361,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J361" s="13" t="str">
@@ -11166,7 +11282,7 @@
         <v/>
       </c>
       <c r="I362" s="13" t="str">
-        <f aca="false">IF(OR(A362="",D362=""),"",ROUND(D362*INDEX(Programmes!$L$2:$L$8,MATCH(A362,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A362="",D362=""),"",IFERROR(ROUND(D362*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A362,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A362,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A362,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J362" s="13" t="str">
@@ -11187,7 +11303,7 @@
         <v/>
       </c>
       <c r="I363" s="13" t="str">
-        <f aca="false">IF(OR(A363="",D363=""),"",ROUND(D363*INDEX(Programmes!$L$2:$L$8,MATCH(A363,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A363="",D363=""),"",IFERROR(ROUND(D363*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A363,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A363,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A363,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J363" s="13" t="str">
@@ -11208,7 +11324,7 @@
         <v/>
       </c>
       <c r="I364" s="13" t="str">
-        <f aca="false">IF(OR(A364="",D364=""),"",ROUND(D364*INDEX(Programmes!$L$2:$L$8,MATCH(A364,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A364="",D364=""),"",IFERROR(ROUND(D364*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A364,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A364,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A364,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J364" s="13" t="str">
@@ -11229,7 +11345,7 @@
         <v/>
       </c>
       <c r="I365" s="13" t="str">
-        <f aca="false">IF(OR(A365="",D365=""),"",ROUND(D365*INDEX(Programmes!$L$2:$L$8,MATCH(A365,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A365="",D365=""),"",IFERROR(ROUND(D365*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A365,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A365,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A365,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J365" s="13" t="str">
@@ -11250,7 +11366,7 @@
         <v/>
       </c>
       <c r="I366" s="13" t="str">
-        <f aca="false">IF(OR(A366="",D366=""),"",ROUND(D366*INDEX(Programmes!$L$2:$L$8,MATCH(A366,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A366="",D366=""),"",IFERROR(ROUND(D366*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A366,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A366,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A366,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J366" s="13" t="str">
@@ -11271,7 +11387,7 @@
         <v/>
       </c>
       <c r="I367" s="13" t="str">
-        <f aca="false">IF(OR(A367="",D367=""),"",ROUND(D367*INDEX(Programmes!$L$2:$L$8,MATCH(A367,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A367="",D367=""),"",IFERROR(ROUND(D367*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A367,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A367,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A367,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J367" s="13" t="str">
@@ -11292,7 +11408,7 @@
         <v/>
       </c>
       <c r="I368" s="13" t="str">
-        <f aca="false">IF(OR(A368="",D368=""),"",ROUND(D368*INDEX(Programmes!$L$2:$L$8,MATCH(A368,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A368="",D368=""),"",IFERROR(ROUND(D368*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A368,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A368,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A368,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J368" s="13" t="str">
@@ -11313,7 +11429,7 @@
         <v/>
       </c>
       <c r="I369" s="13" t="str">
-        <f aca="false">IF(OR(A369="",D369=""),"",ROUND(D369*INDEX(Programmes!$L$2:$L$8,MATCH(A369,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A369="",D369=""),"",IFERROR(ROUND(D369*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A369,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A369,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A369,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J369" s="13" t="str">
@@ -11334,7 +11450,7 @@
         <v/>
       </c>
       <c r="I370" s="13" t="str">
-        <f aca="false">IF(OR(A370="",D370=""),"",ROUND(D370*INDEX(Programmes!$L$2:$L$8,MATCH(A370,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A370="",D370=""),"",IFERROR(ROUND(D370*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A370,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A370,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A370,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J370" s="13" t="str">
@@ -11355,7 +11471,7 @@
         <v/>
       </c>
       <c r="I371" s="13" t="str">
-        <f aca="false">IF(OR(A371="",D371=""),"",ROUND(D371*INDEX(Programmes!$L$2:$L$8,MATCH(A371,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A371="",D371=""),"",IFERROR(ROUND(D371*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A371,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A371,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A371,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J371" s="13" t="str">
@@ -11376,7 +11492,7 @@
         <v/>
       </c>
       <c r="I372" s="13" t="str">
-        <f aca="false">IF(OR(A372="",D372=""),"",ROUND(D372*INDEX(Programmes!$L$2:$L$8,MATCH(A372,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A372="",D372=""),"",IFERROR(ROUND(D372*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A372,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A372,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A372,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J372" s="13" t="str">
@@ -11397,7 +11513,7 @@
         <v/>
       </c>
       <c r="I373" s="13" t="str">
-        <f aca="false">IF(OR(A373="",D373=""),"",ROUND(D373*INDEX(Programmes!$L$2:$L$8,MATCH(A373,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A373="",D373=""),"",IFERROR(ROUND(D373*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A373,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A373,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A373,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J373" s="13" t="str">
@@ -11418,7 +11534,7 @@
         <v/>
       </c>
       <c r="I374" s="13" t="str">
-        <f aca="false">IF(OR(A374="",D374=""),"",ROUND(D374*INDEX(Programmes!$L$2:$L$8,MATCH(A374,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A374="",D374=""),"",IFERROR(ROUND(D374*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A374,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A374,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A374,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J374" s="13" t="str">
@@ -11439,7 +11555,7 @@
         <v/>
       </c>
       <c r="I375" s="13" t="str">
-        <f aca="false">IF(OR(A375="",D375=""),"",ROUND(D375*INDEX(Programmes!$L$2:$L$8,MATCH(A375,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A375="",D375=""),"",IFERROR(ROUND(D375*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A375,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A375,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A375,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J375" s="13" t="str">
@@ -11460,7 +11576,7 @@
         <v/>
       </c>
       <c r="I376" s="13" t="str">
-        <f aca="false">IF(OR(A376="",D376=""),"",ROUND(D376*INDEX(Programmes!$L$2:$L$8,MATCH(A376,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A376="",D376=""),"",IFERROR(ROUND(D376*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A376,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A376,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A376,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J376" s="13" t="str">
@@ -11481,7 +11597,7 @@
         <v/>
       </c>
       <c r="I377" s="13" t="str">
-        <f aca="false">IF(OR(A377="",D377=""),"",ROUND(D377*INDEX(Programmes!$L$2:$L$8,MATCH(A377,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A377="",D377=""),"",IFERROR(ROUND(D377*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A377,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A377,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A377,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J377" s="13" t="str">
@@ -11502,7 +11618,7 @@
         <v/>
       </c>
       <c r="I378" s="13" t="str">
-        <f aca="false">IF(OR(A378="",D378=""),"",ROUND(D378*INDEX(Programmes!$L$2:$L$8,MATCH(A378,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A378="",D378=""),"",IFERROR(ROUND(D378*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A378,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A378,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A378,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J378" s="13" t="str">
@@ -11523,7 +11639,7 @@
         <v/>
       </c>
       <c r="I379" s="13" t="str">
-        <f aca="false">IF(OR(A379="",D379=""),"",ROUND(D379*INDEX(Programmes!$L$2:$L$8,MATCH(A379,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A379="",D379=""),"",IFERROR(ROUND(D379*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A379,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A379,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A379,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J379" s="13" t="str">
@@ -11544,7 +11660,7 @@
         <v/>
       </c>
       <c r="I380" s="13" t="str">
-        <f aca="false">IF(OR(A380="",D380=""),"",ROUND(D380*INDEX(Programmes!$L$2:$L$8,MATCH(A380,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A380="",D380=""),"",IFERROR(ROUND(D380*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A380,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A380,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A380,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J380" s="13" t="str">
@@ -11565,7 +11681,7 @@
         <v/>
       </c>
       <c r="I381" s="13" t="str">
-        <f aca="false">IF(OR(A381="",D381=""),"",ROUND(D381*INDEX(Programmes!$L$2:$L$8,MATCH(A381,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A381="",D381=""),"",IFERROR(ROUND(D381*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A381,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A381,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A381,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J381" s="13" t="str">
@@ -11586,7 +11702,7 @@
         <v/>
       </c>
       <c r="I382" s="13" t="str">
-        <f aca="false">IF(OR(A382="",D382=""),"",ROUND(D382*INDEX(Programmes!$L$2:$L$8,MATCH(A382,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A382="",D382=""),"",IFERROR(ROUND(D382*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A382,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A382,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A382,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J382" s="13" t="str">
@@ -11607,7 +11723,7 @@
         <v/>
       </c>
       <c r="I383" s="13" t="str">
-        <f aca="false">IF(OR(A383="",D383=""),"",ROUND(D383*INDEX(Programmes!$L$2:$L$8,MATCH(A383,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A383="",D383=""),"",IFERROR(ROUND(D383*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A383,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A383,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A383,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J383" s="13" t="str">
@@ -11628,7 +11744,7 @@
         <v/>
       </c>
       <c r="I384" s="13" t="str">
-        <f aca="false">IF(OR(A384="",D384=""),"",ROUND(D384*INDEX(Programmes!$L$2:$L$8,MATCH(A384,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A384="",D384=""),"",IFERROR(ROUND(D384*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A384,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A384,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A384,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J384" s="13" t="str">
@@ -11649,7 +11765,7 @@
         <v/>
       </c>
       <c r="I385" s="13" t="str">
-        <f aca="false">IF(OR(A385="",D385=""),"",ROUND(D385*INDEX(Programmes!$L$2:$L$8,MATCH(A385,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A385="",D385=""),"",IFERROR(ROUND(D385*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A385,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A385,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A385,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J385" s="13" t="str">
@@ -11670,7 +11786,7 @@
         <v/>
       </c>
       <c r="I386" s="13" t="str">
-        <f aca="false">IF(OR(A386="",D386=""),"",ROUND(D386*INDEX(Programmes!$L$2:$L$8,MATCH(A386,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A386="",D386=""),"",IFERROR(ROUND(D386*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A386,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A386,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A386,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J386" s="13" t="str">
@@ -11691,7 +11807,7 @@
         <v/>
       </c>
       <c r="I387" s="13" t="str">
-        <f aca="false">IF(OR(A387="",D387=""),"",ROUND(D387*INDEX(Programmes!$L$2:$L$8,MATCH(A387,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A387="",D387=""),"",IFERROR(ROUND(D387*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A387,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A387,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A387,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J387" s="13" t="str">
@@ -11712,7 +11828,7 @@
         <v/>
       </c>
       <c r="I388" s="13" t="str">
-        <f aca="false">IF(OR(A388="",D388=""),"",ROUND(D388*INDEX(Programmes!$L$2:$L$8,MATCH(A388,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A388="",D388=""),"",IFERROR(ROUND(D388*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A388,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A388,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A388,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J388" s="13" t="str">
@@ -11733,7 +11849,7 @@
         <v/>
       </c>
       <c r="I389" s="13" t="str">
-        <f aca="false">IF(OR(A389="",D389=""),"",ROUND(D389*INDEX(Programmes!$L$2:$L$8,MATCH(A389,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A389="",D389=""),"",IFERROR(ROUND(D389*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A389,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A389,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A389,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J389" s="13" t="str">
@@ -11754,7 +11870,7 @@
         <v/>
       </c>
       <c r="I390" s="13" t="str">
-        <f aca="false">IF(OR(A390="",D390=""),"",ROUND(D390*INDEX(Programmes!$L$2:$L$8,MATCH(A390,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A390="",D390=""),"",IFERROR(ROUND(D390*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A390,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A390,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A390,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J390" s="13" t="str">
@@ -11775,7 +11891,7 @@
         <v/>
       </c>
       <c r="I391" s="13" t="str">
-        <f aca="false">IF(OR(A391="",D391=""),"",ROUND(D391*INDEX(Programmes!$L$2:$L$8,MATCH(A391,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A391="",D391=""),"",IFERROR(ROUND(D391*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A391,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A391,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A391,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J391" s="13" t="str">
@@ -11796,7 +11912,7 @@
         <v/>
       </c>
       <c r="I392" s="13" t="str">
-        <f aca="false">IF(OR(A392="",D392=""),"",ROUND(D392*INDEX(Programmes!$L$2:$L$8,MATCH(A392,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A392="",D392=""),"",IFERROR(ROUND(D392*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A392,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A392,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A392,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J392" s="13" t="str">
@@ -11817,7 +11933,7 @@
         <v/>
       </c>
       <c r="I393" s="13" t="str">
-        <f aca="false">IF(OR(A393="",D393=""),"",ROUND(D393*INDEX(Programmes!$L$2:$L$8,MATCH(A393,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A393="",D393=""),"",IFERROR(ROUND(D393*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A393,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A393,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A393,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J393" s="13" t="str">
@@ -11838,7 +11954,7 @@
         <v/>
       </c>
       <c r="I394" s="13" t="str">
-        <f aca="false">IF(OR(A394="",D394=""),"",ROUND(D394*INDEX(Programmes!$L$2:$L$8,MATCH(A394,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A394="",D394=""),"",IFERROR(ROUND(D394*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A394,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A394,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A394,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J394" s="13" t="str">
@@ -11859,7 +11975,7 @@
         <v/>
       </c>
       <c r="I395" s="13" t="str">
-        <f aca="false">IF(OR(A395="",D395=""),"",ROUND(D395*INDEX(Programmes!$L$2:$L$8,MATCH(A395,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A395="",D395=""),"",IFERROR(ROUND(D395*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A395,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A395,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A395,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J395" s="13" t="str">
@@ -11880,7 +11996,7 @@
         <v/>
       </c>
       <c r="I396" s="13" t="str">
-        <f aca="false">IF(OR(A396="",D396=""),"",ROUND(D396*INDEX(Programmes!$L$2:$L$8,MATCH(A396,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A396="",D396=""),"",IFERROR(ROUND(D396*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A396,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A396,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A396,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J396" s="13" t="str">
@@ -11901,7 +12017,7 @@
         <v/>
       </c>
       <c r="I397" s="13" t="str">
-        <f aca="false">IF(OR(A397="",D397=""),"",ROUND(D397*INDEX(Programmes!$L$2:$L$8,MATCH(A397,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A397="",D397=""),"",IFERROR(ROUND(D397*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A397,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A397,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A397,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J397" s="13" t="str">
@@ -11922,7 +12038,7 @@
         <v/>
       </c>
       <c r="I398" s="13" t="str">
-        <f aca="false">IF(OR(A398="",D398=""),"",ROUND(D398*INDEX(Programmes!$L$2:$L$8,MATCH(A398,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A398="",D398=""),"",IFERROR(ROUND(D398*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A398,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A398,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A398,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J398" s="13" t="str">
@@ -11943,7 +12059,7 @@
         <v/>
       </c>
       <c r="I399" s="13" t="str">
-        <f aca="false">IF(OR(A399="",D399=""),"",ROUND(D399*INDEX(Programmes!$L$2:$L$8,MATCH(A399,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A399="",D399=""),"",IFERROR(ROUND(D399*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A399,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A399,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A399,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J399" s="13" t="str">
@@ -11964,7 +12080,7 @@
         <v/>
       </c>
       <c r="I400" s="13" t="str">
-        <f aca="false">IF(OR(A400="",D400=""),"",ROUND(D400*INDEX(Programmes!$L$2:$L$8,MATCH(A400,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A400="",D400=""),"",IFERROR(ROUND(D400*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A400,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A400,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A400,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J400" s="13" t="str">
@@ -11985,7 +12101,7 @@
         <v/>
       </c>
       <c r="I401" s="13" t="str">
-        <f aca="false">IF(OR(A401="",D401=""),"",ROUND(D401*INDEX(Programmes!$L$2:$L$8,MATCH(A401,Programmes!$A$2:$A$8,0)),1))</f>
+        <f aca="false">IF(OR(A401="",D401=""),"",IFERROR(ROUND(D401*IF(INDEX(Programmes!$L$2:$L$9,MATCH(A401,Programmes!$A$2:$A$9,0))="",INDEX(Programmes!$K$2:$K$9,MATCH(A401,Programmes!$A$2:$A$9,0)),INDEX(Programmes!$L$2:$L$9,MATCH(A401,Programmes!$A$2:$A$9,0))),1),""))</f>
         <v/>
       </c>
       <c r="J401" s="13" t="str">
@@ -11996,7 +12112,7 @@
   </sheetData>
   <dataValidations count="3">
     <dataValidation allowBlank="true" error="Pick one of the options in the drop-down." errorStyle="stop" errorTitle="Choose from the list" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A2:A401" type="list">
-      <formula1>Lists!$A$2:$A$8</formula1>
+      <formula1>Lists!$A$2:$A$9</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Pick one of the options in the drop-down." errorStyle="stop" errorTitle="Choose from the list" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C2:C401" type="list">
@@ -12041,27 +12157,27 @@
         <v>63</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B2" s="12" t="n">
         <v>1</v>
@@ -12070,19 +12186,19 @@
         <v>1</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="G2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B3" s="12" t="n">
         <v>1</v>
@@ -12091,19 +12207,19 @@
         <v>2</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G3" s="12"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B4" s="12" t="n">
         <v>1</v>
@@ -12112,19 +12228,19 @@
         <v>3</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>1</v>
@@ -12133,19 +12249,19 @@
         <v>4</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B6" s="12" t="n">
         <v>2</v>
@@ -12157,16 +12273,16 @@
         <v>35</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="G6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>2</v>
@@ -12175,19 +12291,19 @@
         <v>2</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B8" s="12" t="n">
         <v>2</v>
@@ -12196,19 +12312,19 @@
         <v>3</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B9" s="12" t="n">
         <v>2</v>
@@ -12217,19 +12333,19 @@
         <v>4</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>3</v>
@@ -12238,19 +12354,19 @@
         <v>1</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>3</v>
@@ -12259,19 +12375,19 @@
         <v>2</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B12" s="12" t="n">
         <v>3</v>
@@ -12280,19 +12396,19 @@
         <v>3</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B13" s="12" t="n">
         <v>3</v>
@@ -12301,19 +12417,19 @@
         <v>4</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B14" s="12" t="n">
         <v>4</v>
@@ -12322,19 +12438,19 @@
         <v>1</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B15" s="12" t="n">
         <v>4</v>
@@ -12343,19 +12459,19 @@
         <v>2</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B16" s="12" t="n">
         <v>4</v>
@@ -12364,19 +12480,19 @@
         <v>3</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B17" s="12" t="n">
         <v>4</v>
@@ -12385,19 +12501,19 @@
         <v>4</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="G17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B18" s="12" t="n">
         <v>5</v>
@@ -12409,16 +12525,16 @@
         <v>35</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B19" s="12" t="n">
         <v>5</v>
@@ -12427,19 +12543,19 @@
         <v>2</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G19" s="12"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B20" s="12" t="n">
         <v>5</v>
@@ -12448,19 +12564,19 @@
         <v>3</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B21" s="12" t="n">
         <v>5</v>
@@ -12469,19 +12585,19 @@
         <v>4</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G21" s="12"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B22" s="12" t="n">
         <v>6</v>
@@ -12490,19 +12606,19 @@
         <v>1</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="G22" s="12"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B23" s="12" t="n">
         <v>6</v>
@@ -12511,19 +12627,19 @@
         <v>2</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B24" s="12" t="n">
         <v>6</v>
@@ -12532,19 +12648,19 @@
         <v>3</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B25" s="12" t="n">
         <v>6</v>
@@ -12553,19 +12669,19 @@
         <v>4</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>7</v>
@@ -12574,19 +12690,19 @@
         <v>1</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="G26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>7</v>
@@ -12595,19 +12711,19 @@
         <v>2</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B28" s="12" t="n">
         <v>7</v>
@@ -12616,19 +12732,19 @@
         <v>3</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B29" s="12" t="n">
         <v>7</v>
@@ -12637,19 +12753,19 @@
         <v>4</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B30" s="12" t="n">
         <v>8</v>
@@ -12661,16 +12777,16 @@
         <v>35</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B31" s="12" t="n">
         <v>8</v>
@@ -12679,19 +12795,19 @@
         <v>2</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B32" s="12" t="n">
         <v>8</v>
@@ -12700,19 +12816,19 @@
         <v>3</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="G32" s="12"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B33" s="12" t="n">
         <v>8</v>
@@ -12721,19 +12837,19 @@
         <v>4</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="G33" s="12"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B34" s="12" t="n">
         <v>9</v>
@@ -12742,19 +12858,19 @@
         <v>1</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="G34" s="12"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B35" s="12" t="n">
         <v>9</v>
@@ -12763,19 +12879,19 @@
         <v>2</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G35" s="12"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B36" s="12" t="n">
         <v>9</v>
@@ -12784,19 +12900,19 @@
         <v>3</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G36" s="12"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B37" s="12" t="n">
         <v>9</v>
@@ -12805,19 +12921,19 @@
         <v>4</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G37" s="12"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B38" s="12" t="n">
         <v>10</v>
@@ -12826,19 +12942,19 @@
         <v>1</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="G38" s="12"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B39" s="12" t="n">
         <v>10</v>
@@ -12847,19 +12963,19 @@
         <v>2</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G39" s="12"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B40" s="12" t="n">
         <v>10</v>
@@ -12868,19 +12984,19 @@
         <v>3</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G40" s="12"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B41" s="12" t="n">
         <v>10</v>
@@ -12889,19 +13005,19 @@
         <v>4</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G41" s="12"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B42" s="12" t="n">
         <v>11</v>
@@ -12910,19 +13026,19 @@
         <v>1</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G42" s="12"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B43" s="12" t="n">
         <v>11</v>
@@ -12931,19 +13047,19 @@
         <v>2</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G43" s="12"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B44" s="12" t="n">
         <v>11</v>
@@ -12952,19 +13068,19 @@
         <v>3</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="G44" s="12"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B45" s="12" t="n">
         <v>11</v>
@@ -12973,19 +13089,19 @@
         <v>4</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="G45" s="12"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B46" s="12" t="n">
         <v>12</v>
@@ -12994,19 +13110,19 @@
         <v>1</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="G46" s="12"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B47" s="12" t="n">
         <v>12</v>
@@ -13015,19 +13131,19 @@
         <v>2</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G47" s="12"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B48" s="12" t="n">
         <v>12</v>
@@ -13036,10 +13152,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F48" s="12" t="s">
         <v>42</v>
@@ -13048,7 +13164,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B49" s="12" t="n">
         <v>12</v>
@@ -13060,10 +13176,10 @@
         <v>45</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G49" s="12"/>
     </row>
@@ -16238,7 +16354,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation allowBlank="true" error="Pick one of the options in the drop-down." errorStyle="stop" errorTitle="Choose from the list" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A2:A401" type="list">
-      <formula1>Lists!$A$2:$A$8</formula1>
+      <formula1>Lists!$A$2:$A$9</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Pick one of the options in the drop-down." errorStyle="stop" errorTitle="Choose from the list" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="D2:D401" type="list">
@@ -16275,189 +16391,189 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F2" s="12"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F3" s="12"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="F9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="F10" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -16489,39 +16605,39 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B2" s="12" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="F2" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A2)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
@@ -16530,19 +16646,19 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3" s="12" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="F3" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A3)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
@@ -16551,19 +16667,19 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B4" s="12" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="F4" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A4)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
@@ -16572,19 +16688,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B5" s="12" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>231</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>226</v>
       </c>
       <c r="F5" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A5)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
@@ -16593,19 +16709,19 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B6" s="12" t="n">
         <v>3</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="F6" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A6)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
@@ -16614,19 +16730,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B7" s="12" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="F7" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A7)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
@@ -16635,19 +16751,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B8" s="12" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="F8" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A8)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
@@ -16656,19 +16772,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B9" s="12" t="n">
         <v>5</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="F9" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A9)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
@@ -16712,51 +16828,51 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C2" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
@@ -16766,19 +16882,19 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C3" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F3" s="12"/>
       <c r="G3" s="12"/>
@@ -16788,19 +16904,19 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C4" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="12"/>
@@ -16810,19 +16926,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="12"/>
@@ -16832,19 +16948,19 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>5</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
@@ -16854,19 +16970,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="12"/>
@@ -16876,19 +16992,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
@@ -16898,19 +17014,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
@@ -16920,19 +17036,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="12"/>
@@ -16942,19 +17058,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>5</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F11" s="12"/>
       <c r="G11" s="12"/>
@@ -16964,19 +17080,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C12" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
@@ -16986,19 +17102,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="12"/>
@@ -17008,19 +17124,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D14" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="E14" s="12" t="s">
         <v>262</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>257</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="12"/>
@@ -17030,19 +17146,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C15" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F15" s="12"/>
       <c r="G15" s="12"/>
@@ -17052,19 +17168,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C16" s="12" t="n">
         <v>5</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F16" s="12"/>
       <c r="G16" s="12"/>
@@ -17074,19 +17190,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C17" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="12"/>
@@ -17096,19 +17212,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C18" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="12"/>
@@ -17118,19 +17234,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C19" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="12"/>
@@ -17140,19 +17256,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C20" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="12"/>
@@ -17162,19 +17278,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C21" s="12" t="n">
         <v>5</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F21" s="12"/>
       <c r="G21" s="12"/>
@@ -17184,19 +17300,19 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C22" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F22" s="12"/>
       <c r="G22" s="12"/>
@@ -17206,19 +17322,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C23" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F23" s="12"/>
       <c r="G23" s="12"/>
@@ -17228,19 +17344,19 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C24" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F24" s="12"/>
       <c r="G24" s="12"/>
@@ -17250,19 +17366,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C25" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F25" s="12"/>
       <c r="G25" s="12"/>
@@ -17272,19 +17388,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C26" s="12" t="n">
         <v>5</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F26" s="12"/>
       <c r="G26" s="12"/>
@@ -17294,19 +17410,19 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C27" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F27" s="12"/>
       <c r="G27" s="12"/>
@@ -17316,19 +17432,19 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C28" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F28" s="12"/>
       <c r="G28" s="12"/>
@@ -17338,19 +17454,19 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C29" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F29" s="12"/>
       <c r="G29" s="12"/>
@@ -17360,19 +17476,19 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C30" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F30" s="12"/>
       <c r="G30" s="12"/>
@@ -17382,19 +17498,19 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C31" s="12" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>4</v>
@@ -17412,19 +17528,19 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C32" s="12" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F32" s="12"/>
       <c r="G32" s="12"/>
@@ -17434,19 +17550,19 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C33" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F33" s="12"/>
       <c r="G33" s="12"/>
@@ -17456,19 +17572,19 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C34" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F34" s="12"/>
       <c r="G34" s="12"/>
@@ -17478,19 +17594,19 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C35" s="12" t="n">
         <v>5</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F35" s="12"/>
       <c r="G35" s="12"/>
@@ -17512,7 +17628,7 @@
     </row>
     <row r="37" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="17" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
@@ -21923,7 +22039,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
@@ -21938,30 +22054,30 @@
         <v>63</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C2" s="12" t="n">
         <v>3</v>
@@ -21979,10 +22095,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C3" s="12" t="n">
         <v>2</v>
@@ -22000,10 +22116,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C4" s="12" t="n">
         <v>3</v>
@@ -22021,10 +22137,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>2</v>
@@ -22042,10 +22158,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="16" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>3</v>
@@ -22063,10 +22179,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>2</v>
@@ -22084,10 +22200,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>3</v>
@@ -22105,10 +22221,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>2</v>
@@ -22126,138 +22242,180 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="16" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C10" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="D10" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="E10" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="G10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="16" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="12" t="n">
         <v>8</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="16" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C12" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="D12" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="E12" s="12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="G12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="16" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D13" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E13" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="E13" s="12" t="n">
-        <v>15</v>
-      </c>
       <c r="F13" s="12" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="G13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>4</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C15" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>75</v>
       </c>
       <c r="G15" s="12"/>
     </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="G16" s="12"/>
+    </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14" t="s">
-        <v>280</v>
+      <c r="A17" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="G17" s="12"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="14" t="s">
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -22286,24 +22444,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B2" s="18" t="n">
         <v>8</v>
@@ -22315,12 +22473,12 @@
         <v>25</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B3" s="18" t="n">
         <v>8</v>
@@ -22332,12 +22490,12 @@
         <v>25</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B4" s="18" t="n">
         <v>30</v>
@@ -22349,12 +22507,12 @@
         <v>100</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B5" s="18" t="n">
         <v>10</v>
@@ -22366,12 +22524,12 @@
         <v>32</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B6" s="18" t="n">
         <v>3</v>
@@ -22383,12 +22541,12 @@
         <v>4</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B7" s="19" t="n">
         <v>0.1</v>
@@ -22400,12 +22558,12 @@
         <v>0.12</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B8" s="19" t="n">
         <v>0.3</v>
@@ -22417,12 +22575,12 @@
         <v>0.32</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B9" s="18" t="n">
         <v>15</v>
@@ -22434,12 +22592,12 @@
         <v>50</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B10" s="19" t="n">
         <v>0.06</v>
@@ -22451,12 +22609,12 @@
         <v>0.06</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B11" s="18" t="n">
         <v>1.5</v>
@@ -22468,12 +22626,12 @@
         <v>1.5</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B12" s="18" t="n">
         <v>2.5</v>
@@ -22488,7 +22646,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B13" s="19" t="n">
         <v>0.1</v>
@@ -22500,12 +22658,12 @@
         <v>0.1</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B14" s="18" t="n">
         <v>2</v>
@@ -22517,12 +22675,12 @@
         <v>2</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B15" s="19" t="n">
         <v>0.15</v>
@@ -22537,7 +22695,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B16" s="18" t="n">
         <v>3</v>
@@ -22552,7 +22710,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B17" s="19" t="n">
         <v>0.25</v>
@@ -22567,7 +22725,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B18" s="18" t="n">
         <v>4</v>
@@ -22582,7 +22740,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B19" s="19" t="n">
         <v>0.6</v>
@@ -22594,12 +22752,12 @@
         <v>0.6</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B20" s="19" t="n">
         <v>0.85</v>
@@ -22614,7 +22772,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B21" s="19" t="n">
         <v>0.15</v>
@@ -22629,7 +22787,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B22" s="19" t="n">
         <v>0.6</v>
@@ -22641,12 +22799,12 @@
         <v>0.6</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B23" s="19" t="n">
         <v>0.15</v>
@@ -22658,12 +22816,12 @@
         <v>0.15</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B24" s="19" t="n">
         <v>0.6</v>
@@ -22675,12 +22833,12 @@
         <v>0.6</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>

--- a/programmes/Kinetix Programmes.xlsx
+++ b/programmes/Kinetix Programmes.xlsx
@@ -189,7 +189,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="415">
   <si>
     <t xml:space="preserve">Kinetix programmes</t>
   </si>
@@ -878,123 +878,129 @@
     <t xml:space="preserve">Full body ×1</t>
   </si>
   <si>
+    <t xml:space="preserve">Full body</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Very busy weeks or running-focused plans.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full body A, Full body B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Most runners: two sessions that cover everything.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full body A, Full body B, Full body C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanced hybrid, newer lifters.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upper A, Lower A, Upper B, Lower B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength focus with 4 lifting days.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Push, Pull, Legs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muscle focus with 3 lifting days.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Push / Pull / Legs ×2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Push A, Pull A, Legs A, Push B, Pull B, Legs B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experienced lifters, muscle focus, light running.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upper / Lower / Full</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upper, Lower, Full body</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 days, a bit more volume per muscle than full body.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPL + Upper / Lower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Push, Pull, Legs, Upper, Lower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 lifting days, muscle focus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exercise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reps (low)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reps (high)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rest (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any squat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any horizontal push (bench, press-up)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any hinge accessory (RDL, bridge)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accessory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any horizontal pull (row)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any vertical push (overhead press)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any core</t>
+  </si>
+  <si>
     <t xml:space="preserve">Full body A</t>
   </si>
   <si>
-    <t xml:space="preserve">Very busy weeks or running-focused plans.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full body A, Full body B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Most runners: two sessions that cover everything.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full body A, Full body B, Full body C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Balanced hybrid, newer lifters.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upper A, Lower A, Upper B, Lower B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength focus with 4 lifting days.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Push, Pull, Legs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muscle focus with 3 lifting days.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Push / Pull / Legs ×2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Push A, Pull A, Legs A, Push B, Pull B, Legs B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experienced lifters, muscle focus, light running.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upper / Lower / Full</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upper, Lower, Full body</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 days, a bit more volume per muscle than full body.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPL + Upper / Lower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Push, Pull, Legs, Upper, Lower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 lifting days, muscle focus.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Day name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exercise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reps (low)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reps (high)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rest (s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Any squat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Any horizontal push (bench, press-up)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Any horizontal pull (row)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accessory</t>
-  </si>
-  <si>
     <t xml:space="preserve">Any calf raise</t>
   </si>
   <si>
-    <t xml:space="preserve">Any core</t>
-  </si>
-  <si>
     <t xml:space="preserve">Full body B</t>
   </si>
   <si>
     <t xml:space="preserve">Any hinge (deadlift)</t>
   </si>
   <si>
-    <t xml:space="preserve">Any vertical push (overhead press)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Any vertical pull (pull-up, pulldown)</t>
   </si>
   <si>
@@ -1004,6 +1010,21 @@
     <t xml:space="preserve">Any anti-rotation core</t>
   </si>
   <si>
+    <t xml:space="preserve">Full body C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incline Dumbbell Press</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbell Hip Thrust</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single-Leg Calf Raise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Side Plank</t>
+  </si>
+  <si>
     <t xml:space="preserve">Upper A</t>
   </si>
   <si>
@@ -1013,9 +1034,6 @@
     <t xml:space="preserve">Lower A</t>
   </si>
   <si>
-    <t xml:space="preserve">Any hinge accessory (RDL, bridge)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Upper B</t>
   </si>
   <si>
@@ -1025,306 +1043,348 @@
     <t xml:space="preserve">Push</t>
   </si>
   <si>
+    <t xml:space="preserve">Dumbbell Lateral Raise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Triceps Pushdown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Face Pull</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rear Delt Fly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dumbbell Curl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leg Curl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Push A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pull A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legs A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Push B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incline Barbell Bench Press</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cable Fly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overhead Triceps Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pull B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chin-Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seated Cable Row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hammer Curl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legs B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trap Bar Deadlift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulgarian Split Squat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leg Press</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nordic Hamstring Curl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seated Calf Raise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hanging Leg Raise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step-Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A first draft of every split to edit. 'Any …' lets the app choose for the user's equipment; named exercises are swapped for the closest option if they can't do them. Blank sets/reps/rest use 'Strength by goal'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leg-heavy days are kept away from hard runs and the long run automatically.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current app defaults. Running goals share the 'running' prescription today; set each one as you like.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weights progress automatically (double progression): add reps up to the top of the range, then add weight.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beginner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intermediate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advanced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting volume if they don't run yet (km/week)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Used when the runner answers 0 or doesn't know.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum starting volume (km/week)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Their answer is raised to at least this.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximum starting volume (km/week)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Their answer is capped at this.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longest single run (km)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No run is longer than this (the programme's long-run cap can be lower).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shortest run (km)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Runs shorter than this are dropped or merged.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max weekly increase (fraction)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10 = 10%. Applies to what they actually ran, not just the plan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long run share when 'auto' (fraction of week)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Used when Run weeks → Long run is 'auto'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example runner (km/week)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only for the grey example columns in Run weeks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warm-up and cool-down, each (fraction of week)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added to rep and tempo sessions. Kept between the min and max below.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warm-up minimum (km)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Also used when the long run and sessions already fill the week.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warm-up maximum (km)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fast reps max (fraction of week): I, R, 5K, hills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hard running per session. Lower-volume runners get fewer reps; rep lengths never change.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fast reps floor (km)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Always allowed at least this much, whatever the week's volume.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Threshold reps max (fraction of week): T, 10K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Threshold reps floor (km)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steady reps max (fraction of week): STEADY, M, HM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steady reps floor (km)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recovery run max (fraction of long run)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spare volume beyond these lengths adds an easy run if there's a free day.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Easy run max (fraction of long run)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shakeout max (fraction of week)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recovery week after the programme (fraction of starting)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Easy running only, then the programme repeats from their recent running.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ease down per week when above race-ready (fraction)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Runners doing more than the race needs come down to its race-ready volume this much a week.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Easy first week after a race (fraction of current)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Only if they say in onboarding they've raced in the last two weeks and want an easy week.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current app defaults are filled in; change any yellow value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Session types</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Splits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes / No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exercises</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arnold Press</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbell Back Squat</t>
+  </si>
+  <si>
     <t xml:space="preserve">Barbell Bench Press</t>
   </si>
   <si>
+    <t xml:space="preserve">Barbell Curl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbell Deadlift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbell Row</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burpee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cable Crunch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chest Press Machine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dead Bug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diamond Push-Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dumbbell Floor Press</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dumbbell Fly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dumbbell Pullover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dumbbell Romanian Deadlift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dumbbell Shoulder Press</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dumbbell Split Squat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dumbbell Thruster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farmer's Carry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Front Squat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goblet Squat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good Morning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hack Squat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inverted Row (table or bar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kettlebell Swing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lat Pulldown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leg Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One-Arm Dumbbell Row</t>
+  </si>
+  <si>
     <t xml:space="preserve">Overhead Press</t>
   </si>
   <si>
-    <t xml:space="preserve">Incline Dumbbell Press</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dumbbell Lateral Raise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Triceps Pushdown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full body ×2 and Upper / Lower are today's app sessions; Push is a started example with its own sets/reps. Add the rest of the splits below.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current app defaults. Running goals share the 'running' prescription today; set each one as you like.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weights progress automatically (double progression): add reps up to the top of the range, then add weight.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rule</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beginner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intermediate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advanced</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Starting volume if they don't run yet (km/week)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Used when the runner answers 0 or doesn't know.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minimum starting volume (km/week)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Their answer is raised to at least this.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maximum starting volume (km/week)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Their answer is capped at this.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longest single run (km)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No run is longer than this (the programme's long-run cap can be lower).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shortest run (km)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Runs shorter than this are dropped or merged.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max weekly increase (fraction)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10 = 10%. Applies to what they actually ran, not just the plan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Long run share when 'auto' (fraction of week)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Used when Run weeks → Long run is 'auto'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Example runner (km/week)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only for the grey example columns in Run weeks.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warm-up and cool-down, each (fraction of week)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added to rep and tempo sessions. Kept between the min and max below.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warm-up minimum (km)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Also used when the long run and sessions already fill the week.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warm-up maximum (km)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fast reps max (fraction of week): I, R, 5K, hills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hard running per session. Lower-volume runners get fewer reps; rep lengths never change.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fast reps floor (km)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Always allowed at least this much, whatever the week's volume.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Threshold reps max (fraction of week): T, 10K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Threshold reps floor (km)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steady reps max (fraction of week): STEADY, M, HM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Steady reps floor (km)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recovery run max (fraction of long run)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spare volume beyond these lengths adds an easy run if there's a free day.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Easy run max (fraction of long run)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shakeout max (fraction of week)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recovery week after the programme (fraction of starting)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Easy running only, then the programme repeats from their recent running.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ease down per week when above race-ready (fraction)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Runners doing more than the race needs come down to its race-ready volume this much a week.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Easy first week after a race (fraction of current)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only if they say in onboarding they've raced in the last two weeks and want an easy week.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Current app defaults are filled in; change any yellow value.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Session types</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Splits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes / No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exercises</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arnold Press</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barbell Back Squat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barbell Curl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barbell Deadlift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barbell Hip Thrust</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barbell Row</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulgarian Split Squat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Burpee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cable Crunch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cable Fly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chest Press Machine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chin-Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dead Bug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diamond Push-Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dumbbell Curl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dumbbell Floor Press</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dumbbell Fly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dumbbell Pullover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dumbbell Romanian Deadlift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dumbbell Shoulder Press</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dumbbell Split Squat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dumbbell Thruster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Face Pull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Farmer's Carry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Front Squat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Goblet Squat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Good Morning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hack Squat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hammer Curl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hanging Leg Raise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incline Barbell Bench Press</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inverted Row (table or bar)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kettlebell Swing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lat Pulldown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leg Curl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leg Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leg Press</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nordic Hamstring Curl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One-Arm Dumbbell Row</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overhead Triceps Extension</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pallof Press</t>
   </si>
   <si>
@@ -1343,9 +1403,6 @@
     <t xml:space="preserve">Push-Up</t>
   </si>
   <si>
-    <t xml:space="preserve">Rear Delt Fly</t>
-  </si>
-  <si>
     <t xml:space="preserve">Reverse Lunge</t>
   </si>
   <si>
@@ -1355,18 +1412,6 @@
     <t xml:space="preserve">Russian Twist</t>
   </si>
   <si>
-    <t xml:space="preserve">Seated Cable Row</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seated Calf Raise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Side Plank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single-Leg Calf Raise</t>
-  </si>
-  <si>
     <t xml:space="preserve">Single-Leg Glute Bridge</t>
   </si>
   <si>
@@ -1379,9 +1424,6 @@
     <t xml:space="preserve">Standing Calf Raise</t>
   </si>
   <si>
-    <t xml:space="preserve">Step-Up</t>
-  </si>
-  <si>
     <t xml:space="preserve">T-Bar Row</t>
   </si>
   <si>
@@ -1389,9 +1431,6 @@
   </si>
   <si>
     <t xml:space="preserve">Towel Doorway Row</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trap Bar Deadlift</t>
   </si>
   <si>
     <t xml:space="preserve">Walking Lunge</t>
@@ -2320,28 +2359,28 @@
         <v>8</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>330</v>
+        <v>362</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>27</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>332</v>
+        <v>364</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>333</v>
+        <v>365</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="H1" s="9" t="s">
         <v>110</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>335</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2393,13 +2432,13 @@
         <v>262</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>336</v>
+        <v>368</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>118</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2422,7 +2461,7 @@
         <v>120</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2445,7 +2484,7 @@
         <v>129</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2465,7 +2504,7 @@
         <v>100</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2502,7 +2541,7 @@
         <v>243</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2519,7 +2558,7 @@
         <v>246</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2530,7 +2569,7 @@
         <v>216</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2538,367 +2577,367 @@
         <v>45</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I12" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I13" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I14" s="6" t="s">
-        <v>337</v>
+        <v>369</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I15" s="6" t="s">
-        <v>338</v>
+        <v>370</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I16" s="6" t="s">
-        <v>278</v>
+        <v>371</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I17" s="6" t="s">
-        <v>339</v>
+        <v>372</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I18" s="6" t="s">
-        <v>340</v>
+        <v>373</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I19" s="6" t="s">
-        <v>341</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I20" s="6" t="s">
-        <v>342</v>
+        <v>374</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I21" s="6" t="s">
-        <v>343</v>
+        <v>306</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I22" s="6" t="s">
-        <v>344</v>
+        <v>375</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I23" s="6" t="s">
-        <v>345</v>
+        <v>376</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I24" s="6" t="s">
-        <v>346</v>
+        <v>298</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I25" s="6" t="s">
-        <v>347</v>
+        <v>377</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I26" s="6" t="s">
-        <v>348</v>
+        <v>301</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I27" s="6" t="s">
-        <v>349</v>
+        <v>378</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I28" s="6" t="s">
-        <v>350</v>
+        <v>379</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I29" s="6" t="s">
-        <v>351</v>
+        <v>297</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I30" s="6" t="s">
-        <v>352</v>
+        <v>289</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I31" s="6" t="s">
-        <v>353</v>
+        <v>380</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I32" s="6" t="s">
-        <v>354</v>
+        <v>381</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I33" s="6" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I34" s="6" t="s">
-        <v>355</v>
+        <v>382</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I35" s="6" t="s">
-        <v>356</v>
+        <v>383</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I36" s="6" t="s">
-        <v>357</v>
+        <v>384</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I37" s="6" t="s">
-        <v>358</v>
+        <v>385</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I38" s="6" t="s">
-        <v>359</v>
+        <v>386</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I39" s="6" t="s">
-        <v>360</v>
+        <v>287</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I40" s="6" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I41" s="6" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I42" s="6" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I43" s="6" t="s">
-        <v>364</v>
+        <v>390</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I44" s="6" t="s">
-        <v>365</v>
+        <v>391</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I45" s="6" t="s">
-        <v>366</v>
+        <v>303</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I46" s="6" t="s">
-        <v>367</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I47" s="6" t="s">
-        <v>368</v>
+        <v>296</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I48" s="6" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I49" s="6" t="s">
-        <v>369</v>
+        <v>392</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I50" s="6" t="s">
-        <v>370</v>
+        <v>393</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I51" s="6" t="s">
-        <v>371</v>
+        <v>394</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I52" s="6" t="s">
-        <v>372</v>
+        <v>291</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I53" s="6" t="s">
-        <v>373</v>
+        <v>395</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I54" s="6" t="s">
-        <v>374</v>
+        <v>307</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I55" s="6" t="s">
-        <v>375</v>
+        <v>308</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I56" s="6" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I57" s="6" t="s">
-        <v>279</v>
+        <v>397</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I58" s="6" t="s">
-        <v>377</v>
+        <v>299</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I59" s="6" t="s">
-        <v>378</v>
+        <v>398</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I60" s="6" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I61" s="6" t="s">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I62" s="6" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I63" s="6" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I64" s="6" t="s">
-        <v>383</v>
+        <v>403</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I65" s="6" t="s">
-        <v>384</v>
+        <v>288</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I66" s="6" t="s">
-        <v>385</v>
+        <v>404</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I67" s="6" t="s">
-        <v>386</v>
+        <v>405</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I68" s="6" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I69" s="6" t="s">
-        <v>388</v>
+        <v>302</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I70" s="6" t="s">
-        <v>389</v>
+        <v>309</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I71" s="6" t="s">
-        <v>390</v>
+        <v>277</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I72" s="6" t="s">
-        <v>391</v>
+        <v>276</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I73" s="6" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I74" s="6" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I75" s="6" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I76" s="6" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I77" s="6" t="s">
-        <v>396</v>
+        <v>313</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I78" s="6" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I79" s="6" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I80" s="6" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I81" s="6" t="s">
-        <v>400</v>
+        <v>305</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I82" s="6" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I83" s="6" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -16641,7 +16680,7 @@
       </c>
       <c r="F2" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A2)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16683,7 +16722,7 @@
       </c>
       <c r="F4" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A4)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16725,7 +16764,7 @@
       </c>
       <c r="F6" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A6)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16746,7 +16785,7 @@
       </c>
       <c r="F7" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A7)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16767,7 +16806,7 @@
       </c>
       <c r="F8" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A8)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16788,7 +16827,7 @@
       </c>
       <c r="F9" s="13" t="n">
         <f aca="false">SUMPRODUCT(('Split days'!$A$2:$A$401=A9)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -16860,7 +16899,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>84</v>
+        <v>228</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>229</v>
@@ -16882,7 +16921,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>84</v>
+        <v>228</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>229</v>
@@ -16904,7 +16943,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>84</v>
+        <v>228</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>229</v>
@@ -16926,7 +16965,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>84</v>
+        <v>228</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>229</v>
@@ -16948,7 +16987,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>84</v>
+        <v>228</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>229</v>
@@ -16970,19 +17009,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>84</v>
+        <v>228</v>
       </c>
       <c r="B7" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="C7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>266</v>
-      </c>
       <c r="E7" s="12" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="12"/>
@@ -16995,13 +17034,13 @@
         <v>84</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>259</v>
@@ -17017,16 +17056,16 @@
         <v>84</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
@@ -17039,13 +17078,13 @@
         <v>84</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>262</v>
@@ -17061,13 +17100,13 @@
         <v>84</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>262</v>
@@ -17080,19 +17119,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
@@ -17102,16 +17141,16 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>259</v>
@@ -17124,19 +17163,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F14" s="12"/>
       <c r="G14" s="12"/>
@@ -17146,16 +17185,16 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E15" s="12" t="s">
         <v>262</v>
@@ -17168,16 +17207,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="B16" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" s="12" t="s">
         <v>271</v>
-      </c>
-      <c r="C16" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="E16" s="12" t="s">
         <v>262</v>
@@ -17190,19 +17229,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F17" s="12"/>
       <c r="G17" s="12"/>
@@ -17212,19 +17251,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="12"/>
@@ -17234,19 +17273,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="12"/>
@@ -17256,13 +17295,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>263</v>
@@ -17278,16 +17317,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>262</v>
@@ -17300,19 +17339,19 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F22" s="12"/>
       <c r="G22" s="12"/>
@@ -17322,16 +17361,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E23" s="12" t="s">
         <v>259</v>
@@ -17344,19 +17383,19 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F24" s="12"/>
       <c r="G24" s="12"/>
@@ -17366,16 +17405,16 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="E25" s="12" t="s">
         <v>262</v>
@@ -17388,16 +17427,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="C26" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="E26" s="12" t="s">
         <v>262</v>
@@ -17410,19 +17449,19 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="C27" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F27" s="12"/>
       <c r="G27" s="12"/>
@@ -17432,16 +17471,16 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C28" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E28" s="12" t="s">
         <v>259</v>
@@ -17454,19 +17493,19 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C29" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F29" s="12"/>
       <c r="G29" s="12"/>
@@ -17476,16 +17515,16 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C30" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E30" s="12" t="s">
         <v>262</v>
@@ -17498,49 +17537,41 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C31" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="F31" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="G31" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="H31" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="I31" s="12" t="n">
-        <v>150</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
       <c r="J31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C32" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F32" s="12"/>
       <c r="G32" s="12"/>
@@ -17550,16 +17581,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B33" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D33" s="12" t="s">
         <v>277</v>
-      </c>
-      <c r="C33" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>280</v>
       </c>
       <c r="E33" s="12" t="s">
         <v>262</v>
@@ -17572,19 +17603,19 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C34" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F34" s="12"/>
       <c r="G34" s="12"/>
@@ -17594,19 +17625,19 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C35" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F35" s="12"/>
       <c r="G35" s="12"/>
@@ -17615,25 +17646,43 @@
       <c r="J35" s="12"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="12"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
+      <c r="A36" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="C36" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F36" s="12"/>
       <c r="G36" s="12"/>
       <c r="H36" s="12"/>
       <c r="I36" s="12"/>
       <c r="J36" s="12"/>
     </row>
-    <row r="37" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="17" t="s">
-        <v>283</v>
-      </c>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="C37" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F37" s="12"/>
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
@@ -17641,11 +17690,21 @@
       <c r="J37" s="12"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="12"/>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
+      <c r="A38" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="C38" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F38" s="12"/>
       <c r="G38" s="12"/>
       <c r="H38" s="12"/>
@@ -17653,11 +17712,21 @@
       <c r="J38" s="12"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="12"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
+      <c r="A39" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="C39" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F39" s="12"/>
       <c r="G39" s="12"/>
       <c r="H39" s="12"/>
@@ -17665,11 +17734,21 @@
       <c r="J39" s="12"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="12"/>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
+      <c r="A40" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F40" s="12"/>
       <c r="G40" s="12"/>
       <c r="H40" s="12"/>
@@ -17677,11 +17756,21 @@
       <c r="J40" s="12"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="12"/>
-      <c r="B41" s="12"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
+      <c r="A41" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="C41" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F41" s="12"/>
       <c r="G41" s="12"/>
       <c r="H41" s="12"/>
@@ -17689,11 +17778,21 @@
       <c r="J41" s="12"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="12"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
+      <c r="A42" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F42" s="12"/>
       <c r="G42" s="12"/>
       <c r="H42" s="12"/>
@@ -17701,11 +17800,21 @@
       <c r="J42" s="12"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="12"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
+      <c r="A43" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="C43" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F43" s="12"/>
       <c r="G43" s="12"/>
       <c r="H43" s="12"/>
@@ -17713,11 +17822,21 @@
       <c r="J43" s="12"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="12"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
+      <c r="A44" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="C44" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F44" s="12"/>
       <c r="G44" s="12"/>
       <c r="H44" s="12"/>
@@ -17725,11 +17844,21 @@
       <c r="J44" s="12"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="12"/>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
+      <c r="A45" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="C45" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F45" s="12"/>
       <c r="G45" s="12"/>
       <c r="H45" s="12"/>
@@ -17737,11 +17866,21 @@
       <c r="J45" s="12"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="12"/>
-      <c r="B46" s="12"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
+      <c r="A46" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="C46" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F46" s="12"/>
       <c r="G46" s="12"/>
       <c r="H46" s="12"/>
@@ -17749,11 +17888,21 @@
       <c r="J46" s="12"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="12"/>
-      <c r="B47" s="12"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
+      <c r="A47" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="C47" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F47" s="12"/>
       <c r="G47" s="12"/>
       <c r="H47" s="12"/>
@@ -17761,11 +17910,21 @@
       <c r="J47" s="12"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="12"/>
-      <c r="B48" s="12"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
+      <c r="A48" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="C48" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F48" s="12"/>
       <c r="G48" s="12"/>
       <c r="H48" s="12"/>
@@ -17773,11 +17932,21 @@
       <c r="J48" s="12"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="12"/>
-      <c r="B49" s="12"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
+      <c r="A49" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="C49" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F49" s="12"/>
       <c r="G49" s="12"/>
       <c r="H49" s="12"/>
@@ -17785,11 +17954,21 @@
       <c r="J49" s="12"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="12"/>
-      <c r="B50" s="12"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
+      <c r="A50" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="C50" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F50" s="12"/>
       <c r="G50" s="12"/>
       <c r="H50" s="12"/>
@@ -17797,11 +17976,21 @@
       <c r="J50" s="12"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="12"/>
-      <c r="B51" s="12"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
+      <c r="A51" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="C51" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F51" s="12"/>
       <c r="G51" s="12"/>
       <c r="H51" s="12"/>
@@ -17809,11 +17998,21 @@
       <c r="J51" s="12"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="12"/>
-      <c r="B52" s="12"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
+      <c r="A52" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="C52" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F52" s="12"/>
       <c r="G52" s="12"/>
       <c r="H52" s="12"/>
@@ -17821,11 +18020,21 @@
       <c r="J52" s="12"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="12"/>
-      <c r="B53" s="12"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
+      <c r="A53" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B53" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C53" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F53" s="12"/>
       <c r="G53" s="12"/>
       <c r="H53" s="12"/>
@@ -17833,11 +18042,21 @@
       <c r="J53" s="12"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="12"/>
-      <c r="B54" s="12"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
+      <c r="A54" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C54" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F54" s="12"/>
       <c r="G54" s="12"/>
       <c r="H54" s="12"/>
@@ -17845,11 +18064,21 @@
       <c r="J54" s="12"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="12"/>
-      <c r="B55" s="12"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
+      <c r="A55" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C55" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F55" s="12"/>
       <c r="G55" s="12"/>
       <c r="H55" s="12"/>
@@ -17857,11 +18086,21 @@
       <c r="J55" s="12"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="12"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
+      <c r="A56" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C56" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F56" s="12"/>
       <c r="G56" s="12"/>
       <c r="H56" s="12"/>
@@ -17869,11 +18108,21 @@
       <c r="J56" s="12"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="12"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
+      <c r="A57" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C57" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F57" s="12"/>
       <c r="G57" s="12"/>
       <c r="H57" s="12"/>
@@ -17881,11 +18130,21 @@
       <c r="J57" s="12"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="12"/>
-      <c r="B58" s="12"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
+      <c r="A58" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="C58" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F58" s="12"/>
       <c r="G58" s="12"/>
       <c r="H58" s="12"/>
@@ -17893,11 +18152,21 @@
       <c r="J58" s="12"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="12"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
+      <c r="A59" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="C59" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F59" s="12"/>
       <c r="G59" s="12"/>
       <c r="H59" s="12"/>
@@ -17905,11 +18174,21 @@
       <c r="J59" s="12"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="12"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="12"/>
-      <c r="E60" s="12"/>
+      <c r="A60" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="C60" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F60" s="12"/>
       <c r="G60" s="12"/>
       <c r="H60" s="12"/>
@@ -17917,11 +18196,21 @@
       <c r="J60" s="12"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="12"/>
-      <c r="B61" s="12"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
-      <c r="E61" s="12"/>
+      <c r="A61" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="C61" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F61" s="12"/>
       <c r="G61" s="12"/>
       <c r="H61" s="12"/>
@@ -17929,11 +18218,21 @@
       <c r="J61" s="12"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="12"/>
-      <c r="B62" s="12"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="12"/>
-      <c r="E62" s="12"/>
+      <c r="A62" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="C62" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F62" s="12"/>
       <c r="G62" s="12"/>
       <c r="H62" s="12"/>
@@ -17941,11 +18240,21 @@
       <c r="J62" s="12"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="12"/>
-      <c r="B63" s="12"/>
-      <c r="C63" s="12"/>
-      <c r="D63" s="12"/>
-      <c r="E63" s="12"/>
+      <c r="A63" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B63" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C63" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F63" s="12"/>
       <c r="G63" s="12"/>
       <c r="H63" s="12"/>
@@ -17953,11 +18262,21 @@
       <c r="J63" s="12"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="12"/>
-      <c r="B64" s="12"/>
-      <c r="C64" s="12"/>
-      <c r="D64" s="12"/>
-      <c r="E64" s="12"/>
+      <c r="A64" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C64" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F64" s="12"/>
       <c r="G64" s="12"/>
       <c r="H64" s="12"/>
@@ -17965,11 +18284,21 @@
       <c r="J64" s="12"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="12"/>
-      <c r="B65" s="12"/>
-      <c r="C65" s="12"/>
-      <c r="D65" s="12"/>
-      <c r="E65" s="12"/>
+      <c r="A65" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B65" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C65" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F65" s="12"/>
       <c r="G65" s="12"/>
       <c r="H65" s="12"/>
@@ -17977,11 +18306,21 @@
       <c r="J65" s="12"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="12"/>
-      <c r="B66" s="12"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="12"/>
-      <c r="E66" s="12"/>
+      <c r="A66" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B66" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C66" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F66" s="12"/>
       <c r="G66" s="12"/>
       <c r="H66" s="12"/>
@@ -17989,11 +18328,21 @@
       <c r="J66" s="12"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="12"/>
-      <c r="B67" s="12"/>
-      <c r="C67" s="12"/>
-      <c r="D67" s="12"/>
-      <c r="E67" s="12"/>
+      <c r="A67" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B67" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C67" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F67" s="12"/>
       <c r="G67" s="12"/>
       <c r="H67" s="12"/>
@@ -18001,11 +18350,21 @@
       <c r="J67" s="12"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="12"/>
-      <c r="B68" s="12"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="12"/>
-      <c r="E68" s="12"/>
+      <c r="A68" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B68" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C68" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="E68" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F68" s="12"/>
       <c r="G68" s="12"/>
       <c r="H68" s="12"/>
@@ -18013,11 +18372,21 @@
       <c r="J68" s="12"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="12"/>
-      <c r="B69" s="12"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="12"/>
-      <c r="E69" s="12"/>
+      <c r="A69" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B69" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="C69" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F69" s="12"/>
       <c r="G69" s="12"/>
       <c r="H69" s="12"/>
@@ -18025,11 +18394,21 @@
       <c r="J69" s="12"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="12"/>
-      <c r="B70" s="12"/>
-      <c r="C70" s="12"/>
-      <c r="D70" s="12"/>
-      <c r="E70" s="12"/>
+      <c r="A70" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="C70" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="E70" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F70" s="12"/>
       <c r="G70" s="12"/>
       <c r="H70" s="12"/>
@@ -18037,11 +18416,21 @@
       <c r="J70" s="12"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="12"/>
-      <c r="B71" s="12"/>
-      <c r="C71" s="12"/>
-      <c r="D71" s="12"/>
-      <c r="E71" s="12"/>
+      <c r="A71" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B71" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="C71" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F71" s="12"/>
       <c r="G71" s="12"/>
       <c r="H71" s="12"/>
@@ -18049,11 +18438,21 @@
       <c r="J71" s="12"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="12"/>
-      <c r="B72" s="12"/>
-      <c r="C72" s="12"/>
-      <c r="D72" s="12"/>
-      <c r="E72" s="12"/>
+      <c r="A72" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B72" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="C72" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F72" s="12"/>
       <c r="G72" s="12"/>
       <c r="H72" s="12"/>
@@ -18061,11 +18460,21 @@
       <c r="J72" s="12"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="12"/>
-      <c r="B73" s="12"/>
-      <c r="C73" s="12"/>
-      <c r="D73" s="12"/>
-      <c r="E73" s="12"/>
+      <c r="A73" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B73" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="C73" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F73" s="12"/>
       <c r="G73" s="12"/>
       <c r="H73" s="12"/>
@@ -18073,11 +18482,21 @@
       <c r="J73" s="12"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="12"/>
-      <c r="B74" s="12"/>
-      <c r="C74" s="12"/>
-      <c r="D74" s="12"/>
-      <c r="E74" s="12"/>
+      <c r="A74" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B74" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="C74" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F74" s="12"/>
       <c r="G74" s="12"/>
       <c r="H74" s="12"/>
@@ -18085,11 +18504,21 @@
       <c r="J74" s="12"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="12"/>
-      <c r="B75" s="12"/>
-      <c r="C75" s="12"/>
-      <c r="D75" s="12"/>
-      <c r="E75" s="12"/>
+      <c r="A75" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B75" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="C75" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F75" s="12"/>
       <c r="G75" s="12"/>
       <c r="H75" s="12"/>
@@ -18097,11 +18526,21 @@
       <c r="J75" s="12"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="12"/>
-      <c r="B76" s="12"/>
-      <c r="C76" s="12"/>
-      <c r="D76" s="12"/>
-      <c r="E76" s="12"/>
+      <c r="A76" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="C76" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F76" s="12"/>
       <c r="G76" s="12"/>
       <c r="H76" s="12"/>
@@ -18109,11 +18548,21 @@
       <c r="J76" s="12"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="12"/>
-      <c r="B77" s="12"/>
-      <c r="C77" s="12"/>
-      <c r="D77" s="12"/>
-      <c r="E77" s="12"/>
+      <c r="A77" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B77" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="C77" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="E77" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F77" s="12"/>
       <c r="G77" s="12"/>
       <c r="H77" s="12"/>
@@ -18121,11 +18570,21 @@
       <c r="J77" s="12"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="12"/>
-      <c r="B78" s="12"/>
-      <c r="C78" s="12"/>
-      <c r="D78" s="12"/>
-      <c r="E78" s="12"/>
+      <c r="A78" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B78" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="C78" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F78" s="12"/>
       <c r="G78" s="12"/>
       <c r="H78" s="12"/>
@@ -18133,11 +18592,21 @@
       <c r="J78" s="12"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="12"/>
-      <c r="B79" s="12"/>
-      <c r="C79" s="12"/>
-      <c r="D79" s="12"/>
-      <c r="E79" s="12"/>
+      <c r="A79" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B79" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C79" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="E79" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F79" s="12"/>
       <c r="G79" s="12"/>
       <c r="H79" s="12"/>
@@ -18145,11 +18614,21 @@
       <c r="J79" s="12"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="12"/>
-      <c r="B80" s="12"/>
-      <c r="C80" s="12"/>
-      <c r="D80" s="12"/>
-      <c r="E80" s="12"/>
+      <c r="A80" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C80" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="E80" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F80" s="12"/>
       <c r="G80" s="12"/>
       <c r="H80" s="12"/>
@@ -18157,11 +18636,21 @@
       <c r="J80" s="12"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="12"/>
-      <c r="B81" s="12"/>
-      <c r="C81" s="12"/>
-      <c r="D81" s="12"/>
-      <c r="E81" s="12"/>
+      <c r="A81" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C81" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="E81" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F81" s="12"/>
       <c r="G81" s="12"/>
       <c r="H81" s="12"/>
@@ -18169,11 +18658,21 @@
       <c r="J81" s="12"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="12"/>
-      <c r="B82" s="12"/>
-      <c r="C82" s="12"/>
-      <c r="D82" s="12"/>
-      <c r="E82" s="12"/>
+      <c r="A82" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B82" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C82" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="E82" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F82" s="12"/>
       <c r="G82" s="12"/>
       <c r="H82" s="12"/>
@@ -18181,11 +18680,21 @@
       <c r="J82" s="12"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="12"/>
-      <c r="B83" s="12"/>
-      <c r="C83" s="12"/>
-      <c r="D83" s="12"/>
-      <c r="E83" s="12"/>
+      <c r="A83" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B83" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C83" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="E83" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F83" s="12"/>
       <c r="G83" s="12"/>
       <c r="H83" s="12"/>
@@ -18193,11 +18702,21 @@
       <c r="J83" s="12"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="12"/>
-      <c r="B84" s="12"/>
-      <c r="C84" s="12"/>
-      <c r="D84" s="12"/>
-      <c r="E84" s="12"/>
+      <c r="A84" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B84" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="E84" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F84" s="12"/>
       <c r="G84" s="12"/>
       <c r="H84" s="12"/>
@@ -18205,11 +18724,21 @@
       <c r="J84" s="12"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="12"/>
-      <c r="B85" s="12"/>
-      <c r="C85" s="12"/>
-      <c r="D85" s="12"/>
-      <c r="E85" s="12"/>
+      <c r="A85" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B85" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="C85" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="E85" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F85" s="12"/>
       <c r="G85" s="12"/>
       <c r="H85" s="12"/>
@@ -18217,11 +18746,21 @@
       <c r="J85" s="12"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="12"/>
-      <c r="B86" s="12"/>
-      <c r="C86" s="12"/>
-      <c r="D86" s="12"/>
-      <c r="E86" s="12"/>
+      <c r="A86" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B86" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="C86" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="E86" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F86" s="12"/>
       <c r="G86" s="12"/>
       <c r="H86" s="12"/>
@@ -18229,11 +18768,21 @@
       <c r="J86" s="12"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="12"/>
-      <c r="B87" s="12"/>
-      <c r="C87" s="12"/>
-      <c r="D87" s="12"/>
-      <c r="E87" s="12"/>
+      <c r="A87" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B87" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="C87" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="E87" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F87" s="12"/>
       <c r="G87" s="12"/>
       <c r="H87" s="12"/>
@@ -18241,11 +18790,21 @@
       <c r="J87" s="12"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="12"/>
-      <c r="B88" s="12"/>
-      <c r="C88" s="12"/>
-      <c r="D88" s="12"/>
-      <c r="E88" s="12"/>
+      <c r="A88" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B88" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="C88" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="E88" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F88" s="12"/>
       <c r="G88" s="12"/>
       <c r="H88" s="12"/>
@@ -18253,11 +18812,21 @@
       <c r="J88" s="12"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="12"/>
-      <c r="B89" s="12"/>
-      <c r="C89" s="12"/>
-      <c r="D89" s="12"/>
-      <c r="E89" s="12"/>
+      <c r="A89" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B89" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="C89" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="E89" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F89" s="12"/>
       <c r="G89" s="12"/>
       <c r="H89" s="12"/>
@@ -18265,11 +18834,21 @@
       <c r="J89" s="12"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="12"/>
-      <c r="B90" s="12"/>
-      <c r="C90" s="12"/>
-      <c r="D90" s="12"/>
-      <c r="E90" s="12"/>
+      <c r="A90" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B90" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="C90" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="E90" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F90" s="12"/>
       <c r="G90" s="12"/>
       <c r="H90" s="12"/>
@@ -18277,11 +18856,21 @@
       <c r="J90" s="12"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="12"/>
-      <c r="B91" s="12"/>
-      <c r="C91" s="12"/>
-      <c r="D91" s="12"/>
-      <c r="E91" s="12"/>
+      <c r="A91" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B91" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="C91" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="E91" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F91" s="12"/>
       <c r="G91" s="12"/>
       <c r="H91" s="12"/>
@@ -18289,11 +18878,21 @@
       <c r="J91" s="12"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="12"/>
-      <c r="B92" s="12"/>
-      <c r="C92" s="12"/>
-      <c r="D92" s="12"/>
-      <c r="E92" s="12"/>
+      <c r="A92" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B92" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="C92" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="E92" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F92" s="12"/>
       <c r="G92" s="12"/>
       <c r="H92" s="12"/>
@@ -18301,11 +18900,21 @@
       <c r="J92" s="12"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="12"/>
-      <c r="B93" s="12"/>
-      <c r="C93" s="12"/>
-      <c r="D93" s="12"/>
-      <c r="E93" s="12"/>
+      <c r="A93" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B93" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="C93" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="E93" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F93" s="12"/>
       <c r="G93" s="12"/>
       <c r="H93" s="12"/>
@@ -18313,11 +18922,21 @@
       <c r="J93" s="12"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="12"/>
-      <c r="B94" s="12"/>
-      <c r="C94" s="12"/>
-      <c r="D94" s="12"/>
-      <c r="E94" s="12"/>
+      <c r="A94" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B94" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="C94" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D94" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="E94" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F94" s="12"/>
       <c r="G94" s="12"/>
       <c r="H94" s="12"/>
@@ -18325,11 +18944,21 @@
       <c r="J94" s="12"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="12"/>
-      <c r="B95" s="12"/>
-      <c r="C95" s="12"/>
-      <c r="D95" s="12"/>
-      <c r="E95" s="12"/>
+      <c r="A95" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B95" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="C95" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>305</v>
+      </c>
+      <c r="E95" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F95" s="12"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -18337,11 +18966,21 @@
       <c r="J95" s="12"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="12"/>
-      <c r="B96" s="12"/>
-      <c r="C96" s="12"/>
-      <c r="D96" s="12"/>
-      <c r="E96" s="12"/>
+      <c r="A96" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B96" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="C96" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="E96" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F96" s="12"/>
       <c r="G96" s="12"/>
       <c r="H96" s="12"/>
@@ -18349,11 +18988,21 @@
       <c r="J96" s="12"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="12"/>
-      <c r="B97" s="12"/>
-      <c r="C97" s="12"/>
-      <c r="D97" s="12"/>
-      <c r="E97" s="12"/>
+      <c r="A97" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B97" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="C97" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="E97" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F97" s="12"/>
       <c r="G97" s="12"/>
       <c r="H97" s="12"/>
@@ -18361,11 +19010,21 @@
       <c r="J97" s="12"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="12"/>
-      <c r="B98" s="12"/>
-      <c r="C98" s="12"/>
-      <c r="D98" s="12"/>
-      <c r="E98" s="12"/>
+      <c r="A98" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B98" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="C98" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D98" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="E98" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F98" s="12"/>
       <c r="G98" s="12"/>
       <c r="H98" s="12"/>
@@ -18373,11 +19032,21 @@
       <c r="J98" s="12"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="12"/>
-      <c r="B99" s="12"/>
-      <c r="C99" s="12"/>
-      <c r="D99" s="12"/>
-      <c r="E99" s="12"/>
+      <c r="A99" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B99" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="C99" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="E99" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F99" s="12"/>
       <c r="G99" s="12"/>
       <c r="H99" s="12"/>
@@ -18385,11 +19054,21 @@
       <c r="J99" s="12"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="12"/>
-      <c r="B100" s="12"/>
-      <c r="C100" s="12"/>
-      <c r="D100" s="12"/>
-      <c r="E100" s="12"/>
+      <c r="A100" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B100" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="C100" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D100" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="E100" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F100" s="12"/>
       <c r="G100" s="12"/>
       <c r="H100" s="12"/>
@@ -18397,11 +19076,21 @@
       <c r="J100" s="12"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="12"/>
-      <c r="B101" s="12"/>
-      <c r="C101" s="12"/>
-      <c r="D101" s="12"/>
-      <c r="E101" s="12"/>
+      <c r="A101" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B101" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="C101" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E101" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F101" s="12"/>
       <c r="G101" s="12"/>
       <c r="H101" s="12"/>
@@ -18409,11 +19098,21 @@
       <c r="J101" s="12"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="12"/>
-      <c r="B102" s="12"/>
-      <c r="C102" s="12"/>
-      <c r="D102" s="12"/>
-      <c r="E102" s="12"/>
+      <c r="A102" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B102" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="C102" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="E102" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F102" s="12"/>
       <c r="G102" s="12"/>
       <c r="H102" s="12"/>
@@ -18421,11 +19120,21 @@
       <c r="J102" s="12"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="12"/>
-      <c r="B103" s="12"/>
-      <c r="C103" s="12"/>
-      <c r="D103" s="12"/>
-      <c r="E103" s="12"/>
+      <c r="A103" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B103" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="C103" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="E103" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F103" s="12"/>
       <c r="G103" s="12"/>
       <c r="H103" s="12"/>
@@ -18433,11 +19142,21 @@
       <c r="J103" s="12"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="12"/>
-      <c r="B104" s="12"/>
-      <c r="C104" s="12"/>
-      <c r="D104" s="12"/>
-      <c r="E104" s="12"/>
+      <c r="A104" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B104" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="C104" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D104" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="E104" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F104" s="12"/>
       <c r="G104" s="12"/>
       <c r="H104" s="12"/>
@@ -18445,11 +19164,21 @@
       <c r="J104" s="12"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="12"/>
-      <c r="B105" s="12"/>
-      <c r="C105" s="12"/>
-      <c r="D105" s="12"/>
-      <c r="E105" s="12"/>
+      <c r="A105" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B105" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="C105" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D105" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="E105" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F105" s="12"/>
       <c r="G105" s="12"/>
       <c r="H105" s="12"/>
@@ -18457,11 +19186,21 @@
       <c r="J105" s="12"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="12"/>
-      <c r="B106" s="12"/>
-      <c r="C106" s="12"/>
-      <c r="D106" s="12"/>
-      <c r="E106" s="12"/>
+      <c r="A106" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B106" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="C106" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="E106" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F106" s="12"/>
       <c r="G106" s="12"/>
       <c r="H106" s="12"/>
@@ -18469,11 +19208,21 @@
       <c r="J106" s="12"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="12"/>
-      <c r="B107" s="12"/>
-      <c r="C107" s="12"/>
-      <c r="D107" s="12"/>
-      <c r="E107" s="12"/>
+      <c r="A107" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B107" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="C107" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D107" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="E107" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F107" s="12"/>
       <c r="G107" s="12"/>
       <c r="H107" s="12"/>
@@ -18481,11 +19230,21 @@
       <c r="J107" s="12"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="12"/>
-      <c r="B108" s="12"/>
-      <c r="C108" s="12"/>
-      <c r="D108" s="12"/>
-      <c r="E108" s="12"/>
+      <c r="A108" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B108" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="C108" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D108" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="E108" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F108" s="12"/>
       <c r="G108" s="12"/>
       <c r="H108" s="12"/>
@@ -18493,11 +19252,21 @@
       <c r="J108" s="12"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="12"/>
-      <c r="B109" s="12"/>
-      <c r="C109" s="12"/>
-      <c r="D109" s="12"/>
-      <c r="E109" s="12"/>
+      <c r="A109" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B109" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="C109" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D109" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="E109" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F109" s="12"/>
       <c r="G109" s="12"/>
       <c r="H109" s="12"/>
@@ -18505,11 +19274,21 @@
       <c r="J109" s="12"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="12"/>
-      <c r="B110" s="12"/>
-      <c r="C110" s="12"/>
-      <c r="D110" s="12"/>
-      <c r="E110" s="12"/>
+      <c r="A110" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B110" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="C110" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D110" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="E110" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F110" s="12"/>
       <c r="G110" s="12"/>
       <c r="H110" s="12"/>
@@ -18517,11 +19296,21 @@
       <c r="J110" s="12"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="12"/>
-      <c r="B111" s="12"/>
-      <c r="C111" s="12"/>
-      <c r="D111" s="12"/>
-      <c r="E111" s="12"/>
+      <c r="A111" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B111" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="C111" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="E111" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F111" s="12"/>
       <c r="G111" s="12"/>
       <c r="H111" s="12"/>
@@ -18529,11 +19318,21 @@
       <c r="J111" s="12"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="12"/>
-      <c r="B112" s="12"/>
-      <c r="C112" s="12"/>
-      <c r="D112" s="12"/>
-      <c r="E112" s="12"/>
+      <c r="A112" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B112" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="C112" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D112" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="E112" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F112" s="12"/>
       <c r="G112" s="12"/>
       <c r="H112" s="12"/>
@@ -18541,11 +19340,21 @@
       <c r="J112" s="12"/>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="12"/>
-      <c r="B113" s="12"/>
-      <c r="C113" s="12"/>
-      <c r="D113" s="12"/>
-      <c r="E113" s="12"/>
+      <c r="A113" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B113" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="C113" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D113" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="E113" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F113" s="12"/>
       <c r="G113" s="12"/>
       <c r="H113" s="12"/>
@@ -18553,11 +19362,21 @@
       <c r="J113" s="12"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="12"/>
-      <c r="B114" s="12"/>
-      <c r="C114" s="12"/>
-      <c r="D114" s="12"/>
-      <c r="E114" s="12"/>
+      <c r="A114" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B114" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="C114" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D114" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="E114" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F114" s="12"/>
       <c r="G114" s="12"/>
       <c r="H114" s="12"/>
@@ -18565,11 +19384,21 @@
       <c r="J114" s="12"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="12"/>
-      <c r="B115" s="12"/>
-      <c r="C115" s="12"/>
-      <c r="D115" s="12"/>
-      <c r="E115" s="12"/>
+      <c r="A115" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B115" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="C115" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D115" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="E115" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F115" s="12"/>
       <c r="G115" s="12"/>
       <c r="H115" s="12"/>
@@ -18577,11 +19406,21 @@
       <c r="J115" s="12"/>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="12"/>
-      <c r="B116" s="12"/>
-      <c r="C116" s="12"/>
-      <c r="D116" s="12"/>
-      <c r="E116" s="12"/>
+      <c r="A116" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B116" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C116" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D116" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E116" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F116" s="12"/>
       <c r="G116" s="12"/>
       <c r="H116" s="12"/>
@@ -18589,11 +19428,21 @@
       <c r="J116" s="12"/>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="12"/>
-      <c r="B117" s="12"/>
-      <c r="C117" s="12"/>
-      <c r="D117" s="12"/>
-      <c r="E117" s="12"/>
+      <c r="A117" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B117" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C117" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D117" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="E117" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F117" s="12"/>
       <c r="G117" s="12"/>
       <c r="H117" s="12"/>
@@ -18601,11 +19450,21 @@
       <c r="J117" s="12"/>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="12"/>
-      <c r="B118" s="12"/>
-      <c r="C118" s="12"/>
-      <c r="D118" s="12"/>
-      <c r="E118" s="12"/>
+      <c r="A118" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B118" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C118" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D118" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="E118" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F118" s="12"/>
       <c r="G118" s="12"/>
       <c r="H118" s="12"/>
@@ -18613,11 +19472,21 @@
       <c r="J118" s="12"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="12"/>
-      <c r="B119" s="12"/>
-      <c r="C119" s="12"/>
-      <c r="D119" s="12"/>
-      <c r="E119" s="12"/>
+      <c r="A119" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B119" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C119" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D119" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="E119" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F119" s="12"/>
       <c r="G119" s="12"/>
       <c r="H119" s="12"/>
@@ -18625,11 +19494,21 @@
       <c r="J119" s="12"/>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="12"/>
-      <c r="B120" s="12"/>
-      <c r="C120" s="12"/>
-      <c r="D120" s="12"/>
-      <c r="E120" s="12"/>
+      <c r="A120" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B120" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C120" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D120" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="E120" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F120" s="12"/>
       <c r="G120" s="12"/>
       <c r="H120" s="12"/>
@@ -18637,11 +19516,21 @@
       <c r="J120" s="12"/>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="12"/>
-      <c r="B121" s="12"/>
-      <c r="C121" s="12"/>
-      <c r="D121" s="12"/>
-      <c r="E121" s="12"/>
+      <c r="A121" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B121" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="C121" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="E121" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F121" s="12"/>
       <c r="G121" s="12"/>
       <c r="H121" s="12"/>
@@ -18649,11 +19538,21 @@
       <c r="J121" s="12"/>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="12"/>
-      <c r="B122" s="12"/>
-      <c r="C122" s="12"/>
-      <c r="D122" s="12"/>
-      <c r="E122" s="12"/>
+      <c r="A122" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B122" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="C122" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D122" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="E122" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F122" s="12"/>
       <c r="G122" s="12"/>
       <c r="H122" s="12"/>
@@ -18661,11 +19560,21 @@
       <c r="J122" s="12"/>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="12"/>
-      <c r="B123" s="12"/>
-      <c r="C123" s="12"/>
-      <c r="D123" s="12"/>
-      <c r="E123" s="12"/>
+      <c r="A123" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B123" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="C123" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D123" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="E123" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F123" s="12"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -18673,11 +19582,21 @@
       <c r="J123" s="12"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="12"/>
-      <c r="B124" s="12"/>
-      <c r="C124" s="12"/>
-      <c r="D124" s="12"/>
-      <c r="E124" s="12"/>
+      <c r="A124" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B124" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="C124" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D124" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="E124" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F124" s="12"/>
       <c r="G124" s="12"/>
       <c r="H124" s="12"/>
@@ -18685,11 +19604,21 @@
       <c r="J124" s="12"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="12"/>
-      <c r="B125" s="12"/>
-      <c r="C125" s="12"/>
-      <c r="D125" s="12"/>
-      <c r="E125" s="12"/>
+      <c r="A125" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B125" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="C125" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D125" s="12" t="s">
+        <v>289</v>
+      </c>
+      <c r="E125" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F125" s="12"/>
       <c r="G125" s="12"/>
       <c r="H125" s="12"/>
@@ -18697,11 +19626,21 @@
       <c r="J125" s="12"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="12"/>
-      <c r="B126" s="12"/>
-      <c r="C126" s="12"/>
-      <c r="D126" s="12"/>
-      <c r="E126" s="12"/>
+      <c r="A126" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B126" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C126" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="E126" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F126" s="12"/>
       <c r="G126" s="12"/>
       <c r="H126" s="12"/>
@@ -18709,11 +19648,21 @@
       <c r="J126" s="12"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="12"/>
-      <c r="B127" s="12"/>
-      <c r="C127" s="12"/>
-      <c r="D127" s="12"/>
-      <c r="E127" s="12"/>
+      <c r="A127" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B127" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C127" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D127" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="E127" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F127" s="12"/>
       <c r="G127" s="12"/>
       <c r="H127" s="12"/>
@@ -18721,11 +19670,21 @@
       <c r="J127" s="12"/>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="12"/>
-      <c r="B128" s="12"/>
-      <c r="C128" s="12"/>
-      <c r="D128" s="12"/>
-      <c r="E128" s="12"/>
+      <c r="A128" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B128" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C128" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D128" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="E128" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F128" s="12"/>
       <c r="G128" s="12"/>
       <c r="H128" s="12"/>
@@ -18733,11 +19692,21 @@
       <c r="J128" s="12"/>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="12"/>
-      <c r="B129" s="12"/>
-      <c r="C129" s="12"/>
-      <c r="D129" s="12"/>
-      <c r="E129" s="12"/>
+      <c r="A129" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B129" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C129" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D129" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="E129" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F129" s="12"/>
       <c r="G129" s="12"/>
       <c r="H129" s="12"/>
@@ -18745,11 +19714,21 @@
       <c r="J129" s="12"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="12"/>
-      <c r="B130" s="12"/>
-      <c r="C130" s="12"/>
-      <c r="D130" s="12"/>
-      <c r="E130" s="12"/>
+      <c r="A130" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B130" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C130" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D130" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="E130" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F130" s="12"/>
       <c r="G130" s="12"/>
       <c r="H130" s="12"/>
@@ -18757,11 +19736,21 @@
       <c r="J130" s="12"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="12"/>
-      <c r="B131" s="12"/>
-      <c r="C131" s="12"/>
-      <c r="D131" s="12"/>
-      <c r="E131" s="12"/>
+      <c r="A131" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B131" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C131" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D131" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="E131" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F131" s="12"/>
       <c r="G131" s="12"/>
       <c r="H131" s="12"/>
@@ -18769,11 +19758,21 @@
       <c r="J131" s="12"/>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="12"/>
-      <c r="B132" s="12"/>
-      <c r="C132" s="12"/>
-      <c r="D132" s="12"/>
-      <c r="E132" s="12"/>
+      <c r="A132" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B132" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="C132" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D132" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="E132" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F132" s="12"/>
       <c r="G132" s="12"/>
       <c r="H132" s="12"/>
@@ -18781,11 +19780,21 @@
       <c r="J132" s="12"/>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="12"/>
-      <c r="B133" s="12"/>
-      <c r="C133" s="12"/>
-      <c r="D133" s="12"/>
-      <c r="E133" s="12"/>
+      <c r="A133" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B133" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="C133" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D133" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="E133" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F133" s="12"/>
       <c r="G133" s="12"/>
       <c r="H133" s="12"/>
@@ -18793,11 +19802,21 @@
       <c r="J133" s="12"/>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="12"/>
-      <c r="B134" s="12"/>
-      <c r="C134" s="12"/>
-      <c r="D134" s="12"/>
-      <c r="E134" s="12"/>
+      <c r="A134" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B134" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="C134" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D134" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="E134" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F134" s="12"/>
       <c r="G134" s="12"/>
       <c r="H134" s="12"/>
@@ -18805,11 +19824,21 @@
       <c r="J134" s="12"/>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="12"/>
-      <c r="B135" s="12"/>
-      <c r="C135" s="12"/>
-      <c r="D135" s="12"/>
-      <c r="E135" s="12"/>
+      <c r="A135" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B135" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="C135" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D135" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="E135" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F135" s="12"/>
       <c r="G135" s="12"/>
       <c r="H135" s="12"/>
@@ -18817,11 +19846,21 @@
       <c r="J135" s="12"/>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="12"/>
-      <c r="B136" s="12"/>
-      <c r="C136" s="12"/>
-      <c r="D136" s="12"/>
-      <c r="E136" s="12"/>
+      <c r="A136" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B136" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="C136" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D136" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="E136" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F136" s="12"/>
       <c r="G136" s="12"/>
       <c r="H136" s="12"/>
@@ -18829,11 +19868,21 @@
       <c r="J136" s="12"/>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="12"/>
-      <c r="B137" s="12"/>
-      <c r="C137" s="12"/>
-      <c r="D137" s="12"/>
-      <c r="E137" s="12"/>
+      <c r="A137" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B137" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="C137" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="E137" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F137" s="12"/>
       <c r="G137" s="12"/>
       <c r="H137" s="12"/>
@@ -18841,11 +19890,21 @@
       <c r="J137" s="12"/>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="12"/>
-      <c r="B138" s="12"/>
-      <c r="C138" s="12"/>
-      <c r="D138" s="12"/>
-      <c r="E138" s="12"/>
+      <c r="A138" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B138" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="C138" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D138" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="E138" s="12" t="s">
+        <v>259</v>
+      </c>
       <c r="F138" s="12"/>
       <c r="G138" s="12"/>
       <c r="H138" s="12"/>
@@ -18853,11 +19912,21 @@
       <c r="J138" s="12"/>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="12"/>
-      <c r="B139" s="12"/>
-      <c r="C139" s="12"/>
-      <c r="D139" s="12"/>
-      <c r="E139" s="12"/>
+      <c r="A139" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B139" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="C139" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D139" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="E139" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F139" s="12"/>
       <c r="G139" s="12"/>
       <c r="H139" s="12"/>
@@ -18865,11 +19934,21 @@
       <c r="J139" s="12"/>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="12"/>
-      <c r="B140" s="12"/>
-      <c r="C140" s="12"/>
-      <c r="D140" s="12"/>
-      <c r="E140" s="12"/>
+      <c r="A140" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="B140" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="C140" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D140" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="E140" s="12" t="s">
+        <v>262</v>
+      </c>
       <c r="F140" s="12"/>
       <c r="G140" s="12"/>
       <c r="H140" s="12"/>
@@ -18888,8 +19967,10 @@
       <c r="I141" s="12"/>
       <c r="J141" s="12"/>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="12"/>
+    <row r="142" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="17" t="s">
+        <v>314</v>
+      </c>
       <c r="B142" s="12"/>
       <c r="C142" s="12"/>
       <c r="D142" s="12"/>
@@ -18900,8 +19981,10 @@
       <c r="I142" s="12"/>
       <c r="J142" s="12"/>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="12"/>
+    <row r="143" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="17" t="s">
+        <v>315</v>
+      </c>
       <c r="B143" s="12"/>
       <c r="C143" s="12"/>
       <c r="D143" s="12"/>
@@ -22410,12 +23493,12 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>284</v>
+        <v>316</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>285</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -22444,16 +23527,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>286</v>
+        <v>318</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>287</v>
+        <v>319</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>288</v>
+        <v>320</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>289</v>
+        <v>321</v>
       </c>
       <c r="E1" s="11" t="s">
         <v>257</v>
@@ -22461,7 +23544,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>290</v>
+        <v>322</v>
       </c>
       <c r="B2" s="18" t="n">
         <v>8</v>
@@ -22473,12 +23556,12 @@
         <v>25</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>291</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>292</v>
+        <v>324</v>
       </c>
       <c r="B3" s="18" t="n">
         <v>8</v>
@@ -22490,12 +23573,12 @@
         <v>25</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>293</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>294</v>
+        <v>326</v>
       </c>
       <c r="B4" s="18" t="n">
         <v>30</v>
@@ -22507,12 +23590,12 @@
         <v>100</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>295</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>296</v>
+        <v>328</v>
       </c>
       <c r="B5" s="18" t="n">
         <v>10</v>
@@ -22524,12 +23607,12 @@
         <v>32</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>297</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>298</v>
+        <v>330</v>
       </c>
       <c r="B6" s="18" t="n">
         <v>3</v>
@@ -22541,12 +23624,12 @@
         <v>4</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>299</v>
+        <v>331</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>300</v>
+        <v>332</v>
       </c>
       <c r="B7" s="19" t="n">
         <v>0.1</v>
@@ -22558,12 +23641,12 @@
         <v>0.12</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>301</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>302</v>
+        <v>334</v>
       </c>
       <c r="B8" s="19" t="n">
         <v>0.3</v>
@@ -22575,12 +23658,12 @@
         <v>0.32</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>303</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>304</v>
+        <v>336</v>
       </c>
       <c r="B9" s="18" t="n">
         <v>15</v>
@@ -22592,12 +23675,12 @@
         <v>50</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>305</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>306</v>
+        <v>338</v>
       </c>
       <c r="B10" s="19" t="n">
         <v>0.06</v>
@@ -22609,12 +23692,12 @@
         <v>0.06</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>307</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>308</v>
+        <v>340</v>
       </c>
       <c r="B11" s="18" t="n">
         <v>1.5</v>
@@ -22626,12 +23709,12 @@
         <v>1.5</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>309</v>
+        <v>341</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>310</v>
+        <v>342</v>
       </c>
       <c r="B12" s="18" t="n">
         <v>2.5</v>
@@ -22646,7 +23729,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>311</v>
+        <v>343</v>
       </c>
       <c r="B13" s="19" t="n">
         <v>0.1</v>
@@ -22658,12 +23741,12 @@
         <v>0.1</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>312</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>313</v>
+        <v>345</v>
       </c>
       <c r="B14" s="18" t="n">
         <v>2</v>
@@ -22675,12 +23758,12 @@
         <v>2</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>314</v>
+        <v>346</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>315</v>
+        <v>347</v>
       </c>
       <c r="B15" s="19" t="n">
         <v>0.15</v>
@@ -22695,7 +23778,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>316</v>
+        <v>348</v>
       </c>
       <c r="B16" s="18" t="n">
         <v>3</v>
@@ -22710,7 +23793,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>317</v>
+        <v>349</v>
       </c>
       <c r="B17" s="19" t="n">
         <v>0.25</v>
@@ -22725,7 +23808,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>318</v>
+        <v>350</v>
       </c>
       <c r="B18" s="18" t="n">
         <v>4</v>
@@ -22740,7 +23823,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>319</v>
+        <v>351</v>
       </c>
       <c r="B19" s="19" t="n">
         <v>0.6</v>
@@ -22752,12 +23835,12 @@
         <v>0.6</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>320</v>
+        <v>352</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>321</v>
+        <v>353</v>
       </c>
       <c r="B20" s="19" t="n">
         <v>0.85</v>
@@ -22772,7 +23855,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>322</v>
+        <v>354</v>
       </c>
       <c r="B21" s="19" t="n">
         <v>0.15</v>
@@ -22787,7 +23870,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>323</v>
+        <v>355</v>
       </c>
       <c r="B22" s="19" t="n">
         <v>0.6</v>
@@ -22799,12 +23882,12 @@
         <v>0.6</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>324</v>
+        <v>356</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>325</v>
+        <v>357</v>
       </c>
       <c r="B23" s="19" t="n">
         <v>0.15</v>
@@ -22816,12 +23899,12 @@
         <v>0.15</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>326</v>
+        <v>358</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="B24" s="19" t="n">
         <v>0.6</v>
@@ -22833,12 +23916,12 @@
         <v>0.6</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>328</v>
+        <v>360</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="14" t="s">
-        <v>329</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>

--- a/programmes/Kinetix Programmes.xlsx
+++ b/programmes/Kinetix Programmes.xlsx
@@ -2632,7 +2632,7 @@
         <v>85</v>
       </c>
       <c r="N6" s="32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O6" s="32" t="inlineStr">
         <is>
@@ -4617,13 +4617,37 @@
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="21">
-      <c r="A38" s="32" t="n"/>
-      <c r="B38" s="32" t="n"/>
-      <c r="C38" s="32" t="n"/>
-      <c r="D38" s="35" t="n"/>
-      <c r="E38" s="32" t="n"/>
-      <c r="F38" s="32" t="n"/>
-      <c r="G38" s="32" t="n"/>
+      <c r="A38" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B38" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="32" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D38" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F38" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G38" s="32" t="inlineStr">
+        <is>
+          <t>Settle in: one threshold session and an M-pace progression, everything else easy.</t>
+        </is>
+      </c>
       <c r="H38" s="33">
         <f>IF(A38="","",COUNTIFS('Run sessions'!$A$2:$A$401,A38,'Run sessions'!$B$2:$B$401,B38))</f>
         <v/>
@@ -4638,12 +4662,32 @@
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="21">
-      <c r="A39" s="32" t="n"/>
-      <c r="B39" s="32" t="n"/>
-      <c r="C39" s="32" t="n"/>
-      <c r="D39" s="35" t="n"/>
-      <c r="E39" s="32" t="n"/>
-      <c r="F39" s="32" t="n"/>
+      <c r="A39" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B39" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" s="32" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D39" s="35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E39" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F39" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="G39" s="32" t="n"/>
       <c r="H39" s="33">
         <f>IF(A39="","",COUNTIFS('Run sessions'!$A$2:$A$401,A39,'Run sessions'!$B$2:$B$401,B39))</f>
@@ -4659,12 +4703,32 @@
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="21">
-      <c r="A40" s="32" t="n"/>
-      <c r="B40" s="32" t="n"/>
-      <c r="C40" s="32" t="n"/>
-      <c r="D40" s="35" t="n"/>
-      <c r="E40" s="32" t="n"/>
-      <c r="F40" s="32" t="n"/>
+      <c r="A40" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B40" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" s="32" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D40" s="35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E40" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F40" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="G40" s="32" t="n"/>
       <c r="H40" s="33">
         <f>IF(A40="","",COUNTIFS('Run sessions'!$A$2:$A$401,A40,'Run sessions'!$B$2:$B$401,B40))</f>
@@ -4680,13 +4744,37 @@
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="21">
-      <c r="A41" s="32" t="n"/>
-      <c r="B41" s="32" t="n"/>
-      <c r="C41" s="32" t="n"/>
-      <c r="D41" s="35" t="n"/>
-      <c r="E41" s="32" t="n"/>
-      <c r="F41" s="32" t="n"/>
-      <c r="G41" s="32" t="n"/>
+      <c r="A41" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B41" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" s="32" t="inlineStr">
+        <is>
+          <t>Deload</t>
+        </is>
+      </c>
+      <c r="D41" s="35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E41" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F41" s="32" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G41" s="32" t="inlineStr">
+        <is>
+          <t>Lighter week: let the work sink in.</t>
+        </is>
+      </c>
       <c r="H41" s="33">
         <f>IF(A41="","",COUNTIFS('Run sessions'!$A$2:$A$401,A41,'Run sessions'!$B$2:$B$401,B41))</f>
         <v/>
@@ -4701,13 +4789,37 @@
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="21">
-      <c r="A42" s="32" t="n"/>
-      <c r="B42" s="32" t="n"/>
-      <c r="C42" s="32" t="n"/>
-      <c r="D42" s="35" t="n"/>
-      <c r="E42" s="32" t="n"/>
-      <c r="F42" s="32" t="n"/>
-      <c r="G42" s="32" t="n"/>
+      <c r="A42" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B42" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" s="32" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D42" s="35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E42" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F42" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G42" s="32" t="inlineStr">
+        <is>
+          <t>Marathon pace starts to appear in your long run.</t>
+        </is>
+      </c>
       <c r="H42" s="33">
         <f>IF(A42="","",COUNTIFS('Run sessions'!$A$2:$A$401,A42,'Run sessions'!$B$2:$B$401,B42))</f>
         <v/>
@@ -4722,12 +4834,32 @@
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="21">
-      <c r="A43" s="32" t="n"/>
-      <c r="B43" s="32" t="n"/>
-      <c r="C43" s="32" t="n"/>
-      <c r="D43" s="35" t="n"/>
-      <c r="E43" s="32" t="n"/>
-      <c r="F43" s="32" t="n"/>
+      <c r="A43" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B43" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C43" s="32" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D43" s="35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E43" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F43" s="32" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="G43" s="32" t="n"/>
       <c r="H43" s="33">
         <f>IF(A43="","",COUNTIFS('Run sessions'!$A$2:$A$401,A43,'Run sessions'!$B$2:$B$401,B43))</f>
@@ -4743,12 +4875,32 @@
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="21">
-      <c r="A44" s="32" t="n"/>
-      <c r="B44" s="32" t="n"/>
-      <c r="C44" s="32" t="n"/>
-      <c r="D44" s="35" t="n"/>
-      <c r="E44" s="32" t="n"/>
-      <c r="F44" s="32" t="n"/>
+      <c r="A44" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B44" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C44" s="32" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D44" s="35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E44" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F44" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="G44" s="32" t="n"/>
       <c r="H44" s="33">
         <f>IF(A44="","",COUNTIFS('Run sessions'!$A$2:$A$401,A44,'Run sessions'!$B$2:$B$401,B44))</f>
@@ -4764,13 +4916,37 @@
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="21">
-      <c r="A45" s="32" t="n"/>
-      <c r="B45" s="32" t="n"/>
-      <c r="C45" s="32" t="n"/>
-      <c r="D45" s="35" t="n"/>
-      <c r="E45" s="32" t="n"/>
-      <c r="F45" s="32" t="n"/>
-      <c r="G45" s="32" t="n"/>
+      <c r="A45" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B45" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C45" s="32" t="inlineStr">
+        <is>
+          <t>Deload</t>
+        </is>
+      </c>
+      <c r="D45" s="35" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E45" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F45" s="32" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G45" s="32" t="inlineStr">
+        <is>
+          <t>Lighter week before the big block.</t>
+        </is>
+      </c>
       <c r="H45" s="33">
         <f>IF(A45="","",COUNTIFS('Run sessions'!$A$2:$A$401,A45,'Run sessions'!$B$2:$B$401,B45))</f>
         <v/>
@@ -4785,13 +4961,37 @@
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="21">
-      <c r="A46" s="32" t="n"/>
-      <c r="B46" s="32" t="n"/>
-      <c r="C46" s="32" t="n"/>
-      <c r="D46" s="35" t="n"/>
-      <c r="E46" s="32" t="n"/>
-      <c r="F46" s="32" t="n"/>
-      <c r="G46" s="32" t="n"/>
+      <c r="A46" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B46" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="C46" s="32" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D46" s="35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E46" s="32" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="F46" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G46" s="32" t="inlineStr">
+        <is>
+          <t>First really long run: keep it easy.</t>
+        </is>
+      </c>
       <c r="H46" s="33">
         <f>IF(A46="","",COUNTIFS('Run sessions'!$A$2:$A$401,A46,'Run sessions'!$B$2:$B$401,B46))</f>
         <v/>
@@ -4806,12 +5006,32 @@
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="21">
-      <c r="A47" s="32" t="n"/>
-      <c r="B47" s="32" t="n"/>
-      <c r="C47" s="32" t="n"/>
-      <c r="D47" s="35" t="n"/>
-      <c r="E47" s="32" t="n"/>
-      <c r="F47" s="32" t="n"/>
+      <c r="A47" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B47" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="C47" s="32" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D47" s="35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E47" s="32" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="F47" s="32" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="G47" s="32" t="n"/>
       <c r="H47" s="33">
         <f>IF(A47="","",COUNTIFS('Run sessions'!$A$2:$A$401,A47,'Run sessions'!$B$2:$B$401,B47))</f>
@@ -4827,13 +5047,37 @@
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="21">
-      <c r="A48" s="32" t="n"/>
-      <c r="B48" s="32" t="n"/>
-      <c r="C48" s="32" t="n"/>
-      <c r="D48" s="35" t="n"/>
-      <c r="E48" s="32" t="n"/>
-      <c r="F48" s="32" t="n"/>
-      <c r="G48" s="32" t="n"/>
+      <c r="A48" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B48" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="C48" s="32" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="D48" s="35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E48" s="32" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="F48" s="32" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G48" s="32" t="inlineStr">
+        <is>
+          <t>Peak block: long runs near their longest.</t>
+        </is>
+      </c>
       <c r="H48" s="33">
         <f>IF(A48="","",COUNTIFS('Run sessions'!$A$2:$A$401,A48,'Run sessions'!$B$2:$B$401,B48))</f>
         <v/>
@@ -4848,13 +5092,37 @@
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="21">
-      <c r="A49" s="32" t="n"/>
-      <c r="B49" s="32" t="n"/>
-      <c r="C49" s="32" t="n"/>
-      <c r="D49" s="35" t="n"/>
-      <c r="E49" s="32" t="n"/>
-      <c r="F49" s="32" t="n"/>
-      <c r="G49" s="32" t="n"/>
+      <c r="A49" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B49" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="C49" s="32" t="inlineStr">
+        <is>
+          <t>Deload</t>
+        </is>
+      </c>
+      <c r="D49" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F49" s="32" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G49" s="32" t="inlineStr">
+        <is>
+          <t>Recover before your longest run.</t>
+        </is>
+      </c>
       <c r="H49" s="33">
         <f>IF(A49="","",COUNTIFS('Run sessions'!$A$2:$A$401,A49,'Run sessions'!$B$2:$B$401,B49))</f>
         <v/>
@@ -4869,13 +5137,37 @@
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="21">
-      <c r="A50" s="32" t="n"/>
-      <c r="B50" s="32" t="n"/>
-      <c r="C50" s="32" t="n"/>
-      <c r="D50" s="35" t="n"/>
-      <c r="E50" s="32" t="n"/>
-      <c r="F50" s="32" t="n"/>
-      <c r="G50" s="32" t="n"/>
+      <c r="A50" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B50" s="32" t="n">
+        <v>13</v>
+      </c>
+      <c r="C50" s="32" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="D50" s="35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E50" s="32" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="F50" s="32" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G50" s="32" t="inlineStr">
+        <is>
+          <t>Your longest run of the plan.</t>
+        </is>
+      </c>
       <c r="H50" s="33">
         <f>IF(A50="","",COUNTIFS('Run sessions'!$A$2:$A$401,A50,'Run sessions'!$B$2:$B$401,B50))</f>
         <v/>
@@ -4890,13 +5182,37 @@
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="21">
-      <c r="A51" s="32" t="n"/>
-      <c r="B51" s="32" t="n"/>
-      <c r="C51" s="32" t="n"/>
-      <c r="D51" s="35" t="n"/>
-      <c r="E51" s="32" t="n"/>
-      <c r="F51" s="32" t="n"/>
-      <c r="G51" s="32" t="n"/>
+      <c r="A51" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B51" s="32" t="n">
+        <v>14</v>
+      </c>
+      <c r="C51" s="32" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="D51" s="35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E51" s="32" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="F51" s="32" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G51" s="32" t="inlineStr">
+        <is>
+          <t>Last big week: a long run with plenty of marathon pace.</t>
+        </is>
+      </c>
       <c r="H51" s="33">
         <f>IF(A51="","",COUNTIFS('Run sessions'!$A$2:$A$401,A51,'Run sessions'!$B$2:$B$401,B51))</f>
         <v/>
@@ -4911,13 +5227,37 @@
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="21">
-      <c r="A52" s="32" t="n"/>
-      <c r="B52" s="32" t="n"/>
-      <c r="C52" s="32" t="n"/>
-      <c r="D52" s="35" t="n"/>
-      <c r="E52" s="32" t="n"/>
-      <c r="F52" s="32" t="n"/>
-      <c r="G52" s="32" t="n"/>
+      <c r="A52" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B52" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="C52" s="32" t="inlineStr">
+        <is>
+          <t>Taper</t>
+        </is>
+      </c>
+      <c r="D52" s="35" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E52" s="32" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="F52" s="32" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G52" s="32" t="inlineStr">
+        <is>
+          <t>Taper: less running, keep a little pace.</t>
+        </is>
+      </c>
       <c r="H52" s="33">
         <f>IF(A52="","",COUNTIFS('Run sessions'!$A$2:$A$401,A52,'Run sessions'!$B$2:$B$401,B52))</f>
         <v/>
@@ -4932,13 +5272,37 @@
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" s="21">
-      <c r="A53" s="32" t="n"/>
-      <c r="B53" s="32" t="n"/>
-      <c r="C53" s="32" t="n"/>
-      <c r="D53" s="35" t="n"/>
-      <c r="E53" s="32" t="n"/>
-      <c r="F53" s="32" t="n"/>
-      <c r="G53" s="32" t="n"/>
+      <c r="A53" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B53" s="32" t="n">
+        <v>16</v>
+      </c>
+      <c r="C53" s="32" t="inlineStr">
+        <is>
+          <t>Race week</t>
+        </is>
+      </c>
+      <c r="D53" s="35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E53" s="32" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F53" s="32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G53" s="32" t="inlineStr">
+        <is>
+          <t>Race day!</t>
+        </is>
+      </c>
       <c r="H53" s="33">
         <f>IF(A53="","",COUNTIFS('Run sessions'!$A$2:$A$401,A53,'Run sessions'!$B$2:$B$401,B53))</f>
         <v/>
@@ -16442,714 +16806,2294 @@
       <c r="G141" s="32" t="n"/>
     </row>
     <row r="142" ht="15" customHeight="1" s="21">
-      <c r="A142" s="32" t="n"/>
-      <c r="B142" s="32" t="n"/>
-      <c r="C142" s="32" t="n"/>
-      <c r="D142" s="32" t="n"/>
-      <c r="E142" s="32" t="n"/>
-      <c r="F142" s="32" t="n"/>
+      <c r="A142" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B142" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E142" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F142" s="32" t="inlineStr">
+        <is>
+          <t>6 x 1 km @ T, 90 s jog between</t>
+        </is>
+      </c>
       <c r="G142" s="32" t="n"/>
     </row>
     <row r="143" ht="15" customHeight="1" s="21">
-      <c r="A143" s="32" t="n"/>
-      <c r="B143" s="32" t="n"/>
-      <c r="C143" s="32" t="n"/>
-      <c r="D143" s="32" t="n"/>
-      <c r="E143" s="32" t="n"/>
-      <c r="F143" s="32" t="n"/>
+      <c r="A143" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B143" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D143" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E143" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F143" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G143" s="32" t="n"/>
     </row>
     <row r="144" ht="15" customHeight="1" s="21">
-      <c r="A144" s="32" t="n"/>
-      <c r="B144" s="32" t="n"/>
-      <c r="C144" s="32" t="n"/>
-      <c r="D144" s="32" t="n"/>
-      <c r="E144" s="32" t="n"/>
-      <c r="F144" s="32" t="n"/>
+      <c r="A144" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B144" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C144" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D144" s="32" t="inlineStr">
+        <is>
+          <t>Progression</t>
+        </is>
+      </c>
+      <c r="E144" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F144" s="32" t="inlineStr">
+        <is>
+          <t>5 km E → 4 km STEADY → 2 km M</t>
+        </is>
+      </c>
       <c r="G144" s="32" t="n"/>
     </row>
     <row r="145" ht="15" customHeight="1" s="21">
-      <c r="A145" s="32" t="n"/>
-      <c r="B145" s="32" t="n"/>
-      <c r="C145" s="32" t="n"/>
-      <c r="D145" s="32" t="n"/>
-      <c r="E145" s="32" t="n"/>
-      <c r="F145" s="32" t="n"/>
+      <c r="A145" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B145" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C145" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D145" s="32" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="E145" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F145" s="32" t="inlineStr">
+        <is>
+          <t>Very relaxed recovery run</t>
+        </is>
+      </c>
       <c r="G145" s="32" t="n"/>
     </row>
     <row r="146" ht="15" customHeight="1" s="21">
-      <c r="A146" s="32" t="n"/>
-      <c r="B146" s="32" t="n"/>
-      <c r="C146" s="32" t="n"/>
-      <c r="D146" s="32" t="n"/>
-      <c r="E146" s="32" t="n"/>
-      <c r="F146" s="32" t="n"/>
+      <c r="A146" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B146" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C146" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D146" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E146" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F146" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G146" s="32" t="n"/>
     </row>
     <row r="147" ht="15" customHeight="1" s="21">
-      <c r="A147" s="32" t="n"/>
-      <c r="B147" s="32" t="n"/>
-      <c r="C147" s="32" t="n"/>
-      <c r="D147" s="32" t="n"/>
-      <c r="E147" s="32" t="n"/>
-      <c r="F147" s="32" t="n"/>
+      <c r="A147" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B147" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C147" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E147" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F147" s="32" t="inlineStr">
+        <is>
+          <t>5 x 1.2 km @ T, 90 s jog between</t>
+        </is>
+      </c>
       <c r="G147" s="32" t="n"/>
     </row>
     <row r="148" ht="15" customHeight="1" s="21">
-      <c r="A148" s="32" t="n"/>
-      <c r="B148" s="32" t="n"/>
-      <c r="C148" s="32" t="n"/>
-      <c r="D148" s="32" t="n"/>
-      <c r="E148" s="32" t="n"/>
-      <c r="F148" s="32" t="n"/>
+      <c r="A148" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B148" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C148" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D148" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E148" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F148" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G148" s="32" t="n"/>
     </row>
     <row r="149" ht="15" customHeight="1" s="21">
-      <c r="A149" s="32" t="n"/>
-      <c r="B149" s="32" t="n"/>
-      <c r="C149" s="32" t="n"/>
-      <c r="D149" s="32" t="n"/>
-      <c r="E149" s="32" t="n"/>
-      <c r="F149" s="32" t="n"/>
+      <c r="A149" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B149" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C149" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D149" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E149" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F149" s="32" t="inlineStr">
+        <is>
+          <t>2 x 10 min @ T, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G149" s="32" t="n"/>
     </row>
     <row r="150" ht="15" customHeight="1" s="21">
-      <c r="A150" s="32" t="n"/>
-      <c r="B150" s="32" t="n"/>
-      <c r="C150" s="32" t="n"/>
-      <c r="D150" s="32" t="n"/>
-      <c r="E150" s="32" t="n"/>
-      <c r="F150" s="32" t="n"/>
+      <c r="A150" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B150" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C150" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D150" s="32" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="E150" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F150" s="32" t="inlineStr">
+        <is>
+          <t>Very relaxed recovery run</t>
+        </is>
+      </c>
       <c r="G150" s="32" t="n"/>
     </row>
     <row r="151" ht="15" customHeight="1" s="21">
-      <c r="A151" s="32" t="n"/>
-      <c r="B151" s="32" t="n"/>
-      <c r="C151" s="32" t="n"/>
-      <c r="D151" s="32" t="n"/>
-      <c r="E151" s="32" t="n"/>
-      <c r="F151" s="32" t="n"/>
+      <c r="A151" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B151" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C151" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D151" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E151" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F151" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G151" s="32" t="n"/>
     </row>
     <row r="152" ht="15" customHeight="1" s="21">
-      <c r="A152" s="32" t="n"/>
-      <c r="B152" s="32" t="n"/>
-      <c r="C152" s="32" t="n"/>
-      <c r="D152" s="32" t="n"/>
-      <c r="E152" s="32" t="n"/>
-      <c r="F152" s="32" t="n"/>
+      <c r="A152" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B152" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C152" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E152" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F152" s="32" t="inlineStr">
+        <is>
+          <t>4 x 1.6 km @ T, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G152" s="32" t="n"/>
     </row>
     <row r="153" ht="15" customHeight="1" s="21">
-      <c r="A153" s="32" t="n"/>
-      <c r="B153" s="32" t="n"/>
-      <c r="C153" s="32" t="n"/>
-      <c r="D153" s="32" t="n"/>
-      <c r="E153" s="32" t="n"/>
-      <c r="F153" s="32" t="n"/>
+      <c r="A153" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B153" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C153" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D153" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E153" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F153" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G153" s="32" t="n"/>
     </row>
     <row r="154" ht="15" customHeight="1" s="21">
-      <c r="A154" s="32" t="n"/>
-      <c r="B154" s="32" t="n"/>
-      <c r="C154" s="32" t="n"/>
-      <c r="D154" s="32" t="n"/>
-      <c r="E154" s="32" t="n"/>
-      <c r="F154" s="32" t="n"/>
+      <c r="A154" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B154" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C154" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D154" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E154" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F154" s="32" t="inlineStr">
+        <is>
+          <t>3 x 3 km @ M, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G154" s="32" t="n"/>
     </row>
     <row r="155" ht="15" customHeight="1" s="21">
-      <c r="A155" s="32" t="n"/>
-      <c r="B155" s="32" t="n"/>
-      <c r="C155" s="32" t="n"/>
-      <c r="D155" s="32" t="n"/>
-      <c r="E155" s="32" t="n"/>
-      <c r="F155" s="32" t="n"/>
+      <c r="A155" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B155" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C155" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D155" s="32" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="E155" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F155" s="32" t="inlineStr">
+        <is>
+          <t>Very relaxed recovery run</t>
+        </is>
+      </c>
       <c r="G155" s="32" t="n"/>
     </row>
     <row r="156" ht="15" customHeight="1" s="21">
-      <c r="A156" s="32" t="n"/>
-      <c r="B156" s="32" t="n"/>
-      <c r="C156" s="32" t="n"/>
-      <c r="D156" s="32" t="n"/>
-      <c r="E156" s="32" t="n"/>
-      <c r="F156" s="32" t="n"/>
+      <c r="A156" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B156" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C156" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D156" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E156" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F156" s="32" t="inlineStr">
+        <is>
+          <t>16 km E, final 3 km @ STEADY</t>
+        </is>
+      </c>
       <c r="G156" s="32" t="n"/>
     </row>
     <row r="157" ht="15" customHeight="1" s="21">
-      <c r="A157" s="32" t="n"/>
-      <c r="B157" s="32" t="n"/>
-      <c r="C157" s="32" t="n"/>
-      <c r="D157" s="32" t="n"/>
-      <c r="E157" s="32" t="n"/>
-      <c r="F157" s="32" t="n"/>
+      <c r="A157" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B157" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C157" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E157" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F157" s="32" t="inlineStr">
+        <is>
+          <t>5 x 1 km @ T, 90 s jog between</t>
+        </is>
+      </c>
       <c r="G157" s="32" t="n"/>
     </row>
     <row r="158" ht="15" customHeight="1" s="21">
-      <c r="A158" s="32" t="n"/>
-      <c r="B158" s="32" t="n"/>
-      <c r="C158" s="32" t="n"/>
-      <c r="D158" s="32" t="n"/>
-      <c r="E158" s="32" t="n"/>
-      <c r="F158" s="32" t="n"/>
+      <c r="A158" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B158" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C158" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D158" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E158" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F158" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G158" s="32" t="n"/>
     </row>
     <row r="159" ht="15" customHeight="1" s="21">
-      <c r="A159" s="32" t="n"/>
-      <c r="B159" s="32" t="n"/>
-      <c r="C159" s="32" t="n"/>
-      <c r="D159" s="32" t="n"/>
-      <c r="E159" s="32" t="n"/>
-      <c r="F159" s="32" t="n"/>
+      <c r="A159" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B159" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C159" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D159" s="32" t="inlineStr">
+        <is>
+          <t>Progression</t>
+        </is>
+      </c>
+      <c r="E159" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F159" s="32" t="inlineStr">
+        <is>
+          <t>4 km E → 3 km STEADY</t>
+        </is>
+      </c>
       <c r="G159" s="32" t="n"/>
     </row>
     <row r="160" ht="15" customHeight="1" s="21">
-      <c r="A160" s="32" t="n"/>
-      <c r="B160" s="32" t="n"/>
-      <c r="C160" s="32" t="n"/>
-      <c r="D160" s="32" t="n"/>
-      <c r="E160" s="32" t="n"/>
-      <c r="F160" s="32" t="n"/>
+      <c r="A160" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B160" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C160" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D160" s="32" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="E160" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F160" s="32" t="inlineStr">
+        <is>
+          <t>Very relaxed recovery run</t>
+        </is>
+      </c>
       <c r="G160" s="32" t="n"/>
     </row>
     <row r="161" ht="15" customHeight="1" s="21">
-      <c r="A161" s="32" t="n"/>
-      <c r="B161" s="32" t="n"/>
-      <c r="C161" s="32" t="n"/>
-      <c r="D161" s="32" t="n"/>
-      <c r="E161" s="32" t="n"/>
-      <c r="F161" s="32" t="n"/>
+      <c r="A161" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B161" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C161" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D161" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E161" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F161" s="32" t="inlineStr">
+        <is>
+          <t>Shorter long run, E</t>
+        </is>
+      </c>
       <c r="G161" s="32" t="n"/>
     </row>
     <row r="162" ht="15" customHeight="1" s="21">
-      <c r="A162" s="32" t="n"/>
-      <c r="B162" s="32" t="n"/>
-      <c r="C162" s="32" t="n"/>
-      <c r="D162" s="32" t="n"/>
-      <c r="E162" s="32" t="n"/>
-      <c r="F162" s="32" t="n"/>
+      <c r="A162" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B162" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C162" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E162" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F162" s="32" t="inlineStr">
+        <is>
+          <t>5 x 1.6 km @ T, 90 s jog between</t>
+        </is>
+      </c>
       <c r="G162" s="32" t="n"/>
     </row>
     <row r="163" ht="15" customHeight="1" s="21">
-      <c r="A163" s="32" t="n"/>
-      <c r="B163" s="32" t="n"/>
-      <c r="C163" s="32" t="n"/>
-      <c r="D163" s="32" t="n"/>
-      <c r="E163" s="32" t="n"/>
-      <c r="F163" s="32" t="n"/>
+      <c r="A163" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B163" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C163" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D163" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E163" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F163" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G163" s="32" t="n"/>
     </row>
     <row r="164" ht="15" customHeight="1" s="21">
-      <c r="A164" s="32" t="n"/>
-      <c r="B164" s="32" t="n"/>
-      <c r="C164" s="32" t="n"/>
-      <c r="D164" s="32" t="n"/>
-      <c r="E164" s="32" t="n"/>
-      <c r="F164" s="32" t="n"/>
+      <c r="A164" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B164" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C164" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D164" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E164" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F164" s="32" t="inlineStr">
+        <is>
+          <t>2 x 4 km @ M, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G164" s="32" t="n"/>
     </row>
     <row r="165" ht="15" customHeight="1" s="21">
-      <c r="A165" s="32" t="n"/>
-      <c r="B165" s="32" t="n"/>
-      <c r="C165" s="32" t="n"/>
-      <c r="D165" s="32" t="n"/>
-      <c r="E165" s="32" t="n"/>
-      <c r="F165" s="32" t="n"/>
+      <c r="A165" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B165" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C165" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D165" s="32" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="E165" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F165" s="32" t="inlineStr">
+        <is>
+          <t>Very relaxed recovery run</t>
+        </is>
+      </c>
       <c r="G165" s="32" t="n"/>
     </row>
     <row r="166" ht="15" customHeight="1" s="21">
-      <c r="A166" s="32" t="n"/>
-      <c r="B166" s="32" t="n"/>
-      <c r="C166" s="32" t="n"/>
-      <c r="D166" s="32" t="n"/>
-      <c r="E166" s="32" t="n"/>
-      <c r="F166" s="32" t="n"/>
+      <c r="A166" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B166" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C166" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D166" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E166" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F166" s="32" t="inlineStr">
+        <is>
+          <t>20 km E, final 5 km @ M</t>
+        </is>
+      </c>
       <c r="G166" s="32" t="n"/>
     </row>
     <row r="167" ht="15" customHeight="1" s="21">
-      <c r="A167" s="32" t="n"/>
-      <c r="B167" s="32" t="n"/>
-      <c r="C167" s="32" t="n"/>
-      <c r="D167" s="32" t="n"/>
-      <c r="E167" s="32" t="n"/>
-      <c r="F167" s="32" t="n"/>
+      <c r="A167" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B167" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C167" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D167" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E167" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F167" s="32" t="inlineStr">
+        <is>
+          <t>3 x 3 km @ T, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G167" s="32" t="n"/>
     </row>
     <row r="168" ht="15" customHeight="1" s="21">
-      <c r="A168" s="32" t="n"/>
-      <c r="B168" s="32" t="n"/>
-      <c r="C168" s="32" t="n"/>
-      <c r="D168" s="32" t="n"/>
-      <c r="E168" s="32" t="n"/>
-      <c r="F168" s="32" t="n"/>
+      <c r="A168" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B168" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C168" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D168" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E168" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F168" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G168" s="32" t="n"/>
     </row>
     <row r="169" ht="15" customHeight="1" s="21">
-      <c r="A169" s="32" t="n"/>
-      <c r="B169" s="32" t="n"/>
-      <c r="C169" s="32" t="n"/>
-      <c r="D169" s="32" t="n"/>
-      <c r="E169" s="32" t="n"/>
-      <c r="F169" s="32" t="n"/>
+      <c r="A169" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B169" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C169" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D169" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E169" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F169" s="32" t="inlineStr">
+        <is>
+          <t>20 min continuous @ T</t>
+        </is>
+      </c>
       <c r="G169" s="32" t="n"/>
     </row>
     <row r="170" ht="15" customHeight="1" s="21">
-      <c r="A170" s="32" t="n"/>
-      <c r="B170" s="32" t="n"/>
-      <c r="C170" s="32" t="n"/>
-      <c r="D170" s="32" t="n"/>
-      <c r="E170" s="32" t="n"/>
-      <c r="F170" s="32" t="n"/>
+      <c r="A170" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B170" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C170" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D170" s="32" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="E170" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F170" s="32" t="inlineStr">
+        <is>
+          <t>Very relaxed recovery run</t>
+        </is>
+      </c>
       <c r="G170" s="32" t="n"/>
     </row>
     <row r="171" ht="15" customHeight="1" s="21">
-      <c r="A171" s="32" t="n"/>
-      <c r="B171" s="32" t="n"/>
-      <c r="C171" s="32" t="n"/>
-      <c r="D171" s="32" t="n"/>
-      <c r="E171" s="32" t="n"/>
-      <c r="F171" s="32" t="n"/>
+      <c r="A171" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B171" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C171" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D171" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E171" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F171" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G171" s="32" t="n"/>
     </row>
     <row r="172" ht="15" customHeight="1" s="21">
-      <c r="A172" s="32" t="n"/>
-      <c r="B172" s="32" t="n"/>
-      <c r="C172" s="32" t="n"/>
-      <c r="D172" s="32" t="n"/>
-      <c r="E172" s="32" t="n"/>
-      <c r="F172" s="32" t="n"/>
+      <c r="A172" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B172" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C172" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D172" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E172" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F172" s="32" t="inlineStr">
+        <is>
+          <t>6 x 1.6 km @ T, 90 s jog between</t>
+        </is>
+      </c>
       <c r="G172" s="32" t="n"/>
     </row>
     <row r="173" ht="15" customHeight="1" s="21">
-      <c r="A173" s="32" t="n"/>
-      <c r="B173" s="32" t="n"/>
-      <c r="C173" s="32" t="n"/>
-      <c r="D173" s="32" t="n"/>
-      <c r="E173" s="32" t="n"/>
-      <c r="F173" s="32" t="n"/>
+      <c r="A173" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B173" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C173" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D173" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E173" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F173" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G173" s="32" t="n"/>
     </row>
     <row r="174" ht="15" customHeight="1" s="21">
-      <c r="A174" s="32" t="n"/>
-      <c r="B174" s="32" t="n"/>
-      <c r="C174" s="32" t="n"/>
-      <c r="D174" s="32" t="n"/>
-      <c r="E174" s="32" t="n"/>
-      <c r="F174" s="32" t="n"/>
+      <c r="A174" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B174" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C174" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D174" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E174" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F174" s="32" t="inlineStr">
+        <is>
+          <t>3 x 4 km @ M, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G174" s="32" t="n"/>
     </row>
     <row r="175" ht="15" customHeight="1" s="21">
-      <c r="A175" s="32" t="n"/>
-      <c r="B175" s="32" t="n"/>
-      <c r="C175" s="32" t="n"/>
-      <c r="D175" s="32" t="n"/>
-      <c r="E175" s="32" t="n"/>
-      <c r="F175" s="32" t="n"/>
+      <c r="A175" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B175" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C175" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D175" s="32" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="E175" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F175" s="32" t="inlineStr">
+        <is>
+          <t>Very relaxed recovery run</t>
+        </is>
+      </c>
       <c r="G175" s="32" t="n"/>
     </row>
     <row r="176" ht="15" customHeight="1" s="21">
-      <c r="A176" s="32" t="n"/>
-      <c r="B176" s="32" t="n"/>
-      <c r="C176" s="32" t="n"/>
-      <c r="D176" s="32" t="n"/>
-      <c r="E176" s="32" t="n"/>
-      <c r="F176" s="32" t="n"/>
+      <c r="A176" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B176" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C176" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D176" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E176" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F176" s="32" t="inlineStr">
+        <is>
+          <t>22 km E, final 8 km @ M</t>
+        </is>
+      </c>
       <c r="G176" s="32" t="n"/>
     </row>
     <row r="177" ht="15" customHeight="1" s="21">
-      <c r="A177" s="32" t="n"/>
-      <c r="B177" s="32" t="n"/>
-      <c r="C177" s="32" t="n"/>
-      <c r="D177" s="32" t="n"/>
-      <c r="E177" s="32" t="n"/>
-      <c r="F177" s="32" t="n"/>
+      <c r="A177" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B177" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C177" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D177" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E177" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F177" s="32" t="inlineStr">
+        <is>
+          <t>4 x 1.6 km @ T, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G177" s="32" t="n"/>
     </row>
     <row r="178" ht="15" customHeight="1" s="21">
-      <c r="A178" s="32" t="n"/>
-      <c r="B178" s="32" t="n"/>
-      <c r="C178" s="32" t="n"/>
-      <c r="D178" s="32" t="n"/>
-      <c r="E178" s="32" t="n"/>
-      <c r="F178" s="32" t="n"/>
+      <c r="A178" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B178" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C178" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D178" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E178" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F178" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G178" s="32" t="n"/>
     </row>
     <row r="179" ht="15" customHeight="1" s="21">
-      <c r="A179" s="32" t="n"/>
-      <c r="B179" s="32" t="n"/>
-      <c r="C179" s="32" t="n"/>
-      <c r="D179" s="32" t="n"/>
-      <c r="E179" s="32" t="n"/>
-      <c r="F179" s="32" t="n"/>
+      <c r="A179" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B179" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C179" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D179" s="32" t="inlineStr">
+        <is>
+          <t>Progression</t>
+        </is>
+      </c>
+      <c r="E179" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F179" s="32" t="inlineStr">
+        <is>
+          <t>4 km E → 4 km STEADY → 2 km M</t>
+        </is>
+      </c>
       <c r="G179" s="32" t="n"/>
     </row>
     <row r="180" ht="15" customHeight="1" s="21">
-      <c r="A180" s="32" t="n"/>
-      <c r="B180" s="32" t="n"/>
-      <c r="C180" s="32" t="n"/>
-      <c r="D180" s="32" t="n"/>
-      <c r="E180" s="32" t="n"/>
-      <c r="F180" s="32" t="n"/>
+      <c r="A180" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B180" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C180" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D180" s="32" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="E180" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F180" s="32" t="inlineStr">
+        <is>
+          <t>Very relaxed recovery run</t>
+        </is>
+      </c>
       <c r="G180" s="32" t="n"/>
     </row>
     <row r="181" ht="15" customHeight="1" s="21">
-      <c r="A181" s="32" t="n"/>
-      <c r="B181" s="32" t="n"/>
-      <c r="C181" s="32" t="n"/>
-      <c r="D181" s="32" t="n"/>
-      <c r="E181" s="32" t="n"/>
-      <c r="F181" s="32" t="n"/>
+      <c r="A181" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B181" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C181" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D181" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E181" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F181" s="32" t="inlineStr">
+        <is>
+          <t>Shorter long run, E</t>
+        </is>
+      </c>
       <c r="G181" s="32" t="n"/>
     </row>
     <row r="182" ht="15" customHeight="1" s="21">
-      <c r="A182" s="32" t="n"/>
-      <c r="B182" s="32" t="n"/>
-      <c r="C182" s="32" t="n"/>
-      <c r="D182" s="32" t="n"/>
-      <c r="E182" s="32" t="n"/>
-      <c r="F182" s="32" t="n"/>
+      <c r="A182" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B182" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="C182" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D182" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E182" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F182" s="32" t="inlineStr">
+        <is>
+          <t>4 x 3 km @ T, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G182" s="32" t="n"/>
     </row>
     <row r="183" ht="15" customHeight="1" s="21">
-      <c r="A183" s="32" t="n"/>
-      <c r="B183" s="32" t="n"/>
-      <c r="C183" s="32" t="n"/>
-      <c r="D183" s="32" t="n"/>
-      <c r="E183" s="32" t="n"/>
-      <c r="F183" s="32" t="n"/>
+      <c r="A183" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B183" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="C183" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D183" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E183" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F183" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G183" s="32" t="n"/>
     </row>
     <row r="184" ht="15" customHeight="1" s="21">
-      <c r="A184" s="32" t="n"/>
-      <c r="B184" s="32" t="n"/>
-      <c r="C184" s="32" t="n"/>
-      <c r="D184" s="32" t="n"/>
-      <c r="E184" s="32" t="n"/>
-      <c r="F184" s="32" t="n"/>
+      <c r="A184" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B184" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="C184" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D184" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E184" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F184" s="32" t="inlineStr">
+        <is>
+          <t>50 min continuous @ M</t>
+        </is>
+      </c>
       <c r="G184" s="32" t="n"/>
     </row>
     <row r="185" ht="15" customHeight="1" s="21">
-      <c r="A185" s="32" t="n"/>
-      <c r="B185" s="32" t="n"/>
-      <c r="C185" s="32" t="n"/>
-      <c r="D185" s="32" t="n"/>
-      <c r="E185" s="32" t="n"/>
-      <c r="F185" s="32" t="n"/>
+      <c r="A185" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B185" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="C185" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D185" s="32" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="E185" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F185" s="32" t="inlineStr">
+        <is>
+          <t>Very relaxed recovery run</t>
+        </is>
+      </c>
       <c r="G185" s="32" t="n"/>
     </row>
     <row r="186" ht="15" customHeight="1" s="21">
-      <c r="A186" s="32" t="n"/>
-      <c r="B186" s="32" t="n"/>
-      <c r="C186" s="32" t="n"/>
-      <c r="D186" s="32" t="n"/>
-      <c r="E186" s="32" t="n"/>
-      <c r="F186" s="32" t="n"/>
+      <c r="A186" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B186" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="C186" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D186" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E186" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F186" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G186" s="32" t="n"/>
     </row>
     <row r="187" ht="15" customHeight="1" s="21">
-      <c r="A187" s="32" t="n"/>
-      <c r="B187" s="32" t="n"/>
-      <c r="C187" s="32" t="n"/>
-      <c r="D187" s="32" t="n"/>
-      <c r="E187" s="32" t="n"/>
-      <c r="F187" s="32" t="n"/>
+      <c r="A187" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B187" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="C187" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D187" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E187" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F187" s="32" t="inlineStr">
+        <is>
+          <t>5 x 2 km @ T, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G187" s="32" t="n"/>
     </row>
     <row r="188" ht="15" customHeight="1" s="21">
-      <c r="A188" s="32" t="n"/>
-      <c r="B188" s="32" t="n"/>
-      <c r="C188" s="32" t="n"/>
-      <c r="D188" s="32" t="n"/>
-      <c r="E188" s="32" t="n"/>
-      <c r="F188" s="32" t="n"/>
+      <c r="A188" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B188" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="C188" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D188" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E188" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F188" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G188" s="32" t="n"/>
     </row>
     <row r="189" ht="15" customHeight="1" s="21">
-      <c r="A189" s="32" t="n"/>
-      <c r="B189" s="32" t="n"/>
-      <c r="C189" s="32" t="n"/>
-      <c r="D189" s="32" t="n"/>
-      <c r="E189" s="32" t="n"/>
-      <c r="F189" s="32" t="n"/>
+      <c r="A189" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B189" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="C189" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D189" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E189" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F189" s="32" t="inlineStr">
+        <is>
+          <t>25 min continuous @ T</t>
+        </is>
+      </c>
       <c r="G189" s="32" t="n"/>
     </row>
     <row r="190" ht="15" customHeight="1" s="21">
-      <c r="A190" s="32" t="n"/>
-      <c r="B190" s="32" t="n"/>
-      <c r="C190" s="32" t="n"/>
-      <c r="D190" s="32" t="n"/>
-      <c r="E190" s="32" t="n"/>
-      <c r="F190" s="32" t="n"/>
+      <c r="A190" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B190" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="C190" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D190" s="32" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="E190" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F190" s="32" t="inlineStr">
+        <is>
+          <t>Very relaxed recovery run</t>
+        </is>
+      </c>
       <c r="G190" s="32" t="n"/>
     </row>
     <row r="191" ht="15" customHeight="1" s="21">
-      <c r="A191" s="32" t="n"/>
-      <c r="B191" s="32" t="n"/>
-      <c r="C191" s="32" t="n"/>
-      <c r="D191" s="32" t="n"/>
-      <c r="E191" s="32" t="n"/>
-      <c r="F191" s="32" t="n"/>
+      <c r="A191" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B191" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="C191" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D191" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E191" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F191" s="32" t="inlineStr">
+        <is>
+          <t>26 km E, final 12 km @ M</t>
+        </is>
+      </c>
       <c r="G191" s="32" t="n"/>
     </row>
     <row r="192" ht="15" customHeight="1" s="21">
-      <c r="A192" s="32" t="n"/>
-      <c r="B192" s="32" t="n"/>
-      <c r="C192" s="32" t="n"/>
-      <c r="D192" s="32" t="n"/>
-      <c r="E192" s="32" t="n"/>
-      <c r="F192" s="32" t="n"/>
+      <c r="A192" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B192" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="C192" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D192" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E192" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F192" s="32" t="inlineStr">
+        <is>
+          <t>6 x 1.6 km @ T, 90 s jog between</t>
+        </is>
+      </c>
       <c r="G192" s="32" t="n"/>
     </row>
     <row r="193" ht="15" customHeight="1" s="21">
-      <c r="A193" s="32" t="n"/>
-      <c r="B193" s="32" t="n"/>
-      <c r="C193" s="32" t="n"/>
-      <c r="D193" s="32" t="n"/>
-      <c r="E193" s="32" t="n"/>
-      <c r="F193" s="32" t="n"/>
+      <c r="A193" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B193" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="C193" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D193" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E193" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F193" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G193" s="32" t="n"/>
     </row>
     <row r="194" ht="15" customHeight="1" s="21">
-      <c r="A194" s="32" t="n"/>
-      <c r="B194" s="32" t="n"/>
-      <c r="C194" s="32" t="n"/>
-      <c r="D194" s="32" t="n"/>
-      <c r="E194" s="32" t="n"/>
-      <c r="F194" s="32" t="n"/>
+      <c r="A194" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B194" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="C194" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D194" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E194" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F194" s="32" t="inlineStr">
+        <is>
+          <t>3 x 5 km @ M, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G194" s="32" t="n"/>
     </row>
     <row r="195" ht="15" customHeight="1" s="21">
-      <c r="A195" s="32" t="n"/>
-      <c r="B195" s="32" t="n"/>
-      <c r="C195" s="32" t="n"/>
-      <c r="D195" s="32" t="n"/>
-      <c r="E195" s="32" t="n"/>
-      <c r="F195" s="32" t="n"/>
+      <c r="A195" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B195" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="C195" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D195" s="32" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="E195" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F195" s="32" t="inlineStr">
+        <is>
+          <t>Very relaxed recovery run</t>
+        </is>
+      </c>
       <c r="G195" s="32" t="n"/>
     </row>
     <row r="196" ht="15" customHeight="1" s="21">
-      <c r="A196" s="32" t="n"/>
-      <c r="B196" s="32" t="n"/>
-      <c r="C196" s="32" t="n"/>
-      <c r="D196" s="32" t="n"/>
-      <c r="E196" s="32" t="n"/>
-      <c r="F196" s="32" t="n"/>
+      <c r="A196" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B196" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="C196" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D196" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E196" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F196" s="32" t="inlineStr">
+        <is>
+          <t>30 km E, final 5 km @ STEADY</t>
+        </is>
+      </c>
       <c r="G196" s="32" t="n"/>
     </row>
     <row r="197" ht="15" customHeight="1" s="21">
-      <c r="A197" s="32" t="n"/>
-      <c r="B197" s="32" t="n"/>
-      <c r="C197" s="32" t="n"/>
-      <c r="D197" s="32" t="n"/>
-      <c r="E197" s="32" t="n"/>
-      <c r="F197" s="32" t="n"/>
+      <c r="A197" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B197" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="C197" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D197" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E197" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F197" s="32" t="inlineStr">
+        <is>
+          <t>5 x 1 km @ T, 90 s jog between</t>
+        </is>
+      </c>
       <c r="G197" s="32" t="n"/>
     </row>
     <row r="198" ht="15" customHeight="1" s="21">
-      <c r="A198" s="32" t="n"/>
-      <c r="B198" s="32" t="n"/>
-      <c r="C198" s="32" t="n"/>
-      <c r="D198" s="32" t="n"/>
-      <c r="E198" s="32" t="n"/>
-      <c r="F198" s="32" t="n"/>
+      <c r="A198" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B198" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="C198" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D198" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E198" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F198" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G198" s="32" t="n"/>
     </row>
     <row r="199" ht="15" customHeight="1" s="21">
-      <c r="A199" s="32" t="n"/>
-      <c r="B199" s="32" t="n"/>
-      <c r="C199" s="32" t="n"/>
-      <c r="D199" s="32" t="n"/>
-      <c r="E199" s="32" t="n"/>
-      <c r="F199" s="32" t="n"/>
+      <c r="A199" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B199" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="C199" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D199" s="32" t="inlineStr">
+        <is>
+          <t>Progression</t>
+        </is>
+      </c>
+      <c r="E199" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F199" s="32" t="inlineStr">
+        <is>
+          <t>5 km E → 5 km M</t>
+        </is>
+      </c>
       <c r="G199" s="32" t="n"/>
     </row>
     <row r="200" ht="15" customHeight="1" s="21">
-      <c r="A200" s="32" t="n"/>
-      <c r="B200" s="32" t="n"/>
-      <c r="C200" s="32" t="n"/>
-      <c r="D200" s="32" t="n"/>
-      <c r="E200" s="32" t="n"/>
-      <c r="F200" s="32" t="n"/>
+      <c r="A200" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B200" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="C200" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D200" s="32" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="E200" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F200" s="32" t="inlineStr">
+        <is>
+          <t>Very relaxed recovery run</t>
+        </is>
+      </c>
       <c r="G200" s="32" t="n"/>
     </row>
     <row r="201" ht="15" customHeight="1" s="21">
-      <c r="A201" s="32" t="n"/>
-      <c r="B201" s="32" t="n"/>
-      <c r="C201" s="32" t="n"/>
-      <c r="D201" s="32" t="n"/>
-      <c r="E201" s="32" t="n"/>
-      <c r="F201" s="32" t="n"/>
+      <c r="A201" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B201" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="C201" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D201" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E201" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F201" s="32" t="inlineStr">
+        <is>
+          <t>Shorter long run, E</t>
+        </is>
+      </c>
       <c r="G201" s="32" t="n"/>
     </row>
     <row r="202" ht="15" customHeight="1" s="21">
-      <c r="A202" s="32" t="n"/>
-      <c r="B202" s="32" t="n"/>
-      <c r="C202" s="32" t="n"/>
-      <c r="D202" s="32" t="n"/>
-      <c r="E202" s="32" t="n"/>
-      <c r="F202" s="32" t="n"/>
+      <c r="A202" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B202" s="32" t="n">
+        <v>13</v>
+      </c>
+      <c r="C202" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D202" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E202" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F202" s="32" t="inlineStr">
+        <is>
+          <t>4 x 3 km @ T, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G202" s="32" t="n"/>
     </row>
     <row r="203" ht="15" customHeight="1" s="21">
-      <c r="A203" s="32" t="n"/>
-      <c r="B203" s="32" t="n"/>
-      <c r="C203" s="32" t="n"/>
-      <c r="D203" s="32" t="n"/>
-      <c r="E203" s="32" t="n"/>
-      <c r="F203" s="32" t="n"/>
+      <c r="A203" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B203" s="32" t="n">
+        <v>13</v>
+      </c>
+      <c r="C203" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D203" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E203" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F203" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G203" s="32" t="n"/>
     </row>
     <row r="204" ht="15" customHeight="1" s="21">
-      <c r="A204" s="32" t="n"/>
-      <c r="B204" s="32" t="n"/>
-      <c r="C204" s="32" t="n"/>
-      <c r="D204" s="32" t="n"/>
-      <c r="E204" s="32" t="n"/>
-      <c r="F204" s="32" t="n"/>
+      <c r="A204" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B204" s="32" t="n">
+        <v>13</v>
+      </c>
+      <c r="C204" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D204" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E204" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F204" s="32" t="inlineStr">
+        <is>
+          <t>60 min continuous @ M</t>
+        </is>
+      </c>
       <c r="G204" s="32" t="n"/>
     </row>
     <row r="205" ht="15" customHeight="1" s="21">
-      <c r="A205" s="32" t="n"/>
-      <c r="B205" s="32" t="n"/>
-      <c r="C205" s="32" t="n"/>
-      <c r="D205" s="32" t="n"/>
-      <c r="E205" s="32" t="n"/>
-      <c r="F205" s="32" t="n"/>
+      <c r="A205" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B205" s="32" t="n">
+        <v>13</v>
+      </c>
+      <c r="C205" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D205" s="32" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="E205" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F205" s="32" t="inlineStr">
+        <is>
+          <t>Very relaxed recovery run</t>
+        </is>
+      </c>
       <c r="G205" s="32" t="n"/>
     </row>
     <row r="206" ht="15" customHeight="1" s="21">
-      <c r="A206" s="32" t="n"/>
-      <c r="B206" s="32" t="n"/>
-      <c r="C206" s="32" t="n"/>
-      <c r="D206" s="32" t="n"/>
-      <c r="E206" s="32" t="n"/>
-      <c r="F206" s="32" t="n"/>
+      <c r="A206" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B206" s="32" t="n">
+        <v>13</v>
+      </c>
+      <c r="C206" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D206" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E206" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F206" s="32" t="inlineStr">
+        <is>
+          <t>Longest run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G206" s="32" t="n"/>
     </row>
     <row r="207" ht="15" customHeight="1" s="21">
-      <c r="A207" s="32" t="n"/>
-      <c r="B207" s="32" t="n"/>
-      <c r="C207" s="32" t="n"/>
-      <c r="D207" s="32" t="n"/>
-      <c r="E207" s="32" t="n"/>
-      <c r="F207" s="32" t="n"/>
+      <c r="A207" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B207" s="32" t="n">
+        <v>14</v>
+      </c>
+      <c r="C207" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D207" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E207" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F207" s="32" t="inlineStr">
+        <is>
+          <t>5 x 2 km @ T, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G207" s="32" t="n"/>
     </row>
     <row r="208" ht="15" customHeight="1" s="21">
-      <c r="A208" s="32" t="n"/>
-      <c r="B208" s="32" t="n"/>
-      <c r="C208" s="32" t="n"/>
-      <c r="D208" s="32" t="n"/>
-      <c r="E208" s="32" t="n"/>
-      <c r="F208" s="32" t="n"/>
+      <c r="A208" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B208" s="32" t="n">
+        <v>14</v>
+      </c>
+      <c r="C208" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D208" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E208" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F208" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G208" s="32" t="n"/>
     </row>
     <row r="209" ht="15" customHeight="1" s="21">
-      <c r="A209" s="32" t="n"/>
-      <c r="B209" s="32" t="n"/>
-      <c r="C209" s="32" t="n"/>
-      <c r="D209" s="32" t="n"/>
-      <c r="E209" s="32" t="n"/>
-      <c r="F209" s="32" t="n"/>
+      <c r="A209" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B209" s="32" t="n">
+        <v>14</v>
+      </c>
+      <c r="C209" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D209" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E209" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F209" s="32" t="inlineStr">
+        <is>
+          <t>2 x 6 km @ M, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G209" s="32" t="n"/>
     </row>
     <row r="210" ht="15" customHeight="1" s="21">
-      <c r="A210" s="32" t="n"/>
-      <c r="B210" s="32" t="n"/>
-      <c r="C210" s="32" t="n"/>
-      <c r="D210" s="32" t="n"/>
-      <c r="E210" s="32" t="n"/>
-      <c r="F210" s="32" t="n"/>
+      <c r="A210" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B210" s="32" t="n">
+        <v>14</v>
+      </c>
+      <c r="C210" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D210" s="32" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="E210" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F210" s="32" t="inlineStr">
+        <is>
+          <t>Very relaxed recovery run</t>
+        </is>
+      </c>
       <c r="G210" s="32" t="n"/>
     </row>
     <row r="211" ht="15" customHeight="1" s="21">
-      <c r="A211" s="32" t="n"/>
-      <c r="B211" s="32" t="n"/>
-      <c r="C211" s="32" t="n"/>
-      <c r="D211" s="32" t="n"/>
-      <c r="E211" s="32" t="n"/>
-      <c r="F211" s="32" t="n"/>
+      <c r="A211" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B211" s="32" t="n">
+        <v>14</v>
+      </c>
+      <c r="C211" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D211" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E211" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F211" s="32" t="inlineStr">
+        <is>
+          <t>24 km E, final 12 km @ M</t>
+        </is>
+      </c>
       <c r="G211" s="32" t="n"/>
     </row>
     <row r="212" ht="15" customHeight="1" s="21">
-      <c r="A212" s="32" t="n"/>
-      <c r="B212" s="32" t="n"/>
-      <c r="C212" s="32" t="n"/>
-      <c r="D212" s="32" t="n"/>
-      <c r="E212" s="32" t="n"/>
-      <c r="F212" s="32" t="n"/>
+      <c r="A212" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B212" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="C212" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D212" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E212" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F212" s="32" t="inlineStr">
+        <is>
+          <t>4 x 1.6 km @ T, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G212" s="32" t="n"/>
     </row>
     <row r="213" ht="15" customHeight="1" s="21">
-      <c r="A213" s="32" t="n"/>
-      <c r="B213" s="32" t="n"/>
-      <c r="C213" s="32" t="n"/>
-      <c r="D213" s="32" t="n"/>
-      <c r="E213" s="32" t="n"/>
-      <c r="F213" s="32" t="n"/>
+      <c r="A213" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B213" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="C213" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D213" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E213" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F213" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G213" s="32" t="n"/>
     </row>
     <row r="214" ht="15" customHeight="1" s="21">
-      <c r="A214" s="32" t="n"/>
-      <c r="B214" s="32" t="n"/>
-      <c r="C214" s="32" t="n"/>
-      <c r="D214" s="32" t="n"/>
-      <c r="E214" s="32" t="n"/>
-      <c r="F214" s="32" t="n"/>
+      <c r="A214" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B214" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="C214" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D214" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E214" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F214" s="32" t="inlineStr">
+        <is>
+          <t>2 x 4 km @ M, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G214" s="32" t="n"/>
     </row>
     <row r="215" ht="15" customHeight="1" s="21">
-      <c r="A215" s="32" t="n"/>
-      <c r="B215" s="32" t="n"/>
-      <c r="C215" s="32" t="n"/>
-      <c r="D215" s="32" t="n"/>
-      <c r="E215" s="32" t="n"/>
-      <c r="F215" s="32" t="n"/>
+      <c r="A215" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B215" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="C215" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D215" s="32" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="E215" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F215" s="32" t="inlineStr">
+        <is>
+          <t>Very relaxed recovery run</t>
+        </is>
+      </c>
       <c r="G215" s="32" t="n"/>
     </row>
     <row r="216" ht="15" customHeight="1" s="21">
-      <c r="A216" s="32" t="n"/>
-      <c r="B216" s="32" t="n"/>
-      <c r="C216" s="32" t="n"/>
-      <c r="D216" s="32" t="n"/>
-      <c r="E216" s="32" t="n"/>
-      <c r="F216" s="32" t="n"/>
+      <c r="A216" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B216" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="C216" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D216" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E216" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F216" s="32" t="inlineStr">
+        <is>
+          <t>18 km E, final 4 km @ M</t>
+        </is>
+      </c>
       <c r="G216" s="32" t="n"/>
     </row>
     <row r="217" ht="15" customHeight="1" s="21">
-      <c r="A217" s="32" t="n"/>
-      <c r="B217" s="32" t="n"/>
-      <c r="C217" s="32" t="n"/>
-      <c r="D217" s="32" t="n"/>
-      <c r="E217" s="32" t="n"/>
-      <c r="F217" s="32" t="n"/>
+      <c r="A217" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B217" s="32" t="n">
+        <v>16</v>
+      </c>
+      <c r="C217" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D217" s="32" t="inlineStr">
+        <is>
+          <t>Fartlek</t>
+        </is>
+      </c>
+      <c r="E217" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F217" s="32" t="inlineStr">
+        <is>
+          <t>6 x (1 min @ HM effort / 1 min E)</t>
+        </is>
+      </c>
       <c r="G217" s="32" t="n"/>
     </row>
     <row r="218" ht="15" customHeight="1" s="21">
-      <c r="A218" s="32" t="n"/>
-      <c r="B218" s="32" t="n"/>
-      <c r="C218" s="32" t="n"/>
-      <c r="D218" s="32" t="n"/>
-      <c r="E218" s="32" t="n"/>
-      <c r="F218" s="32" t="n"/>
+      <c r="A218" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B218" s="32" t="n">
+        <v>16</v>
+      </c>
+      <c r="C218" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D218" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E218" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F218" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G218" s="32" t="n"/>
     </row>
     <row r="219" ht="15" customHeight="1" s="21">
-      <c r="A219" s="32" t="n"/>
-      <c r="B219" s="32" t="n"/>
-      <c r="C219" s="32" t="n"/>
-      <c r="D219" s="32" t="n"/>
-      <c r="E219" s="32" t="n"/>
-      <c r="F219" s="32" t="n"/>
+      <c r="A219" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B219" s="32" t="n">
+        <v>16</v>
+      </c>
+      <c r="C219" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D219" s="32" t="inlineStr">
+        <is>
+          <t>Shakeout</t>
+        </is>
+      </c>
+      <c r="E219" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F219" s="32" t="inlineStr">
+        <is>
+          <t>4 km E + 4 x 20 s strides</t>
+        </is>
+      </c>
       <c r="G219" s="32" t="n"/>
     </row>
     <row r="220" ht="15" customHeight="1" s="21">
-      <c r="A220" s="32" t="n"/>
-      <c r="B220" s="32" t="n"/>
-      <c r="C220" s="32" t="n"/>
-      <c r="D220" s="32" t="n"/>
-      <c r="E220" s="32" t="n"/>
-      <c r="F220" s="32" t="n"/>
+      <c r="A220" s="32" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
+      <c r="B220" s="32" t="n">
+        <v>16</v>
+      </c>
+      <c r="C220" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D220" s="32" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="E220" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F220" s="32" t="inlineStr">
+        <is>
+          <t>MARATHON – race at goal M pace</t>
+        </is>
+      </c>
       <c r="G220" s="32" t="n"/>
     </row>
     <row r="221" ht="15" customHeight="1" s="21">
@@ -30080,7 +32024,7 @@
       </c>
       <c r="E5" s="34" t="inlineStr">
         <is>
-          <t>No run is longer than this (the programme's long-run cap can be lower).</t>
+          <t>No run is longer than this, except in race programmes (5K to marathon, Hyrox), which use their own long-run cap on the Programmes tab.</t>
         </is>
       </c>
     </row>
@@ -30455,6 +32399,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="15" customHeight="1" s="21">
       <c r="A26" s="34" t="inlineStr">
         <is>

--- a/programmes/Kinetix Programmes.xlsx
+++ b/programmes/Kinetix Programmes.xlsx
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="C3" s="32" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D3" s="32" t="inlineStr">
         <is>
@@ -5317,13 +5317,37 @@
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="21">
-      <c r="A54" s="32" t="n"/>
-      <c r="B54" s="32" t="n"/>
-      <c r="C54" s="32" t="n"/>
-      <c r="D54" s="35" t="n"/>
-      <c r="E54" s="32" t="n"/>
-      <c r="F54" s="32" t="n"/>
-      <c r="G54" s="32" t="n"/>
+      <c r="A54" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B54" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="32" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D54" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F54" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G54" s="32" t="inlineStr">
+        <is>
+          <t>Settle in: one quality session, the rest easy.</t>
+        </is>
+      </c>
       <c r="H54" s="33">
         <f>IF(A54="","",COUNTIFS('Run sessions'!$A$2:$A$401,A54,'Run sessions'!$B$2:$B$401,B54))</f>
         <v/>
@@ -5338,12 +5362,32 @@
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="21">
-      <c r="A55" s="32" t="n"/>
-      <c r="B55" s="32" t="n"/>
-      <c r="C55" s="32" t="n"/>
-      <c r="D55" s="35" t="n"/>
-      <c r="E55" s="32" t="n"/>
-      <c r="F55" s="32" t="n"/>
+      <c r="A55" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B55" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" s="32" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D55" s="35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E55" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F55" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="G55" s="32" t="n"/>
       <c r="H55" s="33">
         <f>IF(A55="","",COUNTIFS('Run sessions'!$A$2:$A$401,A55,'Run sessions'!$B$2:$B$401,B55))</f>
@@ -5359,12 +5403,32 @@
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="21">
-      <c r="A56" s="32" t="n"/>
-      <c r="B56" s="32" t="n"/>
-      <c r="C56" s="32" t="n"/>
-      <c r="D56" s="35" t="n"/>
-      <c r="E56" s="32" t="n"/>
-      <c r="F56" s="32" t="n"/>
+      <c r="A56" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B56" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" s="32" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D56" s="35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E56" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F56" s="32" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="G56" s="32" t="n"/>
       <c r="H56" s="33">
         <f>IF(A56="","",COUNTIFS('Run sessions'!$A$2:$A$401,A56,'Run sessions'!$B$2:$B$401,B56))</f>
@@ -5380,13 +5444,37 @@
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" s="21">
-      <c r="A57" s="32" t="n"/>
-      <c r="B57" s="32" t="n"/>
-      <c r="C57" s="32" t="n"/>
-      <c r="D57" s="35" t="n"/>
-      <c r="E57" s="32" t="n"/>
-      <c r="F57" s="32" t="n"/>
-      <c r="G57" s="32" t="n"/>
+      <c r="A57" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B57" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C57" s="32" t="inlineStr">
+        <is>
+          <t>Deload</t>
+        </is>
+      </c>
+      <c r="D57" s="35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E57" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F57" s="32" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G57" s="32" t="inlineStr">
+        <is>
+          <t>Lighter week: let the work sink in.</t>
+        </is>
+      </c>
       <c r="H57" s="33">
         <f>IF(A57="","",COUNTIFS('Run sessions'!$A$2:$A$401,A57,'Run sessions'!$B$2:$B$401,B57))</f>
         <v/>
@@ -5401,12 +5489,32 @@
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" s="21">
-      <c r="A58" s="32" t="n"/>
-      <c r="B58" s="32" t="n"/>
-      <c r="C58" s="32" t="n"/>
-      <c r="D58" s="35" t="n"/>
-      <c r="E58" s="32" t="n"/>
-      <c r="F58" s="32" t="n"/>
+      <c r="A58" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B58" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C58" s="32" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D58" s="35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E58" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F58" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="G58" s="32" t="n"/>
       <c r="H58" s="33">
         <f>IF(A58="","",COUNTIFS('Run sessions'!$A$2:$A$401,A58,'Run sessions'!$B$2:$B$401,B58))</f>
@@ -5422,12 +5530,32 @@
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="21">
-      <c r="A59" s="32" t="n"/>
-      <c r="B59" s="32" t="n"/>
-      <c r="C59" s="32" t="n"/>
-      <c r="D59" s="35" t="n"/>
-      <c r="E59" s="32" t="n"/>
-      <c r="F59" s="32" t="n"/>
+      <c r="A59" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B59" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C59" s="32" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D59" s="35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E59" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F59" s="32" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="G59" s="32" t="n"/>
       <c r="H59" s="33">
         <f>IF(A59="","",COUNTIFS('Run sessions'!$A$2:$A$401,A59,'Run sessions'!$B$2:$B$401,B59))</f>
@@ -5443,12 +5571,32 @@
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="21">
-      <c r="A60" s="32" t="n"/>
-      <c r="B60" s="32" t="n"/>
-      <c r="C60" s="32" t="n"/>
-      <c r="D60" s="35" t="n"/>
-      <c r="E60" s="32" t="n"/>
-      <c r="F60" s="32" t="n"/>
+      <c r="A60" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B60" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C60" s="32" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D60" s="35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E60" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F60" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="G60" s="32" t="n"/>
       <c r="H60" s="33">
         <f>IF(A60="","",COUNTIFS('Run sessions'!$A$2:$A$401,A60,'Run sessions'!$B$2:$B$401,B60))</f>
@@ -5464,13 +5612,37 @@
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" s="21">
-      <c r="A61" s="32" t="n"/>
-      <c r="B61" s="32" t="n"/>
-      <c r="C61" s="32" t="n"/>
-      <c r="D61" s="35" t="n"/>
-      <c r="E61" s="32" t="n"/>
-      <c r="F61" s="32" t="n"/>
-      <c r="G61" s="32" t="n"/>
+      <c r="A61" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B61" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C61" s="32" t="inlineStr">
+        <is>
+          <t>Deload</t>
+        </is>
+      </c>
+      <c r="D61" s="35" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E61" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F61" s="32" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G61" s="32" t="inlineStr">
+        <is>
+          <t>Lighter week before the peak.</t>
+        </is>
+      </c>
       <c r="H61" s="33">
         <f>IF(A61="","",COUNTIFS('Run sessions'!$A$2:$A$401,A61,'Run sessions'!$B$2:$B$401,B61))</f>
         <v/>
@@ -5485,13 +5657,37 @@
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="21">
-      <c r="A62" s="32" t="n"/>
-      <c r="B62" s="32" t="n"/>
-      <c r="C62" s="32" t="n"/>
-      <c r="D62" s="35" t="n"/>
-      <c r="E62" s="32" t="n"/>
-      <c r="F62" s="32" t="n"/>
-      <c r="G62" s="32" t="n"/>
+      <c r="A62" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B62" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="C62" s="32" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="D62" s="35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E62" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F62" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G62" s="32" t="inlineStr">
+        <is>
+          <t>Biggest week.</t>
+        </is>
+      </c>
       <c r="H62" s="33">
         <f>IF(A62="","",COUNTIFS('Run sessions'!$A$2:$A$401,A62,'Run sessions'!$B$2:$B$401,B62))</f>
         <v/>
@@ -5506,12 +5702,32 @@
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="21">
-      <c r="A63" s="32" t="n"/>
-      <c r="B63" s="32" t="n"/>
-      <c r="C63" s="32" t="n"/>
-      <c r="D63" s="35" t="n"/>
-      <c r="E63" s="32" t="n"/>
-      <c r="F63" s="32" t="n"/>
+      <c r="A63" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B63" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="C63" s="32" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="D63" s="35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E63" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F63" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="G63" s="32" t="n"/>
       <c r="H63" s="33">
         <f>IF(A63="","",COUNTIFS('Run sessions'!$A$2:$A$401,A63,'Run sessions'!$B$2:$B$401,B63))</f>
@@ -5527,13 +5743,37 @@
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="21">
-      <c r="A64" s="32" t="n"/>
-      <c r="B64" s="32" t="n"/>
-      <c r="C64" s="32" t="n"/>
-      <c r="D64" s="35" t="n"/>
-      <c r="E64" s="32" t="n"/>
-      <c r="F64" s="32" t="n"/>
-      <c r="G64" s="32" t="n"/>
+      <c r="A64" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B64" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="C64" s="32" t="inlineStr">
+        <is>
+          <t>Taper</t>
+        </is>
+      </c>
+      <c r="D64" s="35" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E64" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F64" s="32" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G64" s="32" t="inlineStr">
+        <is>
+          <t>Freshen up.</t>
+        </is>
+      </c>
       <c r="H64" s="33">
         <f>IF(A64="","",COUNTIFS('Run sessions'!$A$2:$A$401,A64,'Run sessions'!$B$2:$B$401,B64))</f>
         <v/>
@@ -5548,13 +5788,37 @@
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="21">
-      <c r="A65" s="32" t="n"/>
-      <c r="B65" s="32" t="n"/>
-      <c r="C65" s="32" t="n"/>
-      <c r="D65" s="35" t="n"/>
-      <c r="E65" s="32" t="n"/>
-      <c r="F65" s="32" t="n"/>
-      <c r="G65" s="32" t="n"/>
+      <c r="A65" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B65" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="C65" s="32" t="inlineStr">
+        <is>
+          <t>Race week</t>
+        </is>
+      </c>
+      <c r="D65" s="35" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E65" s="32" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F65" s="32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G65" s="32" t="inlineStr">
+        <is>
+          <t>Race day!</t>
+        </is>
+      </c>
       <c r="H65" s="33">
         <f>IF(A65="","",COUNTIFS('Run sessions'!$A$2:$A$401,A65,'Run sessions'!$B$2:$B$401,B65))</f>
         <v/>
@@ -19097,435 +19361,1395 @@
       <c r="G220" s="32" t="n"/>
     </row>
     <row r="221" ht="15" customHeight="1" s="21">
-      <c r="A221" s="32" t="n"/>
-      <c r="B221" s="32" t="n"/>
-      <c r="C221" s="32" t="n"/>
-      <c r="D221" s="32" t="n"/>
-      <c r="E221" s="32" t="n"/>
-      <c r="F221" s="32" t="n"/>
+      <c r="A221" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B221" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C221" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D221" s="32" t="inlineStr">
+        <is>
+          <t>Fartlek</t>
+        </is>
+      </c>
+      <c r="E221" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F221" s="32" t="inlineStr">
+        <is>
+          <t>8 x (1 min @ I effort / 1 min E)</t>
+        </is>
+      </c>
       <c r="G221" s="32" t="n"/>
     </row>
     <row r="222" ht="15" customHeight="1" s="21">
-      <c r="A222" s="32" t="n"/>
-      <c r="B222" s="32" t="n"/>
-      <c r="C222" s="32" t="n"/>
-      <c r="D222" s="32" t="n"/>
-      <c r="E222" s="32" t="n"/>
-      <c r="F222" s="32" t="n"/>
+      <c r="A222" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B222" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C222" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D222" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E222" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F222" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G222" s="32" t="n"/>
     </row>
     <row r="223" ht="15" customHeight="1" s="21">
-      <c r="A223" s="32" t="n"/>
-      <c r="B223" s="32" t="n"/>
-      <c r="C223" s="32" t="n"/>
-      <c r="D223" s="32" t="n"/>
-      <c r="E223" s="32" t="n"/>
-      <c r="F223" s="32" t="n"/>
+      <c r="A223" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B223" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C223" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D223" s="32" t="inlineStr">
+        <is>
+          <t>Progression</t>
+        </is>
+      </c>
+      <c r="E223" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F223" s="32" t="inlineStr">
+        <is>
+          <t>3 km E → 2 km STEADY → 1 km T</t>
+        </is>
+      </c>
       <c r="G223" s="32" t="n"/>
     </row>
     <row r="224" ht="15" customHeight="1" s="21">
-      <c r="A224" s="32" t="n"/>
-      <c r="B224" s="32" t="n"/>
-      <c r="C224" s="32" t="n"/>
-      <c r="D224" s="32" t="n"/>
-      <c r="E224" s="32" t="n"/>
-      <c r="F224" s="32" t="n"/>
+      <c r="A224" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B224" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C224" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D224" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E224" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F224" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G224" s="32" t="n"/>
     </row>
     <row r="225" ht="15" customHeight="1" s="21">
-      <c r="A225" s="32" t="n"/>
-      <c r="B225" s="32" t="n"/>
-      <c r="C225" s="32" t="n"/>
-      <c r="D225" s="32" t="n"/>
-      <c r="E225" s="32" t="n"/>
-      <c r="F225" s="32" t="n"/>
+      <c r="A225" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B225" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C225" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D225" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E225" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F225" s="32" t="inlineStr">
+        <is>
+          <t>10 x 400 m @ I, 75 s jog between</t>
+        </is>
+      </c>
       <c r="G225" s="32" t="n"/>
     </row>
     <row r="226" ht="15" customHeight="1" s="21">
-      <c r="A226" s="32" t="n"/>
-      <c r="B226" s="32" t="n"/>
-      <c r="C226" s="32" t="n"/>
-      <c r="D226" s="32" t="n"/>
-      <c r="E226" s="32" t="n"/>
-      <c r="F226" s="32" t="n"/>
+      <c r="A226" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B226" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C226" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D226" s="32" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="E226" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F226" s="32" t="inlineStr">
+        <is>
+          <t>Very relaxed recovery run</t>
+        </is>
+      </c>
       <c r="G226" s="32" t="n"/>
     </row>
     <row r="227" ht="15" customHeight="1" s="21">
-      <c r="A227" s="32" t="n"/>
-      <c r="B227" s="32" t="n"/>
-      <c r="C227" s="32" t="n"/>
-      <c r="D227" s="32" t="n"/>
-      <c r="E227" s="32" t="n"/>
-      <c r="F227" s="32" t="n"/>
+      <c r="A227" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B227" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C227" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D227" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E227" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F227" s="32" t="inlineStr">
+        <is>
+          <t>2 x 8 min @ T, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G227" s="32" t="n"/>
     </row>
     <row r="228" ht="15" customHeight="1" s="21">
-      <c r="A228" s="32" t="n"/>
-      <c r="B228" s="32" t="n"/>
-      <c r="C228" s="32" t="n"/>
-      <c r="D228" s="32" t="n"/>
-      <c r="E228" s="32" t="n"/>
-      <c r="F228" s="32" t="n"/>
+      <c r="A228" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B228" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C228" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D228" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E228" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F228" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G228" s="32" t="n"/>
     </row>
     <row r="229" ht="15" customHeight="1" s="21">
-      <c r="A229" s="32" t="n"/>
-      <c r="B229" s="32" t="n"/>
-      <c r="C229" s="32" t="n"/>
-      <c r="D229" s="32" t="n"/>
-      <c r="E229" s="32" t="n"/>
-      <c r="F229" s="32" t="n"/>
+      <c r="A229" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B229" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C229" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D229" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E229" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F229" s="32" t="inlineStr">
+        <is>
+          <t>6 x 600 m @ I, 90 s jog between</t>
+        </is>
+      </c>
       <c r="G229" s="32" t="n"/>
     </row>
     <row r="230" ht="15" customHeight="1" s="21">
-      <c r="A230" s="32" t="n"/>
-      <c r="B230" s="32" t="n"/>
-      <c r="C230" s="32" t="n"/>
-      <c r="D230" s="32" t="n"/>
-      <c r="E230" s="32" t="n"/>
-      <c r="F230" s="32" t="n"/>
+      <c r="A230" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B230" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C230" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D230" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E230" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F230" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G230" s="32" t="n"/>
     </row>
     <row r="231" ht="15" customHeight="1" s="21">
-      <c r="A231" s="32" t="n"/>
-      <c r="B231" s="32" t="n"/>
-      <c r="C231" s="32" t="n"/>
-      <c r="D231" s="32" t="n"/>
-      <c r="E231" s="32" t="n"/>
-      <c r="F231" s="32" t="n"/>
+      <c r="A231" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B231" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C231" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D231" s="32" t="inlineStr">
+        <is>
+          <t>Progression</t>
+        </is>
+      </c>
+      <c r="E231" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F231" s="32" t="inlineStr">
+        <is>
+          <t>3 km E → 2 km STEADY → 2 km T</t>
+        </is>
+      </c>
       <c r="G231" s="32" t="n"/>
     </row>
     <row r="232" ht="15" customHeight="1" s="21">
-      <c r="A232" s="32" t="n"/>
-      <c r="B232" s="32" t="n"/>
-      <c r="C232" s="32" t="n"/>
-      <c r="D232" s="32" t="n"/>
-      <c r="E232" s="32" t="n"/>
-      <c r="F232" s="32" t="n"/>
+      <c r="A232" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B232" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C232" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D232" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E232" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F232" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G232" s="32" t="n"/>
     </row>
     <row r="233" ht="15" customHeight="1" s="21">
-      <c r="A233" s="32" t="n"/>
-      <c r="B233" s="32" t="n"/>
-      <c r="C233" s="32" t="n"/>
-      <c r="D233" s="32" t="n"/>
-      <c r="E233" s="32" t="n"/>
-      <c r="F233" s="32" t="n"/>
+      <c r="A233" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B233" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C233" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D233" s="32" t="inlineStr">
+        <is>
+          <t>Fartlek</t>
+        </is>
+      </c>
+      <c r="E233" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F233" s="32" t="inlineStr">
+        <is>
+          <t>6 x (2 min @ 5K effort / 1 min E)</t>
+        </is>
+      </c>
       <c r="G233" s="32" t="n"/>
     </row>
     <row r="234" ht="15" customHeight="1" s="21">
-      <c r="A234" s="32" t="n"/>
-      <c r="B234" s="32" t="n"/>
-      <c r="C234" s="32" t="n"/>
-      <c r="D234" s="32" t="n"/>
-      <c r="E234" s="32" t="n"/>
-      <c r="F234" s="32" t="n"/>
+      <c r="A234" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B234" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C234" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D234" s="32" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="E234" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F234" s="32" t="inlineStr">
+        <is>
+          <t>Very relaxed recovery run</t>
+        </is>
+      </c>
       <c r="G234" s="32" t="n"/>
     </row>
     <row r="235" ht="15" customHeight="1" s="21">
-      <c r="A235" s="32" t="n"/>
-      <c r="B235" s="32" t="n"/>
-      <c r="C235" s="32" t="n"/>
-      <c r="D235" s="32" t="n"/>
-      <c r="E235" s="32" t="n"/>
-      <c r="F235" s="32" t="n"/>
+      <c r="A235" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B235" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C235" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D235" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E235" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F235" s="32" t="inlineStr">
+        <is>
+          <t>15 min continuous @ T</t>
+        </is>
+      </c>
       <c r="G235" s="32" t="n"/>
     </row>
     <row r="236" ht="15" customHeight="1" s="21">
-      <c r="A236" s="32" t="n"/>
-      <c r="B236" s="32" t="n"/>
-      <c r="C236" s="32" t="n"/>
-      <c r="D236" s="32" t="n"/>
-      <c r="E236" s="32" t="n"/>
-      <c r="F236" s="32" t="n"/>
+      <c r="A236" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B236" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C236" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D236" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E236" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F236" s="32" t="inlineStr">
+        <is>
+          <t>Shorter long run, E</t>
+        </is>
+      </c>
       <c r="G236" s="32" t="n"/>
     </row>
     <row r="237" ht="15" customHeight="1" s="21">
-      <c r="A237" s="32" t="n"/>
-      <c r="B237" s="32" t="n"/>
-      <c r="C237" s="32" t="n"/>
-      <c r="D237" s="32" t="n"/>
-      <c r="E237" s="32" t="n"/>
-      <c r="F237" s="32" t="n"/>
+      <c r="A237" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B237" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C237" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D237" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E237" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F237" s="32" t="inlineStr">
+        <is>
+          <t>5 x 800 m @ I, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G237" s="32" t="n"/>
     </row>
     <row r="238" ht="15" customHeight="1" s="21">
-      <c r="A238" s="32" t="n"/>
-      <c r="B238" s="32" t="n"/>
-      <c r="C238" s="32" t="n"/>
-      <c r="D238" s="32" t="n"/>
-      <c r="E238" s="32" t="n"/>
-      <c r="F238" s="32" t="n"/>
+      <c r="A238" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B238" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C238" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D238" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E238" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F238" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G238" s="32" t="n"/>
     </row>
     <row r="239" ht="15" customHeight="1" s="21">
-      <c r="A239" s="32" t="n"/>
-      <c r="B239" s="32" t="n"/>
-      <c r="C239" s="32" t="n"/>
-      <c r="D239" s="32" t="n"/>
-      <c r="E239" s="32" t="n"/>
-      <c r="F239" s="32" t="n"/>
+      <c r="A239" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B239" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C239" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D239" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E239" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F239" s="32" t="inlineStr">
+        <is>
+          <t>3 x 8 min @ T, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G239" s="32" t="n"/>
     </row>
     <row r="240" ht="15" customHeight="1" s="21">
-      <c r="A240" s="32" t="n"/>
-      <c r="B240" s="32" t="n"/>
-      <c r="C240" s="32" t="n"/>
-      <c r="D240" s="32" t="n"/>
-      <c r="E240" s="32" t="n"/>
-      <c r="F240" s="32" t="n"/>
+      <c r="A240" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B240" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C240" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D240" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E240" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F240" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G240" s="32" t="n"/>
     </row>
     <row r="241" ht="15" customHeight="1" s="21">
-      <c r="A241" s="32" t="n"/>
-      <c r="B241" s="32" t="n"/>
-      <c r="C241" s="32" t="n"/>
-      <c r="D241" s="32" t="n"/>
-      <c r="E241" s="32" t="n"/>
-      <c r="F241" s="32" t="n"/>
+      <c r="A241" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B241" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C241" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D241" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E241" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F241" s="32" t="inlineStr">
+        <is>
+          <t>12 x 400 m @ I, 60 s jog between</t>
+        </is>
+      </c>
       <c r="G241" s="32" t="n"/>
     </row>
     <row r="242" ht="15" customHeight="1" s="21">
-      <c r="A242" s="32" t="n"/>
-      <c r="B242" s="32" t="n"/>
-      <c r="C242" s="32" t="n"/>
-      <c r="D242" s="32" t="n"/>
-      <c r="E242" s="32" t="n"/>
-      <c r="F242" s="32" t="n"/>
+      <c r="A242" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B242" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C242" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D242" s="32" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="E242" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F242" s="32" t="inlineStr">
+        <is>
+          <t>Very relaxed recovery run</t>
+        </is>
+      </c>
       <c r="G242" s="32" t="n"/>
     </row>
     <row r="243" ht="15" customHeight="1" s="21">
-      <c r="A243" s="32" t="n"/>
-      <c r="B243" s="32" t="n"/>
-      <c r="C243" s="32" t="n"/>
-      <c r="D243" s="32" t="n"/>
-      <c r="E243" s="32" t="n"/>
-      <c r="F243" s="32" t="n"/>
+      <c r="A243" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B243" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C243" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D243" s="32" t="inlineStr">
+        <is>
+          <t>Progression</t>
+        </is>
+      </c>
+      <c r="E243" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F243" s="32" t="inlineStr">
+        <is>
+          <t>3 km E → 3 km STEADY → 2 km T</t>
+        </is>
+      </c>
       <c r="G243" s="32" t="n"/>
     </row>
     <row r="244" ht="15" customHeight="1" s="21">
-      <c r="A244" s="32" t="n"/>
-      <c r="B244" s="32" t="n"/>
-      <c r="C244" s="32" t="n"/>
-      <c r="D244" s="32" t="n"/>
-      <c r="E244" s="32" t="n"/>
-      <c r="F244" s="32" t="n"/>
+      <c r="A244" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B244" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C244" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D244" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E244" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F244" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G244" s="32" t="n"/>
     </row>
     <row r="245" ht="15" customHeight="1" s="21">
-      <c r="A245" s="32" t="n"/>
-      <c r="B245" s="32" t="n"/>
-      <c r="C245" s="32" t="n"/>
-      <c r="D245" s="32" t="n"/>
-      <c r="E245" s="32" t="n"/>
-      <c r="F245" s="32" t="n"/>
+      <c r="A245" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B245" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C245" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D245" s="32" t="inlineStr">
+        <is>
+          <t>Fartlek</t>
+        </is>
+      </c>
+      <c r="E245" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F245" s="32" t="inlineStr">
+        <is>
+          <t>5 x (3 min @ 5K / 1 min @ I / 2 min E)</t>
+        </is>
+      </c>
       <c r="G245" s="32" t="n"/>
     </row>
     <row r="246" ht="15" customHeight="1" s="21">
-      <c r="A246" s="32" t="n"/>
-      <c r="B246" s="32" t="n"/>
-      <c r="C246" s="32" t="n"/>
-      <c r="D246" s="32" t="n"/>
-      <c r="E246" s="32" t="n"/>
-      <c r="F246" s="32" t="n"/>
+      <c r="A246" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B246" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C246" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D246" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E246" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F246" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G246" s="32" t="n"/>
     </row>
     <row r="247" ht="15" customHeight="1" s="21">
-      <c r="A247" s="32" t="n"/>
-      <c r="B247" s="32" t="n"/>
-      <c r="C247" s="32" t="n"/>
-      <c r="D247" s="32" t="n"/>
-      <c r="E247" s="32" t="n"/>
-      <c r="F247" s="32" t="n"/>
+      <c r="A247" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B247" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C247" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D247" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E247" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F247" s="32" t="inlineStr">
+        <is>
+          <t>2 x 12 min @ T, 3 min jog between</t>
+        </is>
+      </c>
       <c r="G247" s="32" t="n"/>
     </row>
     <row r="248" ht="15" customHeight="1" s="21">
-      <c r="A248" s="32" t="n"/>
-      <c r="B248" s="32" t="n"/>
-      <c r="C248" s="32" t="n"/>
-      <c r="D248" s="32" t="n"/>
-      <c r="E248" s="32" t="n"/>
-      <c r="F248" s="32" t="n"/>
+      <c r="A248" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B248" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C248" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D248" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E248" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F248" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G248" s="32" t="n"/>
     </row>
     <row r="249" ht="15" customHeight="1" s="21">
-      <c r="A249" s="32" t="n"/>
-      <c r="B249" s="32" t="n"/>
-      <c r="C249" s="32" t="n"/>
-      <c r="D249" s="32" t="n"/>
-      <c r="E249" s="32" t="n"/>
-      <c r="F249" s="32" t="n"/>
+      <c r="A249" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B249" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C249" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D249" s="32" t="inlineStr">
+        <is>
+          <t>Fartlek</t>
+        </is>
+      </c>
+      <c r="E249" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F249" s="32" t="inlineStr">
+        <is>
+          <t>8 x (1 min @ I effort / 1 min E)</t>
+        </is>
+      </c>
       <c r="G249" s="32" t="n"/>
     </row>
     <row r="250" ht="15" customHeight="1" s="21">
-      <c r="A250" s="32" t="n"/>
-      <c r="B250" s="32" t="n"/>
-      <c r="C250" s="32" t="n"/>
-      <c r="D250" s="32" t="n"/>
-      <c r="E250" s="32" t="n"/>
-      <c r="F250" s="32" t="n"/>
+      <c r="A250" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B250" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C250" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D250" s="32" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="E250" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F250" s="32" t="inlineStr">
+        <is>
+          <t>Very relaxed recovery run</t>
+        </is>
+      </c>
       <c r="G250" s="32" t="n"/>
     </row>
     <row r="251" ht="15" customHeight="1" s="21">
-      <c r="A251" s="32" t="n"/>
-      <c r="B251" s="32" t="n"/>
-      <c r="C251" s="32" t="n"/>
-      <c r="D251" s="32" t="n"/>
-      <c r="E251" s="32" t="n"/>
-      <c r="F251" s="32" t="n"/>
+      <c r="A251" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B251" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C251" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D251" s="32" t="inlineStr">
+        <is>
+          <t>Progression</t>
+        </is>
+      </c>
+      <c r="E251" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F251" s="32" t="inlineStr">
+        <is>
+          <t>3 km E → 2 km STEADY → 2 km T</t>
+        </is>
+      </c>
       <c r="G251" s="32" t="n"/>
     </row>
     <row r="252" ht="15" customHeight="1" s="21">
-      <c r="A252" s="32" t="n"/>
-      <c r="B252" s="32" t="n"/>
-      <c r="C252" s="32" t="n"/>
-      <c r="D252" s="32" t="n"/>
-      <c r="E252" s="32" t="n"/>
-      <c r="F252" s="32" t="n"/>
+      <c r="A252" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B252" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C252" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D252" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E252" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F252" s="32" t="inlineStr">
+        <is>
+          <t>Shorter long run, E</t>
+        </is>
+      </c>
       <c r="G252" s="32" t="n"/>
     </row>
     <row r="253" ht="15" customHeight="1" s="21">
-      <c r="A253" s="32" t="n"/>
-      <c r="B253" s="32" t="n"/>
-      <c r="C253" s="32" t="n"/>
-      <c r="D253" s="32" t="n"/>
-      <c r="E253" s="32" t="n"/>
-      <c r="F253" s="32" t="n"/>
+      <c r="A253" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B253" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="C253" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D253" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E253" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F253" s="32" t="inlineStr">
+        <is>
+          <t>5 x 1 km @ I, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G253" s="32" t="n"/>
     </row>
     <row r="254" ht="15" customHeight="1" s="21">
-      <c r="A254" s="32" t="n"/>
-      <c r="B254" s="32" t="n"/>
-      <c r="C254" s="32" t="n"/>
-      <c r="D254" s="32" t="n"/>
-      <c r="E254" s="32" t="n"/>
-      <c r="F254" s="32" t="n"/>
+      <c r="A254" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B254" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="C254" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D254" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E254" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F254" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G254" s="32" t="n"/>
     </row>
     <row r="255" ht="15" customHeight="1" s="21">
-      <c r="A255" s="32" t="n"/>
-      <c r="B255" s="32" t="n"/>
-      <c r="C255" s="32" t="n"/>
-      <c r="D255" s="32" t="n"/>
-      <c r="E255" s="32" t="n"/>
-      <c r="F255" s="32" t="n"/>
+      <c r="A255" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B255" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="C255" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D255" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E255" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F255" s="32" t="inlineStr">
+        <is>
+          <t>25 min continuous @ T</t>
+        </is>
+      </c>
       <c r="G255" s="32" t="n"/>
     </row>
     <row r="256" ht="15" customHeight="1" s="21">
-      <c r="A256" s="32" t="n"/>
-      <c r="B256" s="32" t="n"/>
-      <c r="C256" s="32" t="n"/>
-      <c r="D256" s="32" t="n"/>
-      <c r="E256" s="32" t="n"/>
-      <c r="F256" s="32" t="n"/>
+      <c r="A256" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B256" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="C256" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D256" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E256" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F256" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G256" s="32" t="n"/>
     </row>
     <row r="257" ht="15" customHeight="1" s="21">
-      <c r="A257" s="32" t="n"/>
-      <c r="B257" s="32" t="n"/>
-      <c r="C257" s="32" t="n"/>
-      <c r="D257" s="32" t="n"/>
-      <c r="E257" s="32" t="n"/>
-      <c r="F257" s="32" t="n"/>
+      <c r="A257" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B257" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="C257" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D257" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E257" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F257" s="32" t="inlineStr">
+        <is>
+          <t>8 x 600 m @ I, 90 s jog between</t>
+        </is>
+      </c>
       <c r="G257" s="32" t="n"/>
     </row>
     <row r="258" ht="15" customHeight="1" s="21">
-      <c r="A258" s="32" t="n"/>
-      <c r="B258" s="32" t="n"/>
-      <c r="C258" s="32" t="n"/>
-      <c r="D258" s="32" t="n"/>
-      <c r="E258" s="32" t="n"/>
-      <c r="F258" s="32" t="n"/>
+      <c r="A258" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B258" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="C258" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D258" s="32" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="E258" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F258" s="32" t="inlineStr">
+        <is>
+          <t>Very relaxed recovery run</t>
+        </is>
+      </c>
       <c r="G258" s="32" t="n"/>
     </row>
     <row r="259" ht="15" customHeight="1" s="21">
-      <c r="A259" s="32" t="n"/>
-      <c r="B259" s="32" t="n"/>
-      <c r="C259" s="32" t="n"/>
-      <c r="D259" s="32" t="n"/>
-      <c r="E259" s="32" t="n"/>
-      <c r="F259" s="32" t="n"/>
+      <c r="A259" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B259" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="C259" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D259" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E259" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F259" s="32" t="inlineStr">
+        <is>
+          <t>3 x 2 km @ T, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G259" s="32" t="n"/>
     </row>
     <row r="260" ht="15" customHeight="1" s="21">
-      <c r="A260" s="32" t="n"/>
-      <c r="B260" s="32" t="n"/>
-      <c r="C260" s="32" t="n"/>
-      <c r="D260" s="32" t="n"/>
-      <c r="E260" s="32" t="n"/>
-      <c r="F260" s="32" t="n"/>
+      <c r="A260" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B260" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="C260" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D260" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E260" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F260" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G260" s="32" t="n"/>
     </row>
     <row r="261" ht="15" customHeight="1" s="21">
-      <c r="A261" s="32" t="n"/>
-      <c r="B261" s="32" t="n"/>
-      <c r="C261" s="32" t="n"/>
-      <c r="D261" s="32" t="n"/>
-      <c r="E261" s="32" t="n"/>
-      <c r="F261" s="32" t="n"/>
+      <c r="A261" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B261" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="C261" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D261" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E261" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F261" s="32" t="inlineStr">
+        <is>
+          <t>6 x 400 m @ I, 90 s jog between</t>
+        </is>
+      </c>
       <c r="G261" s="32" t="n"/>
     </row>
     <row r="262" ht="15" customHeight="1" s="21">
-      <c r="A262" s="32" t="n"/>
-      <c r="B262" s="32" t="n"/>
-      <c r="C262" s="32" t="n"/>
-      <c r="D262" s="32" t="n"/>
-      <c r="E262" s="32" t="n"/>
-      <c r="F262" s="32" t="n"/>
+      <c r="A262" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B262" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="C262" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D262" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E262" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F262" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G262" s="32" t="n"/>
     </row>
     <row r="263" ht="15" customHeight="1" s="21">
-      <c r="A263" s="32" t="n"/>
-      <c r="B263" s="32" t="n"/>
-      <c r="C263" s="32" t="n"/>
-      <c r="D263" s="32" t="n"/>
-      <c r="E263" s="32" t="n"/>
-      <c r="F263" s="32" t="n"/>
+      <c r="A263" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B263" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="C263" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D263" s="32" t="inlineStr">
+        <is>
+          <t>Fartlek</t>
+        </is>
+      </c>
+      <c r="E263" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F263" s="32" t="inlineStr">
+        <is>
+          <t>6 x (90 s @ 5K / 90 s E)</t>
+        </is>
+      </c>
       <c r="G263" s="32" t="n"/>
     </row>
     <row r="264" ht="15" customHeight="1" s="21">
-      <c r="A264" s="32" t="n"/>
-      <c r="B264" s="32" t="n"/>
-      <c r="C264" s="32" t="n"/>
-      <c r="D264" s="32" t="n"/>
-      <c r="E264" s="32" t="n"/>
-      <c r="F264" s="32" t="n"/>
+      <c r="A264" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B264" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="C264" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D264" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E264" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F264" s="32" t="inlineStr">
+        <is>
+          <t>Reduced long run, E</t>
+        </is>
+      </c>
       <c r="G264" s="32" t="n"/>
     </row>
     <row r="265" ht="15" customHeight="1" s="21">
-      <c r="A265" s="32" t="n"/>
-      <c r="B265" s="32" t="n"/>
-      <c r="C265" s="32" t="n"/>
-      <c r="D265" s="32" t="n"/>
-      <c r="E265" s="32" t="n"/>
-      <c r="F265" s="32" t="n"/>
+      <c r="A265" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B265" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="C265" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D265" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E265" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F265" s="32" t="inlineStr">
+        <is>
+          <t>4 x 400 m @ 5K, 90 s jog between</t>
+        </is>
+      </c>
       <c r="G265" s="32" t="n"/>
     </row>
     <row r="266" ht="15" customHeight="1" s="21">
-      <c r="A266" s="32" t="n"/>
-      <c r="B266" s="32" t="n"/>
-      <c r="C266" s="32" t="n"/>
-      <c r="D266" s="32" t="n"/>
-      <c r="E266" s="32" t="n"/>
-      <c r="F266" s="32" t="n"/>
+      <c r="A266" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B266" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="C266" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D266" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E266" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F266" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G266" s="32" t="n"/>
     </row>
     <row r="267" ht="15" customHeight="1" s="21">
-      <c r="A267" s="32" t="n"/>
-      <c r="B267" s="32" t="n"/>
-      <c r="C267" s="32" t="n"/>
-      <c r="D267" s="32" t="n"/>
-      <c r="E267" s="32" t="n"/>
-      <c r="F267" s="32" t="n"/>
+      <c r="A267" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B267" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="C267" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D267" s="32" t="inlineStr">
+        <is>
+          <t>Shakeout</t>
+        </is>
+      </c>
+      <c r="E267" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F267" s="32" t="inlineStr">
+        <is>
+          <t>3 km E + 4 x 20 s strides</t>
+        </is>
+      </c>
       <c r="G267" s="32" t="n"/>
     </row>
     <row r="268" ht="15" customHeight="1" s="21">
-      <c r="A268" s="32" t="n"/>
-      <c r="B268" s="32" t="n"/>
-      <c r="C268" s="32" t="n"/>
-      <c r="D268" s="32" t="n"/>
-      <c r="E268" s="32" t="n"/>
-      <c r="F268" s="32" t="n"/>
+      <c r="A268" s="32" t="inlineStr">
+        <is>
+          <t>Faster 5K</t>
+        </is>
+      </c>
+      <c r="B268" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="C268" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D268" s="32" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="E268" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F268" s="32" t="inlineStr">
+        <is>
+          <t>5K RACE – race at goal 5K pace</t>
+        </is>
+      </c>
       <c r="G268" s="32" t="n"/>
     </row>
     <row r="269" ht="15" customHeight="1" s="21">
@@ -32399,7 +33623,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26" ht="15" customHeight="1" s="21">
       <c r="A26" s="34" t="inlineStr">
         <is>

--- a/programmes/Kinetix Programmes.xlsx
+++ b/programmes/Kinetix Programmes.xlsx
@@ -2316,7 +2316,7 @@
         <v>3</v>
       </c>
       <c r="F2" s="32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" s="32" t="n">
         <v>1</v>
@@ -5833,13 +5833,37 @@
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="21">
-      <c r="A66" s="32" t="n"/>
-      <c r="B66" s="32" t="n"/>
-      <c r="C66" s="32" t="n"/>
-      <c r="D66" s="35" t="n"/>
-      <c r="E66" s="32" t="n"/>
-      <c r="F66" s="32" t="n"/>
-      <c r="G66" s="32" t="n"/>
+      <c r="A66" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B66" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" s="32" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D66" s="35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E66" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F66" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G66" s="32" t="inlineStr">
+        <is>
+          <t>Run/walk: short runs with walking breaks. Easy enough to chat throughout.</t>
+        </is>
+      </c>
       <c r="H66" s="33">
         <f>IF(A66="","",COUNTIFS('Run sessions'!$A$2:$A$401,A66,'Run sessions'!$B$2:$B$401,B66))</f>
         <v/>
@@ -5854,12 +5878,32 @@
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" s="21">
-      <c r="A67" s="32" t="n"/>
-      <c r="B67" s="32" t="n"/>
-      <c r="C67" s="32" t="n"/>
-      <c r="D67" s="35" t="n"/>
-      <c r="E67" s="32" t="n"/>
-      <c r="F67" s="32" t="n"/>
+      <c r="A67" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B67" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C67" s="32" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D67" s="35" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E67" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F67" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="G67" s="32" t="n"/>
       <c r="H67" s="33">
         <f>IF(A67="","",COUNTIFS('Run sessions'!$A$2:$A$401,A67,'Run sessions'!$B$2:$B$401,B67))</f>
@@ -5875,12 +5919,32 @@
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" s="21">
-      <c r="A68" s="32" t="n"/>
-      <c r="B68" s="32" t="n"/>
-      <c r="C68" s="32" t="n"/>
-      <c r="D68" s="35" t="n"/>
-      <c r="E68" s="32" t="n"/>
-      <c r="F68" s="32" t="n"/>
+      <c r="A68" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C68" s="32" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D68" s="35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E68" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F68" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="G68" s="32" t="n"/>
       <c r="H68" s="33">
         <f>IF(A68="","",COUNTIFS('Run sessions'!$A$2:$A$401,A68,'Run sessions'!$B$2:$B$401,B68))</f>
@@ -5896,13 +5960,37 @@
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="21">
-      <c r="A69" s="32" t="n"/>
-      <c r="B69" s="32" t="n"/>
-      <c r="C69" s="32" t="n"/>
-      <c r="D69" s="35" t="n"/>
-      <c r="E69" s="32" t="n"/>
-      <c r="F69" s="32" t="n"/>
-      <c r="G69" s="32" t="n"/>
+      <c r="A69" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C69" s="32" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D69" s="35" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E69" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F69" s="32" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G69" s="32" t="inlineStr">
+        <is>
+          <t>Longer runs, fewer walks.</t>
+        </is>
+      </c>
       <c r="H69" s="33">
         <f>IF(A69="","",COUNTIFS('Run sessions'!$A$2:$A$401,A69,'Run sessions'!$B$2:$B$401,B69))</f>
         <v/>
@@ -5917,13 +6005,37 @@
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="21">
-      <c r="A70" s="32" t="n"/>
-      <c r="B70" s="32" t="n"/>
-      <c r="C70" s="32" t="n"/>
-      <c r="D70" s="35" t="n"/>
-      <c r="E70" s="32" t="n"/>
-      <c r="F70" s="32" t="n"/>
-      <c r="G70" s="32" t="n"/>
+      <c r="A70" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D70" s="35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F70" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="inlineStr">
+        <is>
+          <t>A few short pick-ups to wake the legs up.</t>
+        </is>
+      </c>
       <c r="H70" s="33">
         <f>IF(A70="","",COUNTIFS('Run sessions'!$A$2:$A$401,A70,'Run sessions'!$B$2:$B$401,B70))</f>
         <v/>
@@ -5938,13 +6050,37 @@
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="21">
-      <c r="A71" s="32" t="n"/>
-      <c r="B71" s="32" t="n"/>
-      <c r="C71" s="32" t="n"/>
-      <c r="D71" s="35" t="n"/>
-      <c r="E71" s="32" t="n"/>
-      <c r="F71" s="32" t="n"/>
-      <c r="G71" s="32" t="n"/>
+      <c r="A71" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D71" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F71" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G71" s="32" t="inlineStr">
+        <is>
+          <t>Your first 20 minutes without stopping.</t>
+        </is>
+      </c>
       <c r="H71" s="33">
         <f>IF(A71="","",COUNTIFS('Run sessions'!$A$2:$A$401,A71,'Run sessions'!$B$2:$B$401,B71))</f>
         <v/>
@@ -5959,13 +6095,37 @@
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" s="21">
-      <c r="A72" s="32" t="n"/>
-      <c r="B72" s="32" t="n"/>
-      <c r="C72" s="32" t="n"/>
-      <c r="D72" s="35" t="n"/>
-      <c r="E72" s="32" t="n"/>
-      <c r="F72" s="32" t="n"/>
-      <c r="G72" s="32" t="n"/>
+      <c r="A72" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C72" s="32" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="D72" s="35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F72" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G72" s="32" t="inlineStr">
+        <is>
+          <t>25 minutes non-stop: you're nearly there.</t>
+        </is>
+      </c>
       <c r="H72" s="33">
         <f>IF(A72="","",COUNTIFS('Run sessions'!$A$2:$A$401,A72,'Run sessions'!$B$2:$B$401,B72))</f>
         <v/>
@@ -5980,13 +6140,37 @@
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" s="21">
-      <c r="A73" s="32" t="n"/>
-      <c r="B73" s="32" t="n"/>
-      <c r="C73" s="32" t="n"/>
-      <c r="D73" s="35" t="n"/>
-      <c r="E73" s="32" t="n"/>
-      <c r="F73" s="32" t="n"/>
-      <c r="G73" s="32" t="n"/>
+      <c r="A73" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C73" s="32" t="inlineStr">
+        <is>
+          <t>Race week</t>
+        </is>
+      </c>
+      <c r="D73" s="35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="F73" s="32" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G73" s="32" t="inlineStr">
+        <is>
+          <t>Race day! Run it comfortably and finish strong.</t>
+        </is>
+      </c>
       <c r="H73" s="33">
         <f>IF(A73="","",COUNTIFS('Run sessions'!$A$2:$A$401,A73,'Run sessions'!$B$2:$B$401,B73))</f>
         <v/>
@@ -20753,219 +20937,699 @@
       <c r="G268" s="32" t="n"/>
     </row>
     <row r="269" ht="15" customHeight="1" s="21">
-      <c r="A269" s="32" t="n"/>
-      <c r="B269" s="32" t="n"/>
-      <c r="C269" s="32" t="n"/>
-      <c r="D269" s="32" t="n"/>
-      <c r="E269" s="32" t="n"/>
-      <c r="F269" s="32" t="n"/>
+      <c r="A269" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B269" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C269" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D269" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E269" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F269" s="32" t="inlineStr">
+        <is>
+          <t>8 x 1 min @ E effort, 90 s walk between</t>
+        </is>
+      </c>
       <c r="G269" s="32" t="n"/>
     </row>
     <row r="270" ht="15" customHeight="1" s="21">
-      <c r="A270" s="32" t="n"/>
-      <c r="B270" s="32" t="n"/>
-      <c r="C270" s="32" t="n"/>
-      <c r="D270" s="32" t="n"/>
-      <c r="E270" s="32" t="n"/>
-      <c r="F270" s="32" t="n"/>
+      <c r="A270" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B270" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C270" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D270" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E270" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F270" s="32" t="inlineStr">
+        <is>
+          <t>8 x 1 min @ E effort, 90 s walk between</t>
+        </is>
+      </c>
       <c r="G270" s="32" t="n"/>
     </row>
     <row r="271" ht="15" customHeight="1" s="21">
-      <c r="A271" s="32" t="n"/>
-      <c r="B271" s="32" t="n"/>
-      <c r="C271" s="32" t="n"/>
-      <c r="D271" s="32" t="n"/>
-      <c r="E271" s="32" t="n"/>
-      <c r="F271" s="32" t="n"/>
+      <c r="A271" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B271" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C271" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D271" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E271" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F271" s="32" t="inlineStr">
+        <is>
+          <t>8 x 1 min @ E effort, 90 s walk between</t>
+        </is>
+      </c>
       <c r="G271" s="32" t="n"/>
     </row>
     <row r="272" ht="15" customHeight="1" s="21">
-      <c r="A272" s="32" t="n"/>
-      <c r="B272" s="32" t="n"/>
-      <c r="C272" s="32" t="n"/>
-      <c r="D272" s="32" t="n"/>
-      <c r="E272" s="32" t="n"/>
-      <c r="F272" s="32" t="n"/>
+      <c r="A272" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B272" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C272" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D272" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E272" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F272" s="32" t="inlineStr">
+        <is>
+          <t>6 x 2 min @ E effort, 2 min walk between</t>
+        </is>
+      </c>
       <c r="G272" s="32" t="n"/>
     </row>
     <row r="273" ht="15" customHeight="1" s="21">
-      <c r="A273" s="32" t="n"/>
-      <c r="B273" s="32" t="n"/>
-      <c r="C273" s="32" t="n"/>
-      <c r="D273" s="32" t="n"/>
-      <c r="E273" s="32" t="n"/>
-      <c r="F273" s="32" t="n"/>
+      <c r="A273" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B273" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C273" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D273" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E273" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F273" s="32" t="inlineStr">
+        <is>
+          <t>6 x 2 min @ E effort, 90 s walk between</t>
+        </is>
+      </c>
       <c r="G273" s="32" t="n"/>
     </row>
     <row r="274" ht="15" customHeight="1" s="21">
-      <c r="A274" s="32" t="n"/>
-      <c r="B274" s="32" t="n"/>
-      <c r="C274" s="32" t="n"/>
-      <c r="D274" s="32" t="n"/>
-      <c r="E274" s="32" t="n"/>
-      <c r="F274" s="32" t="n"/>
+      <c r="A274" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B274" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C274" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D274" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E274" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F274" s="32" t="inlineStr">
+        <is>
+          <t>5 x 3 min @ E effort, 2 min walk between</t>
+        </is>
+      </c>
       <c r="G274" s="32" t="n"/>
     </row>
     <row r="275" ht="15" customHeight="1" s="21">
-      <c r="A275" s="32" t="n"/>
-      <c r="B275" s="32" t="n"/>
-      <c r="C275" s="32" t="n"/>
-      <c r="D275" s="32" t="n"/>
-      <c r="E275" s="32" t="n"/>
-      <c r="F275" s="32" t="n"/>
+      <c r="A275" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B275" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C275" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D275" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E275" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F275" s="32" t="inlineStr">
+        <is>
+          <t>5 x 3 min @ E effort, 90 s walk between</t>
+        </is>
+      </c>
       <c r="G275" s="32" t="n"/>
     </row>
     <row r="276" ht="15" customHeight="1" s="21">
-      <c r="A276" s="32" t="n"/>
-      <c r="B276" s="32" t="n"/>
-      <c r="C276" s="32" t="n"/>
-      <c r="D276" s="32" t="n"/>
-      <c r="E276" s="32" t="n"/>
-      <c r="F276" s="32" t="n"/>
+      <c r="A276" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B276" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C276" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D276" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E276" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F276" s="32" t="inlineStr">
+        <is>
+          <t>4 x 4 min @ E effort, 90 s walk between</t>
+        </is>
+      </c>
       <c r="G276" s="32" t="n"/>
     </row>
     <row r="277" ht="15" customHeight="1" s="21">
-      <c r="A277" s="32" t="n"/>
-      <c r="B277" s="32" t="n"/>
-      <c r="C277" s="32" t="n"/>
-      <c r="D277" s="32" t="n"/>
-      <c r="E277" s="32" t="n"/>
-      <c r="F277" s="32" t="n"/>
+      <c r="A277" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B277" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C277" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D277" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E277" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F277" s="32" t="inlineStr">
+        <is>
+          <t>4 x 5 min @ E effort, 2 min walk between</t>
+        </is>
+      </c>
       <c r="G277" s="32" t="n"/>
     </row>
     <row r="278" ht="15" customHeight="1" s="21">
-      <c r="A278" s="32" t="n"/>
-      <c r="B278" s="32" t="n"/>
-      <c r="C278" s="32" t="n"/>
-      <c r="D278" s="32" t="n"/>
-      <c r="E278" s="32" t="n"/>
-      <c r="F278" s="32" t="n"/>
+      <c r="A278" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B278" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C278" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D278" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E278" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F278" s="32" t="inlineStr">
+        <is>
+          <t>3 x 6 min @ E effort, 2 min walk between</t>
+        </is>
+      </c>
       <c r="G278" s="32" t="n"/>
     </row>
     <row r="279" ht="15" customHeight="1" s="21">
-      <c r="A279" s="32" t="n"/>
-      <c r="B279" s="32" t="n"/>
-      <c r="C279" s="32" t="n"/>
-      <c r="D279" s="32" t="n"/>
-      <c r="E279" s="32" t="n"/>
-      <c r="F279" s="32" t="n"/>
+      <c r="A279" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B279" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C279" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D279" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E279" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F279" s="32" t="inlineStr">
+        <is>
+          <t>3 x 7 min @ E effort, 90 s walk between</t>
+        </is>
+      </c>
       <c r="G279" s="32" t="n"/>
     </row>
     <row r="280" ht="15" customHeight="1" s="21">
-      <c r="A280" s="32" t="n"/>
-      <c r="B280" s="32" t="n"/>
-      <c r="C280" s="32" t="n"/>
-      <c r="D280" s="32" t="n"/>
-      <c r="E280" s="32" t="n"/>
-      <c r="F280" s="32" t="n"/>
+      <c r="A280" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B280" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C280" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D280" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E280" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F280" s="32" t="inlineStr">
+        <is>
+          <t>2 x 10 min @ E effort, 2 min walk between</t>
+        </is>
+      </c>
       <c r="G280" s="32" t="n"/>
     </row>
     <row r="281" ht="15" customHeight="1" s="21">
-      <c r="A281" s="32" t="n"/>
-      <c r="B281" s="32" t="n"/>
-      <c r="C281" s="32" t="n"/>
-      <c r="D281" s="32" t="n"/>
-      <c r="E281" s="32" t="n"/>
-      <c r="F281" s="32" t="n"/>
+      <c r="A281" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B281" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C281" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D281" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E281" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F281" s="32" t="inlineStr">
+        <is>
+          <t>2 x 10 min @ E effort, 90 s walk between</t>
+        </is>
+      </c>
       <c r="G281" s="32" t="n"/>
     </row>
     <row r="282" ht="15" customHeight="1" s="21">
-      <c r="A282" s="32" t="n"/>
-      <c r="B282" s="32" t="n"/>
-      <c r="C282" s="32" t="n"/>
-      <c r="D282" s="32" t="n"/>
-      <c r="E282" s="32" t="n"/>
-      <c r="F282" s="32" t="n"/>
+      <c r="A282" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B282" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C282" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D282" s="32" t="inlineStr">
+        <is>
+          <t>Fartlek</t>
+        </is>
+      </c>
+      <c r="E282" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F282" s="32" t="inlineStr">
+        <is>
+          <t>5 x (3 min @ E effort / 30 s @ 5K effort / 90 s walk)</t>
+        </is>
+      </c>
       <c r="G282" s="32" t="n"/>
     </row>
     <row r="283" ht="15" customHeight="1" s="21">
-      <c r="A283" s="32" t="n"/>
-      <c r="B283" s="32" t="n"/>
-      <c r="C283" s="32" t="n"/>
-      <c r="D283" s="32" t="n"/>
-      <c r="E283" s="32" t="n"/>
-      <c r="F283" s="32" t="n"/>
+      <c r="A283" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B283" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C283" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D283" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E283" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F283" s="32" t="inlineStr">
+        <is>
+          <t>2 x 12 min @ E effort, 90 s walk between</t>
+        </is>
+      </c>
       <c r="G283" s="32" t="n"/>
     </row>
     <row r="284" ht="15" customHeight="1" s="21">
-      <c r="A284" s="32" t="n"/>
-      <c r="B284" s="32" t="n"/>
-      <c r="C284" s="32" t="n"/>
-      <c r="D284" s="32" t="n"/>
-      <c r="E284" s="32" t="n"/>
-      <c r="F284" s="32" t="n"/>
+      <c r="A284" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B284" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C284" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D284" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E284" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F284" s="32" t="inlineStr">
+        <is>
+          <t>2 x 12 min @ E effort, 90 s walk between</t>
+        </is>
+      </c>
       <c r="G284" s="32" t="n"/>
     </row>
     <row r="285" ht="15" customHeight="1" s="21">
-      <c r="A285" s="32" t="n"/>
-      <c r="B285" s="32" t="n"/>
-      <c r="C285" s="32" t="n"/>
-      <c r="D285" s="32" t="n"/>
-      <c r="E285" s="32" t="n"/>
-      <c r="F285" s="32" t="n"/>
+      <c r="A285" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B285" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C285" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D285" s="32" t="inlineStr">
+        <is>
+          <t>Fartlek</t>
+        </is>
+      </c>
+      <c r="E285" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F285" s="32" t="inlineStr">
+        <is>
+          <t>6 x (3 min @ E effort / 30 s @ 5K effort / 90 s walk)</t>
+        </is>
+      </c>
       <c r="G285" s="32" t="n"/>
     </row>
     <row r="286" ht="15" customHeight="1" s="21">
-      <c r="A286" s="32" t="n"/>
-      <c r="B286" s="32" t="n"/>
-      <c r="C286" s="32" t="n"/>
-      <c r="D286" s="32" t="n"/>
-      <c r="E286" s="32" t="n"/>
-      <c r="F286" s="32" t="n"/>
+      <c r="A286" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B286" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C286" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D286" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E286" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F286" s="32" t="inlineStr">
+        <is>
+          <t>1 x 20 min @ E effort, 2 min walk between</t>
+        </is>
+      </c>
       <c r="G286" s="32" t="n"/>
     </row>
     <row r="287" ht="15" customHeight="1" s="21">
-      <c r="A287" s="32" t="n"/>
-      <c r="B287" s="32" t="n"/>
-      <c r="C287" s="32" t="n"/>
-      <c r="D287" s="32" t="n"/>
-      <c r="E287" s="32" t="n"/>
-      <c r="F287" s="32" t="n"/>
+      <c r="A287" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B287" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C287" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D287" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E287" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F287" s="32" t="inlineStr">
+        <is>
+          <t>1 x 20 min @ E effort, 2 min walk between</t>
+        </is>
+      </c>
       <c r="G287" s="32" t="n"/>
     </row>
     <row r="288" ht="15" customHeight="1" s="21">
-      <c r="A288" s="32" t="n"/>
-      <c r="B288" s="32" t="n"/>
-      <c r="C288" s="32" t="n"/>
-      <c r="D288" s="32" t="n"/>
-      <c r="E288" s="32" t="n"/>
-      <c r="F288" s="32" t="n"/>
+      <c r="A288" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B288" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C288" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D288" s="32" t="inlineStr">
+        <is>
+          <t>Fartlek</t>
+        </is>
+      </c>
+      <c r="E288" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F288" s="32" t="inlineStr">
+        <is>
+          <t>6 x (4 min @ E effort / 30 s @ 5K effort / 60 s walk)</t>
+        </is>
+      </c>
       <c r="G288" s="32" t="n"/>
     </row>
     <row r="289" ht="15" customHeight="1" s="21">
-      <c r="A289" s="32" t="n"/>
-      <c r="B289" s="32" t="n"/>
-      <c r="C289" s="32" t="n"/>
-      <c r="D289" s="32" t="n"/>
-      <c r="E289" s="32" t="n"/>
-      <c r="F289" s="32" t="n"/>
+      <c r="A289" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B289" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C289" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D289" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E289" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F289" s="32" t="inlineStr">
+        <is>
+          <t>1 x 25 min @ E effort, 2 min walk between</t>
+        </is>
+      </c>
       <c r="G289" s="32" t="n"/>
     </row>
     <row r="290" ht="15" customHeight="1" s="21">
-      <c r="A290" s="32" t="n"/>
-      <c r="B290" s="32" t="n"/>
-      <c r="C290" s="32" t="n"/>
-      <c r="D290" s="32" t="n"/>
-      <c r="E290" s="32" t="n"/>
-      <c r="F290" s="32" t="n"/>
+      <c r="A290" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B290" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C290" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D290" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E290" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F290" s="32" t="inlineStr">
+        <is>
+          <t>1 x 15 min @ E effort, 2 min walk between</t>
+        </is>
+      </c>
       <c r="G290" s="32" t="n"/>
     </row>
     <row r="291" ht="15" customHeight="1" s="21">
-      <c r="A291" s="32" t="n"/>
-      <c r="B291" s="32" t="n"/>
-      <c r="C291" s="32" t="n"/>
-      <c r="D291" s="32" t="n"/>
-      <c r="E291" s="32" t="n"/>
-      <c r="F291" s="32" t="n"/>
+      <c r="A291" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B291" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C291" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D291" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E291" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F291" s="32" t="inlineStr">
+        <is>
+          <t>1 x 10 min @ E effort, 2 min walk between</t>
+        </is>
+      </c>
       <c r="G291" s="32" t="n"/>
     </row>
     <row r="292" ht="15" customHeight="1" s="21">
-      <c r="A292" s="32" t="n"/>
-      <c r="B292" s="32" t="n"/>
-      <c r="C292" s="32" t="n"/>
-      <c r="D292" s="32" t="n"/>
-      <c r="E292" s="32" t="n"/>
-      <c r="F292" s="32" t="n"/>
+      <c r="A292" s="32" t="inlineStr">
+        <is>
+          <t>First 5K</t>
+        </is>
+      </c>
+      <c r="B292" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C292" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D292" s="32" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="E292" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F292" s="32" t="inlineStr">
+        <is>
+          <t>5K – run it comfortably and finish strong</t>
+        </is>
+      </c>
       <c r="G292" s="32" t="n"/>
     </row>
     <row r="293" ht="15" customHeight="1" s="21">

--- a/programmes/Kinetix Programmes.xlsx
+++ b/programmes/Kinetix Programmes.xlsx
@@ -2834,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" s="32" t="n">
         <v>2</v>
@@ -2858,7 +2858,7 @@
         <v>40</v>
       </c>
       <c r="N9" s="32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" s="32" t="inlineStr">
         <is>
@@ -6185,13 +6185,37 @@
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" s="21">
-      <c r="A74" s="32" t="n"/>
-      <c r="B74" s="32" t="n"/>
-      <c r="C74" s="32" t="n"/>
-      <c r="D74" s="35" t="n"/>
-      <c r="E74" s="32" t="n"/>
-      <c r="F74" s="32" t="n"/>
-      <c r="G74" s="32" t="n"/>
+      <c r="A74" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D74" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F74" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="inlineStr">
+        <is>
+          <t>Settle in: one quality run, the rest easy, and full-body lifting.</t>
+        </is>
+      </c>
       <c r="H74" s="33">
         <f>IF(A74="","",COUNTIFS('Run sessions'!$A$2:$A$401,A74,'Run sessions'!$B$2:$B$401,B74))</f>
         <v/>
@@ -6206,12 +6230,32 @@
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" s="21">
-      <c r="A75" s="32" t="n"/>
-      <c r="B75" s="32" t="n"/>
-      <c r="C75" s="32" t="n"/>
-      <c r="D75" s="35" t="n"/>
-      <c r="E75" s="32" t="n"/>
-      <c r="F75" s="32" t="n"/>
+      <c r="A75" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B75" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C75" s="32" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D75" s="35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E75" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F75" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="G75" s="32" t="n"/>
       <c r="H75" s="33">
         <f>IF(A75="","",COUNTIFS('Run sessions'!$A$2:$A$401,A75,'Run sessions'!$B$2:$B$401,B75))</f>
@@ -6227,12 +6271,32 @@
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" s="21">
-      <c r="A76" s="32" t="n"/>
-      <c r="B76" s="32" t="n"/>
-      <c r="C76" s="32" t="n"/>
-      <c r="D76" s="35" t="n"/>
-      <c r="E76" s="32" t="n"/>
-      <c r="F76" s="32" t="n"/>
+      <c r="A76" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C76" s="32" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D76" s="35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E76" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F76" s="32" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="G76" s="32" t="n"/>
       <c r="H76" s="33">
         <f>IF(A76="","",COUNTIFS('Run sessions'!$A$2:$A$401,A76,'Run sessions'!$B$2:$B$401,B76))</f>
@@ -6248,13 +6312,37 @@
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="21">
-      <c r="A77" s="32" t="n"/>
-      <c r="B77" s="32" t="n"/>
-      <c r="C77" s="32" t="n"/>
-      <c r="D77" s="35" t="n"/>
-      <c r="E77" s="32" t="n"/>
-      <c r="F77" s="32" t="n"/>
-      <c r="G77" s="32" t="n"/>
+      <c r="A77" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C77" s="32" t="inlineStr">
+        <is>
+          <t>Deload</t>
+        </is>
+      </c>
+      <c r="D77" s="35" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E77" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F77" s="32" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G77" s="32" t="inlineStr">
+        <is>
+          <t>Lighter week for running and lifting.</t>
+        </is>
+      </c>
       <c r="H77" s="33">
         <f>IF(A77="","",COUNTIFS('Run sessions'!$A$2:$A$401,A77,'Run sessions'!$B$2:$B$401,B77))</f>
         <v/>
@@ -6269,12 +6357,32 @@
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" s="21">
-      <c r="A78" s="32" t="n"/>
-      <c r="B78" s="32" t="n"/>
-      <c r="C78" s="32" t="n"/>
-      <c r="D78" s="35" t="n"/>
-      <c r="E78" s="32" t="n"/>
-      <c r="F78" s="32" t="n"/>
+      <c r="A78" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D78" s="35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F78" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="G78" s="32" t="n"/>
       <c r="H78" s="33">
         <f>IF(A78="","",COUNTIFS('Run sessions'!$A$2:$A$401,A78,'Run sessions'!$B$2:$B$401,B78))</f>
@@ -6290,12 +6398,32 @@
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" s="21">
-      <c r="A79" s="32" t="n"/>
-      <c r="B79" s="32" t="n"/>
-      <c r="C79" s="32" t="n"/>
-      <c r="D79" s="35" t="n"/>
-      <c r="E79" s="32" t="n"/>
-      <c r="F79" s="32" t="n"/>
+      <c r="A79" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B79" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D79" s="35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E79" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F79" s="32" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="G79" s="32" t="n"/>
       <c r="H79" s="33">
         <f>IF(A79="","",COUNTIFS('Run sessions'!$A$2:$A$401,A79,'Run sessions'!$B$2:$B$401,B79))</f>
@@ -6311,13 +6439,37 @@
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" s="21">
-      <c r="A80" s="32" t="n"/>
-      <c r="B80" s="32" t="n"/>
-      <c r="C80" s="32" t="n"/>
-      <c r="D80" s="35" t="n"/>
-      <c r="E80" s="32" t="n"/>
-      <c r="F80" s="32" t="n"/>
-      <c r="G80" s="32" t="n"/>
+      <c r="A80" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C80" s="32" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="D80" s="35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F80" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="inlineStr">
+        <is>
+          <t>Biggest week of the block.</t>
+        </is>
+      </c>
       <c r="H80" s="33">
         <f>IF(A80="","",COUNTIFS('Run sessions'!$A$2:$A$401,A80,'Run sessions'!$B$2:$B$401,B80))</f>
         <v/>
@@ -6332,13 +6484,37 @@
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" s="21">
-      <c r="A81" s="32" t="n"/>
-      <c r="B81" s="32" t="n"/>
-      <c r="C81" s="32" t="n"/>
-      <c r="D81" s="35" t="n"/>
-      <c r="E81" s="32" t="n"/>
-      <c r="F81" s="32" t="n"/>
-      <c r="G81" s="32" t="n"/>
+      <c r="A81" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>Deload</t>
+        </is>
+      </c>
+      <c r="D81" s="35" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E81" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F81" s="32" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G81" s="32" t="inlineStr">
+        <is>
+          <t>Lighter week with a 5K time trial: your result can update your paces for the next block.</t>
+        </is>
+      </c>
       <c r="H81" s="33">
         <f>IF(A81="","",COUNTIFS('Run sessions'!$A$2:$A$401,A81,'Run sessions'!$B$2:$B$401,B81))</f>
         <v/>
@@ -21633,219 +21809,699 @@
       <c r="G292" s="32" t="n"/>
     </row>
     <row r="293" ht="15" customHeight="1" s="21">
-      <c r="A293" s="32" t="n"/>
-      <c r="B293" s="32" t="n"/>
-      <c r="C293" s="32" t="n"/>
-      <c r="D293" s="32" t="n"/>
-      <c r="E293" s="32" t="n"/>
-      <c r="F293" s="32" t="n"/>
+      <c r="A293" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B293" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C293" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D293" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E293" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F293" s="32" t="inlineStr">
+        <is>
+          <t>6 x 800 m @ I, 90 s jog between</t>
+        </is>
+      </c>
       <c r="G293" s="32" t="n"/>
     </row>
     <row r="294" ht="15" customHeight="1" s="21">
-      <c r="A294" s="32" t="n"/>
-      <c r="B294" s="32" t="n"/>
-      <c r="C294" s="32" t="n"/>
-      <c r="D294" s="32" t="n"/>
-      <c r="E294" s="32" t="n"/>
-      <c r="F294" s="32" t="n"/>
+      <c r="A294" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B294" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C294" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D294" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E294" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F294" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G294" s="32" t="n"/>
     </row>
     <row r="295" ht="15" customHeight="1" s="21">
-      <c r="A295" s="32" t="n"/>
-      <c r="B295" s="32" t="n"/>
-      <c r="C295" s="32" t="n"/>
-      <c r="D295" s="32" t="n"/>
-      <c r="E295" s="32" t="n"/>
-      <c r="F295" s="32" t="n"/>
+      <c r="A295" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B295" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C295" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D295" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E295" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F295" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G295" s="32" t="n"/>
     </row>
     <row r="296" ht="15" customHeight="1" s="21">
-      <c r="A296" s="32" t="n"/>
-      <c r="B296" s="32" t="n"/>
-      <c r="C296" s="32" t="n"/>
-      <c r="D296" s="32" t="n"/>
-      <c r="E296" s="32" t="n"/>
-      <c r="F296" s="32" t="n"/>
+      <c r="A296" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B296" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C296" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D296" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E296" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F296" s="32" t="inlineStr">
+        <is>
+          <t>2 x 10 min @ T, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G296" s="32" t="n"/>
     </row>
     <row r="297" ht="15" customHeight="1" s="21">
-      <c r="A297" s="32" t="n"/>
-      <c r="B297" s="32" t="n"/>
-      <c r="C297" s="32" t="n"/>
-      <c r="D297" s="32" t="n"/>
-      <c r="E297" s="32" t="n"/>
-      <c r="F297" s="32" t="n"/>
+      <c r="A297" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B297" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C297" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D297" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E297" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F297" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G297" s="32" t="n"/>
     </row>
     <row r="298" ht="15" customHeight="1" s="21">
-      <c r="A298" s="32" t="n"/>
-      <c r="B298" s="32" t="n"/>
-      <c r="C298" s="32" t="n"/>
-      <c r="D298" s="32" t="n"/>
-      <c r="E298" s="32" t="n"/>
-      <c r="F298" s="32" t="n"/>
+      <c r="A298" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B298" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C298" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D298" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E298" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F298" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G298" s="32" t="n"/>
     </row>
     <row r="299" ht="15" customHeight="1" s="21">
-      <c r="A299" s="32" t="n"/>
-      <c r="B299" s="32" t="n"/>
-      <c r="C299" s="32" t="n"/>
-      <c r="D299" s="32" t="n"/>
-      <c r="E299" s="32" t="n"/>
-      <c r="F299" s="32" t="n"/>
+      <c r="A299" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B299" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C299" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D299" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E299" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F299" s="32" t="inlineStr">
+        <is>
+          <t>5 x 1 km @ I, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G299" s="32" t="n"/>
     </row>
     <row r="300" ht="15" customHeight="1" s="21">
-      <c r="A300" s="32" t="n"/>
-      <c r="B300" s="32" t="n"/>
-      <c r="C300" s="32" t="n"/>
-      <c r="D300" s="32" t="n"/>
-      <c r="E300" s="32" t="n"/>
-      <c r="F300" s="32" t="n"/>
+      <c r="A300" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B300" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C300" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D300" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E300" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F300" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G300" s="32" t="n"/>
     </row>
     <row r="301" ht="15" customHeight="1" s="21">
-      <c r="A301" s="32" t="n"/>
-      <c r="B301" s="32" t="n"/>
-      <c r="C301" s="32" t="n"/>
-      <c r="D301" s="32" t="n"/>
-      <c r="E301" s="32" t="n"/>
-      <c r="F301" s="32" t="n"/>
+      <c r="A301" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B301" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C301" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D301" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E301" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F301" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G301" s="32" t="n"/>
     </row>
     <row r="302" ht="15" customHeight="1" s="21">
-      <c r="A302" s="32" t="n"/>
-      <c r="B302" s="32" t="n"/>
-      <c r="C302" s="32" t="n"/>
-      <c r="D302" s="32" t="n"/>
-      <c r="E302" s="32" t="n"/>
-      <c r="F302" s="32" t="n"/>
+      <c r="A302" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B302" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C302" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D302" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E302" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F302" s="32" t="inlineStr">
+        <is>
+          <t>15 min continuous @ T</t>
+        </is>
+      </c>
       <c r="G302" s="32" t="n"/>
     </row>
     <row r="303" ht="15" customHeight="1" s="21">
-      <c r="A303" s="32" t="n"/>
-      <c r="B303" s="32" t="n"/>
-      <c r="C303" s="32" t="n"/>
-      <c r="D303" s="32" t="n"/>
-      <c r="E303" s="32" t="n"/>
-      <c r="F303" s="32" t="n"/>
+      <c r="A303" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B303" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C303" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D303" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E303" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F303" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G303" s="32" t="n"/>
     </row>
     <row r="304" ht="15" customHeight="1" s="21">
-      <c r="A304" s="32" t="n"/>
-      <c r="B304" s="32" t="n"/>
-      <c r="C304" s="32" t="n"/>
-      <c r="D304" s="32" t="n"/>
-      <c r="E304" s="32" t="n"/>
-      <c r="F304" s="32" t="n"/>
+      <c r="A304" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B304" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C304" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D304" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E304" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F304" s="32" t="inlineStr">
+        <is>
+          <t>Shorter long run, E</t>
+        </is>
+      </c>
       <c r="G304" s="32" t="n"/>
     </row>
     <row r="305" ht="15" customHeight="1" s="21">
-      <c r="A305" s="32" t="n"/>
-      <c r="B305" s="32" t="n"/>
-      <c r="C305" s="32" t="n"/>
-      <c r="D305" s="32" t="n"/>
-      <c r="E305" s="32" t="n"/>
-      <c r="F305" s="32" t="n"/>
+      <c r="A305" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B305" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C305" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D305" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E305" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F305" s="32" t="inlineStr">
+        <is>
+          <t>8 x 600 m @ I, 75 s jog between</t>
+        </is>
+      </c>
       <c r="G305" s="32" t="n"/>
     </row>
     <row r="306" ht="15" customHeight="1" s="21">
-      <c r="A306" s="32" t="n"/>
-      <c r="B306" s="32" t="n"/>
-      <c r="C306" s="32" t="n"/>
-      <c r="D306" s="32" t="n"/>
-      <c r="E306" s="32" t="n"/>
-      <c r="F306" s="32" t="n"/>
+      <c r="A306" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B306" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C306" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D306" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E306" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F306" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G306" s="32" t="n"/>
     </row>
     <row r="307" ht="15" customHeight="1" s="21">
-      <c r="A307" s="32" t="n"/>
-      <c r="B307" s="32" t="n"/>
-      <c r="C307" s="32" t="n"/>
-      <c r="D307" s="32" t="n"/>
-      <c r="E307" s="32" t="n"/>
-      <c r="F307" s="32" t="n"/>
+      <c r="A307" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B307" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C307" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D307" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E307" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F307" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G307" s="32" t="n"/>
     </row>
     <row r="308" ht="15" customHeight="1" s="21">
-      <c r="A308" s="32" t="n"/>
-      <c r="B308" s="32" t="n"/>
-      <c r="C308" s="32" t="n"/>
-      <c r="D308" s="32" t="n"/>
-      <c r="E308" s="32" t="n"/>
-      <c r="F308" s="32" t="n"/>
+      <c r="A308" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B308" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C308" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D308" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E308" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F308" s="32" t="inlineStr">
+        <is>
+          <t>3 x 8 min @ T, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G308" s="32" t="n"/>
     </row>
     <row r="309" ht="15" customHeight="1" s="21">
-      <c r="A309" s="32" t="n"/>
-      <c r="B309" s="32" t="n"/>
-      <c r="C309" s="32" t="n"/>
-      <c r="D309" s="32" t="n"/>
-      <c r="E309" s="32" t="n"/>
-      <c r="F309" s="32" t="n"/>
+      <c r="A309" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B309" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C309" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D309" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E309" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F309" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G309" s="32" t="n"/>
     </row>
     <row r="310" ht="15" customHeight="1" s="21">
-      <c r="A310" s="32" t="n"/>
-      <c r="B310" s="32" t="n"/>
-      <c r="C310" s="32" t="n"/>
-      <c r="D310" s="32" t="n"/>
-      <c r="E310" s="32" t="n"/>
-      <c r="F310" s="32" t="n"/>
+      <c r="A310" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B310" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C310" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D310" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E310" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F310" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G310" s="32" t="n"/>
     </row>
     <row r="311" ht="15" customHeight="1" s="21">
-      <c r="A311" s="32" t="n"/>
-      <c r="B311" s="32" t="n"/>
-      <c r="C311" s="32" t="n"/>
-      <c r="D311" s="32" t="n"/>
-      <c r="E311" s="32" t="n"/>
-      <c r="F311" s="32" t="n"/>
+      <c r="A311" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B311" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C311" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D311" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E311" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F311" s="32" t="inlineStr">
+        <is>
+          <t>6 x 1 km @ I, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G311" s="32" t="n"/>
     </row>
     <row r="312" ht="15" customHeight="1" s="21">
-      <c r="A312" s="32" t="n"/>
-      <c r="B312" s="32" t="n"/>
-      <c r="C312" s="32" t="n"/>
-      <c r="D312" s="32" t="n"/>
-      <c r="E312" s="32" t="n"/>
-      <c r="F312" s="32" t="n"/>
+      <c r="A312" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B312" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C312" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D312" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E312" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F312" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G312" s="32" t="n"/>
     </row>
     <row r="313" ht="15" customHeight="1" s="21">
-      <c r="A313" s="32" t="n"/>
-      <c r="B313" s="32" t="n"/>
-      <c r="C313" s="32" t="n"/>
-      <c r="D313" s="32" t="n"/>
-      <c r="E313" s="32" t="n"/>
-      <c r="F313" s="32" t="n"/>
+      <c r="A313" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B313" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C313" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D313" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E313" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F313" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G313" s="32" t="n"/>
     </row>
     <row r="314" ht="15" customHeight="1" s="21">
-      <c r="A314" s="32" t="n"/>
-      <c r="B314" s="32" t="n"/>
-      <c r="C314" s="32" t="n"/>
-      <c r="D314" s="32" t="n"/>
-      <c r="E314" s="32" t="n"/>
-      <c r="F314" s="32" t="n"/>
+      <c r="A314" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B314" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C314" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D314" s="32" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="E314" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F314" s="32" t="inlineStr">
+        <is>
+          <t>5K time trial – hard but even, to update your paces</t>
+        </is>
+      </c>
       <c r="G314" s="32" t="n"/>
     </row>
     <row r="315" ht="15" customHeight="1" s="21">
-      <c r="A315" s="32" t="n"/>
-      <c r="B315" s="32" t="n"/>
-      <c r="C315" s="32" t="n"/>
-      <c r="D315" s="32" t="n"/>
-      <c r="E315" s="32" t="n"/>
-      <c r="F315" s="32" t="n"/>
+      <c r="A315" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B315" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C315" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D315" s="32" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="E315" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F315" s="32" t="inlineStr">
+        <is>
+          <t>E continuous run</t>
+        </is>
+      </c>
       <c r="G315" s="32" t="n"/>
     </row>
     <row r="316" ht="15" customHeight="1" s="21">
-      <c r="A316" s="32" t="n"/>
-      <c r="B316" s="32" t="n"/>
-      <c r="C316" s="32" t="n"/>
-      <c r="D316" s="32" t="n"/>
-      <c r="E316" s="32" t="n"/>
-      <c r="F316" s="32" t="n"/>
+      <c r="A316" s="32" t="inlineStr">
+        <is>
+          <t>Balanced hybrid</t>
+        </is>
+      </c>
+      <c r="B316" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C316" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D316" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E316" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F316" s="32" t="inlineStr">
+        <is>
+          <t>Shorter long run, E</t>
+        </is>
+      </c>
       <c r="G316" s="32" t="n"/>
     </row>
     <row r="317" ht="15" customHeight="1" s="21">

--- a/programmes/Kinetix Programmes.xlsx
+++ b/programmes/Kinetix Programmes.xlsx
@@ -2682,7 +2682,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" s="32" t="n">
         <v>2</v>
@@ -2706,7 +2706,7 @@
         <v>25</v>
       </c>
       <c r="N7" s="32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" s="32" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" s="32" t="n">
         <v>3</v>
@@ -2780,7 +2780,7 @@
         <v>25</v>
       </c>
       <c r="N8" s="32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" s="32" t="inlineStr">
         <is>
@@ -6529,13 +6529,37 @@
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" s="21">
-      <c r="A82" s="32" t="n"/>
-      <c r="B82" s="32" t="n"/>
-      <c r="C82" s="32" t="n"/>
-      <c r="D82" s="35" t="n"/>
-      <c r="E82" s="32" t="n"/>
-      <c r="F82" s="32" t="n"/>
-      <c r="G82" s="32" t="n"/>
+      <c r="A82" s="32" t="inlineStr">
+        <is>
+          <t>Build strength</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D82" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F82" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G82" s="32" t="inlineStr">
+        <is>
+          <t>Settle in: heavy lifting with two runs to keep your engine.</t>
+        </is>
+      </c>
       <c r="H82" s="33">
         <f>IF(A82="","",COUNTIFS('Run sessions'!$A$2:$A$401,A82,'Run sessions'!$B$2:$B$401,B82))</f>
         <v/>
@@ -6550,12 +6574,32 @@
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" s="21">
-      <c r="A83" s="32" t="n"/>
-      <c r="B83" s="32" t="n"/>
-      <c r="C83" s="32" t="n"/>
-      <c r="D83" s="35" t="n"/>
-      <c r="E83" s="32" t="n"/>
-      <c r="F83" s="32" t="n"/>
+      <c r="A83" s="32" t="inlineStr">
+        <is>
+          <t>Build strength</t>
+        </is>
+      </c>
+      <c r="B83" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C83" s="32" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D83" s="35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E83" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F83" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="G83" s="32" t="n"/>
       <c r="H83" s="33">
         <f>IF(A83="","",COUNTIFS('Run sessions'!$A$2:$A$401,A83,'Run sessions'!$B$2:$B$401,B83))</f>
@@ -6571,12 +6615,32 @@
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" s="21">
-      <c r="A84" s="32" t="n"/>
-      <c r="B84" s="32" t="n"/>
-      <c r="C84" s="32" t="n"/>
-      <c r="D84" s="35" t="n"/>
-      <c r="E84" s="32" t="n"/>
-      <c r="F84" s="32" t="n"/>
+      <c r="A84" s="32" t="inlineStr">
+        <is>
+          <t>Build strength</t>
+        </is>
+      </c>
+      <c r="B84" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C84" s="32" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D84" s="35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E84" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F84" s="32" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="G84" s="32" t="n"/>
       <c r="H84" s="33">
         <f>IF(A84="","",COUNTIFS('Run sessions'!$A$2:$A$401,A84,'Run sessions'!$B$2:$B$401,B84))</f>
@@ -6592,12 +6656,32 @@
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" s="21">
-      <c r="A85" s="32" t="n"/>
-      <c r="B85" s="32" t="n"/>
-      <c r="C85" s="32" t="n"/>
-      <c r="D85" s="35" t="n"/>
-      <c r="E85" s="32" t="n"/>
-      <c r="F85" s="32" t="n"/>
+      <c r="A85" s="32" t="inlineStr">
+        <is>
+          <t>Build strength</t>
+        </is>
+      </c>
+      <c r="B85" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C85" s="32" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D85" s="35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E85" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F85" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="G85" s="32" t="n"/>
       <c r="H85" s="33">
         <f>IF(A85="","",COUNTIFS('Run sessions'!$A$2:$A$401,A85,'Run sessions'!$B$2:$B$401,B85))</f>
@@ -6613,12 +6697,32 @@
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" s="21">
-      <c r="A86" s="32" t="n"/>
-      <c r="B86" s="32" t="n"/>
-      <c r="C86" s="32" t="n"/>
-      <c r="D86" s="35" t="n"/>
-      <c r="E86" s="32" t="n"/>
-      <c r="F86" s="32" t="n"/>
+      <c r="A86" s="32" t="inlineStr">
+        <is>
+          <t>Build strength</t>
+        </is>
+      </c>
+      <c r="B86" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C86" s="32" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D86" s="35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E86" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F86" s="32" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="G86" s="32" t="n"/>
       <c r="H86" s="33">
         <f>IF(A86="","",COUNTIFS('Run sessions'!$A$2:$A$401,A86,'Run sessions'!$B$2:$B$401,B86))</f>
@@ -6634,12 +6738,32 @@
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" s="21">
-      <c r="A87" s="32" t="n"/>
-      <c r="B87" s="32" t="n"/>
-      <c r="C87" s="32" t="n"/>
-      <c r="D87" s="35" t="n"/>
-      <c r="E87" s="32" t="n"/>
-      <c r="F87" s="32" t="n"/>
+      <c r="A87" s="32" t="inlineStr">
+        <is>
+          <t>Build strength</t>
+        </is>
+      </c>
+      <c r="B87" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C87" s="32" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D87" s="35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E87" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F87" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="G87" s="32" t="n"/>
       <c r="H87" s="33">
         <f>IF(A87="","",COUNTIFS('Run sessions'!$A$2:$A$401,A87,'Run sessions'!$B$2:$B$401,B87))</f>
@@ -6655,13 +6779,37 @@
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="21">
-      <c r="A88" s="32" t="n"/>
-      <c r="B88" s="32" t="n"/>
-      <c r="C88" s="32" t="n"/>
-      <c r="D88" s="35" t="n"/>
-      <c r="E88" s="32" t="n"/>
-      <c r="F88" s="32" t="n"/>
-      <c r="G88" s="32" t="n"/>
+      <c r="A88" s="32" t="inlineStr">
+        <is>
+          <t>Build strength</t>
+        </is>
+      </c>
+      <c r="B88" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C88" s="32" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="D88" s="35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E88" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F88" s="32" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="G88" s="32" t="inlineStr">
+        <is>
+          <t>Hardest week of the block.</t>
+        </is>
+      </c>
       <c r="H88" s="33">
         <f>IF(A88="","",COUNTIFS('Run sessions'!$A$2:$A$401,A88,'Run sessions'!$B$2:$B$401,B88))</f>
         <v/>
@@ -6676,13 +6824,37 @@
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="21">
-      <c r="A89" s="32" t="n"/>
-      <c r="B89" s="32" t="n"/>
-      <c r="C89" s="32" t="n"/>
-      <c r="D89" s="35" t="n"/>
-      <c r="E89" s="32" t="n"/>
-      <c r="F89" s="32" t="n"/>
-      <c r="G89" s="32" t="n"/>
+      <c r="A89" s="32" t="inlineStr">
+        <is>
+          <t>Build strength</t>
+        </is>
+      </c>
+      <c r="B89" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C89" s="32" t="inlineStr">
+        <is>
+          <t>Deload</t>
+        </is>
+      </c>
+      <c r="D89" s="35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E89" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F89" s="32" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G89" s="32" t="inlineStr">
+        <is>
+          <t>Deload: lighter lifting and easy running before the next block.</t>
+        </is>
+      </c>
       <c r="H89" s="33">
         <f>IF(A89="","",COUNTIFS('Run sessions'!$A$2:$A$401,A89,'Run sessions'!$B$2:$B$401,B89))</f>
         <v/>
@@ -6697,13 +6869,37 @@
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="21">
-      <c r="A90" s="32" t="n"/>
-      <c r="B90" s="32" t="n"/>
-      <c r="C90" s="32" t="n"/>
-      <c r="D90" s="35" t="n"/>
-      <c r="E90" s="32" t="n"/>
-      <c r="F90" s="32" t="n"/>
-      <c r="G90" s="32" t="n"/>
+      <c r="A90" s="32" t="inlineStr">
+        <is>
+          <t>Build muscle</t>
+        </is>
+      </c>
+      <c r="B90" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" s="32" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D90" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F90" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="G90" s="32" t="inlineStr">
+        <is>
+          <t>Settle in: muscle-building lifting with two runs to keep your engine.</t>
+        </is>
+      </c>
       <c r="H90" s="33">
         <f>IF(A90="","",COUNTIFS('Run sessions'!$A$2:$A$401,A90,'Run sessions'!$B$2:$B$401,B90))</f>
         <v/>
@@ -6718,12 +6914,32 @@
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="21">
-      <c r="A91" s="32" t="n"/>
-      <c r="B91" s="32" t="n"/>
-      <c r="C91" s="32" t="n"/>
-      <c r="D91" s="35" t="n"/>
-      <c r="E91" s="32" t="n"/>
-      <c r="F91" s="32" t="n"/>
+      <c r="A91" s="32" t="inlineStr">
+        <is>
+          <t>Build muscle</t>
+        </is>
+      </c>
+      <c r="B91" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C91" s="32" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D91" s="35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E91" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F91" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="G91" s="32" t="n"/>
       <c r="H91" s="33">
         <f>IF(A91="","",COUNTIFS('Run sessions'!$A$2:$A$401,A91,'Run sessions'!$B$2:$B$401,B91))</f>
@@ -6739,12 +6955,32 @@
       </c>
     </row>
     <row r="92" ht="15" customHeight="1" s="21">
-      <c r="A92" s="32" t="n"/>
-      <c r="B92" s="32" t="n"/>
-      <c r="C92" s="32" t="n"/>
-      <c r="D92" s="35" t="n"/>
-      <c r="E92" s="32" t="n"/>
-      <c r="F92" s="32" t="n"/>
+      <c r="A92" s="32" t="inlineStr">
+        <is>
+          <t>Build muscle</t>
+        </is>
+      </c>
+      <c r="B92" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C92" s="32" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D92" s="35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E92" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F92" s="32" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="G92" s="32" t="n"/>
       <c r="H92" s="33">
         <f>IF(A92="","",COUNTIFS('Run sessions'!$A$2:$A$401,A92,'Run sessions'!$B$2:$B$401,B92))</f>
@@ -6760,12 +6996,32 @@
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" s="21">
-      <c r="A93" s="32" t="n"/>
-      <c r="B93" s="32" t="n"/>
-      <c r="C93" s="32" t="n"/>
-      <c r="D93" s="35" t="n"/>
-      <c r="E93" s="32" t="n"/>
-      <c r="F93" s="32" t="n"/>
+      <c r="A93" s="32" t="inlineStr">
+        <is>
+          <t>Build muscle</t>
+        </is>
+      </c>
+      <c r="B93" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C93" s="32" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D93" s="35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E93" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F93" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="G93" s="32" t="n"/>
       <c r="H93" s="33">
         <f>IF(A93="","",COUNTIFS('Run sessions'!$A$2:$A$401,A93,'Run sessions'!$B$2:$B$401,B93))</f>
@@ -6781,12 +7037,32 @@
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" s="21">
-      <c r="A94" s="32" t="n"/>
-      <c r="B94" s="32" t="n"/>
-      <c r="C94" s="32" t="n"/>
-      <c r="D94" s="35" t="n"/>
-      <c r="E94" s="32" t="n"/>
-      <c r="F94" s="32" t="n"/>
+      <c r="A94" s="32" t="inlineStr">
+        <is>
+          <t>Build muscle</t>
+        </is>
+      </c>
+      <c r="B94" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C94" s="32" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D94" s="35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E94" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F94" s="32" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="G94" s="32" t="n"/>
       <c r="H94" s="33">
         <f>IF(A94="","",COUNTIFS('Run sessions'!$A$2:$A$401,A94,'Run sessions'!$B$2:$B$401,B94))</f>
@@ -6802,12 +7078,32 @@
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="21">
-      <c r="A95" s="32" t="n"/>
-      <c r="B95" s="32" t="n"/>
-      <c r="C95" s="32" t="n"/>
-      <c r="D95" s="35" t="n"/>
-      <c r="E95" s="32" t="n"/>
-      <c r="F95" s="32" t="n"/>
+      <c r="A95" s="32" t="inlineStr">
+        <is>
+          <t>Build muscle</t>
+        </is>
+      </c>
+      <c r="B95" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C95" s="32" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="D95" s="35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E95" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F95" s="32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
       <c r="G95" s="32" t="n"/>
       <c r="H95" s="33">
         <f>IF(A95="","",COUNTIFS('Run sessions'!$A$2:$A$401,A95,'Run sessions'!$B$2:$B$401,B95))</f>
@@ -6823,13 +7119,37 @@
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="21">
-      <c r="A96" s="32" t="n"/>
-      <c r="B96" s="32" t="n"/>
-      <c r="C96" s="32" t="n"/>
-      <c r="D96" s="35" t="n"/>
-      <c r="E96" s="32" t="n"/>
-      <c r="F96" s="32" t="n"/>
-      <c r="G96" s="32" t="n"/>
+      <c r="A96" s="32" t="inlineStr">
+        <is>
+          <t>Build muscle</t>
+        </is>
+      </c>
+      <c r="B96" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C96" s="32" t="inlineStr">
+        <is>
+          <t>Peak</t>
+        </is>
+      </c>
+      <c r="D96" s="35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E96" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F96" s="32" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="G96" s="32" t="inlineStr">
+        <is>
+          <t>Hardest week of the block.</t>
+        </is>
+      </c>
       <c r="H96" s="33">
         <f>IF(A96="","",COUNTIFS('Run sessions'!$A$2:$A$401,A96,'Run sessions'!$B$2:$B$401,B96))</f>
         <v/>
@@ -6844,13 +7164,37 @@
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="21">
-      <c r="A97" s="32" t="n"/>
-      <c r="B97" s="32" t="n"/>
-      <c r="C97" s="32" t="n"/>
-      <c r="D97" s="35" t="n"/>
-      <c r="E97" s="32" t="n"/>
-      <c r="F97" s="32" t="n"/>
-      <c r="G97" s="32" t="n"/>
+      <c r="A97" s="32" t="inlineStr">
+        <is>
+          <t>Build muscle</t>
+        </is>
+      </c>
+      <c r="B97" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C97" s="32" t="inlineStr">
+        <is>
+          <t>Deload</t>
+        </is>
+      </c>
+      <c r="D97" s="35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E97" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F97" s="32" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="G97" s="32" t="inlineStr">
+        <is>
+          <t>Deload: lighter lifting and easy running before the next block.</t>
+        </is>
+      </c>
       <c r="H97" s="33">
         <f>IF(A97="","",COUNTIFS('Run sessions'!$A$2:$A$401,A97,'Run sessions'!$B$2:$B$401,B97))</f>
         <v/>
@@ -22505,291 +22849,931 @@
       <c r="G316" s="32" t="n"/>
     </row>
     <row r="317" ht="15" customHeight="1" s="21">
-      <c r="A317" s="32" t="n"/>
-      <c r="B317" s="32" t="n"/>
-      <c r="C317" s="32" t="n"/>
-      <c r="D317" s="32" t="n"/>
-      <c r="E317" s="32" t="n"/>
-      <c r="F317" s="32" t="n"/>
+      <c r="A317" s="32" t="inlineStr">
+        <is>
+          <t>Build strength</t>
+        </is>
+      </c>
+      <c r="B317" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C317" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D317" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E317" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F317" s="32" t="inlineStr">
+        <is>
+          <t>2 x 8 min @ T, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G317" s="32" t="n"/>
     </row>
     <row r="318" ht="15" customHeight="1" s="21">
-      <c r="A318" s="32" t="n"/>
-      <c r="B318" s="32" t="n"/>
-      <c r="C318" s="32" t="n"/>
-      <c r="D318" s="32" t="n"/>
-      <c r="E318" s="32" t="n"/>
-      <c r="F318" s="32" t="n"/>
+      <c r="A318" s="32" t="inlineStr">
+        <is>
+          <t>Build strength</t>
+        </is>
+      </c>
+      <c r="B318" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C318" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D318" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E318" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F318" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G318" s="32" t="n"/>
     </row>
     <row r="319" ht="15" customHeight="1" s="21">
-      <c r="A319" s="32" t="n"/>
-      <c r="B319" s="32" t="n"/>
-      <c r="C319" s="32" t="n"/>
-      <c r="D319" s="32" t="n"/>
-      <c r="E319" s="32" t="n"/>
-      <c r="F319" s="32" t="n"/>
+      <c r="A319" s="32" t="inlineStr">
+        <is>
+          <t>Build strength</t>
+        </is>
+      </c>
+      <c r="B319" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C319" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D319" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E319" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F319" s="32" t="inlineStr">
+        <is>
+          <t>6 x 600 m @ I, 90 s jog between</t>
+        </is>
+      </c>
       <c r="G319" s="32" t="n"/>
     </row>
     <row r="320" ht="15" customHeight="1" s="21">
-      <c r="A320" s="32" t="n"/>
-      <c r="B320" s="32" t="n"/>
-      <c r="C320" s="32" t="n"/>
-      <c r="D320" s="32" t="n"/>
-      <c r="E320" s="32" t="n"/>
-      <c r="F320" s="32" t="n"/>
+      <c r="A320" s="32" t="inlineStr">
+        <is>
+          <t>Build strength</t>
+        </is>
+      </c>
+      <c r="B320" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C320" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D320" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E320" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F320" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G320" s="32" t="n"/>
     </row>
     <row r="321" ht="15" customHeight="1" s="21">
-      <c r="A321" s="32" t="n"/>
-      <c r="B321" s="32" t="n"/>
-      <c r="C321" s="32" t="n"/>
-      <c r="D321" s="32" t="n"/>
-      <c r="E321" s="32" t="n"/>
-      <c r="F321" s="32" t="n"/>
+      <c r="A321" s="32" t="inlineStr">
+        <is>
+          <t>Build strength</t>
+        </is>
+      </c>
+      <c r="B321" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C321" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D321" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E321" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F321" s="32" t="inlineStr">
+        <is>
+          <t>15 min continuous @ T</t>
+        </is>
+      </c>
       <c r="G321" s="32" t="n"/>
     </row>
     <row r="322" ht="15" customHeight="1" s="21">
-      <c r="A322" s="32" t="n"/>
-      <c r="B322" s="32" t="n"/>
-      <c r="C322" s="32" t="n"/>
-      <c r="D322" s="32" t="n"/>
-      <c r="E322" s="32" t="n"/>
-      <c r="F322" s="32" t="n"/>
+      <c r="A322" s="32" t="inlineStr">
+        <is>
+          <t>Build strength</t>
+        </is>
+      </c>
+      <c r="B322" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C322" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D322" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E322" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F322" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G322" s="32" t="n"/>
     </row>
     <row r="323" ht="15" customHeight="1" s="21">
-      <c r="A323" s="32" t="n"/>
-      <c r="B323" s="32" t="n"/>
-      <c r="C323" s="32" t="n"/>
-      <c r="D323" s="32" t="n"/>
-      <c r="E323" s="32" t="n"/>
-      <c r="F323" s="32" t="n"/>
+      <c r="A323" s="32" t="inlineStr">
+        <is>
+          <t>Build strength</t>
+        </is>
+      </c>
+      <c r="B323" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C323" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D323" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E323" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F323" s="32" t="inlineStr">
+        <is>
+          <t>5 x 800 m @ I, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G323" s="32" t="n"/>
     </row>
     <row r="324" ht="15" customHeight="1" s="21">
-      <c r="A324" s="32" t="n"/>
-      <c r="B324" s="32" t="n"/>
-      <c r="C324" s="32" t="n"/>
-      <c r="D324" s="32" t="n"/>
-      <c r="E324" s="32" t="n"/>
-      <c r="F324" s="32" t="n"/>
+      <c r="A324" s="32" t="inlineStr">
+        <is>
+          <t>Build strength</t>
+        </is>
+      </c>
+      <c r="B324" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C324" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D324" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E324" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F324" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G324" s="32" t="n"/>
     </row>
     <row r="325" ht="15" customHeight="1" s="21">
-      <c r="A325" s="32" t="n"/>
-      <c r="B325" s="32" t="n"/>
-      <c r="C325" s="32" t="n"/>
-      <c r="D325" s="32" t="n"/>
-      <c r="E325" s="32" t="n"/>
-      <c r="F325" s="32" t="n"/>
+      <c r="A325" s="32" t="inlineStr">
+        <is>
+          <t>Build strength</t>
+        </is>
+      </c>
+      <c r="B325" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C325" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D325" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E325" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F325" s="32" t="inlineStr">
+        <is>
+          <t>3 x 6 min @ T, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G325" s="32" t="n"/>
     </row>
     <row r="326" ht="15" customHeight="1" s="21">
-      <c r="A326" s="32" t="n"/>
-      <c r="B326" s="32" t="n"/>
-      <c r="C326" s="32" t="n"/>
-      <c r="D326" s="32" t="n"/>
-      <c r="E326" s="32" t="n"/>
-      <c r="F326" s="32" t="n"/>
+      <c r="A326" s="32" t="inlineStr">
+        <is>
+          <t>Build strength</t>
+        </is>
+      </c>
+      <c r="B326" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C326" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D326" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E326" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F326" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G326" s="32" t="n"/>
     </row>
     <row r="327" ht="15" customHeight="1" s="21">
-      <c r="A327" s="32" t="n"/>
-      <c r="B327" s="32" t="n"/>
-      <c r="C327" s="32" t="n"/>
-      <c r="D327" s="32" t="n"/>
-      <c r="E327" s="32" t="n"/>
-      <c r="F327" s="32" t="n"/>
+      <c r="A327" s="32" t="inlineStr">
+        <is>
+          <t>Build strength</t>
+        </is>
+      </c>
+      <c r="B327" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C327" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D327" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E327" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F327" s="32" t="inlineStr">
+        <is>
+          <t>6 x 800 m @ I, 90 s jog between</t>
+        </is>
+      </c>
       <c r="G327" s="32" t="n"/>
     </row>
     <row r="328" ht="15" customHeight="1" s="21">
-      <c r="A328" s="32" t="n"/>
-      <c r="B328" s="32" t="n"/>
-      <c r="C328" s="32" t="n"/>
-      <c r="D328" s="32" t="n"/>
-      <c r="E328" s="32" t="n"/>
-      <c r="F328" s="32" t="n"/>
+      <c r="A328" s="32" t="inlineStr">
+        <is>
+          <t>Build strength</t>
+        </is>
+      </c>
+      <c r="B328" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C328" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D328" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E328" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F328" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G328" s="32" t="n"/>
     </row>
     <row r="329" ht="15" customHeight="1" s="21">
-      <c r="A329" s="32" t="n"/>
-      <c r="B329" s="32" t="n"/>
-      <c r="C329" s="32" t="n"/>
-      <c r="D329" s="32" t="n"/>
-      <c r="E329" s="32" t="n"/>
-      <c r="F329" s="32" t="n"/>
+      <c r="A329" s="32" t="inlineStr">
+        <is>
+          <t>Build strength</t>
+        </is>
+      </c>
+      <c r="B329" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C329" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D329" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E329" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F329" s="32" t="inlineStr">
+        <is>
+          <t>20 min continuous @ T</t>
+        </is>
+      </c>
       <c r="G329" s="32" t="n"/>
     </row>
     <row r="330" ht="15" customHeight="1" s="21">
-      <c r="A330" s="32" t="n"/>
-      <c r="B330" s="32" t="n"/>
-      <c r="C330" s="32" t="n"/>
-      <c r="D330" s="32" t="n"/>
-      <c r="E330" s="32" t="n"/>
-      <c r="F330" s="32" t="n"/>
+      <c r="A330" s="32" t="inlineStr">
+        <is>
+          <t>Build strength</t>
+        </is>
+      </c>
+      <c r="B330" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C330" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D330" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E330" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F330" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G330" s="32" t="n"/>
     </row>
     <row r="331" ht="15" customHeight="1" s="21">
-      <c r="A331" s="32" t="n"/>
-      <c r="B331" s="32" t="n"/>
-      <c r="C331" s="32" t="n"/>
-      <c r="D331" s="32" t="n"/>
-      <c r="E331" s="32" t="n"/>
-      <c r="F331" s="32" t="n"/>
+      <c r="A331" s="32" t="inlineStr">
+        <is>
+          <t>Build strength</t>
+        </is>
+      </c>
+      <c r="B331" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C331" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D331" s="32" t="inlineStr">
+        <is>
+          <t>Fartlek</t>
+        </is>
+      </c>
+      <c r="E331" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F331" s="32" t="inlineStr">
+        <is>
+          <t>6 x (1 min @ T effort / 1 min E)</t>
+        </is>
+      </c>
       <c r="G331" s="32" t="n"/>
     </row>
     <row r="332" ht="15" customHeight="1" s="21">
-      <c r="A332" s="32" t="n"/>
-      <c r="B332" s="32" t="n"/>
-      <c r="C332" s="32" t="n"/>
-      <c r="D332" s="32" t="n"/>
-      <c r="E332" s="32" t="n"/>
-      <c r="F332" s="32" t="n"/>
+      <c r="A332" s="32" t="inlineStr">
+        <is>
+          <t>Build strength</t>
+        </is>
+      </c>
+      <c r="B332" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C332" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D332" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E332" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F332" s="32" t="inlineStr">
+        <is>
+          <t>Shorter long run, E</t>
+        </is>
+      </c>
       <c r="G332" s="32" t="n"/>
     </row>
     <row r="333" ht="15" customHeight="1" s="21">
-      <c r="A333" s="32" t="n"/>
-      <c r="B333" s="32" t="n"/>
-      <c r="C333" s="32" t="n"/>
-      <c r="D333" s="32" t="n"/>
-      <c r="E333" s="32" t="n"/>
-      <c r="F333" s="32" t="n"/>
+      <c r="A333" s="32" t="inlineStr">
+        <is>
+          <t>Build muscle</t>
+        </is>
+      </c>
+      <c r="B333" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C333" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D333" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E333" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F333" s="32" t="inlineStr">
+        <is>
+          <t>2 x 8 min @ T, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G333" s="32" t="n"/>
     </row>
     <row r="334" ht="15" customHeight="1" s="21">
-      <c r="A334" s="32" t="n"/>
-      <c r="B334" s="32" t="n"/>
-      <c r="C334" s="32" t="n"/>
-      <c r="D334" s="32" t="n"/>
-      <c r="E334" s="32" t="n"/>
-      <c r="F334" s="32" t="n"/>
+      <c r="A334" s="32" t="inlineStr">
+        <is>
+          <t>Build muscle</t>
+        </is>
+      </c>
+      <c r="B334" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C334" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D334" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E334" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F334" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G334" s="32" t="n"/>
     </row>
     <row r="335" ht="15" customHeight="1" s="21">
-      <c r="A335" s="32" t="n"/>
-      <c r="B335" s="32" t="n"/>
-      <c r="C335" s="32" t="n"/>
-      <c r="D335" s="32" t="n"/>
-      <c r="E335" s="32" t="n"/>
-      <c r="F335" s="32" t="n"/>
+      <c r="A335" s="32" t="inlineStr">
+        <is>
+          <t>Build muscle</t>
+        </is>
+      </c>
+      <c r="B335" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C335" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D335" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E335" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F335" s="32" t="inlineStr">
+        <is>
+          <t>6 x 600 m @ I, 90 s jog between</t>
+        </is>
+      </c>
       <c r="G335" s="32" t="n"/>
     </row>
     <row r="336" ht="15" customHeight="1" s="21">
-      <c r="A336" s="32" t="n"/>
-      <c r="B336" s="32" t="n"/>
-      <c r="C336" s="32" t="n"/>
-      <c r="D336" s="32" t="n"/>
-      <c r="E336" s="32" t="n"/>
-      <c r="F336" s="32" t="n"/>
+      <c r="A336" s="32" t="inlineStr">
+        <is>
+          <t>Build muscle</t>
+        </is>
+      </c>
+      <c r="B336" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C336" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D336" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E336" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F336" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G336" s="32" t="n"/>
     </row>
     <row r="337" ht="15" customHeight="1" s="21">
-      <c r="A337" s="32" t="n"/>
-      <c r="B337" s="32" t="n"/>
-      <c r="C337" s="32" t="n"/>
-      <c r="D337" s="32" t="n"/>
-      <c r="E337" s="32" t="n"/>
-      <c r="F337" s="32" t="n"/>
+      <c r="A337" s="32" t="inlineStr">
+        <is>
+          <t>Build muscle</t>
+        </is>
+      </c>
+      <c r="B337" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C337" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D337" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E337" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F337" s="32" t="inlineStr">
+        <is>
+          <t>15 min continuous @ T</t>
+        </is>
+      </c>
       <c r="G337" s="32" t="n"/>
     </row>
     <row r="338" ht="15" customHeight="1" s="21">
-      <c r="A338" s="32" t="n"/>
-      <c r="B338" s="32" t="n"/>
-      <c r="C338" s="32" t="n"/>
-      <c r="D338" s="32" t="n"/>
-      <c r="E338" s="32" t="n"/>
-      <c r="F338" s="32" t="n"/>
+      <c r="A338" s="32" t="inlineStr">
+        <is>
+          <t>Build muscle</t>
+        </is>
+      </c>
+      <c r="B338" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C338" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D338" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E338" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F338" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G338" s="32" t="n"/>
     </row>
     <row r="339" ht="15" customHeight="1" s="21">
-      <c r="A339" s="32" t="n"/>
-      <c r="B339" s="32" t="n"/>
-      <c r="C339" s="32" t="n"/>
-      <c r="D339" s="32" t="n"/>
-      <c r="E339" s="32" t="n"/>
-      <c r="F339" s="32" t="n"/>
+      <c r="A339" s="32" t="inlineStr">
+        <is>
+          <t>Build muscle</t>
+        </is>
+      </c>
+      <c r="B339" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C339" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D339" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E339" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F339" s="32" t="inlineStr">
+        <is>
+          <t>5 x 800 m @ I, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G339" s="32" t="n"/>
     </row>
     <row r="340" ht="15" customHeight="1" s="21">
-      <c r="A340" s="32" t="n"/>
-      <c r="B340" s="32" t="n"/>
-      <c r="C340" s="32" t="n"/>
-      <c r="D340" s="32" t="n"/>
-      <c r="E340" s="32" t="n"/>
-      <c r="F340" s="32" t="n"/>
+      <c r="A340" s="32" t="inlineStr">
+        <is>
+          <t>Build muscle</t>
+        </is>
+      </c>
+      <c r="B340" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C340" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D340" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E340" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F340" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G340" s="32" t="n"/>
     </row>
     <row r="341" ht="15" customHeight="1" s="21">
-      <c r="A341" s="32" t="n"/>
-      <c r="B341" s="32" t="n"/>
-      <c r="C341" s="32" t="n"/>
-      <c r="D341" s="32" t="n"/>
-      <c r="E341" s="32" t="n"/>
-      <c r="F341" s="32" t="n"/>
+      <c r="A341" s="32" t="inlineStr">
+        <is>
+          <t>Build muscle</t>
+        </is>
+      </c>
+      <c r="B341" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C341" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D341" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E341" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F341" s="32" t="inlineStr">
+        <is>
+          <t>3 x 6 min @ T, 2 min jog between</t>
+        </is>
+      </c>
       <c r="G341" s="32" t="n"/>
     </row>
     <row r="342" ht="15" customHeight="1" s="21">
-      <c r="A342" s="32" t="n"/>
-      <c r="B342" s="32" t="n"/>
-      <c r="C342" s="32" t="n"/>
-      <c r="D342" s="32" t="n"/>
-      <c r="E342" s="32" t="n"/>
-      <c r="F342" s="32" t="n"/>
+      <c r="A342" s="32" t="inlineStr">
+        <is>
+          <t>Build muscle</t>
+        </is>
+      </c>
+      <c r="B342" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C342" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D342" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E342" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F342" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G342" s="32" t="n"/>
     </row>
     <row r="343" ht="15" customHeight="1" s="21">
-      <c r="A343" s="32" t="n"/>
-      <c r="B343" s="32" t="n"/>
-      <c r="C343" s="32" t="n"/>
-      <c r="D343" s="32" t="n"/>
-      <c r="E343" s="32" t="n"/>
-      <c r="F343" s="32" t="n"/>
+      <c r="A343" s="32" t="inlineStr">
+        <is>
+          <t>Build muscle</t>
+        </is>
+      </c>
+      <c r="B343" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C343" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D343" s="32" t="inlineStr">
+        <is>
+          <t>Intervals</t>
+        </is>
+      </c>
+      <c r="E343" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F343" s="32" t="inlineStr">
+        <is>
+          <t>6 x 800 m @ I, 90 s jog between</t>
+        </is>
+      </c>
       <c r="G343" s="32" t="n"/>
     </row>
     <row r="344" ht="15" customHeight="1" s="21">
-      <c r="A344" s="32" t="n"/>
-      <c r="B344" s="32" t="n"/>
-      <c r="C344" s="32" t="n"/>
-      <c r="D344" s="32" t="n"/>
-      <c r="E344" s="32" t="n"/>
-      <c r="F344" s="32" t="n"/>
+      <c r="A344" s="32" t="inlineStr">
+        <is>
+          <t>Build muscle</t>
+        </is>
+      </c>
+      <c r="B344" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C344" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D344" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E344" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F344" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G344" s="32" t="n"/>
     </row>
     <row r="345" ht="15" customHeight="1" s="21">
-      <c r="A345" s="32" t="n"/>
-      <c r="B345" s="32" t="n"/>
-      <c r="C345" s="32" t="n"/>
-      <c r="D345" s="32" t="n"/>
-      <c r="E345" s="32" t="n"/>
-      <c r="F345" s="32" t="n"/>
+      <c r="A345" s="32" t="inlineStr">
+        <is>
+          <t>Build muscle</t>
+        </is>
+      </c>
+      <c r="B345" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C345" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D345" s="32" t="inlineStr">
+        <is>
+          <t>Tempo</t>
+        </is>
+      </c>
+      <c r="E345" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F345" s="32" t="inlineStr">
+        <is>
+          <t>20 min continuous @ T</t>
+        </is>
+      </c>
       <c r="G345" s="32" t="n"/>
     </row>
     <row r="346" ht="15" customHeight="1" s="21">
-      <c r="A346" s="32" t="n"/>
-      <c r="B346" s="32" t="n"/>
-      <c r="C346" s="32" t="n"/>
-      <c r="D346" s="32" t="n"/>
-      <c r="E346" s="32" t="n"/>
-      <c r="F346" s="32" t="n"/>
+      <c r="A346" s="32" t="inlineStr">
+        <is>
+          <t>Build muscle</t>
+        </is>
+      </c>
+      <c r="B346" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="C346" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D346" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E346" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F346" s="32" t="inlineStr">
+        <is>
+          <t>Long run, conversational throughout</t>
+        </is>
+      </c>
       <c r="G346" s="32" t="n"/>
     </row>
     <row r="347" ht="15" customHeight="1" s="21">
-      <c r="A347" s="32" t="n"/>
-      <c r="B347" s="32" t="n"/>
-      <c r="C347" s="32" t="n"/>
-      <c r="D347" s="32" t="n"/>
-      <c r="E347" s="32" t="n"/>
-      <c r="F347" s="32" t="n"/>
+      <c r="A347" s="32" t="inlineStr">
+        <is>
+          <t>Build muscle</t>
+        </is>
+      </c>
+      <c r="B347" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C347" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D347" s="32" t="inlineStr">
+        <is>
+          <t>Fartlek</t>
+        </is>
+      </c>
+      <c r="E347" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F347" s="32" t="inlineStr">
+        <is>
+          <t>6 x (1 min @ T effort / 1 min E)</t>
+        </is>
+      </c>
       <c r="G347" s="32" t="n"/>
     </row>
     <row r="348" ht="15" customHeight="1" s="21">
-      <c r="A348" s="32" t="n"/>
-      <c r="B348" s="32" t="n"/>
-      <c r="C348" s="32" t="n"/>
-      <c r="D348" s="32" t="n"/>
-      <c r="E348" s="32" t="n"/>
-      <c r="F348" s="32" t="n"/>
+      <c r="A348" s="32" t="inlineStr">
+        <is>
+          <t>Build muscle</t>
+        </is>
+      </c>
+      <c r="B348" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C348" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D348" s="32" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="E348" s="32" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="F348" s="32" t="inlineStr">
+        <is>
+          <t>Shorter long run, E</t>
+        </is>
+      </c>
       <c r="G348" s="32" t="n"/>
     </row>
     <row r="349" ht="15" customHeight="1" s="21">

--- a/programmes/Kinetix Programmes.xlsx
+++ b/programmes/Kinetix Programmes.xlsx
@@ -1595,6 +1595,11 @@
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="21">
+      <c r="E14" s="27" t="inlineStr">
+        <is>
+          <t>Runner strength ×1</t>
+        </is>
+      </c>
       <c r="I14" s="27" t="inlineStr">
         <is>
           <t>Any Hyrox station</t>
@@ -1602,6 +1607,11 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="21">
+      <c r="E15" s="27" t="inlineStr">
+        <is>
+          <t>Runner strength ×2</t>
+        </is>
+      </c>
       <c r="I15" s="27" t="inlineStr">
         <is>
           <t>Arnold Press</t>
@@ -2361,7 +2371,11 @@
         <f>COUNTIF('Run sessions'!$A$2:$A$401,A2)</f>
         <v/>
       </c>
-      <c r="T2" s="32" t="n"/>
+      <c r="T2" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength ×2, Runner strength ×1</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="21">
       <c r="A3" s="30" t="inlineStr">
@@ -2435,7 +2449,11 @@
         <f>COUNTIF('Run sessions'!$A$2:$A$401,A3)</f>
         <v/>
       </c>
-      <c r="T3" s="32" t="n"/>
+      <c r="T3" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength ×2, Runner strength ×1</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="21">
       <c r="A4" s="30" t="inlineStr">
@@ -2509,7 +2527,11 @@
         <f>COUNTIF('Run sessions'!$A$2:$A$401,A4)</f>
         <v/>
       </c>
-      <c r="T4" s="32" t="n"/>
+      <c r="T4" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength ×2, Runner strength ×1</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="21">
       <c r="A5" s="30" t="inlineStr">
@@ -2583,7 +2605,11 @@
         <f>COUNTIF('Run sessions'!$A$2:$A$401,A5)</f>
         <v/>
       </c>
-      <c r="T5" s="32" t="n"/>
+      <c r="T5" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength ×2, Runner strength ×1</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="21">
       <c r="A6" s="30" t="inlineStr">
@@ -2657,7 +2683,11 @@
         <f>COUNTIF('Run sessions'!$A$2:$A$401,A6)</f>
         <v/>
       </c>
-      <c r="T6" s="32" t="n"/>
+      <c r="T6" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength ×2, Runner strength ×1</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="21">
       <c r="A7" s="30" t="inlineStr">
@@ -2959,6 +2989,7 @@
       </c>
       <c r="T10" s="32" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="21">
       <c r="A12" s="34" t="inlineStr">
         <is>
@@ -2973,7 +3004,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation sqref="O2:O10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Choose from the list" error="Pick one of the options in the drop-down." promptTitle="Tip" prompt="The split suggested in onboarding (the user can change it)." type="list" errorStyle="stop" operator="between">
-      <formula1>Lists!$E$2:$E$13</formula1>
+      <formula1>Lists!$E$2:$E$15</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation sqref="Q2:Q10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Choose from the list" error="Pick one of the options in the drop-down." promptTitle="Tip" prompt="Which runners see this goal in onboarding." type="list" errorStyle="stop" operator="between">
@@ -2981,7 +3012,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation sqref="T2:T10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Lists!$E$2:$E$13</formula1>
+      <formula1>Lists!$E$2:$E$15</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -24592,7 +24623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="20" min="1" max="1"/>
@@ -24980,6 +25011,64 @@
       </c>
       <c r="F13" s="33">
         <f>SUMPRODUCT(('Split days'!$A$2:$A$401=A13)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>Runner strength ×1</t>
+        </is>
+      </c>
+      <c r="B14" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>Runners: one short session of single-leg strength, calves and core to stay strong and injury-resistant.</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F14" s="33">
+        <f>SUMPRODUCT(('Split days'!$A$2:$A$401=A14)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t>Runner strength ×2</t>
+        </is>
+      </c>
+      <c r="B15" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength A, Runner strength B</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>Runners: single-leg strength, hamstrings and calves, plus hip power. Short sessions that fit around running.</t>
+        </is>
+      </c>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F15" s="33">
+        <f>SUMPRODUCT(('Split days'!$A$2:$A$401=A15)/COUNTIFS('Split days'!$A$2:$A$401,'Split days'!$A$2:$A$401&amp;"",'Split days'!$B$2:$B$401,'Split days'!$B$2:$B$401&amp;""))</f>
         <v/>
       </c>
     </row>
@@ -32466,215 +32555,681 @@
       <c r="J226" s="32" t="n"/>
     </row>
     <row r="227" ht="15" customHeight="1" s="21">
-      <c r="A227" s="32" t="n"/>
-      <c r="B227" s="32" t="n"/>
-      <c r="C227" s="32" t="n"/>
-      <c r="D227" s="32" t="n"/>
-      <c r="E227" s="32" t="n"/>
-      <c r="F227" s="32" t="n"/>
-      <c r="G227" s="32" t="n"/>
-      <c r="H227" s="32" t="n"/>
-      <c r="I227" s="32" t="n"/>
-      <c r="J227" s="32" t="n"/>
+      <c r="A227" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength ×1</t>
+        </is>
+      </c>
+      <c r="B227" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength</t>
+        </is>
+      </c>
+      <c r="C227" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D227" s="32" t="inlineStr">
+        <is>
+          <t>Bulgarian Split Squat</t>
+        </is>
+      </c>
+      <c r="E227" s="32" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="F227" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G227" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H227" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="I227" s="32" t="n">
+        <v>120</v>
+      </c>
+      <c r="J227" s="32" t="inlineStr">
+        <is>
+          <t>Each leg. Back foot on a bench.</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="15" customHeight="1" s="21">
-      <c r="A228" s="37" t="inlineStr">
-        <is>
-          <t>A first draft of every split to edit. 'Any …' lets the app choose for the user's equipment; named exercises are swapped for the closest option if they can't do them. Blank sets/reps/rest use 'Strength by goal'.</t>
-        </is>
-      </c>
-      <c r="B228" s="32" t="n"/>
-      <c r="C228" s="32" t="n"/>
-      <c r="D228" s="32" t="n"/>
-      <c r="E228" s="32" t="n"/>
-      <c r="F228" s="32" t="n"/>
-      <c r="G228" s="32" t="n"/>
-      <c r="H228" s="32" t="n"/>
-      <c r="I228" s="32" t="n"/>
+      <c r="A228" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength ×1</t>
+        </is>
+      </c>
+      <c r="B228" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength</t>
+        </is>
+      </c>
+      <c r="C228" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D228" s="32" t="inlineStr">
+        <is>
+          <t>Romanian Deadlift</t>
+        </is>
+      </c>
+      <c r="E228" s="32" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="F228" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G228" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H228" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="I228" s="32" t="n">
+        <v>120</v>
+      </c>
       <c r="J228" s="32" t="n"/>
     </row>
     <row r="229" ht="15" customHeight="1" s="21">
-      <c r="A229" s="37" t="inlineStr">
-        <is>
-          <t>Leg-heavy days are kept away from hard runs and the long run automatically.</t>
-        </is>
-      </c>
-      <c r="B229" s="32" t="n"/>
-      <c r="C229" s="32" t="n"/>
-      <c r="D229" s="32" t="n"/>
-      <c r="E229" s="32" t="n"/>
-      <c r="F229" s="32" t="n"/>
-      <c r="G229" s="32" t="n"/>
-      <c r="H229" s="32" t="n"/>
-      <c r="I229" s="32" t="n"/>
-      <c r="J229" s="32" t="n"/>
+      <c r="A229" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength ×1</t>
+        </is>
+      </c>
+      <c r="B229" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength</t>
+        </is>
+      </c>
+      <c r="C229" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D229" s="32" t="inlineStr">
+        <is>
+          <t>Step-Up</t>
+        </is>
+      </c>
+      <c r="E229" s="32" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+      <c r="F229" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G229" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="H229" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="I229" s="32" t="n">
+        <v>60</v>
+      </c>
+      <c r="J229" s="32" t="inlineStr">
+        <is>
+          <t>Each leg. Drive the knee up.</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="15" customHeight="1" s="21">
-      <c r="A230" s="32" t="n"/>
-      <c r="B230" s="32" t="n"/>
-      <c r="C230" s="32" t="n"/>
-      <c r="D230" s="32" t="n"/>
-      <c r="E230" s="32" t="n"/>
-      <c r="F230" s="32" t="n"/>
-      <c r="G230" s="32" t="n"/>
-      <c r="H230" s="32" t="n"/>
-      <c r="I230" s="32" t="n"/>
-      <c r="J230" s="32" t="n"/>
+      <c r="A230" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength ×1</t>
+        </is>
+      </c>
+      <c r="B230" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength</t>
+        </is>
+      </c>
+      <c r="C230" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D230" s="32" t="inlineStr">
+        <is>
+          <t>Single-Leg Calf Raise</t>
+        </is>
+      </c>
+      <c r="E230" s="32" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+      <c r="F230" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G230" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="H230" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="I230" s="32" t="n">
+        <v>45</v>
+      </c>
+      <c r="J230" s="32" t="inlineStr">
+        <is>
+          <t>Each leg. Pause at the bottom.</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="15" customHeight="1" s="21">
-      <c r="A231" s="32" t="n"/>
-      <c r="B231" s="32" t="n"/>
-      <c r="C231" s="32" t="n"/>
-      <c r="D231" s="32" t="n"/>
-      <c r="E231" s="32" t="n"/>
-      <c r="F231" s="32" t="n"/>
-      <c r="G231" s="32" t="n"/>
-      <c r="H231" s="32" t="n"/>
-      <c r="I231" s="32" t="n"/>
+      <c r="A231" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength ×1</t>
+        </is>
+      </c>
+      <c r="B231" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength</t>
+        </is>
+      </c>
+      <c r="C231" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D231" s="32" t="inlineStr">
+        <is>
+          <t>Any horizontal pull (row)</t>
+        </is>
+      </c>
+      <c r="E231" s="32" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+      <c r="F231" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G231" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="H231" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="I231" s="32" t="n">
+        <v>60</v>
+      </c>
       <c r="J231" s="32" t="n"/>
     </row>
     <row r="232" ht="15" customHeight="1" s="21">
-      <c r="A232" s="32" t="n"/>
-      <c r="B232" s="32" t="n"/>
-      <c r="C232" s="32" t="n"/>
-      <c r="D232" s="32" t="n"/>
-      <c r="E232" s="32" t="n"/>
-      <c r="F232" s="32" t="n"/>
-      <c r="G232" s="32" t="n"/>
-      <c r="H232" s="32" t="n"/>
-      <c r="I232" s="32" t="n"/>
+      <c r="A232" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength ×1</t>
+        </is>
+      </c>
+      <c r="B232" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength</t>
+        </is>
+      </c>
+      <c r="C232" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="D232" s="32" t="inlineStr">
+        <is>
+          <t>Any anti-rotation core</t>
+        </is>
+      </c>
+      <c r="E232" s="32" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+      <c r="F232" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G232" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="H232" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="I232" s="32" t="n">
+        <v>45</v>
+      </c>
       <c r="J232" s="32" t="n"/>
     </row>
     <row r="233" ht="15" customHeight="1" s="21">
-      <c r="A233" s="32" t="n"/>
-      <c r="B233" s="32" t="n"/>
-      <c r="C233" s="32" t="n"/>
-      <c r="D233" s="32" t="n"/>
-      <c r="E233" s="32" t="n"/>
-      <c r="F233" s="32" t="n"/>
-      <c r="G233" s="32" t="n"/>
-      <c r="H233" s="32" t="n"/>
-      <c r="I233" s="32" t="n"/>
+      <c r="A233" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength ×2</t>
+        </is>
+      </c>
+      <c r="B233" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength A</t>
+        </is>
+      </c>
+      <c r="C233" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D233" s="32" t="inlineStr">
+        <is>
+          <t>Any squat</t>
+        </is>
+      </c>
+      <c r="E233" s="32" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="F233" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G233" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H233" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="I233" s="32" t="n">
+        <v>150</v>
+      </c>
       <c r="J233" s="32" t="n"/>
     </row>
     <row r="234" ht="15" customHeight="1" s="21">
-      <c r="A234" s="32" t="n"/>
-      <c r="B234" s="32" t="n"/>
-      <c r="C234" s="32" t="n"/>
-      <c r="D234" s="32" t="n"/>
-      <c r="E234" s="32" t="n"/>
-      <c r="F234" s="32" t="n"/>
-      <c r="G234" s="32" t="n"/>
-      <c r="H234" s="32" t="n"/>
-      <c r="I234" s="32" t="n"/>
-      <c r="J234" s="32" t="n"/>
+      <c r="A234" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength ×2</t>
+        </is>
+      </c>
+      <c r="B234" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength A</t>
+        </is>
+      </c>
+      <c r="C234" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D234" s="32" t="inlineStr">
+        <is>
+          <t>Bulgarian Split Squat</t>
+        </is>
+      </c>
+      <c r="E234" s="32" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+      <c r="F234" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G234" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="H234" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="I234" s="32" t="n">
+        <v>90</v>
+      </c>
+      <c r="J234" s="32" t="inlineStr">
+        <is>
+          <t>Each leg. Back foot on a bench.</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="15" customHeight="1" s="21">
-      <c r="A235" s="32" t="n"/>
-      <c r="B235" s="32" t="n"/>
-      <c r="C235" s="32" t="n"/>
-      <c r="D235" s="32" t="n"/>
-      <c r="E235" s="32" t="n"/>
-      <c r="F235" s="32" t="n"/>
-      <c r="G235" s="32" t="n"/>
-      <c r="H235" s="32" t="n"/>
-      <c r="I235" s="32" t="n"/>
-      <c r="J235" s="32" t="n"/>
+      <c r="A235" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength ×2</t>
+        </is>
+      </c>
+      <c r="B235" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength A</t>
+        </is>
+      </c>
+      <c r="C235" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D235" s="32" t="inlineStr">
+        <is>
+          <t>Nordic Hamstring Curl</t>
+        </is>
+      </c>
+      <c r="E235" s="32" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+      <c r="F235" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G235" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H235" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="I235" s="32" t="n">
+        <v>90</v>
+      </c>
+      <c r="J235" s="32" t="inlineStr">
+        <is>
+          <t>Lower as slowly as you can.</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="15" customHeight="1" s="21">
-      <c r="A236" s="32" t="n"/>
-      <c r="B236" s="32" t="n"/>
-      <c r="C236" s="32" t="n"/>
-      <c r="D236" s="32" t="n"/>
-      <c r="E236" s="32" t="n"/>
-      <c r="F236" s="32" t="n"/>
-      <c r="G236" s="32" t="n"/>
-      <c r="H236" s="32" t="n"/>
-      <c r="I236" s="32" t="n"/>
-      <c r="J236" s="32" t="n"/>
+      <c r="A236" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength ×2</t>
+        </is>
+      </c>
+      <c r="B236" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength A</t>
+        </is>
+      </c>
+      <c r="C236" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D236" s="32" t="inlineStr">
+        <is>
+          <t>Single-Leg Calf Raise</t>
+        </is>
+      </c>
+      <c r="E236" s="32" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+      <c r="F236" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G236" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="H236" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="I236" s="32" t="n">
+        <v>45</v>
+      </c>
+      <c r="J236" s="32" t="inlineStr">
+        <is>
+          <t>Each leg. Pause at the bottom.</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="15" customHeight="1" s="21">
-      <c r="A237" s="32" t="n"/>
-      <c r="B237" s="32" t="n"/>
-      <c r="C237" s="32" t="n"/>
-      <c r="D237" s="32" t="n"/>
-      <c r="E237" s="32" t="n"/>
-      <c r="F237" s="32" t="n"/>
-      <c r="G237" s="32" t="n"/>
-      <c r="H237" s="32" t="n"/>
-      <c r="I237" s="32" t="n"/>
+      <c r="A237" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength ×2</t>
+        </is>
+      </c>
+      <c r="B237" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength A</t>
+        </is>
+      </c>
+      <c r="C237" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D237" s="32" t="inlineStr">
+        <is>
+          <t>Any anti-rotation core</t>
+        </is>
+      </c>
+      <c r="E237" s="32" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+      <c r="F237" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G237" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="H237" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="I237" s="32" t="n">
+        <v>45</v>
+      </c>
       <c r="J237" s="32" t="n"/>
     </row>
     <row r="238" ht="15" customHeight="1" s="21">
-      <c r="A238" s="32" t="n"/>
-      <c r="B238" s="32" t="n"/>
-      <c r="C238" s="32" t="n"/>
-      <c r="D238" s="32" t="n"/>
-      <c r="E238" s="32" t="n"/>
-      <c r="F238" s="32" t="n"/>
-      <c r="G238" s="32" t="n"/>
-      <c r="H238" s="32" t="n"/>
-      <c r="I238" s="32" t="n"/>
+      <c r="A238" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength ×2</t>
+        </is>
+      </c>
+      <c r="B238" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength B</t>
+        </is>
+      </c>
+      <c r="C238" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D238" s="32" t="inlineStr">
+        <is>
+          <t>Any hinge (deadlift)</t>
+        </is>
+      </c>
+      <c r="E238" s="32" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="F238" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G238" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H238" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="I238" s="32" t="n">
+        <v>150</v>
+      </c>
       <c r="J238" s="32" t="n"/>
     </row>
     <row r="239" ht="15" customHeight="1" s="21">
-      <c r="A239" s="32" t="n"/>
-      <c r="B239" s="32" t="n"/>
-      <c r="C239" s="32" t="n"/>
-      <c r="D239" s="32" t="n"/>
-      <c r="E239" s="32" t="n"/>
-      <c r="F239" s="32" t="n"/>
-      <c r="G239" s="32" t="n"/>
-      <c r="H239" s="32" t="n"/>
-      <c r="I239" s="32" t="n"/>
-      <c r="J239" s="32" t="n"/>
+      <c r="A239" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength ×2</t>
+        </is>
+      </c>
+      <c r="B239" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength B</t>
+        </is>
+      </c>
+      <c r="C239" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D239" s="32" t="inlineStr">
+        <is>
+          <t>Step-Up</t>
+        </is>
+      </c>
+      <c r="E239" s="32" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+      <c r="F239" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G239" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="H239" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="I239" s="32" t="n">
+        <v>60</v>
+      </c>
+      <c r="J239" s="32" t="inlineStr">
+        <is>
+          <t>Each leg. Drive the knee up.</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="15" customHeight="1" s="21">
-      <c r="A240" s="32" t="n"/>
-      <c r="B240" s="32" t="n"/>
-      <c r="C240" s="32" t="n"/>
-      <c r="D240" s="32" t="n"/>
-      <c r="E240" s="32" t="n"/>
-      <c r="F240" s="32" t="n"/>
-      <c r="G240" s="32" t="n"/>
-      <c r="H240" s="32" t="n"/>
-      <c r="I240" s="32" t="n"/>
+      <c r="A240" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength ×2</t>
+        </is>
+      </c>
+      <c r="B240" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength B</t>
+        </is>
+      </c>
+      <c r="C240" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D240" s="32" t="inlineStr">
+        <is>
+          <t>Barbell Hip Thrust</t>
+        </is>
+      </c>
+      <c r="E240" s="32" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+      <c r="F240" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G240" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="H240" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="I240" s="32" t="n">
+        <v>90</v>
+      </c>
       <c r="J240" s="32" t="n"/>
     </row>
     <row r="241" ht="15" customHeight="1" s="21">
-      <c r="A241" s="32" t="n"/>
-      <c r="B241" s="32" t="n"/>
-      <c r="C241" s="32" t="n"/>
-      <c r="D241" s="32" t="n"/>
-      <c r="E241" s="32" t="n"/>
-      <c r="F241" s="32" t="n"/>
-      <c r="G241" s="32" t="n"/>
-      <c r="H241" s="32" t="n"/>
-      <c r="I241" s="32" t="n"/>
-      <c r="J241" s="32" t="n"/>
+      <c r="A241" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength ×2</t>
+        </is>
+      </c>
+      <c r="B241" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength B</t>
+        </is>
+      </c>
+      <c r="C241" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D241" s="32" t="inlineStr">
+        <is>
+          <t>Kettlebell Swing</t>
+        </is>
+      </c>
+      <c r="E241" s="32" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+      <c r="F241" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="G241" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="H241" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="I241" s="32" t="n">
+        <v>60</v>
+      </c>
+      <c r="J241" s="32" t="inlineStr">
+        <is>
+          <t>Snap the hips: power for running.</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="15" customHeight="1" s="21">
-      <c r="A242" s="32" t="n"/>
-      <c r="B242" s="32" t="n"/>
-      <c r="C242" s="32" t="n"/>
-      <c r="D242" s="32" t="n"/>
-      <c r="E242" s="32" t="n"/>
-      <c r="F242" s="32" t="n"/>
-      <c r="G242" s="32" t="n"/>
-      <c r="H242" s="32" t="n"/>
-      <c r="I242" s="32" t="n"/>
+      <c r="A242" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength ×2</t>
+        </is>
+      </c>
+      <c r="B242" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength B</t>
+        </is>
+      </c>
+      <c r="C242" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D242" s="32" t="inlineStr">
+        <is>
+          <t>Any horizontal pull (row)</t>
+        </is>
+      </c>
+      <c r="E242" s="32" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+      <c r="F242" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G242" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="H242" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="I242" s="32" t="n">
+        <v>60</v>
+      </c>
       <c r="J242" s="32" t="n"/>
     </row>
     <row r="243" ht="15" customHeight="1" s="21">
-      <c r="A243" s="32" t="n"/>
-      <c r="B243" s="32" t="n"/>
-      <c r="C243" s="32" t="n"/>
-      <c r="D243" s="32" t="n"/>
-      <c r="E243" s="32" t="n"/>
-      <c r="F243" s="32" t="n"/>
-      <c r="G243" s="32" t="n"/>
-      <c r="H243" s="32" t="n"/>
-      <c r="I243" s="32" t="n"/>
+      <c r="A243" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength ×2</t>
+        </is>
+      </c>
+      <c r="B243" s="32" t="inlineStr">
+        <is>
+          <t>Runner strength B</t>
+        </is>
+      </c>
+      <c r="C243" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="D243" s="32" t="inlineStr">
+        <is>
+          <t>Any core</t>
+        </is>
+      </c>
+      <c r="E243" s="32" t="inlineStr">
+        <is>
+          <t>Accessory</t>
+        </is>
+      </c>
+      <c r="F243" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G243" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="H243" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="I243" s="32" t="n">
+        <v>45</v>
+      </c>
       <c r="J243" s="32" t="n"/>
     </row>
     <row r="244" ht="15" customHeight="1" s="21">
@@ -32690,7 +33245,11 @@
       <c r="J244" s="32" t="n"/>
     </row>
     <row r="245" ht="15" customHeight="1" s="21">
-      <c r="A245" s="32" t="n"/>
+      <c r="A245" s="37" t="inlineStr">
+        <is>
+          <t>A first draft of every split to edit. 'Any …' lets the app choose for the user's equipment; named exercises are swapped for the closest option if they can't do them. Blank sets/reps/rest use 'Strength by goal'.</t>
+        </is>
+      </c>
       <c r="B245" s="32" t="n"/>
       <c r="C245" s="32" t="n"/>
       <c r="D245" s="32" t="n"/>
@@ -32702,7 +33261,11 @@
       <c r="J245" s="32" t="n"/>
     </row>
     <row r="246" ht="15" customHeight="1" s="21">
-      <c r="A246" s="32" t="n"/>
+      <c r="A246" s="37" t="inlineStr">
+        <is>
+          <t>Leg-heavy days are kept away from hard runs and the long run automatically.</t>
+        </is>
+      </c>
       <c r="B246" s="32" t="n"/>
       <c r="C246" s="32" t="n"/>
       <c r="D246" s="32" t="n"/>
@@ -34888,7 +35451,7 @@
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="A2:A401" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Choose from the list" error="Pick one of the options in the drop-down." type="list" errorStyle="stop" operator="between">
-      <formula1>Lists!$E$2:$E$13</formula1>
+      <formula1>Lists!$E$2:$E$15</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation sqref="D2:D401" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Choose from the list" error="Pick one of the options in the drop-down." promptTitle="Tip" prompt="Pick 'Any …' to let the app choose for the user's equipment, or a named exercise." type="list" errorStyle="stop" operator="between">
